--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD3E35E1-6161-8A49-B96F-D402C6DB88A0}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C57F4E3-50C7-6549-840E-777C7A68D7C4}"/>
   <bookViews>
-    <workbookView xWindow="-3440" yWindow="-20980" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Criteria" sheetId="1" r:id="rId1"/>
+    <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Phase0" sheetId="2" r:id="rId2"/>
     <sheet name="criteria_full" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
-    <sheet name="calcs" sheetId="3" r:id="rId6"/>
+    <sheet name="calcs" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -795,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="229">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1371,73 +1369,13 @@
     <t>lag</t>
   </si>
   <si>
-    <t>SL Balance Test</t>
-  </si>
-  <si>
-    <t>SL Squat Quality</t>
-  </si>
-  <si>
-    <t>SL Squat Endurance</t>
-  </si>
-  <si>
-    <t>SL Bridge</t>
-  </si>
-  <si>
-    <t>SL Heel Raises</t>
-  </si>
-  <si>
-    <t>Est. 1RM Squat</t>
-  </si>
-  <si>
-    <t>Y-Balance Anterior</t>
-  </si>
-  <si>
-    <t>Y-Balance Posteromedial</t>
-  </si>
-  <si>
-    <t>Y-Balance Posterolateral</t>
-  </si>
-  <si>
     <t>reps</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>%BM</t>
-  </si>
-  <si>
-    <t>﻿Subjects lie prone on a treatment bed with the lower legs off the end allowing full passive knee extension. The heel height difference is measured (approx 1cm = 1°)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> The patient is then required to maintain full active extension of the knee when the therapist removes support.</t>
   </si>
   <si>
     <t>With the patient sitting on the edge of a treatment bed, the therapist takes the relaxed knee into full passive extension.</t>
-  </si>
-  <si>
-    <t>﻿Subjects lie supine on the floor with one heel on a box or plinth at 60cm high. The knee of the test leg is slightly bent at 20° and opposite leg is bent to 90° hip and knee flexion with their arms crossed over chest. Subjects elevate the hips as high as possible and the assessor places a hand at this height. Repeat this action as many times as possible touching the assessors hand each time. The test concludes when the subject is unable to bridge to the original height (assessors hand but lets use an actual target).</t>
-  </si>
-  <si>
-    <t>﻿Subjects stand on one foot on the edge of the step and perform a calf raise through full range of motion. Calf raises are performed at 1 repetition every 2 seconds. The test concludes when subjects are unable to move through full range or slow below the cadence outlined above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">﻿Subjects stand on one leg with other leg raised and arms crossed over the chest. The assessor uses a stopwatch to time how long stance is maintained on one leg with a) eyes open, and b) eyes closed. </t>
-  </si>
-  <si>
-    <t>Time ends when; Arms are used (uncrossed) /  Use of the raised foot (touches down or other leg)  / Movement of the stance foot  / 45 secs has elapsed (maximum time)  / Eyes opened on eyes closed trials</t>
-  </si>
-  <si>
-    <t>Seat position is at 90 degrees to the slide, and the foot should be placed so that the hip is flexed to 90 degrees. A valid repetition is where the weight is lowered to a depth of 90 degrees knee flexion and then extended back to full knee extension.</t>
-  </si>
-  <si>
-    <t>1RM Squat squat to 90 deg knee flexion</t>
-  </si>
-  <si>
-    <t>she cannot squat 1.5x BM pre injury. Max back squat = 80kg at 70kg BM</t>
-  </si>
-  <si>
-    <t>note</t>
   </si>
   <si>
     <t>Y-Balance (Anterior)</t>
@@ -1553,6 +1491,24 @@
   <si>
     <t>Injured side dorsiflexion should be &gt; 10cm and &gt; 90% of un-injured side.</t>
   </si>
+  <si>
+    <t>Operator Code</t>
+  </si>
+  <si>
+    <t>Operator Pretty</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>Goal Pretty</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
 </sst>
 </file>
 
@@ -1562,11 +1518,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1763,15 +1726,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial (Body)"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial (Body)"/>
     </font>
     <font>
       <sz val="12"/>
@@ -2024,331 +1978,316 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="25" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2603,13 +2542,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2667,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="105" t="s">
+      <c r="G4" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2700,7 +2639,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="103"/>
+      <c r="G5" s="118"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2728,7 +2667,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="103"/>
+      <c r="G6" s="118"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2752,7 +2691,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="103"/>
+      <c r="G7" s="118"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2775,7 +2714,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="103"/>
+      <c r="G8" s="118"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2803,7 +2742,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="103"/>
+      <c r="G9" s="118"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2886,13 +2825,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -2947,24 +2886,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="114">
+      <c r="H16" s="119">
         <v>45359</v>
       </c>
-      <c r="I16" s="113"/>
-      <c r="J16" s="115">
+      <c r="I16" s="120"/>
+      <c r="J16" s="121">
         <v>47204</v>
       </c>
-      <c r="K16" s="113"/>
-      <c r="L16" s="116" t="s">
+      <c r="K16" s="120"/>
+      <c r="L16" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="113"/>
-      <c r="N16" s="114">
+      <c r="M16" s="120"/>
+      <c r="N16" s="119">
         <v>45429</v>
       </c>
-      <c r="O16" s="113"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="113"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="120"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3038,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="105" t="s">
+      <c r="G18" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3082,7 +3021,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="103"/>
+      <c r="G19" s="118"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3120,7 +3059,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="103"/>
+      <c r="G20" s="118"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3166,7 +3105,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="103"/>
+      <c r="G21" s="118"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3202,7 +3141,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="103"/>
+      <c r="G22" s="118"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3240,7 +3179,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="103"/>
+      <c r="G23" s="118"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3280,7 +3219,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="103"/>
+      <c r="G24" s="118"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3471,13 +3410,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3522,12 +3461,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="112" t="s">
+      <c r="H33" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="113"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="113"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="120"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3552,7 +3491,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="105" t="s">
+      <c r="G34" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3583,7 +3522,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="103"/>
+      <c r="G35" s="118"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3612,7 +3551,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="103"/>
+      <c r="G36" s="118"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3641,7 +3580,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="103"/>
+      <c r="G37" s="118"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3670,7 +3609,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="103"/>
+      <c r="G38" s="118"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3691,7 +3630,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="103"/>
+      <c r="G39" s="118"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3720,7 +3659,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="103"/>
+      <c r="G40" s="118"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3741,7 +3680,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="103"/>
+      <c r="G41" s="118"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3770,7 +3709,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="103"/>
+      <c r="G42" s="118"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3791,7 +3730,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="103"/>
+      <c r="G43" s="118"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3814,17 +3753,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="106" t="s">
+      <c r="C44" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="106" t="s">
+      <c r="D44" s="125" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="103"/>
+      <c r="G44" s="118"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3839,13 +3778,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="103"/>
+      <c r="G45" s="118"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3874,7 +3813,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="103"/>
+      <c r="G46" s="118"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -3895,7 +3834,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="103"/>
+      <c r="G47" s="118"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -3924,7 +3863,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="103"/>
+      <c r="G48" s="118"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -3953,7 +3892,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="103"/>
+      <c r="G49" s="118"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -3980,7 +3919,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="103"/>
+      <c r="G50" s="118"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4076,10 +4015,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="102">
+      <c r="B54" s="130">
         <v>16</v>
       </c>
-      <c r="C54" s="107" t="s">
+      <c r="C54" s="131" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4100,8 +4039,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="103"/>
-      <c r="C55" s="103"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="118"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4120,10 +4059,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="108">
+      <c r="B56" s="126">
         <v>17</v>
       </c>
-      <c r="C56" s="110" t="s">
+      <c r="C56" s="128" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4145,8 +4084,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="109"/>
-      <c r="C57" s="111"/>
+      <c r="B57" s="127"/>
+      <c r="C57" s="129"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4166,10 +4105,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="102">
+      <c r="B58" s="130">
         <v>18</v>
       </c>
-      <c r="C58" s="107" t="s">
+      <c r="C58" s="131" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4190,8 +4129,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="103"/>
-      <c r="C59" s="103"/>
+      <c r="B59" s="118"/>
+      <c r="C59" s="118"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4210,10 +4149,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="108">
+      <c r="B60" s="126">
         <v>19</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="128" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4235,8 +4174,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="109"/>
-      <c r="C61" s="111"/>
+      <c r="B61" s="127"/>
+      <c r="C61" s="129"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4256,7 +4195,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="102">
+      <c r="B62" s="130">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4280,7 +4219,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="103"/>
+      <c r="B63" s="118"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4456,13 +4395,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="104" t="s">
+      <c r="B74" s="117" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="103"/>
-      <c r="D74" s="103"/>
-      <c r="E74" s="103"/>
-      <c r="F74" s="103"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="118"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="118"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4541,7 +4480,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="105" t="s">
+      <c r="G76" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4568,7 +4507,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="103"/>
+      <c r="G77" s="118"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4593,7 +4532,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="103"/>
+      <c r="G78" s="118"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4620,7 +4559,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="103"/>
+      <c r="G79" s="118"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4652,7 +4591,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="103"/>
+      <c r="G80" s="118"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4681,7 +4620,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="103"/>
+      <c r="G81" s="118"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4710,7 +4649,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="103"/>
+      <c r="G82" s="118"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4739,7 +4678,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="103"/>
+      <c r="G83" s="118"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4768,7 +4707,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="103"/>
+      <c r="G84" s="118"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4797,7 +4736,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="103"/>
+      <c r="G85" s="118"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4826,7 +4765,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="103"/>
+      <c r="G86" s="118"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4855,7 +4794,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="103"/>
+      <c r="G87" s="118"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8601,22 +8540,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8627,6 +8550,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8920,20 +8859,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3C897E-C35E-744B-BB5A-048B2D3C5B40}">
-  <dimension ref="A1:F28"/>
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="99"/>
     <col min="2" max="2" width="23.5" style="98" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="98"/>
-    <col min="4" max="4" width="73.1640625" style="98" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="116" style="98" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" style="98" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.6640625" style="98" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="98"/>
+    <col min="4" max="4" width="16.5" style="98" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" style="98" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="98" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="98"/>
+    <col min="8" max="8" width="73.1640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="116" style="98" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="98" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="98" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="101" t="s">
         <v>182</v>
       </c>
@@ -8943,17 +8890,35 @@
       <c r="C1" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="G1" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="I1" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="J1" s="100" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="82" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1" s="82" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="99">
         <v>0</v>
       </c>
@@ -8963,17 +8928,33 @@
       <c r="C2" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="114" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="78">
+        <v>0</v>
+      </c>
+      <c r="H2" s="92" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="I2" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="J2" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" s="81">
+        <v>1</v>
+      </c>
+      <c r="L2" s="81"/>
+    </row>
+    <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="99">
         <v>0</v>
       </c>
@@ -8983,17 +8964,33 @@
       <c r="C3" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="D3" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="78">
+        <v>125</v>
+      </c>
+      <c r="H3" s="92" t="s">
         <v>180</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="I3" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="98" t="s">
+      <c r="J3" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K3" s="81">
+        <v>1</v>
+      </c>
+      <c r="L3" s="81"/>
+    </row>
+    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="99">
         <v>0</v>
       </c>
@@ -9003,17 +9000,31 @@
       <c r="C4" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="92" t="s">
+      <c r="D4" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="78">
+        <v>1</v>
+      </c>
+      <c r="G4" s="78">
+        <v>1</v>
+      </c>
+      <c r="H4" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="I4" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="J4" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+    </row>
+    <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="99">
         <v>0</v>
       </c>
@@ -9023,17 +9034,35 @@
       <c r="C5" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="115" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="116" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="78">
+        <v>90</v>
+      </c>
+      <c r="H5" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="I5" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="F5" s="98" t="s">
+      <c r="J5" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" s="81">
+        <v>2</v>
+      </c>
+      <c r="L5" s="81" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="99">
         <v>0</v>
       </c>
@@ -9043,17 +9072,35 @@
       <c r="C6" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="115" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="116" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="78">
+        <v>90</v>
+      </c>
+      <c r="H6" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="I6" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="98" t="s">
+      <c r="J6" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K6" s="81">
+        <v>2</v>
+      </c>
+      <c r="L6" s="81" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="99">
         <v>0</v>
       </c>
@@ -9063,37 +9110,55 @@
       <c r="C7" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="116" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" s="84">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="I7" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="98" t="s">
+      <c r="J7" s="98" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" s="133" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="131">
+      <c r="K7" s="81">
+        <v>2</v>
+      </c>
+      <c r="L7" s="94" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="108" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="106">
         <v>1</v>
       </c>
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="107" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="133" t="s">
+      <c r="C8" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="134" t="s">
+      <c r="H8" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="E8" s="135" t="s">
+      <c r="I8" s="110" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="133" t="s">
+      <c r="J8" s="108" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="99">
         <v>1</v>
       </c>
@@ -9103,17 +9168,17 @@
       <c r="C9" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="H9" s="92" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="I9" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="98" t="s">
+      <c r="J9" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="99">
         <v>1</v>
       </c>
@@ -9123,17 +9188,17 @@
       <c r="C10" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="H10" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="81" t="s">
+      <c r="I10" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="J10" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="99">
         <v>1</v>
       </c>
@@ -9143,37 +9208,37 @@
       <c r="C11" s="98" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="92" t="s">
-        <v>204</v>
-      </c>
-      <c r="E11" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" s="98" t="s">
+      <c r="H11" s="92" t="s">
+        <v>192</v>
+      </c>
+      <c r="I11" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="133" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="131">
+    <row r="12" spans="1:12" s="108" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="106">
         <v>2</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="107" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="133" t="s">
+      <c r="C12" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="134" t="s">
+      <c r="H12" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="E12" s="135" t="s">
+      <c r="I12" s="110" t="s">
         <v>150</v>
       </c>
-      <c r="F12" s="133" t="s">
+      <c r="J12" s="108" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="99">
         <v>2</v>
       </c>
@@ -9183,17 +9248,17 @@
       <c r="C13" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="H13" s="92" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="81" t="s">
+      <c r="I13" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="J13" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="99">
         <v>2</v>
       </c>
@@ -9203,177 +9268,209 @@
       <c r="C14" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="D14" s="92" t="s">
+      <c r="H14" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="91" t="s">
+      <c r="I14" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="98" t="s">
+      <c r="J14" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="99">
         <v>2</v>
       </c>
-      <c r="B15" s="125" t="s">
+      <c r="B15" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="125" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" s="136" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="136" t="s">
-        <v>216</v>
-      </c>
-      <c r="F15" s="98" t="s">
+      <c r="C15" s="104" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="111" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="111" t="s">
+        <v>196</v>
+      </c>
+      <c r="J15" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="99">
         <v>2</v>
       </c>
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="103" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="123" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="123" t="s">
-        <v>220</v>
-      </c>
-      <c r="F16" s="98" t="s">
+      <c r="I16" s="103" t="s">
+        <v>200</v>
+      </c>
+      <c r="J16" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="99">
         <v>2</v>
       </c>
-      <c r="B17" s="125" t="s">
+      <c r="B17" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="125" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="125" t="s">
-        <v>223</v>
-      </c>
-      <c r="E17" s="123" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" s="98" t="s">
+      <c r="C17" s="104" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="I17" s="103" t="s">
+        <v>200</v>
+      </c>
+      <c r="J17" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="99">
         <v>2</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="D18" s="123" t="s">
-        <v>224</v>
-      </c>
-      <c r="E18" s="123" t="s">
-        <v>221</v>
-      </c>
-      <c r="F18" s="98" t="s">
+      <c r="C18" s="103" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="I18" s="103" t="s">
+        <v>201</v>
+      </c>
+      <c r="J18" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="99">
         <v>2</v>
       </c>
-      <c r="B19" s="127" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="127" t="s">
-        <v>199</v>
-      </c>
-      <c r="D19" s="127" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="123" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="98" t="s">
+      <c r="B19" s="105" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105" t="s">
+        <v>206</v>
+      </c>
+      <c r="I19" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="J19" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="99">
         <v>2</v>
       </c>
-      <c r="B20" s="122" t="s">
-        <v>228</v>
-      </c>
-      <c r="C20" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="D20" s="123" t="s">
-        <v>230</v>
-      </c>
-      <c r="E20" s="137" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="98" t="s">
+      <c r="B20" s="102" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="103" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" s="112" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="99">
         <v>2</v>
       </c>
-      <c r="B21" s="122" t="s">
-        <v>229</v>
-      </c>
-      <c r="C21" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="D21" s="123" t="s">
-        <v>231</v>
-      </c>
-      <c r="E21" s="137" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="98" t="s">
+      <c r="B21" s="102" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="112" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="99">
         <v>2</v>
       </c>
-      <c r="B22" s="122" t="s">
-        <v>235</v>
-      </c>
-      <c r="C22" s="123" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22" s="137" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22" s="137" t="s">
-        <v>237</v>
-      </c>
-      <c r="F22" s="98" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="112" t="s">
+        <v>216</v>
+      </c>
+      <c r="I22" s="112" t="s">
+        <v>217</v>
+      </c>
+      <c r="J22" s="98" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="99">
         <v>2</v>
       </c>
@@ -9383,17 +9480,17 @@
       <c r="C23" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="81" t="s">
+      <c r="H23" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="138" t="s">
-        <v>240</v>
-      </c>
-      <c r="F23" s="98" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="113" t="s">
+        <v>220</v>
+      </c>
+      <c r="J23" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="99">
         <v>2</v>
       </c>
@@ -9403,479 +9500,91 @@
       <c r="C24" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="81" t="s">
+      <c r="H24" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="E24" s="138" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="98" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I24" s="113" t="s">
+        <v>220</v>
+      </c>
+      <c r="J24" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="99">
         <v>2</v>
       </c>
-      <c r="B25" s="125" t="s">
+      <c r="B25" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="125" t="s">
+      <c r="C25" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="81" t="s">
-        <v>241</v>
-      </c>
-      <c r="E25" s="138" t="s">
-        <v>242</v>
-      </c>
-      <c r="F25" s="98" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="81" t="s">
+        <v>221</v>
+      </c>
+      <c r="I25" s="113" t="s">
+        <v>222</v>
+      </c>
+      <c r="J25" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="99">
         <v>2</v>
       </c>
-      <c r="B26" s="122" t="s">
-        <v>213</v>
+      <c r="B26" s="102" t="s">
+        <v>193</v>
       </c>
       <c r="C26" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="F26" s="98" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J26" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="99">
         <v>2</v>
       </c>
-      <c r="B27" s="122" t="s">
-        <v>214</v>
+      <c r="B27" s="102" t="s">
+        <v>194</v>
       </c>
       <c r="C27" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="F27" s="98" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J27" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="99">
         <v>2</v>
       </c>
-      <c r="B28" s="122" t="s">
-        <v>215</v>
+      <c r="B28" s="102" t="s">
+        <v>195</v>
       </c>
       <c r="C28" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="F28" s="98" t="s">
-        <v>238</v>
+      <c r="J28" s="98" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="F6" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C9BD343-8327-2B43-A044-910E263A1831}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="7.1640625" style="121" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27" style="121" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="22.33203125" style="121" customWidth="1"/>
-    <col min="9" max="9" width="55.5" style="121" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" style="121" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="121"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A1" s="117" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="118" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="118" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1" s="119" t="s">
-        <v>148</v>
-      </c>
-      <c r="E1" s="119" t="s">
-        <v>149</v>
-      </c>
-      <c r="F1" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120" t="s">
-        <v>183</v>
-      </c>
-      <c r="J1" s="119" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="129"/>
-      <c r="B2" s="125" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="125" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="125" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="125" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="I2" s="125"/>
-      <c r="J2" s="126" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="128"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="126" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="130"/>
-      <c r="B4" s="122" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="121" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" s="122" t="s">
-        <v>118</v>
-      </c>
-      <c r="J4" s="124"/>
-    </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="120"/>
-      <c r="B5" s="122" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="126"/>
-    </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="120"/>
-      <c r="B6" s="122" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="125"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125" t="s">
-        <v>119</v>
-      </c>
-      <c r="J6" s="126"/>
-    </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="120"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="126"/>
-    </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="120"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="126"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80124898-5C1F-5248-8006-92D5689A5FC6}">
-  <dimension ref="B2:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="2:6" ht="340" x14ac:dyDescent="0.2">
-      <c r="B2" s="99">
-        <v>2</v>
-      </c>
-      <c r="C2" s="97" t="s">
-        <v>146</v>
-      </c>
-      <c r="D2" s="98" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="81" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="B3" s="99">
-        <v>2</v>
-      </c>
-      <c r="C3" s="97" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="98" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="81" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B4" s="99">
-        <v>2</v>
-      </c>
-      <c r="C4" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="98" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="81" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="B5" s="99">
-        <v>2</v>
-      </c>
-      <c r="C5" s="98" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="92" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="81"/>
-    </row>
-    <row r="6" spans="2:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="B6" s="99">
-        <v>2</v>
-      </c>
-      <c r="C6" s="98" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="E6" s="92" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="81"/>
-    </row>
-    <row r="7" spans="2:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B7" s="99">
-        <v>2</v>
-      </c>
-      <c r="C7" s="98" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="E7" s="92" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="81" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B8" s="99">
-        <v>2</v>
-      </c>
-      <c r="C8" s="98" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B9" s="99">
-        <v>2</v>
-      </c>
-      <c r="C9" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="92" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="81" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B10" s="99">
-        <v>2</v>
-      </c>
-      <c r="C10" s="98" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="98" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="92" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="81" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="B11" s="99">
-        <v>2</v>
-      </c>
-      <c r="C11" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="98" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B12" s="99">
-        <v>2</v>
-      </c>
-      <c r="C12" s="98" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="98" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" s="81"/>
-    </row>
-    <row r="13" spans="2:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="99">
-        <v>2</v>
-      </c>
-      <c r="C13" s="98" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="98" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="81"/>
-    </row>
-    <row r="14" spans="2:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="99">
-        <v>2</v>
-      </c>
-      <c r="C14" s="98" t="s">
-        <v>196</v>
-      </c>
-      <c r="D14" s="98" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" s="92"/>
-      <c r="F14" s="81"/>
-    </row>
-    <row r="15" spans="2:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="99">
-        <v>2</v>
-      </c>
-      <c r="C15" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" s="98" t="s">
-        <v>187</v>
-      </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-    </row>
-    <row r="16" spans="2:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="99">
-        <v>2</v>
-      </c>
-      <c r="C16" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="98" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01440D2E-D5CB-624F-A307-D0DE876488BF}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C57F4E3-50C7-6549-840E-777C7A68D7C4}"/>
+  <xr:revisionPtr revIDLastSave="595" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01AB87C3-0ECB-5A4A-9E37-BF12E9CD6300}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="230">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1508,6 +1508,9 @@
   </si>
   <si>
     <t>90%</t>
+  </si>
+  <si>
+    <t>&lt;</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1779,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1975,12 +1978,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2252,28 +2264,21 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2283,11 +2288,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2542,7 +2572,7 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="119" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="118"/>
@@ -2606,7 +2636,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="123" t="s">
+      <c r="G4" s="120" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2825,7 +2855,7 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="119" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="118"/>
@@ -2886,24 +2916,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="119">
+      <c r="H16" s="129">
         <v>45359</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="121">
+      <c r="I16" s="128"/>
+      <c r="J16" s="130">
         <v>47204</v>
       </c>
-      <c r="K16" s="120"/>
-      <c r="L16" s="122" t="s">
+      <c r="K16" s="128"/>
+      <c r="L16" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="120"/>
-      <c r="N16" s="119">
+      <c r="M16" s="128"/>
+      <c r="N16" s="129">
         <v>45429</v>
       </c>
-      <c r="O16" s="120"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="120"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="129"/>
+      <c r="Q16" s="128"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -2977,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="123" t="s">
+      <c r="G18" s="120" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3410,7 +3440,7 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="117" t="s">
+      <c r="B32" s="119" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="118"/>
@@ -3461,12 +3491,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="124" t="s">
+      <c r="H33" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="120"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="120"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="129"/>
+      <c r="K33" s="128"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3491,7 +3521,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="123" t="s">
+      <c r="G34" s="120" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3753,10 +3783,10 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="C44" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="125" t="s">
+      <c r="D44" s="121" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
@@ -4015,10 +4045,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="130">
+      <c r="B54" s="117">
         <v>16</v>
       </c>
-      <c r="C54" s="131" t="s">
+      <c r="C54" s="122" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4059,10 +4089,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="126">
+      <c r="B56" s="123">
         <v>17</v>
       </c>
-      <c r="C56" s="128" t="s">
+      <c r="C56" s="125" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4084,8 +4114,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="127"/>
-      <c r="C57" s="129"/>
+      <c r="B57" s="124"/>
+      <c r="C57" s="126"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4105,10 +4135,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="130">
+      <c r="B58" s="117">
         <v>18</v>
       </c>
-      <c r="C58" s="131" t="s">
+      <c r="C58" s="122" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4149,10 +4179,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="126">
+      <c r="B60" s="123">
         <v>19</v>
       </c>
-      <c r="C60" s="128" t="s">
+      <c r="C60" s="125" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4174,8 +4204,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="127"/>
-      <c r="C61" s="129"/>
+      <c r="B61" s="124"/>
+      <c r="C61" s="126"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4195,7 +4225,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="130">
+      <c r="B62" s="117">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4395,7 +4425,7 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="117" t="s">
+      <c r="B74" s="119" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="118"/>
@@ -4480,7 +4510,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="123" t="s">
+      <c r="G76" s="120" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -8540,6 +8570,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8550,22 +8596,6 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8868,10 +8898,10 @@
     <col min="1" max="1" width="10.83203125" style="99"/>
     <col min="2" max="2" width="23.5" style="98" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="98"/>
-    <col min="4" max="4" width="16.5" style="98" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" style="98" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="98" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="98"/>
+    <col min="4" max="4" width="16.5" style="99" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" style="99" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="99"/>
     <col min="8" max="8" width="73.1640625" style="98" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="116" style="98" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.33203125" style="98" bestFit="1" customWidth="1"/>
@@ -8890,16 +8920,16 @@
       <c r="C1" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="101" t="s">
         <v>224</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="101" t="s">
         <v>223</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="101" t="s">
         <v>227</v>
       </c>
-      <c r="G1" s="100" t="s">
+      <c r="G1" s="101" t="s">
         <v>145</v>
       </c>
       <c r="H1" s="82" t="s">
@@ -9072,16 +9102,16 @@
       <c r="C6" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="132" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="115" t="s">
+      <c r="E6" s="133" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="116" t="s">
+      <c r="F6" s="134" t="s">
         <v>228</v>
       </c>
-      <c r="G6" s="78">
+      <c r="G6" s="132">
         <v>90</v>
       </c>
       <c r="H6" s="81" t="s">
@@ -9148,6 +9178,18 @@
       <c r="C8" s="108" t="s">
         <v>184</v>
       </c>
+      <c r="D8" s="114" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="78">
+        <v>0</v>
+      </c>
       <c r="H8" s="109" t="s">
         <v>180</v>
       </c>
@@ -9168,6 +9210,18 @@
       <c r="C9" s="98" t="s">
         <v>184</v>
       </c>
+      <c r="D9" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="115" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="78">
+        <v>125</v>
+      </c>
       <c r="H9" s="92" t="s">
         <v>180</v>
       </c>
@@ -9188,6 +9242,18 @@
       <c r="C10" s="98" t="s">
         <v>185</v>
       </c>
+      <c r="D10" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="78">
+        <v>1</v>
+      </c>
+      <c r="G10" s="78">
+        <v>1</v>
+      </c>
       <c r="H10" s="92" t="s">
         <v>177</v>
       </c>
@@ -9208,6 +9274,18 @@
       <c r="C11" s="98" t="s">
         <v>189</v>
       </c>
+      <c r="D11" s="99" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="99">
+        <v>5</v>
+      </c>
+      <c r="G11" s="99">
+        <v>5</v>
+      </c>
       <c r="H11" s="92" t="s">
         <v>192</v>
       </c>
@@ -9228,6 +9306,10 @@
       <c r="C12" s="108" t="s">
         <v>184</v>
       </c>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
       <c r="H12" s="109" t="s">
         <v>180</v>
       </c>
@@ -9288,10 +9370,10 @@
       <c r="C15" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
       <c r="H15" s="111" t="s">
         <v>198</v>
       </c>
@@ -9312,10 +9394,10 @@
       <c r="C16" s="103" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
       <c r="H16" s="103" t="s">
         <v>199</v>
       </c>
@@ -9336,10 +9418,10 @@
       <c r="C17" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
       <c r="H17" s="104" t="s">
         <v>203</v>
       </c>
@@ -9360,10 +9442,10 @@
       <c r="C18" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
       <c r="H18" s="103" t="s">
         <v>204</v>
       </c>
@@ -9384,10 +9466,10 @@
       <c r="C19" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
       <c r="H19" s="105" t="s">
         <v>206</v>
       </c>
@@ -9408,10 +9490,10 @@
       <c r="C20" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
       <c r="H20" s="103" t="s">
         <v>210</v>
       </c>
@@ -9432,10 +9514,10 @@
       <c r="C21" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
       <c r="H21" s="103" t="s">
         <v>211</v>
       </c>
@@ -9456,10 +9538,10 @@
       <c r="C22" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
       <c r="H22" s="112" t="s">
         <v>216</v>
       </c>
@@ -9520,10 +9602,10 @@
       <c r="C25" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
       <c r="H25" s="81" t="s">
         <v>221</v>
       </c>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="595" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01AB87C3-0ECB-5A4A-9E37-BF12E9CD6300}"/>
+  <xr:revisionPtr revIDLastSave="596" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2728F22B-8A8B-7D40-8498-113709D554AE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2264,43 +2264,6 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2318,6 +2281,43 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2572,13 +2572,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2636,7 +2636,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="120" t="s">
+      <c r="G4" s="129" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2669,7 +2669,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="118"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2697,7 +2697,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="118"/>
+      <c r="G6" s="124"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2721,7 +2721,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="118"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2744,7 +2744,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="118"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2772,7 +2772,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="118"/>
+      <c r="G9" s="124"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2855,13 +2855,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -2916,24 +2916,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="129">
+      <c r="H16" s="125">
         <v>45359</v>
       </c>
-      <c r="I16" s="128"/>
-      <c r="J16" s="130">
+      <c r="I16" s="126"/>
+      <c r="J16" s="127">
         <v>47204</v>
       </c>
-      <c r="K16" s="128"/>
-      <c r="L16" s="131" t="s">
+      <c r="K16" s="126"/>
+      <c r="L16" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="128"/>
-      <c r="N16" s="129">
+      <c r="M16" s="126"/>
+      <c r="N16" s="125">
         <v>45429</v>
       </c>
-      <c r="O16" s="128"/>
-      <c r="P16" s="129"/>
-      <c r="Q16" s="128"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="125"/>
+      <c r="Q16" s="126"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="129" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3051,7 +3051,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="118"/>
+      <c r="G19" s="124"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3089,7 +3089,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="118"/>
+      <c r="G20" s="124"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="118"/>
+      <c r="G21" s="124"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3171,7 +3171,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="118"/>
+      <c r="G22" s="124"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3209,7 +3209,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="118"/>
+      <c r="G23" s="124"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="118"/>
+      <c r="G24" s="124"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3440,13 +3440,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="119" t="s">
+      <c r="B32" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3491,12 +3491,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="127" t="s">
+      <c r="H33" s="130" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="128"/>
-      <c r="J33" s="129"/>
-      <c r="K33" s="128"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="125"/>
+      <c r="K33" s="126"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3521,7 +3521,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="120" t="s">
+      <c r="G34" s="129" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3552,7 +3552,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="118"/>
+      <c r="G35" s="124"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3581,7 +3581,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="118"/>
+      <c r="G36" s="124"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3610,7 +3610,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="118"/>
+      <c r="G37" s="124"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3639,7 +3639,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="118"/>
+      <c r="G38" s="124"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3660,7 +3660,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="118"/>
+      <c r="G39" s="124"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3689,7 +3689,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="118"/>
+      <c r="G40" s="124"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3710,7 +3710,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="118"/>
+      <c r="G41" s="124"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3739,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="118"/>
+      <c r="G42" s="124"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3760,7 +3760,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="118"/>
+      <c r="G43" s="124"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3783,17 +3783,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="121" t="s">
+      <c r="C44" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="121" t="s">
+      <c r="D44" s="131" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="118"/>
+      <c r="G44" s="124"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3808,13 +3808,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
+      <c r="C45" s="124"/>
+      <c r="D45" s="124"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="118"/>
+      <c r="G45" s="124"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3843,7 +3843,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="118"/>
+      <c r="G46" s="124"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -3864,7 +3864,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="118"/>
+      <c r="G47" s="124"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -3893,7 +3893,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="118"/>
+      <c r="G48" s="124"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -3922,7 +3922,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="118"/>
+      <c r="G49" s="124"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -3949,7 +3949,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="118"/>
+      <c r="G50" s="124"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4045,10 +4045,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="117">
+      <c r="B54" s="136">
         <v>16</v>
       </c>
-      <c r="C54" s="122" t="s">
+      <c r="C54" s="137" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4069,8 +4069,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="118"/>
-      <c r="C55" s="118"/>
+      <c r="B55" s="124"/>
+      <c r="C55" s="124"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4089,10 +4089,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="123">
+      <c r="B56" s="132">
         <v>17</v>
       </c>
-      <c r="C56" s="125" t="s">
+      <c r="C56" s="134" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4114,8 +4114,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="124"/>
-      <c r="C57" s="126"/>
+      <c r="B57" s="133"/>
+      <c r="C57" s="135"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4135,10 +4135,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="117">
+      <c r="B58" s="136">
         <v>18</v>
       </c>
-      <c r="C58" s="122" t="s">
+      <c r="C58" s="137" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4159,8 +4159,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="118"/>
-      <c r="C59" s="118"/>
+      <c r="B59" s="124"/>
+      <c r="C59" s="124"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4179,10 +4179,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="123">
+      <c r="B60" s="132">
         <v>19</v>
       </c>
-      <c r="C60" s="125" t="s">
+      <c r="C60" s="134" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4204,8 +4204,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="124"/>
-      <c r="C61" s="126"/>
+      <c r="B61" s="133"/>
+      <c r="C61" s="135"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4225,7 +4225,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="117">
+      <c r="B62" s="136">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="118"/>
+      <c r="B63" s="124"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4425,13 +4425,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="119" t="s">
+      <c r="B74" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="118"/>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="118"/>
+      <c r="C74" s="124"/>
+      <c r="D74" s="124"/>
+      <c r="E74" s="124"/>
+      <c r="F74" s="124"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4510,7 +4510,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="120" t="s">
+      <c r="G76" s="129" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4537,7 +4537,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="118"/>
+      <c r="G77" s="124"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="118"/>
+      <c r="G78" s="124"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4589,7 +4589,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="118"/>
+      <c r="G79" s="124"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4621,7 +4621,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="118"/>
+      <c r="G80" s="124"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4650,7 +4650,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="118"/>
+      <c r="G81" s="124"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4679,7 +4679,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="118"/>
+      <c r="G82" s="124"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4708,7 +4708,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="118"/>
+      <c r="G83" s="124"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4737,7 +4737,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="118"/>
+      <c r="G84" s="124"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4766,7 +4766,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="118"/>
+      <c r="G85" s="124"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4795,7 +4795,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="118"/>
+      <c r="G86" s="124"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4824,7 +4824,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="118"/>
+      <c r="G87" s="124"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8570,22 +8570,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8596,6 +8580,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9102,16 +9102,16 @@
       <c r="C6" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="132" t="s">
+      <c r="D6" s="117" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="133" t="s">
+      <c r="E6" s="118" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="134" t="s">
+      <c r="F6" s="119" t="s">
         <v>228</v>
       </c>
-      <c r="G6" s="132">
+      <c r="G6" s="117">
         <v>90</v>
       </c>
       <c r="H6" s="81" t="s">
@@ -9278,7 +9278,7 @@
         <v>229</v>
       </c>
       <c r="E11" s="99" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="F11" s="99">
         <v>5</v>
@@ -9370,10 +9370,10 @@
       <c r="C15" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
       <c r="H15" s="111" t="s">
         <v>198</v>
       </c>
@@ -9394,10 +9394,10 @@
       <c r="C16" s="103" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
       <c r="H16" s="103" t="s">
         <v>199</v>
       </c>
@@ -9418,10 +9418,10 @@
       <c r="C17" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
       <c r="H17" s="104" t="s">
         <v>203</v>
       </c>
@@ -9442,10 +9442,10 @@
       <c r="C18" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
       <c r="H18" s="103" t="s">
         <v>204</v>
       </c>
@@ -9466,10 +9466,10 @@
       <c r="C19" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="135"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
       <c r="H19" s="105" t="s">
         <v>206</v>
       </c>
@@ -9490,10 +9490,10 @@
       <c r="C20" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
       <c r="H20" s="103" t="s">
         <v>210</v>
       </c>
@@ -9514,10 +9514,10 @@
       <c r="C21" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
       <c r="H21" s="103" t="s">
         <v>211</v>
       </c>
@@ -9538,10 +9538,10 @@
       <c r="C22" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="122"/>
       <c r="H22" s="112" t="s">
         <v>216</v>
       </c>
@@ -9602,10 +9602,10 @@
       <c r="C25" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
       <c r="H25" s="81" t="s">
         <v>221</v>
       </c>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="596" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2728F22B-8A8B-7D40-8498-113709D554AE}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D53C39B-2242-804B-9CDD-B34E5247F7C6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="236">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1385,25 +1385,6 @@
   </si>
   <si>
     <t>Y-Balance (Postero-Lateral)</t>
-  </si>
-  <si>
-    <t>For a subject to be rated “good”; 
-• Maintain balance 
-• Perform the movement smoothly 
-• Squat must be to at least 60 degrees 
-• No trunk movement (lateral deviation, rotation, lateral flexion, forward flexion)
-• No pelvic movement (shunt or lateral deviation, rotation, or tilt)
-• No hip adduction or internal rotation 
-• No knee valgus 
-• Centre of knee remains over centre of foot</t>
-  </si>
-  <si>
-    <t>quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">﻿Subjects stand on one leg on a 20cm box with arms crossed. 
-5 x single leg squats are performed in a slow controlled manner (at a rate of 2 seconds per squat). 
-The task is rated as “good”, “fair” or “poor”. </t>
   </si>
   <si>
     <t>﻿Subjects lie supine on the floor with one heel on a 60cm (~24") high box. The knee of the test leg is slightly bent at 20° and opposite leg is bent to 90° hip and knee flexion with their arms crossed over chest. Subjects elevate the hips as high as possible and the assessor places a target at this height. Repeat this action as many times as possible touching the target each time. The test concludes when the subject is unable to bridge to the target ﻿(Freckleton et al, 2013).</t>
@@ -1511,6 +1492,35 @@
   </si>
   <si>
     <t>&lt;</t>
+  </si>
+  <si>
+    <t>30s</t>
+  </si>
+  <si>
+    <t>20 Reps</t>
+  </si>
+  <si>
+    <t>45s</t>
+  </si>
+  <si>
+    <t>10cm</t>
+  </si>
+  <si>
+    <t>Hands must stay on hips, heel must stay down and athlete must maintain balance throughout the trial. 
+Perform 3 successful repetittions on each leg before moving on.
+The score will be recorded as the maximum distance from each direction, to the nearest 0.5cm.</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>Standing on one leg, hands on hips, slide the first box forward as far as possible and return back to the start position.</t>
+  </si>
+  <si>
+    <t>Standing on one leg, hands on hips, slide the box backwards and behind the stance leg as far as possible and return back to the start position.</t>
+  </si>
+  <si>
+    <t>Standing on one leg, hands on hips, slide the box backwards and away from the stance leg as far as possible and return back to the start position.</t>
   </si>
 </sst>
 </file>
@@ -1521,11 +1531,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1990,334 +2007,335 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="20" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="19" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="20" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2572,13 +2590,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2636,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="129" t="s">
+      <c r="G4" s="127" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2669,7 +2687,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="124"/>
+      <c r="G5" s="122"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2697,7 +2715,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="124"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2721,7 +2739,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="124"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2744,7 +2762,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="124"/>
+      <c r="G8" s="122"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2772,7 +2790,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="124"/>
+      <c r="G9" s="122"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2855,13 +2873,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="123" t="s">
+      <c r="B15" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -2916,24 +2934,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="125">
+      <c r="H16" s="123">
         <v>45359</v>
       </c>
-      <c r="I16" s="126"/>
-      <c r="J16" s="127">
+      <c r="I16" s="124"/>
+      <c r="J16" s="125">
         <v>47204</v>
       </c>
-      <c r="K16" s="126"/>
-      <c r="L16" s="128" t="s">
+      <c r="K16" s="124"/>
+      <c r="L16" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="126"/>
-      <c r="N16" s="125">
+      <c r="M16" s="124"/>
+      <c r="N16" s="123">
         <v>45429</v>
       </c>
-      <c r="O16" s="126"/>
-      <c r="P16" s="125"/>
-      <c r="Q16" s="126"/>
+      <c r="O16" s="124"/>
+      <c r="P16" s="123"/>
+      <c r="Q16" s="124"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3007,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="129" t="s">
+      <c r="G18" s="127" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3051,7 +3069,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="124"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3089,7 +3107,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="124"/>
+      <c r="G20" s="122"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3135,7 +3153,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="124"/>
+      <c r="G21" s="122"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3171,7 +3189,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="124"/>
+      <c r="G22" s="122"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3209,7 +3227,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="124"/>
+      <c r="G23" s="122"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3249,7 +3267,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="124"/>
+      <c r="G24" s="122"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3440,13 +3458,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="123" t="s">
+      <c r="B32" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="124"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3491,12 +3509,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="130" t="s">
+      <c r="H33" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="126"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="126"/>
+      <c r="I33" s="124"/>
+      <c r="J33" s="123"/>
+      <c r="K33" s="124"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3521,7 +3539,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="129" t="s">
+      <c r="G34" s="127" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3552,7 +3570,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="124"/>
+      <c r="G35" s="122"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3581,7 +3599,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="124"/>
+      <c r="G36" s="122"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3610,7 +3628,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="124"/>
+      <c r="G37" s="122"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3639,7 +3657,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="124"/>
+      <c r="G38" s="122"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3660,7 +3678,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="124"/>
+      <c r="G39" s="122"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3689,7 +3707,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="124"/>
+      <c r="G40" s="122"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3710,7 +3728,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="124"/>
+      <c r="G41" s="122"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3739,7 +3757,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="124"/>
+      <c r="G42" s="122"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3760,7 +3778,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="124"/>
+      <c r="G43" s="122"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3783,17 +3801,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="131" t="s">
+      <c r="C44" s="129" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="131" t="s">
+      <c r="D44" s="129" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="124"/>
+      <c r="G44" s="122"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3808,13 +3826,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="124"/>
-      <c r="D45" s="124"/>
+      <c r="C45" s="122"/>
+      <c r="D45" s="122"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="124"/>
+      <c r="G45" s="122"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3843,7 +3861,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="124"/>
+      <c r="G46" s="122"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -3864,7 +3882,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="124"/>
+      <c r="G47" s="122"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -3893,7 +3911,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="124"/>
+      <c r="G48" s="122"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -3922,7 +3940,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="124"/>
+      <c r="G49" s="122"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -3949,7 +3967,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="124"/>
+      <c r="G50" s="122"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4045,10 +4063,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="136">
+      <c r="B54" s="134">
         <v>16</v>
       </c>
-      <c r="C54" s="137" t="s">
+      <c r="C54" s="135" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4069,8 +4087,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="124"/>
-      <c r="C55" s="124"/>
+      <c r="B55" s="122"/>
+      <c r="C55" s="122"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4089,10 +4107,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="132">
+      <c r="B56" s="130">
         <v>17</v>
       </c>
-      <c r="C56" s="134" t="s">
+      <c r="C56" s="132" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4114,8 +4132,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="133"/>
-      <c r="C57" s="135"/>
+      <c r="B57" s="131"/>
+      <c r="C57" s="133"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4135,10 +4153,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="136">
+      <c r="B58" s="134">
         <v>18</v>
       </c>
-      <c r="C58" s="137" t="s">
+      <c r="C58" s="135" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4159,8 +4177,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="124"/>
-      <c r="C59" s="124"/>
+      <c r="B59" s="122"/>
+      <c r="C59" s="122"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4179,10 +4197,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="132">
+      <c r="B60" s="130">
         <v>19</v>
       </c>
-      <c r="C60" s="134" t="s">
+      <c r="C60" s="132" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4204,8 +4222,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="133"/>
-      <c r="C61" s="135"/>
+      <c r="B61" s="131"/>
+      <c r="C61" s="133"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4225,7 +4243,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="136">
+      <c r="B62" s="134">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4249,7 +4267,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="124"/>
+      <c r="B63" s="122"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4425,13 +4443,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="123" t="s">
+      <c r="B74" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="124"/>
-      <c r="D74" s="124"/>
-      <c r="E74" s="124"/>
-      <c r="F74" s="124"/>
+      <c r="C74" s="122"/>
+      <c r="D74" s="122"/>
+      <c r="E74" s="122"/>
+      <c r="F74" s="122"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4510,7 +4528,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="129" t="s">
+      <c r="G76" s="127" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4537,7 +4555,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="124"/>
+      <c r="G77" s="122"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4562,7 +4580,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="124"/>
+      <c r="G78" s="122"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4589,7 +4607,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="124"/>
+      <c r="G79" s="122"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4621,7 +4639,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="124"/>
+      <c r="G80" s="122"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4650,7 +4668,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="124"/>
+      <c r="G81" s="122"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4679,7 +4697,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="124"/>
+      <c r="G82" s="122"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4708,7 +4726,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="124"/>
+      <c r="G83" s="122"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4737,7 +4755,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="124"/>
+      <c r="G84" s="122"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4766,7 +4784,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="124"/>
+      <c r="G85" s="122"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4795,7 +4813,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="124"/>
+      <c r="G86" s="122"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4824,7 +4842,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="124"/>
+      <c r="G87" s="122"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8892,7 +8910,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="99"/>
@@ -8921,13 +8939,13 @@
         <v>183</v>
       </c>
       <c r="D1" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="101" t="s">
+        <v>220</v>
+      </c>
+      <c r="F1" s="101" t="s">
         <v>224</v>
-      </c>
-      <c r="E1" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="F1" s="101" t="s">
-        <v>227</v>
       </c>
       <c r="G1" s="101" t="s">
         <v>145</v>
@@ -8958,11 +8976,11 @@
       <c r="C2" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="114" t="s">
+      <c r="D2" s="113" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="114" t="s">
-        <v>226</v>
+      <c r="E2" s="113" t="s">
+        <v>223</v>
       </c>
       <c r="F2" s="78" t="s">
         <v>8</v>
@@ -8997,8 +9015,8 @@
       <c r="D3" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="115" t="s">
-        <v>225</v>
+      <c r="E3" s="114" t="s">
+        <v>222</v>
       </c>
       <c r="F3" s="78" t="s">
         <v>151</v>
@@ -9033,8 +9051,8 @@
       <c r="D4" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="114" t="s">
-        <v>226</v>
+      <c r="E4" s="113" t="s">
+        <v>223</v>
       </c>
       <c r="F4" s="78">
         <v>1</v>
@@ -9067,11 +9085,11 @@
       <c r="D5" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="115" t="s">
+      <c r="E5" s="114" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="116" t="s">
-        <v>228</v>
+      <c r="F5" s="115" t="s">
+        <v>225</v>
       </c>
       <c r="G5" s="78">
         <v>90</v>
@@ -9102,16 +9120,16 @@
       <c r="C6" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="116" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="118" t="s">
+      <c r="E6" s="117" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="119" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="117">
+      <c r="F6" s="118" t="s">
+        <v>225</v>
+      </c>
+      <c r="G6" s="116">
         <v>90</v>
       </c>
       <c r="H6" s="81" t="s">
@@ -9130,7 +9148,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="99">
         <v>0</v>
       </c>
@@ -9143,11 +9161,11 @@
       <c r="D7" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="115" t="s">
         <v>225</v>
-      </c>
-      <c r="F7" s="116" t="s">
-        <v>228</v>
       </c>
       <c r="G7" s="84">
         <v>0.9</v>
@@ -9178,11 +9196,11 @@
       <c r="C8" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="114" t="s">
+      <c r="D8" s="113" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="114" t="s">
-        <v>226</v>
+      <c r="E8" s="113" t="s">
+        <v>223</v>
       </c>
       <c r="F8" s="78" t="s">
         <v>8</v>
@@ -9213,8 +9231,8 @@
       <c r="D9" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="115" t="s">
-        <v>225</v>
+      <c r="E9" s="114" t="s">
+        <v>222</v>
       </c>
       <c r="F9" s="78" t="s">
         <v>151</v>
@@ -9245,8 +9263,8 @@
       <c r="D10" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="114" t="s">
-        <v>226</v>
+      <c r="E10" s="113" t="s">
+        <v>223</v>
       </c>
       <c r="F10" s="78">
         <v>1</v>
@@ -9274,16 +9292,16 @@
       <c r="C11" s="98" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="99" t="s">
-        <v>229</v>
-      </c>
-      <c r="E11" s="99" t="s">
-        <v>229</v>
-      </c>
-      <c r="F11" s="99">
+      <c r="D11" s="120" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="120" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" s="120">
         <v>5</v>
       </c>
-      <c r="G11" s="99">
+      <c r="G11" s="120">
         <v>5</v>
       </c>
       <c r="H11" s="92" t="s">
@@ -9306,10 +9324,18 @@
       <c r="C12" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
+      <c r="D12" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="113" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="78">
+        <v>0</v>
+      </c>
       <c r="H12" s="109" t="s">
         <v>180</v>
       </c>
@@ -9330,6 +9356,18 @@
       <c r="C13" s="98" t="s">
         <v>184</v>
       </c>
+      <c r="D13" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="78">
+        <v>125</v>
+      </c>
       <c r="H13" s="92" t="s">
         <v>180</v>
       </c>
@@ -9350,6 +9388,18 @@
       <c r="C14" s="98" t="s">
         <v>185</v>
       </c>
+      <c r="D14" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="113" t="s">
+        <v>223</v>
+      </c>
+      <c r="F14" s="78">
+        <v>0</v>
+      </c>
+      <c r="G14" s="78">
+        <v>0</v>
+      </c>
       <c r="H14" s="92" t="s">
         <v>177</v>
       </c>
@@ -9364,21 +9414,29 @@
       <c r="A15" s="99">
         <v>2</v>
       </c>
-      <c r="B15" s="104" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="104" t="s">
+      <c r="B15" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="119" t="s">
+        <v>228</v>
+      </c>
+      <c r="G15" s="119">
+        <v>20</v>
+      </c>
+      <c r="H15" s="103" t="s">
+        <v>196</v>
+      </c>
+      <c r="I15" s="103" t="s">
         <v>197</v>
-      </c>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="111" t="s">
-        <v>198</v>
-      </c>
-      <c r="I15" s="111" t="s">
-        <v>196</v>
       </c>
       <c r="J15" s="98" t="s">
         <v>124</v>
@@ -9388,274 +9446,402 @@
       <c r="A16" s="99">
         <v>2</v>
       </c>
-      <c r="B16" s="102" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="103" t="s">
+      <c r="B16" s="104" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="103" t="s">
-        <v>199</v>
+      <c r="D16" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="119">
+        <v>20</v>
+      </c>
+      <c r="G16" s="119">
+        <v>20</v>
+      </c>
+      <c r="H16" s="104" t="s">
+        <v>200</v>
       </c>
       <c r="I16" s="103" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J16" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="99">
         <v>2</v>
       </c>
-      <c r="B17" s="104" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="104" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="104" t="s">
-        <v>203</v>
+      <c r="B17" s="102" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17" s="119">
+        <v>30</v>
+      </c>
+      <c r="H17" s="103" t="s">
+        <v>201</v>
       </c>
       <c r="I17" s="103" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J17" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="99">
         <v>2</v>
       </c>
-      <c r="B18" s="102" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="103" t="s">
-        <v>204</v>
+      <c r="B18" s="105" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F18" s="119">
+        <v>10</v>
+      </c>
+      <c r="G18" s="119">
+        <v>10</v>
+      </c>
+      <c r="H18" s="105" t="s">
+        <v>203</v>
       </c>
       <c r="I18" s="103" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J18" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="99">
         <v>2</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="102" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="105" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="105" t="s">
-        <v>206</v>
-      </c>
-      <c r="I19" s="103" t="s">
-        <v>202</v>
+      <c r="C19" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="119" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="119" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="119">
+        <v>45</v>
+      </c>
+      <c r="H19" s="103" t="s">
+        <v>207</v>
+      </c>
+      <c r="I19" s="111" t="s">
+        <v>209</v>
       </c>
       <c r="J19" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="99">
         <v>2</v>
       </c>
       <c r="B20" s="102" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="119" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" s="119">
+        <v>9</v>
+      </c>
+      <c r="G20" s="119">
+        <v>9</v>
+      </c>
+      <c r="H20" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="103" t="s">
-        <v>207</v>
-      </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="103" t="s">
+      <c r="I20" s="111" t="s">
         <v>210</v>
-      </c>
-      <c r="I20" s="112" t="s">
-        <v>212</v>
       </c>
       <c r="J20" s="98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="99">
         <v>2</v>
       </c>
       <c r="B21" s="102" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C21" s="103" t="s">
-        <v>207</v>
-      </c>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="103" t="s">
         <v>211</v>
       </c>
-      <c r="I21" s="112" t="s">
+      <c r="D21" s="119" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="119" t="s">
+        <v>222</v>
+      </c>
+      <c r="F21" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="119">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="111" t="s">
         <v>213</v>
       </c>
+      <c r="I21" s="111" t="s">
+        <v>214</v>
+      </c>
       <c r="J21" s="98" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="99">
         <v>2</v>
       </c>
-      <c r="B22" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="C22" s="103" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="112" t="s">
-        <v>216</v>
+      <c r="B22" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="136" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="137" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="78">
+        <v>75</v>
+      </c>
+      <c r="H22" s="81" t="s">
+        <v>157</v>
       </c>
       <c r="I22" s="112" t="s">
         <v>217</v>
       </c>
       <c r="J22" s="98" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="99">
         <v>2</v>
       </c>
       <c r="B23" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="136" t="s">
         <v>186</v>
+      </c>
+      <c r="D23" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="137" t="s">
+        <v>232</v>
+      </c>
+      <c r="G23" s="78">
+        <v>75</v>
       </c>
       <c r="H23" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="I23" s="113" t="s">
-        <v>220</v>
+      <c r="I23" s="112" t="s">
+        <v>217</v>
       </c>
       <c r="J23" s="98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="99">
         <v>2</v>
       </c>
-      <c r="B24" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="98" t="s">
-        <v>186</v>
+      <c r="B24" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="114" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" s="119" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" s="119">
+        <v>10</v>
       </c>
       <c r="H24" s="81" t="s">
-        <v>157</v>
-      </c>
-      <c r="I24" s="113" t="s">
-        <v>220</v>
+        <v>218</v>
+      </c>
+      <c r="I24" s="112" t="s">
+        <v>219</v>
       </c>
       <c r="J24" s="98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="99">
         <v>2</v>
       </c>
-      <c r="B25" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="104" t="s">
+      <c r="B25" s="102" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="81" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" s="113" t="s">
-        <v>222</v>
+      <c r="D25" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="137" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="78">
+        <v>75</v>
+      </c>
+      <c r="H25" s="98" t="s">
+        <v>233</v>
+      </c>
+      <c r="I25" s="138" t="s">
+        <v>231</v>
       </c>
       <c r="J25" s="98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+      <c r="K25" s="98">
+        <v>3</v>
+      </c>
+      <c r="L25" s="98" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="99">
         <v>2</v>
       </c>
       <c r="B26" s="102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C26" s="98" t="s">
         <v>187</v>
       </c>
+      <c r="D26" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="137" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="78">
+        <v>75</v>
+      </c>
+      <c r="H26" s="98" t="s">
+        <v>234</v>
+      </c>
+      <c r="I26" s="138" t="s">
+        <v>231</v>
+      </c>
       <c r="J26" s="98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+      <c r="K26" s="98">
+        <v>3</v>
+      </c>
+      <c r="L26" s="98" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="99">
         <v>2</v>
       </c>
       <c r="B27" s="102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C27" s="98" t="s">
         <v>187</v>
       </c>
+      <c r="D27" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="137" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="78">
+        <v>75</v>
+      </c>
+      <c r="H27" s="98" t="s">
+        <v>235</v>
+      </c>
+      <c r="I27" s="138" t="s">
+        <v>231</v>
+      </c>
       <c r="J27" s="98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="99">
-        <v>2</v>
-      </c>
-      <c r="B28" s="102" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="98" t="s">
-        <v>187</v>
-      </c>
-      <c r="J28" s="98" t="s">
-        <v>218</v>
+        <v>215</v>
+      </c>
+      <c r="K27" s="98">
+        <v>3</v>
+      </c>
+      <c r="L27" s="98" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="698" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D53C39B-2242-804B-9CDD-B34E5247F7C6}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2DBC3FA-4DDD-2E4F-803D-8A6EDE42DF9C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1415,12 +1415,6 @@
     <t>seconds</t>
   </si>
   <si>
-    <t>SL Balance (eyes open)</t>
-  </si>
-  <si>
-    <t>SL Balance (eyes closed)</t>
-  </si>
-  <si>
     <t>﻿Subjects stand on one leg with other leg raised and arms crossed over the chest. The assessor uses a stopwatch to time how long stance is maintained with eyes open (Springer et al, 2007).</t>
   </si>
   <si>
@@ -1521,6 +1515,12 @@
   </si>
   <si>
     <t>Standing on one leg, hands on hips, slide the box backwards and away from the stance leg as far as possible and return back to the start position.</t>
+  </si>
+  <si>
+    <t>Single Leg Balance (Eyes Open)</t>
+  </si>
+  <si>
+    <t>Single Leg Balance (Eyes Closed)</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2009,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2230,12 +2230,6 @@
     <xf numFmtId="16" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2244,7 +2238,6 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2252,9 +2245,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2336,6 +2326,27 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2590,13 +2601,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2654,7 +2665,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="127" t="s">
+      <c r="G4" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2687,7 +2698,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="122"/>
+      <c r="G5" s="118"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2715,7 +2726,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="122"/>
+      <c r="G6" s="118"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2739,7 +2750,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="122"/>
+      <c r="G7" s="118"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2762,7 +2773,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="122"/>
+      <c r="G8" s="118"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2790,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="122"/>
+      <c r="G9" s="118"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2873,13 +2884,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="121" t="s">
+      <c r="B15" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -2934,24 +2945,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="123">
+      <c r="H16" s="119">
         <v>45359</v>
       </c>
-      <c r="I16" s="124"/>
-      <c r="J16" s="125">
+      <c r="I16" s="120"/>
+      <c r="J16" s="121">
         <v>47204</v>
       </c>
-      <c r="K16" s="124"/>
-      <c r="L16" s="126" t="s">
+      <c r="K16" s="120"/>
+      <c r="L16" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="124"/>
-      <c r="N16" s="123">
+      <c r="M16" s="120"/>
+      <c r="N16" s="119">
         <v>45429</v>
       </c>
-      <c r="O16" s="124"/>
-      <c r="P16" s="123"/>
-      <c r="Q16" s="124"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="120"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3025,7 +3036,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="127" t="s">
+      <c r="G18" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3069,7 +3080,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="122"/>
+      <c r="G19" s="118"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3107,7 +3118,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="122"/>
+      <c r="G20" s="118"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3153,7 +3164,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="122"/>
+      <c r="G21" s="118"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3189,7 +3200,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="122"/>
+      <c r="G22" s="118"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3227,7 +3238,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="122"/>
+      <c r="G23" s="118"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3267,7 +3278,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="122"/>
+      <c r="G24" s="118"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3458,13 +3469,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="121" t="s">
+      <c r="B32" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="122"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="122"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3509,12 +3520,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="128" t="s">
+      <c r="H33" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="124"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="124"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="120"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3539,7 +3550,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="127" t="s">
+      <c r="G34" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3570,7 +3581,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="122"/>
+      <c r="G35" s="118"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3599,7 +3610,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="122"/>
+      <c r="G36" s="118"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3628,7 +3639,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="122"/>
+      <c r="G37" s="118"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3657,7 +3668,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="122"/>
+      <c r="G38" s="118"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3678,7 +3689,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="122"/>
+      <c r="G39" s="118"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3707,7 +3718,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="122"/>
+      <c r="G40" s="118"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3728,7 +3739,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="122"/>
+      <c r="G41" s="118"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3757,7 +3768,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="122"/>
+      <c r="G42" s="118"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3778,7 +3789,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="122"/>
+      <c r="G43" s="118"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3801,17 +3812,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="129" t="s">
+      <c r="C44" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="129" t="s">
+      <c r="D44" s="125" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="122"/>
+      <c r="G44" s="118"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3826,13 +3837,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="122"/>
-      <c r="D45" s="122"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="122"/>
+      <c r="G45" s="118"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3861,7 +3872,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="122"/>
+      <c r="G46" s="118"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -3882,7 +3893,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="122"/>
+      <c r="G47" s="118"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -3911,7 +3922,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="122"/>
+      <c r="G48" s="118"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -3940,7 +3951,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="122"/>
+      <c r="G49" s="118"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -3967,7 +3978,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="122"/>
+      <c r="G50" s="118"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4063,10 +4074,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="134">
+      <c r="B54" s="130">
         <v>16</v>
       </c>
-      <c r="C54" s="135" t="s">
+      <c r="C54" s="131" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4087,8 +4098,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="122"/>
-      <c r="C55" s="122"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="118"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4107,10 +4118,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="130">
+      <c r="B56" s="126">
         <v>17</v>
       </c>
-      <c r="C56" s="132" t="s">
+      <c r="C56" s="128" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4132,8 +4143,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="131"/>
-      <c r="C57" s="133"/>
+      <c r="B57" s="127"/>
+      <c r="C57" s="129"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4153,10 +4164,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="134">
+      <c r="B58" s="130">
         <v>18</v>
       </c>
-      <c r="C58" s="135" t="s">
+      <c r="C58" s="131" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4177,8 +4188,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="122"/>
-      <c r="C59" s="122"/>
+      <c r="B59" s="118"/>
+      <c r="C59" s="118"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4197,10 +4208,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="130">
+      <c r="B60" s="126">
         <v>19</v>
       </c>
-      <c r="C60" s="132" t="s">
+      <c r="C60" s="128" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4222,8 +4233,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="131"/>
-      <c r="C61" s="133"/>
+      <c r="B61" s="127"/>
+      <c r="C61" s="129"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4243,7 +4254,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="134">
+      <c r="B62" s="130">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4267,7 +4278,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="122"/>
+      <c r="B63" s="118"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4443,13 +4454,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="121" t="s">
+      <c r="B74" s="117" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="122"/>
-      <c r="D74" s="122"/>
-      <c r="E74" s="122"/>
-      <c r="F74" s="122"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="118"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="118"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4528,7 +4539,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="127" t="s">
+      <c r="G76" s="123" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4555,7 +4566,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="122"/>
+      <c r="G77" s="118"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4580,7 +4591,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="122"/>
+      <c r="G78" s="118"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4607,7 +4618,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="122"/>
+      <c r="G79" s="118"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4639,7 +4650,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="122"/>
+      <c r="G80" s="118"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4668,7 +4679,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="122"/>
+      <c r="G81" s="118"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4697,7 +4708,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="122"/>
+      <c r="G82" s="118"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4726,7 +4737,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="122"/>
+      <c r="G83" s="118"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4755,7 +4766,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="122"/>
+      <c r="G84" s="118"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4784,7 +4795,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="122"/>
+      <c r="G85" s="118"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4813,7 +4824,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="122"/>
+      <c r="G86" s="118"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4842,7 +4853,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="122"/>
+      <c r="G87" s="118"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8913,41 +8924,41 @@
   <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="99"/>
-    <col min="2" max="2" width="23.5" style="98" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="98"/>
-    <col min="4" max="4" width="16.5" style="99" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" style="99" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="99"/>
-    <col min="8" max="8" width="73.1640625" style="98" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="116" style="98" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="98" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" style="98" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="98" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="98"/>
+    <col min="1" max="1" width="10.83203125" style="97"/>
+    <col min="2" max="2" width="23.5" style="138" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="96"/>
+    <col min="4" max="4" width="16.5" style="97" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" style="97" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="97" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="97"/>
+    <col min="8" max="8" width="73.1640625" style="96" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="116" style="96" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="96" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="96" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="96" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="96"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="135" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="E1" s="101" t="s">
-        <v>220</v>
-      </c>
-      <c r="F1" s="101" t="s">
-        <v>224</v>
-      </c>
-      <c r="G1" s="101" t="s">
+      <c r="D1" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="99" t="s">
         <v>145</v>
       </c>
       <c r="H1" s="82" t="s">
@@ -8956,7 +8967,7 @@
       <c r="I1" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="100" t="s">
+      <c r="J1" s="98" t="s">
         <v>144</v>
       </c>
       <c r="K1" s="82" t="s">
@@ -8967,20 +8978,20 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="99">
+      <c r="A2" s="97">
         <v>0</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="136" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="96" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="113" t="s">
-        <v>223</v>
+      <c r="E2" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F2" s="78" t="s">
         <v>8</v>
@@ -8994,7 +9005,7 @@
       <c r="I2" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="98" t="s">
+      <c r="J2" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K2" s="81">
@@ -9003,20 +9014,20 @@
       <c r="L2" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="99">
+      <c r="A3" s="97">
         <v>0</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="98" t="s">
+      <c r="C3" s="96" t="s">
         <v>184</v>
       </c>
       <c r="D3" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="114" t="s">
-        <v>222</v>
+      <c r="E3" s="110" t="s">
+        <v>220</v>
       </c>
       <c r="F3" s="78" t="s">
         <v>151</v>
@@ -9030,7 +9041,7 @@
       <c r="I3" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="98" t="s">
+      <c r="J3" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K3" s="81">
@@ -9039,20 +9050,20 @@
       <c r="L3" s="81"/>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="99">
+      <c r="A4" s="97">
         <v>0</v>
       </c>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="96" t="s">
         <v>185</v>
       </c>
       <c r="D4" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="113" t="s">
-        <v>223</v>
+      <c r="E4" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F4" s="78">
         <v>1</v>
@@ -9066,30 +9077,30 @@
       <c r="I4" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="98" t="s">
+      <c r="J4" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
     </row>
     <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="99">
+      <c r="A5" s="97">
         <v>0</v>
       </c>
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="136" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="96" t="s">
         <v>186</v>
       </c>
       <c r="D5" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="114" t="s">
+      <c r="E5" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="115" t="s">
-        <v>225</v>
+      <c r="F5" s="111" t="s">
+        <v>223</v>
       </c>
       <c r="G5" s="78">
         <v>90</v>
@@ -9100,7 +9111,7 @@
       <c r="I5" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="98" t="s">
+      <c r="J5" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K5" s="81">
@@ -9111,25 +9122,25 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="99">
+      <c r="A6" s="97">
         <v>0</v>
       </c>
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="136" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="96" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="116" t="s">
+      <c r="D6" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="117" t="s">
+      <c r="E6" s="113" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="118" t="s">
-        <v>225</v>
-      </c>
-      <c r="G6" s="116">
+      <c r="F6" s="114" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="112">
         <v>90</v>
       </c>
       <c r="H6" s="81" t="s">
@@ -9138,7 +9149,7 @@
       <c r="I6" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K6" s="81">
@@ -9149,23 +9160,23 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="99">
+      <c r="A7" s="97">
         <v>0</v>
       </c>
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="136" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="98" t="s">
+      <c r="C7" s="96" t="s">
         <v>187</v>
       </c>
       <c r="D7" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F7" s="115" t="s">
-        <v>225</v>
+      <c r="E7" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="111" t="s">
+        <v>223</v>
       </c>
       <c r="G7" s="84">
         <v>0.9</v>
@@ -9176,7 +9187,7 @@
       <c r="I7" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="98" t="s">
+      <c r="J7" s="96" t="s">
         <v>124</v>
       </c>
       <c r="K7" s="81">
@@ -9186,21 +9197,21 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="108" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="106">
+    <row r="8" spans="1:12" s="104" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="103">
         <v>1</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="108" t="s">
+      <c r="C8" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="113" t="s">
+      <c r="D8" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="113" t="s">
-        <v>223</v>
+      <c r="E8" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F8" s="78" t="s">
         <v>8</v>
@@ -9208,31 +9219,31 @@
       <c r="G8" s="78">
         <v>0</v>
       </c>
-      <c r="H8" s="109" t="s">
+      <c r="H8" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="110" t="s">
+      <c r="I8" s="106" t="s">
         <v>150</v>
       </c>
-      <c r="J8" s="108" t="s">
+      <c r="J8" s="104" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="99">
+      <c r="A9" s="97">
         <v>1</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="96" t="s">
         <v>184</v>
       </c>
       <c r="D9" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="114" t="s">
-        <v>222</v>
+      <c r="E9" s="110" t="s">
+        <v>220</v>
       </c>
       <c r="F9" s="78" t="s">
         <v>151</v>
@@ -9246,25 +9257,25 @@
       <c r="I9" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J9" s="98" t="s">
+      <c r="J9" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="99">
+      <c r="A10" s="97">
         <v>1</v>
       </c>
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="96" t="s">
         <v>185</v>
       </c>
       <c r="D10" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="113" t="s">
-        <v>223</v>
+      <c r="E10" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F10" s="78">
         <v>1</v>
@@ -9278,30 +9289,30 @@
       <c r="I10" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="J10" s="98" t="s">
+      <c r="J10" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="99">
+      <c r="A11" s="97">
         <v>1</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="138" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="96" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="120" t="s">
-        <v>226</v>
-      </c>
-      <c r="E11" s="120" t="s">
-        <v>226</v>
-      </c>
-      <c r="F11" s="120">
+      <c r="D11" s="116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="116" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="116">
         <v>5</v>
       </c>
-      <c r="G11" s="120">
+      <c r="G11" s="116">
         <v>5</v>
       </c>
       <c r="H11" s="92" t="s">
@@ -9310,25 +9321,25 @@
       <c r="I11" s="81" t="s">
         <v>191</v>
       </c>
-      <c r="J11" s="98" t="s">
+      <c r="J11" s="96" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="108" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="106">
+    <row r="12" spans="1:12" s="104" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="103">
         <v>2</v>
       </c>
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="108" t="s">
+      <c r="C12" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="113" t="s">
+      <c r="D12" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="E12" s="113" t="s">
-        <v>223</v>
+      <c r="E12" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F12" s="78" t="s">
         <v>8</v>
@@ -9336,31 +9347,31 @@
       <c r="G12" s="78">
         <v>0</v>
       </c>
-      <c r="H12" s="109" t="s">
+      <c r="H12" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="110" t="s">
+      <c r="I12" s="106" t="s">
         <v>150</v>
       </c>
-      <c r="J12" s="108" t="s">
+      <c r="J12" s="104" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="99">
+      <c r="A13" s="97">
         <v>2</v>
       </c>
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="98" t="s">
+      <c r="C13" s="96" t="s">
         <v>184</v>
       </c>
       <c r="D13" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E13" s="114" t="s">
-        <v>222</v>
+      <c r="E13" s="110" t="s">
+        <v>220</v>
       </c>
       <c r="F13" s="78" t="s">
         <v>151</v>
@@ -9374,25 +9385,25 @@
       <c r="I13" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J13" s="98" t="s">
+      <c r="J13" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="99">
+      <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="96" t="s">
         <v>185</v>
       </c>
       <c r="D14" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E14" s="113" t="s">
-        <v>223</v>
+      <c r="E14" s="109" t="s">
+        <v>221</v>
       </c>
       <c r="F14" s="78">
         <v>0</v>
@@ -9406,252 +9417,252 @@
       <c r="I14" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="J14" s="98" t="s">
+      <c r="J14" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="99">
+      <c r="A15" s="97">
         <v>2</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="103" t="s">
+      <c r="C15" s="100" t="s">
         <v>190</v>
       </c>
       <c r="D15" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F15" s="119" t="s">
-        <v>228</v>
-      </c>
-      <c r="G15" s="119">
+      <c r="E15" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" s="115" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" s="115">
         <v>20</v>
       </c>
-      <c r="H15" s="103" t="s">
+      <c r="H15" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="I15" s="103" t="s">
+      <c r="I15" s="100" t="s">
         <v>197</v>
       </c>
-      <c r="J15" s="98" t="s">
+      <c r="J15" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="99">
+      <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="101" t="s">
         <v>190</v>
       </c>
       <c r="D16" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F16" s="119">
+      <c r="E16" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F16" s="115">
         <v>20</v>
       </c>
-      <c r="G16" s="119">
+      <c r="G16" s="115">
         <v>20</v>
       </c>
-      <c r="H16" s="104" t="s">
+      <c r="H16" s="101" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="103" t="s">
+      <c r="I16" s="100" t="s">
         <v>197</v>
       </c>
-      <c r="J16" s="98" t="s">
+      <c r="J16" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="99">
+      <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="139" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="100" t="s">
         <v>204</v>
       </c>
       <c r="D17" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E17" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F17" s="119" t="s">
-        <v>227</v>
-      </c>
-      <c r="G17" s="119">
+      <c r="E17" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" s="115" t="s">
+        <v>225</v>
+      </c>
+      <c r="G17" s="115">
         <v>30</v>
       </c>
-      <c r="H17" s="103" t="s">
+      <c r="H17" s="100" t="s">
         <v>201</v>
       </c>
-      <c r="I17" s="103" t="s">
+      <c r="I17" s="100" t="s">
         <v>198</v>
       </c>
-      <c r="J17" s="98" t="s">
+      <c r="J17" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="99">
+      <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="141" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="102" t="s">
         <v>190</v>
       </c>
       <c r="D18" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F18" s="119">
+      <c r="E18" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F18" s="115">
         <v>10</v>
       </c>
-      <c r="G18" s="119">
+      <c r="G18" s="115">
         <v>10</v>
       </c>
-      <c r="H18" s="105" t="s">
+      <c r="H18" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="103" t="s">
+      <c r="I18" s="100" t="s">
         <v>199</v>
       </c>
-      <c r="J18" s="98" t="s">
+      <c r="J18" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="99">
+      <c r="A19" s="97">
         <v>2</v>
       </c>
-      <c r="B19" s="102" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" s="103" t="s">
+      <c r="B19" s="139" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="100" t="s">
         <v>204</v>
       </c>
       <c r="D19" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="119" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="119" t="s">
-        <v>229</v>
-      </c>
-      <c r="G19" s="119">
+      <c r="E19" s="115" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="115" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19" s="115">
         <v>45</v>
       </c>
-      <c r="H19" s="103" t="s">
+      <c r="H19" s="100" t="s">
+        <v>205</v>
+      </c>
+      <c r="I19" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="I19" s="111" t="s">
-        <v>209</v>
-      </c>
-      <c r="J19" s="98" t="s">
+      <c r="J19" s="96" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="99">
+      <c r="A20" s="97">
         <v>2</v>
       </c>
-      <c r="B20" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="C20" s="103" t="s">
+      <c r="B20" s="139" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" s="100" t="s">
         <v>204</v>
       </c>
       <c r="D20" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="119" t="s">
-        <v>222</v>
-      </c>
-      <c r="F20" s="119">
+      <c r="E20" s="115" t="s">
+        <v>220</v>
+      </c>
+      <c r="F20" s="115">
         <v>9</v>
       </c>
-      <c r="G20" s="119">
+      <c r="G20" s="115">
         <v>9</v>
       </c>
-      <c r="H20" s="103" t="s">
+      <c r="H20" s="100" t="s">
+        <v>206</v>
+      </c>
+      <c r="I20" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="I20" s="111" t="s">
+      <c r="J20" s="96" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="97">
+        <v>2</v>
+      </c>
+      <c r="B21" s="139" t="s">
         <v>210</v>
       </c>
-      <c r="J20" s="98" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="99">
+      <c r="C21" s="100" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="115" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="115" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" s="115" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="115">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="107" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="107" t="s">
+        <v>212</v>
+      </c>
+      <c r="J21" s="96" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="102" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="D21" s="119" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="119" t="s">
-        <v>222</v>
-      </c>
-      <c r="F21" s="119" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="119">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="111" t="s">
-        <v>213</v>
-      </c>
-      <c r="I21" s="111" t="s">
-        <v>214</v>
-      </c>
-      <c r="J21" s="98" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="99">
-        <v>2</v>
-      </c>
-      <c r="B22" s="97" t="s">
+      <c r="B22" s="136" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="136" t="s">
+      <c r="C22" s="132" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="114" t="s">
+      <c r="E22" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="137" t="s">
-        <v>232</v>
+      <c r="F22" s="133" t="s">
+        <v>230</v>
       </c>
       <c r="G22" s="78">
         <v>75</v>
@@ -9659,31 +9670,31 @@
       <c r="H22" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="I22" s="112" t="s">
-        <v>217</v>
-      </c>
-      <c r="J22" s="98" t="s">
+      <c r="I22" s="108" t="s">
         <v>215</v>
       </c>
+      <c r="J22" s="96" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="99">
+      <c r="A23" s="97">
         <v>2</v>
       </c>
-      <c r="B23" s="97" t="s">
+      <c r="B23" s="136" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="136" t="s">
+      <c r="C23" s="132" t="s">
         <v>186</v>
       </c>
       <c r="D23" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="114" t="s">
+      <c r="E23" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="137" t="s">
-        <v>232</v>
+      <c r="F23" s="133" t="s">
+        <v>230</v>
       </c>
       <c r="G23" s="78">
         <v>75</v>
@@ -9691,156 +9702,156 @@
       <c r="H23" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="I23" s="112" t="s">
-        <v>217</v>
-      </c>
-      <c r="J23" s="98" t="s">
+      <c r="I23" s="108" t="s">
         <v>215</v>
       </c>
+      <c r="J23" s="96" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="24" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="99">
+      <c r="A24" s="97">
         <v>2</v>
       </c>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="140" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="103" t="s">
+      <c r="C24" s="100" t="s">
         <v>187</v>
       </c>
       <c r="D24" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="F24" s="119" t="s">
-        <v>230</v>
-      </c>
-      <c r="G24" s="119">
+      <c r="E24" s="110" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="115" t="s">
+        <v>228</v>
+      </c>
+      <c r="G24" s="115">
         <v>10</v>
       </c>
       <c r="H24" s="81" t="s">
-        <v>218</v>
-      </c>
-      <c r="I24" s="112" t="s">
-        <v>219</v>
-      </c>
-      <c r="J24" s="98" t="s">
-        <v>215</v>
+        <v>216</v>
+      </c>
+      <c r="I24" s="108" t="s">
+        <v>217</v>
+      </c>
+      <c r="J24" s="96" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="99">
+      <c r="A25" s="97">
         <v>2</v>
       </c>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="98" t="s">
+      <c r="C25" s="96" t="s">
         <v>187</v>
       </c>
       <c r="D25" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="114" t="s">
+      <c r="E25" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F25" s="137" t="s">
-        <v>232</v>
+      <c r="F25" s="133" t="s">
+        <v>230</v>
       </c>
       <c r="G25" s="78">
         <v>75</v>
       </c>
-      <c r="H25" s="98" t="s">
-        <v>233</v>
-      </c>
-      <c r="I25" s="138" t="s">
+      <c r="H25" s="96" t="s">
         <v>231</v>
       </c>
-      <c r="J25" s="98" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="98">
+      <c r="I25" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J25" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="K25" s="96">
         <v>3</v>
       </c>
-      <c r="L25" s="98" t="s">
+      <c r="L25" s="96" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="99">
+      <c r="A26" s="97">
         <v>2</v>
       </c>
-      <c r="B26" s="102" t="s">
+      <c r="B26" s="139" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="98" t="s">
+      <c r="C26" s="96" t="s">
         <v>187</v>
       </c>
       <c r="D26" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E26" s="114" t="s">
+      <c r="E26" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="137" t="s">
-        <v>232</v>
+      <c r="F26" s="133" t="s">
+        <v>230</v>
       </c>
       <c r="G26" s="78">
         <v>75</v>
       </c>
-      <c r="H26" s="98" t="s">
-        <v>234</v>
-      </c>
-      <c r="I26" s="138" t="s">
-        <v>231</v>
-      </c>
-      <c r="J26" s="98" t="s">
-        <v>215</v>
-      </c>
-      <c r="K26" s="98">
+      <c r="H26" s="96" t="s">
+        <v>232</v>
+      </c>
+      <c r="I26" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J26" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="K26" s="96">
         <v>3</v>
       </c>
-      <c r="L26" s="98" t="s">
+      <c r="L26" s="96" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="99">
+      <c r="A27" s="97">
         <v>2</v>
       </c>
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="98" t="s">
+      <c r="C27" s="96" t="s">
         <v>187</v>
       </c>
       <c r="D27" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="114" t="s">
+      <c r="E27" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="137" t="s">
-        <v>232</v>
+      <c r="F27" s="133" t="s">
+        <v>230</v>
       </c>
       <c r="G27" s="78">
         <v>75</v>
       </c>
-      <c r="H27" s="98" t="s">
-        <v>235</v>
-      </c>
-      <c r="I27" s="138" t="s">
-        <v>231</v>
-      </c>
-      <c r="J27" s="98" t="s">
-        <v>215</v>
-      </c>
-      <c r="K27" s="98">
+      <c r="H27" s="96" t="s">
+        <v>233</v>
+      </c>
+      <c r="I27" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J27" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27" s="96">
         <v>3</v>
       </c>
-      <c r="L27" s="98" t="s">
+      <c r="L27" s="96" t="s">
         <v>170</v>
       </c>
     </row>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="704" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2DBC3FA-4DDD-2E4F-803D-8A6EDE42DF9C}"/>
+  <xr:revisionPtr revIDLastSave="891" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AAA66E7-96E1-244C-A1BE-61537AA7936E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="255">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1521,6 +1521,73 @@
   </si>
   <si>
     <t>Single Leg Balance (Eyes Closed)</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Athlete stands on one leg and hops as far forward as possible, landing on the same leg. 
+</t>
+  </si>
+  <si>
+    <t>Measure from toe at take-off to heel at landing. Arms are free to swing. The athlete must demonstrate control by sticking the landing for a minimum of 3s.
+The score for each limb is calculated as a mean of 2 successful reps.  A limb symmetry index is calculated by dividing the mean distance (in cms) of the involved limb by the mean distance of the noninvolved limb then multiplying by 100</t>
+  </si>
+  <si>
+    <t>15s</t>
+  </si>
+  <si>
+    <t>Athletes stands on one leg and hops forwards three consecutive times on one foot, sticking the final landing.</t>
+  </si>
+  <si>
+    <t>Measure from toe at take off to heel at landing. Arms are free to swing. The athlete must demonstrate control by sticking the final landing for a minimum of 3s.
+The total distance is measured, and the mean of 2 valid tests is recorded.  A limb symmetry index is calculated by dividing the mean distance (in cms) of the involved limb by the mean distance of the noninvolved limb then multiplying by 100.</t>
+  </si>
+  <si>
+    <t>This test is performed on a course consisting of a 15cm marking strip on the floor which is 6m long. The athlete is required to hop three consecutive times on one foot going in a medial to lateral to medial direction, crossing the strip on each hop.</t>
+  </si>
+  <si>
+    <t>Measure from toe at take-off to heel at landing. Arms are free to swing. The athlete must demonstrate control by sticking the final landing for a minimum of 3s.
+The total distance is measured, and the average (mean) of 2 valid hop tests is recorded.  A limb symmetry index is calculated by dividing the mean distance (in cms) of the involved limb by the mean distance of the noninvolved limb then multiplying by 100.</t>
+  </si>
+  <si>
+    <t>Subjects stands on test leg with hands behind the back and jumps from side to side between two parallel strips of tape, placed 40 cm apart on the floor. (Gustavsson et al., 2006)</t>
+  </si>
+  <si>
+    <t>Subject jumps as many times as possible during 30sec. The number of successful jumps performed, without touching the tape is recorded.  A limb symmetry index is calculated by dividing the total reps performed on the involved limb by the total reps performed on the noninvolved limb then multiplying by 100.</t>
+  </si>
+  <si>
+    <t>Subjects sit on a chair (or a plinth) with test leg bent to 90°, and 10cm from edge of chair. (Culvenor et al., 2016 &amp; Thorstensson et al., 2004)</t>
+  </si>
+  <si>
+    <t>With hands behind the back, the subject aims to stand up from the sitting position, and sit down as many times as possible.
+Record the total number of valid repetitions performed.  There is no symmetry criteria, the athlete must perform 22 reps on each leg to meet this criteria.</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Vestibular Balance (Horizontal)</t>
+  </si>
+  <si>
+    <t>Vestibular Balance (Vertical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper &amp; Hughes Sports Vestibular Balance Test 2: Up and down
+Subjects stand on one leg with a small amount of flexion in the hip, knee and ankle, and place their hands on their waist.
+At a rate of 60 beats per minute, subjects repeatedly tilt their head up and down (looking floor to ceiling) for a period of 15 seconds. </t>
+  </si>
+  <si>
+    <t>Vision needs to be inline with head position (no visual fixing).
+The test is passed if subjects can maintain single leg stance and do not take their hands off their waist for both assessments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper &amp; Hughes Sports Vestibular Balance Test 1: Side to Side
+Subjects stand on one leg with a small amount of flexion in the hip, knee and ankle, and place their hands on their waist.
+At a rate of 60 beats per minute, subjects repeatedly turn their head from side to side (70-90 degree turn) for a period of 15 seconds. Vision needs to be inline with head position (no visual fixing). </t>
+  </si>
+  <si>
+    <t>95%</t>
   </si>
 </sst>
 </file>
@@ -1531,11 +1598,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2007,346 +2081,382 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="21" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="20" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="20" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2601,13 +2711,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2665,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="123" t="s">
+      <c r="G4" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2698,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="118"/>
+      <c r="G5" s="136"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2726,7 +2836,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="118"/>
+      <c r="G6" s="136"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2750,7 +2860,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="118"/>
+      <c r="G7" s="136"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2773,7 +2883,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="118"/>
+      <c r="G8" s="136"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2801,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="118"/>
+      <c r="G9" s="136"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2884,13 +2994,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -2945,24 +3055,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="119">
+      <c r="H16" s="137">
         <v>45359</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="121">
+      <c r="I16" s="138"/>
+      <c r="J16" s="139">
         <v>47204</v>
       </c>
-      <c r="K16" s="120"/>
-      <c r="L16" s="122" t="s">
+      <c r="K16" s="138"/>
+      <c r="L16" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="120"/>
-      <c r="N16" s="119">
+      <c r="M16" s="138"/>
+      <c r="N16" s="137">
         <v>45429</v>
       </c>
-      <c r="O16" s="120"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="120"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="138"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3036,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="123" t="s">
+      <c r="G18" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3080,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="118"/>
+      <c r="G19" s="136"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3118,7 +3228,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="118"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3164,7 +3274,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="118"/>
+      <c r="G21" s="136"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3200,7 +3310,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="118"/>
+      <c r="G22" s="136"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3238,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="118"/>
+      <c r="G23" s="136"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3278,7 +3388,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="118"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3469,13 +3579,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="117" t="s">
+      <c r="B32" s="135" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="136"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3520,12 +3630,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="124" t="s">
+      <c r="H33" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="120"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="120"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="137"/>
+      <c r="K33" s="138"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3550,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="123" t="s">
+      <c r="G34" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3581,7 +3691,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="118"/>
+      <c r="G35" s="136"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3610,7 +3720,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="118"/>
+      <c r="G36" s="136"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3639,7 +3749,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="118"/>
+      <c r="G37" s="136"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3668,7 +3778,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="118"/>
+      <c r="G38" s="136"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3689,7 +3799,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="118"/>
+      <c r="G39" s="136"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3718,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="118"/>
+      <c r="G40" s="136"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3739,7 +3849,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="118"/>
+      <c r="G41" s="136"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3768,7 +3878,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="118"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3789,7 +3899,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="118"/>
+      <c r="G43" s="136"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3812,17 +3922,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="125" t="s">
+      <c r="C44" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="125" t="s">
+      <c r="D44" s="143" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="118"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3837,13 +3947,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
+      <c r="C45" s="136"/>
+      <c r="D45" s="136"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="118"/>
+      <c r="G45" s="136"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3872,7 +3982,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="118"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -3893,7 +4003,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="118"/>
+      <c r="G47" s="136"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -3922,7 +4032,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="118"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -3951,7 +4061,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="118"/>
+      <c r="G49" s="136"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -3978,7 +4088,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="118"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4074,10 +4184,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="130">
+      <c r="B54" s="148">
         <v>16</v>
       </c>
-      <c r="C54" s="131" t="s">
+      <c r="C54" s="149" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4098,8 +4208,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="118"/>
-      <c r="C55" s="118"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4118,10 +4228,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="126">
+      <c r="B56" s="144">
         <v>17</v>
       </c>
-      <c r="C56" s="128" t="s">
+      <c r="C56" s="146" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4143,8 +4253,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="127"/>
-      <c r="C57" s="129"/>
+      <c r="B57" s="145"/>
+      <c r="C57" s="147"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4164,10 +4274,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="130">
+      <c r="B58" s="148">
         <v>18</v>
       </c>
-      <c r="C58" s="131" t="s">
+      <c r="C58" s="149" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4188,8 +4298,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="118"/>
-      <c r="C59" s="118"/>
+      <c r="B59" s="136"/>
+      <c r="C59" s="136"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4208,10 +4318,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="126">
+      <c r="B60" s="144">
         <v>19</v>
       </c>
-      <c r="C60" s="128" t="s">
+      <c r="C60" s="146" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4233,8 +4343,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="127"/>
-      <c r="C61" s="129"/>
+      <c r="B61" s="145"/>
+      <c r="C61" s="147"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4254,7 +4364,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="130">
+      <c r="B62" s="148">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4278,7 +4388,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="118"/>
+      <c r="B63" s="136"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4454,13 +4564,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="117" t="s">
+      <c r="B74" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="118"/>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="118"/>
+      <c r="C74" s="136"/>
+      <c r="D74" s="136"/>
+      <c r="E74" s="136"/>
+      <c r="F74" s="136"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4539,7 +4649,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="123" t="s">
+      <c r="G76" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4566,7 +4676,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="118"/>
+      <c r="G77" s="136"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4591,7 +4701,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="118"/>
+      <c r="G78" s="136"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4618,7 +4728,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="118"/>
+      <c r="G79" s="136"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4650,7 +4760,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="118"/>
+      <c r="G80" s="136"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4679,7 +4789,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="118"/>
+      <c r="G81" s="136"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4708,7 +4818,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="118"/>
+      <c r="G82" s="136"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4737,7 +4847,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="118"/>
+      <c r="G83" s="136"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4766,7 +4876,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="118"/>
+      <c r="G84" s="136"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4795,7 +4905,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="118"/>
+      <c r="G85" s="136"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4824,7 +4934,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="118"/>
+      <c r="G86" s="136"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4853,7 +4963,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="118"/>
+      <c r="G87" s="136"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8921,11 +9031,11 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
-    <col min="2" max="2" width="23.5" style="138" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47" style="122" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="96"/>
     <col min="4" max="4" width="16.5" style="97" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.1640625" style="97" customWidth="1"/>
@@ -8933,9 +9043,9 @@
     <col min="7" max="7" width="10.83203125" style="97"/>
     <col min="8" max="8" width="73.1640625" style="96" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="116" style="96" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" style="96" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" style="96" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="96" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="97" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="97" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="97" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="96"/>
   </cols>
   <sheetData>
@@ -8943,7 +9053,7 @@
       <c r="A1" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="119" t="s">
         <v>143</v>
       </c>
       <c r="C1" s="98" t="s">
@@ -8967,7 +9077,7 @@
       <c r="I1" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="98" t="s">
+      <c r="J1" s="99" t="s">
         <v>144</v>
       </c>
       <c r="K1" s="82" t="s">
@@ -8981,16 +9091,16 @@
       <c r="A2" s="97">
         <v>0</v>
       </c>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="120" t="s">
         <v>146</v>
       </c>
       <c r="C2" s="96" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="108" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="109" t="s">
+      <c r="E2" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F2" s="78" t="s">
@@ -8999,13 +9109,13 @@
       <c r="G2" s="78">
         <v>0</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="126" t="s">
         <v>180</v>
       </c>
       <c r="I2" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="96" t="s">
+      <c r="J2" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K2" s="81">
@@ -9017,7 +9127,7 @@
       <c r="A3" s="97">
         <v>0</v>
       </c>
-      <c r="B3" s="136" t="s">
+      <c r="B3" s="120" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="96" t="s">
@@ -9026,7 +9136,7 @@
       <c r="D3" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="109" t="s">
         <v>220</v>
       </c>
       <c r="F3" s="78" t="s">
@@ -9035,13 +9145,13 @@
       <c r="G3" s="78">
         <v>125</v>
       </c>
-      <c r="H3" s="92" t="s">
+      <c r="H3" s="126" t="s">
         <v>180</v>
       </c>
       <c r="I3" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="96" t="s">
+      <c r="J3" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K3" s="81">
@@ -9053,7 +9163,7 @@
       <c r="A4" s="97">
         <v>0</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="120" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="96" t="s">
@@ -9062,7 +9172,7 @@
       <c r="D4" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="109" t="s">
+      <c r="E4" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F4" s="78">
@@ -9071,13 +9181,13 @@
       <c r="G4" s="78">
         <v>1</v>
       </c>
-      <c r="H4" s="92" t="s">
+      <c r="H4" s="126" t="s">
         <v>177</v>
       </c>
       <c r="I4" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="96" t="s">
+      <c r="J4" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K4" s="81"/>
@@ -9087,7 +9197,7 @@
       <c r="A5" s="97">
         <v>0</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="120" t="s">
         <v>155</v>
       </c>
       <c r="C5" s="96" t="s">
@@ -9096,22 +9206,22 @@
       <c r="D5" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="111" t="s">
+      <c r="F5" s="110" t="s">
         <v>223</v>
       </c>
       <c r="G5" s="78">
         <v>90</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="126" t="s">
         <v>157</v>
       </c>
       <c r="I5" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="96" t="s">
+      <c r="J5" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K5" s="81">
@@ -9125,31 +9235,31 @@
       <c r="A6" s="97">
         <v>0</v>
       </c>
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="120" t="s">
         <v>156</v>
       </c>
       <c r="C6" s="96" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="112" t="s">
+      <c r="D6" s="111" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="113" t="s">
+      <c r="E6" s="112" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="114" t="s">
+      <c r="F6" s="113" t="s">
         <v>223</v>
       </c>
-      <c r="G6" s="112">
+      <c r="G6" s="111">
         <v>90</v>
       </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="126" t="s">
         <v>157</v>
       </c>
       <c r="I6" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="96" t="s">
+      <c r="J6" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K6" s="81">
@@ -9163,7 +9273,7 @@
       <c r="A7" s="97">
         <v>0</v>
       </c>
-      <c r="B7" s="136" t="s">
+      <c r="B7" s="120" t="s">
         <v>162</v>
       </c>
       <c r="C7" s="96" t="s">
@@ -9172,22 +9282,22 @@
       <c r="D7" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="110" t="s">
+      <c r="E7" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F7" s="111" t="s">
+      <c r="F7" s="110" t="s">
         <v>223</v>
       </c>
       <c r="G7" s="84">
         <v>0.9</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="126" t="s">
         <v>163</v>
       </c>
       <c r="I7" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="96" t="s">
+      <c r="J7" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K7" s="81">
@@ -9201,16 +9311,16 @@
       <c r="A8" s="103">
         <v>1</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="121" t="s">
         <v>146</v>
       </c>
       <c r="C8" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="109" t="s">
+      <c r="D8" s="108" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F8" s="78" t="s">
@@ -9219,21 +9329,23 @@
       <c r="G8" s="78">
         <v>0</v>
       </c>
-      <c r="H8" s="105" t="s">
+      <c r="H8" s="127" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="106" t="s">
+      <c r="I8" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="J8" s="104" t="s">
+      <c r="J8" s="103" t="s">
         <v>124</v>
       </c>
+      <c r="K8" s="103"/>
+      <c r="L8" s="103"/>
     </row>
     <row r="9" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="97">
         <v>1</v>
       </c>
-      <c r="B9" s="136" t="s">
+      <c r="B9" s="120" t="s">
         <v>147</v>
       </c>
       <c r="C9" s="96" t="s">
@@ -9242,7 +9354,7 @@
       <c r="D9" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="110" t="s">
+      <c r="E9" s="109" t="s">
         <v>220</v>
       </c>
       <c r="F9" s="78" t="s">
@@ -9251,13 +9363,13 @@
       <c r="G9" s="78">
         <v>125</v>
       </c>
-      <c r="H9" s="92" t="s">
+      <c r="H9" s="126" t="s">
         <v>180</v>
       </c>
       <c r="I9" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J9" s="96" t="s">
+      <c r="J9" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9265,7 +9377,7 @@
       <c r="A10" s="97">
         <v>1</v>
       </c>
-      <c r="B10" s="136" t="s">
+      <c r="B10" s="120" t="s">
         <v>176</v>
       </c>
       <c r="C10" s="96" t="s">
@@ -9274,7 +9386,7 @@
       <c r="D10" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="109" t="s">
+      <c r="E10" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F10" s="78">
@@ -9283,13 +9395,13 @@
       <c r="G10" s="78">
         <v>1</v>
       </c>
-      <c r="H10" s="92" t="s">
+      <c r="H10" s="126" t="s">
         <v>177</v>
       </c>
       <c r="I10" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="J10" s="96" t="s">
+      <c r="J10" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9297,31 +9409,31 @@
       <c r="A11" s="97">
         <v>1</v>
       </c>
-      <c r="B11" s="138" t="s">
+      <c r="B11" s="122" t="s">
         <v>188</v>
       </c>
       <c r="C11" s="96" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="D11" s="115" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="116" t="s">
+      <c r="E11" s="115" t="s">
         <v>224</v>
       </c>
-      <c r="F11" s="116">
+      <c r="F11" s="115">
         <v>5</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="115">
         <v>5</v>
       </c>
-      <c r="H11" s="92" t="s">
+      <c r="H11" s="126" t="s">
         <v>192</v>
       </c>
       <c r="I11" s="81" t="s">
         <v>191</v>
       </c>
-      <c r="J11" s="96" t="s">
+      <c r="J11" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9329,16 +9441,16 @@
       <c r="A12" s="103">
         <v>2</v>
       </c>
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="121" t="s">
         <v>146</v>
       </c>
       <c r="C12" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="109" t="s">
+      <c r="D12" s="108" t="s">
         <v>172</v>
       </c>
-      <c r="E12" s="109" t="s">
+      <c r="E12" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F12" s="78" t="s">
@@ -9347,21 +9459,23 @@
       <c r="G12" s="78">
         <v>0</v>
       </c>
-      <c r="H12" s="105" t="s">
+      <c r="H12" s="127" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="106" t="s">
+      <c r="I12" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="J12" s="104" t="s">
+      <c r="J12" s="103" t="s">
         <v>124</v>
       </c>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="97">
         <v>2</v>
       </c>
-      <c r="B13" s="136" t="s">
+      <c r="B13" s="120" t="s">
         <v>147</v>
       </c>
       <c r="C13" s="96" t="s">
@@ -9370,7 +9484,7 @@
       <c r="D13" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E13" s="110" t="s">
+      <c r="E13" s="109" t="s">
         <v>220</v>
       </c>
       <c r="F13" s="78" t="s">
@@ -9379,13 +9493,13 @@
       <c r="G13" s="78">
         <v>125</v>
       </c>
-      <c r="H13" s="92" t="s">
+      <c r="H13" s="126" t="s">
         <v>180</v>
       </c>
       <c r="I13" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J13" s="96" t="s">
+      <c r="J13" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9393,7 +9507,7 @@
       <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="120" t="s">
         <v>176</v>
       </c>
       <c r="C14" s="96" t="s">
@@ -9402,7 +9516,7 @@
       <c r="D14" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E14" s="109" t="s">
+      <c r="E14" s="108" t="s">
         <v>221</v>
       </c>
       <c r="F14" s="78">
@@ -9411,13 +9525,13 @@
       <c r="G14" s="78">
         <v>0</v>
       </c>
-      <c r="H14" s="92" t="s">
+      <c r="H14" s="126" t="s">
         <v>177</v>
       </c>
       <c r="I14" s="91" t="s">
         <v>154</v>
       </c>
-      <c r="J14" s="96" t="s">
+      <c r="J14" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9425,7 +9539,7 @@
       <c r="A15" s="97">
         <v>2</v>
       </c>
-      <c r="B15" s="139" t="s">
+      <c r="B15" s="123" t="s">
         <v>78</v>
       </c>
       <c r="C15" s="100" t="s">
@@ -9434,13 +9548,13 @@
       <c r="D15" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="110" t="s">
+      <c r="E15" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="115" t="s">
+      <c r="F15" s="114" t="s">
         <v>226</v>
       </c>
-      <c r="G15" s="115">
+      <c r="G15" s="114">
         <v>20</v>
       </c>
       <c r="H15" s="100" t="s">
@@ -9449,7 +9563,7 @@
       <c r="I15" s="100" t="s">
         <v>197</v>
       </c>
-      <c r="J15" s="96" t="s">
+      <c r="J15" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9457,7 +9571,7 @@
       <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="140" t="s">
+      <c r="B16" s="124" t="s">
         <v>82</v>
       </c>
       <c r="C16" s="101" t="s">
@@ -9466,13 +9580,13 @@
       <c r="D16" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="110" t="s">
+      <c r="E16" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F16" s="115">
+      <c r="F16" s="114">
         <v>20</v>
       </c>
-      <c r="G16" s="115">
+      <c r="G16" s="114">
         <v>20</v>
       </c>
       <c r="H16" s="101" t="s">
@@ -9481,7 +9595,7 @@
       <c r="I16" s="100" t="s">
         <v>197</v>
       </c>
-      <c r="J16" s="96" t="s">
+      <c r="J16" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9489,7 +9603,7 @@
       <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="139" t="s">
+      <c r="B17" s="123" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="100" t="s">
@@ -9498,13 +9612,13 @@
       <c r="D17" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="115" t="s">
+      <c r="F17" s="114" t="s">
         <v>225</v>
       </c>
-      <c r="G17" s="115">
+      <c r="G17" s="114">
         <v>30</v>
       </c>
       <c r="H17" s="100" t="s">
@@ -9513,7 +9627,7 @@
       <c r="I17" s="100" t="s">
         <v>198</v>
       </c>
-      <c r="J17" s="96" t="s">
+      <c r="J17" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9521,7 +9635,7 @@
       <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="141" t="s">
+      <c r="B18" s="125" t="s">
         <v>202</v>
       </c>
       <c r="C18" s="102" t="s">
@@ -9530,13 +9644,13 @@
       <c r="D18" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="110" t="s">
+      <c r="E18" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="115">
+      <c r="F18" s="114">
         <v>10</v>
       </c>
-      <c r="G18" s="115">
+      <c r="G18" s="114">
         <v>10</v>
       </c>
       <c r="H18" s="102" t="s">
@@ -9545,7 +9659,7 @@
       <c r="I18" s="100" t="s">
         <v>199</v>
       </c>
-      <c r="J18" s="96" t="s">
+      <c r="J18" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9553,7 +9667,7 @@
       <c r="A19" s="97">
         <v>2</v>
       </c>
-      <c r="B19" s="139" t="s">
+      <c r="B19" s="123" t="s">
         <v>234</v>
       </c>
       <c r="C19" s="100" t="s">
@@ -9562,22 +9676,22 @@
       <c r="D19" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="115" t="s">
+      <c r="E19" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="115" t="s">
+      <c r="F19" s="114" t="s">
         <v>227</v>
       </c>
-      <c r="G19" s="115">
+      <c r="G19" s="114">
         <v>45</v>
       </c>
       <c r="H19" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="107" t="s">
+      <c r="I19" s="106" t="s">
         <v>207</v>
       </c>
-      <c r="J19" s="96" t="s">
+      <c r="J19" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9585,7 +9699,7 @@
       <c r="A20" s="97">
         <v>2</v>
       </c>
-      <c r="B20" s="139" t="s">
+      <c r="B20" s="123" t="s">
         <v>235</v>
       </c>
       <c r="C20" s="100" t="s">
@@ -9594,22 +9708,22 @@
       <c r="D20" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="115" t="s">
+      <c r="E20" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F20" s="115">
+      <c r="F20" s="114">
         <v>9</v>
       </c>
-      <c r="G20" s="115">
+      <c r="G20" s="114">
         <v>9</v>
       </c>
       <c r="H20" s="100" t="s">
         <v>206</v>
       </c>
-      <c r="I20" s="107" t="s">
+      <c r="I20" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="J20" s="96" t="s">
+      <c r="J20" s="97" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9617,31 +9731,31 @@
       <c r="A21" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="139" t="s">
+      <c r="B21" s="123" t="s">
         <v>210</v>
       </c>
       <c r="C21" s="100" t="s">
         <v>209</v>
       </c>
-      <c r="D21" s="115" t="s">
+      <c r="D21" s="114" t="s">
         <v>153</v>
       </c>
-      <c r="E21" s="115" t="s">
+      <c r="E21" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F21" s="115" t="s">
+      <c r="F21" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="115">
+      <c r="G21" s="114">
         <v>1.5</v>
       </c>
-      <c r="H21" s="107" t="s">
+      <c r="H21" s="106" t="s">
         <v>211</v>
       </c>
-      <c r="I21" s="107" t="s">
+      <c r="I21" s="106" t="s">
         <v>212</v>
       </c>
-      <c r="J21" s="96" t="s">
+      <c r="J21" s="97" t="s">
         <v>214</v>
       </c>
     </row>
@@ -9649,31 +9763,31 @@
       <c r="A22" s="97">
         <v>2</v>
       </c>
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="120" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="132" t="s">
+      <c r="C22" s="116" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="110" t="s">
+      <c r="E22" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="133" t="s">
+      <c r="F22" s="117" t="s">
         <v>230</v>
       </c>
       <c r="G22" s="78">
         <v>75</v>
       </c>
-      <c r="H22" s="81" t="s">
+      <c r="H22" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="107" t="s">
         <v>215</v>
       </c>
-      <c r="J22" s="96" t="s">
+      <c r="J22" s="97" t="s">
         <v>213</v>
       </c>
     </row>
@@ -9681,31 +9795,31 @@
       <c r="A23" s="97">
         <v>2</v>
       </c>
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="120" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="132" t="s">
+      <c r="C23" s="116" t="s">
         <v>186</v>
       </c>
       <c r="D23" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="110" t="s">
+      <c r="E23" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="133" t="s">
+      <c r="F23" s="117" t="s">
         <v>230</v>
       </c>
       <c r="G23" s="78">
         <v>75</v>
       </c>
-      <c r="H23" s="81" t="s">
+      <c r="H23" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="I23" s="108" t="s">
+      <c r="I23" s="107" t="s">
         <v>215</v>
       </c>
-      <c r="J23" s="96" t="s">
+      <c r="J23" s="97" t="s">
         <v>213</v>
       </c>
     </row>
@@ -9713,7 +9827,7 @@
       <c r="A24" s="97">
         <v>2</v>
       </c>
-      <c r="B24" s="140" t="s">
+      <c r="B24" s="124" t="s">
         <v>115</v>
       </c>
       <c r="C24" s="100" t="s">
@@ -9722,22 +9836,22 @@
       <c r="D24" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="110" t="s">
+      <c r="E24" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F24" s="115" t="s">
+      <c r="F24" s="114" t="s">
         <v>228</v>
       </c>
-      <c r="G24" s="115">
+      <c r="G24" s="114">
         <v>10</v>
       </c>
-      <c r="H24" s="81" t="s">
+      <c r="H24" s="126" t="s">
         <v>216</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="107" t="s">
         <v>217</v>
       </c>
-      <c r="J24" s="96" t="s">
+      <c r="J24" s="97" t="s">
         <v>213</v>
       </c>
     </row>
@@ -9745,7 +9859,7 @@
       <c r="A25" s="97">
         <v>2</v>
       </c>
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="123" t="s">
         <v>193</v>
       </c>
       <c r="C25" s="96" t="s">
@@ -9754,10 +9868,10 @@
       <c r="D25" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="110" t="s">
+      <c r="E25" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F25" s="133" t="s">
+      <c r="F25" s="117" t="s">
         <v>230</v>
       </c>
       <c r="G25" s="78">
@@ -9766,16 +9880,16 @@
       <c r="H25" s="96" t="s">
         <v>231</v>
       </c>
-      <c r="I25" s="134" t="s">
+      <c r="I25" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="J25" s="96" t="s">
+      <c r="J25" s="97" t="s">
         <v>213</v>
       </c>
-      <c r="K25" s="96">
+      <c r="K25" s="97">
         <v>3</v>
       </c>
-      <c r="L25" s="96" t="s">
+      <c r="L25" s="97" t="s">
         <v>170</v>
       </c>
     </row>
@@ -9783,7 +9897,7 @@
       <c r="A26" s="97">
         <v>2</v>
       </c>
-      <c r="B26" s="139" t="s">
+      <c r="B26" s="123" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="96" t="s">
@@ -9792,10 +9906,10 @@
       <c r="D26" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E26" s="110" t="s">
+      <c r="E26" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="133" t="s">
+      <c r="F26" s="117" t="s">
         <v>230</v>
       </c>
       <c r="G26" s="78">
@@ -9804,16 +9918,16 @@
       <c r="H26" s="96" t="s">
         <v>232</v>
       </c>
-      <c r="I26" s="134" t="s">
+      <c r="I26" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="J26" s="96" t="s">
+      <c r="J26" s="97" t="s">
         <v>213</v>
       </c>
-      <c r="K26" s="96">
+      <c r="K26" s="97">
         <v>3</v>
       </c>
-      <c r="L26" s="96" t="s">
+      <c r="L26" s="97" t="s">
         <v>170</v>
       </c>
     </row>
@@ -9821,7 +9935,7 @@
       <c r="A27" s="97">
         <v>2</v>
       </c>
-      <c r="B27" s="139" t="s">
+      <c r="B27" s="123" t="s">
         <v>195</v>
       </c>
       <c r="C27" s="96" t="s">
@@ -9830,10 +9944,10 @@
       <c r="D27" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="110" t="s">
+      <c r="E27" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="133" t="s">
+      <c r="F27" s="117" t="s">
         <v>230</v>
       </c>
       <c r="G27" s="78">
@@ -9842,18 +9956,473 @@
       <c r="H27" s="96" t="s">
         <v>233</v>
       </c>
-      <c r="I27" s="134" t="s">
+      <c r="I27" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="J27" s="96" t="s">
+      <c r="J27" s="97" t="s">
         <v>213</v>
       </c>
-      <c r="K27" s="96">
+      <c r="K27" s="97">
         <v>3</v>
       </c>
-      <c r="L27" s="96" t="s">
+      <c r="L27" s="97" t="s">
         <v>170</v>
       </c>
+    </row>
+    <row r="28" spans="1:12" s="104" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A28" s="103">
+        <v>3</v>
+      </c>
+      <c r="B28" s="130" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="128" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="129" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="150" t="s">
+        <v>254</v>
+      </c>
+      <c r="G28" s="103">
+        <v>95</v>
+      </c>
+      <c r="H28" s="131" t="s">
+        <v>237</v>
+      </c>
+      <c r="I28" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="J28" s="103" t="s">
+        <v>124</v>
+      </c>
+      <c r="K28" s="103">
+        <v>2</v>
+      </c>
+      <c r="L28" s="103" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A29" s="97">
+        <v>3</v>
+      </c>
+      <c r="B29" s="132" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F29" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G29" s="97">
+        <v>95</v>
+      </c>
+      <c r="H29" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="I29" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="J29" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K29" s="97">
+        <v>2</v>
+      </c>
+      <c r="L29" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A30" s="97">
+        <v>3</v>
+      </c>
+      <c r="B30" s="132" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F30" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="97">
+        <v>95</v>
+      </c>
+      <c r="H30" s="133" t="s">
+        <v>242</v>
+      </c>
+      <c r="I30" s="134" t="s">
+        <v>243</v>
+      </c>
+      <c r="J30" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K30" s="97">
+        <v>2</v>
+      </c>
+      <c r="L30" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A31" s="97">
+        <v>3</v>
+      </c>
+      <c r="B31" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G31" s="97">
+        <v>95</v>
+      </c>
+      <c r="H31" s="133" t="s">
+        <v>244</v>
+      </c>
+      <c r="I31" s="134" t="s">
+        <v>245</v>
+      </c>
+      <c r="J31" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K31" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A32" s="97">
+        <v>3</v>
+      </c>
+      <c r="B32" s="132" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F32" s="97">
+        <v>22</v>
+      </c>
+      <c r="G32" s="97">
+        <v>22</v>
+      </c>
+      <c r="H32" s="134" t="s">
+        <v>246</v>
+      </c>
+      <c r="I32" s="134" t="s">
+        <v>247</v>
+      </c>
+      <c r="J32" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K32" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A33" s="97">
+        <v>3</v>
+      </c>
+      <c r="B33" s="132" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F33" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G33" s="97">
+        <v>95</v>
+      </c>
+      <c r="H33" s="134" t="s">
+        <v>231</v>
+      </c>
+      <c r="I33" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J33" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33" s="97">
+        <v>3</v>
+      </c>
+      <c r="L33" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A34" s="97">
+        <v>3</v>
+      </c>
+      <c r="B34" s="132" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F34" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="97">
+        <v>95</v>
+      </c>
+      <c r="H34" s="134" t="s">
+        <v>232</v>
+      </c>
+      <c r="I34" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J34" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="97">
+        <v>3</v>
+      </c>
+      <c r="L34" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A35" s="97">
+        <v>3</v>
+      </c>
+      <c r="B35" s="132" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" s="151" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="97">
+        <v>95</v>
+      </c>
+      <c r="H35" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="I35" s="134" t="s">
+        <v>229</v>
+      </c>
+      <c r="J35" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" s="97">
+        <v>3</v>
+      </c>
+      <c r="L35" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A36" s="97">
+        <v>3</v>
+      </c>
+      <c r="B36" s="132" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="97" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="114" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" s="97" t="s">
+        <v>239</v>
+      </c>
+      <c r="G36" s="97">
+        <v>15</v>
+      </c>
+      <c r="H36" s="134" t="s">
+        <v>253</v>
+      </c>
+      <c r="I36" s="134" t="s">
+        <v>252</v>
+      </c>
+      <c r="J36" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K36" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A37" s="97">
+        <v>3</v>
+      </c>
+      <c r="B37" s="132" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" s="97" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="114" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="97" t="s">
+        <v>239</v>
+      </c>
+      <c r="G37" s="97">
+        <v>15</v>
+      </c>
+      <c r="H37" s="134" t="s">
+        <v>251</v>
+      </c>
+      <c r="I37" s="134" t="s">
+        <v>252</v>
+      </c>
+      <c r="J37" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K37" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="97">
+        <v>3</v>
+      </c>
+      <c r="B38" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="114" t="s">
+        <v>209</v>
+      </c>
+      <c r="D38" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="114" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" s="114">
+        <v>1.8</v>
+      </c>
+      <c r="H38" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="I38" s="134" t="s">
+        <v>248</v>
+      </c>
+      <c r="J38" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="L38" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="115" customFormat="1" ht="68" x14ac:dyDescent="0.15">
+      <c r="A39" s="115">
+        <v>3</v>
+      </c>
+      <c r="B39" s="152" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="152" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" s="152" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="152" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="152" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="152">
+        <v>1.8</v>
+      </c>
+      <c r="H39" s="153" t="s">
+        <v>211</v>
+      </c>
+      <c r="I39" s="153" t="s">
+        <v>212</v>
+      </c>
+      <c r="J39" s="115" t="s">
+        <v>214</v>
+      </c>
+      <c r="L39" s="115" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="132"/>
+      <c r="C40" s="97"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="134"/>
+    </row>
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="123"/>
+      <c r="I41" s="134"/>
+    </row>
+    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" s="123"/>
+      <c r="I42" s="97"/>
+    </row>
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="I43" s="97"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="891" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AAA66E7-96E1-244C-A1BE-61537AA7936E}"/>
+  <xr:revisionPtr revIDLastSave="899" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B160EFCB-19D6-5C4E-82A9-9568FFC12958}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2409,6 +2409,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2445,18 +2457,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2711,13 +2711,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="141" t="s">
+      <c r="G4" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2808,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="136"/>
+      <c r="G5" s="140"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2836,7 +2836,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="136"/>
+      <c r="G6" s="140"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2860,7 +2860,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="136"/>
+      <c r="G7" s="140"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2883,7 +2883,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="136"/>
+      <c r="G8" s="140"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2911,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="136"/>
+      <c r="G9" s="140"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -2994,13 +2994,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="135" t="s">
+      <c r="B15" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3055,24 +3055,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="137">
+      <c r="H16" s="141">
         <v>45359</v>
       </c>
-      <c r="I16" s="138"/>
-      <c r="J16" s="139">
+      <c r="I16" s="142"/>
+      <c r="J16" s="143">
         <v>47204</v>
       </c>
-      <c r="K16" s="138"/>
-      <c r="L16" s="140" t="s">
+      <c r="K16" s="142"/>
+      <c r="L16" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="138"/>
-      <c r="N16" s="137">
+      <c r="M16" s="142"/>
+      <c r="N16" s="141">
         <v>45429</v>
       </c>
-      <c r="O16" s="138"/>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="138"/>
+      <c r="O16" s="142"/>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="142"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="141" t="s">
+      <c r="G18" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3190,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="136"/>
+      <c r="G19" s="140"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3228,7 +3228,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="136"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="136"/>
+      <c r="G21" s="140"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3310,7 +3310,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="136"/>
+      <c r="G22" s="140"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3348,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="136"/>
+      <c r="G23" s="140"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="136"/>
+      <c r="G24" s="140"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3579,13 +3579,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="135" t="s">
+      <c r="B32" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3630,12 +3630,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="142" t="s">
+      <c r="H33" s="146" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="138"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="138"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="141"/>
+      <c r="K33" s="142"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3660,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="141" t="s">
+      <c r="G34" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3691,7 +3691,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="136"/>
+      <c r="G35" s="140"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3720,7 +3720,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="136"/>
+      <c r="G36" s="140"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3749,7 +3749,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="136"/>
+      <c r="G37" s="140"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3778,7 +3778,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="136"/>
+      <c r="G38" s="140"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3799,7 +3799,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="136"/>
+      <c r="G39" s="140"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3828,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="136"/>
+      <c r="G40" s="140"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3849,7 +3849,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="136"/>
+      <c r="G41" s="140"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3878,7 +3878,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="136"/>
+      <c r="G42" s="140"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3899,7 +3899,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="136"/>
+      <c r="G43" s="140"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3922,17 +3922,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="143" t="s">
+      <c r="C44" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="D44" s="147" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="136"/>
+      <c r="G44" s="140"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3947,13 +3947,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="136"/>
+      <c r="G45" s="140"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3982,7 +3982,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="136"/>
+      <c r="G46" s="140"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4003,7 +4003,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="136"/>
+      <c r="G47" s="140"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4032,7 +4032,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="136"/>
+      <c r="G48" s="140"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4061,7 +4061,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="136"/>
+      <c r="G49" s="140"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4088,7 +4088,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="136"/>
+      <c r="G50" s="140"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4184,10 +4184,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="148">
+      <c r="B54" s="152">
         <v>16</v>
       </c>
-      <c r="C54" s="149" t="s">
+      <c r="C54" s="153" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4208,8 +4208,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="136"/>
-      <c r="C55" s="136"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="140"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4228,10 +4228,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="144">
+      <c r="B56" s="148">
         <v>17</v>
       </c>
-      <c r="C56" s="146" t="s">
+      <c r="C56" s="150" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4253,8 +4253,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="145"/>
-      <c r="C57" s="147"/>
+      <c r="B57" s="149"/>
+      <c r="C57" s="151"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4274,10 +4274,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="148">
+      <c r="B58" s="152">
         <v>18</v>
       </c>
-      <c r="C58" s="149" t="s">
+      <c r="C58" s="153" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4298,8 +4298,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="136"/>
-      <c r="C59" s="136"/>
+      <c r="B59" s="140"/>
+      <c r="C59" s="140"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4318,10 +4318,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="144">
+      <c r="B60" s="148">
         <v>19</v>
       </c>
-      <c r="C60" s="146" t="s">
+      <c r="C60" s="150" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4343,8 +4343,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="145"/>
-      <c r="C61" s="147"/>
+      <c r="B61" s="149"/>
+      <c r="C61" s="151"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4364,7 +4364,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="148">
+      <c r="B62" s="152">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="136"/>
+      <c r="B63" s="140"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4564,13 +4564,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="135" t="s">
+      <c r="B74" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="136"/>
-      <c r="D74" s="136"/>
-      <c r="E74" s="136"/>
-      <c r="F74" s="136"/>
+      <c r="C74" s="140"/>
+      <c r="D74" s="140"/>
+      <c r="E74" s="140"/>
+      <c r="F74" s="140"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4649,7 +4649,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="141" t="s">
+      <c r="G76" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4676,7 +4676,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="136"/>
+      <c r="G77" s="140"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4701,7 +4701,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="136"/>
+      <c r="G78" s="140"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4728,7 +4728,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="136"/>
+      <c r="G79" s="140"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4760,7 +4760,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="136"/>
+      <c r="G80" s="140"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4789,7 +4789,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="136"/>
+      <c r="G81" s="140"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4818,7 +4818,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="136"/>
+      <c r="G82" s="140"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4847,7 +4847,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="136"/>
+      <c r="G83" s="140"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4876,7 +4876,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="136"/>
+      <c r="G84" s="140"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4905,7 +4905,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="136"/>
+      <c r="G85" s="140"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4934,7 +4934,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="136"/>
+      <c r="G86" s="140"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4963,7 +4963,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="136"/>
+      <c r="G87" s="140"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -9985,7 +9985,7 @@
       <c r="E28" s="129" t="s">
         <v>220</v>
       </c>
-      <c r="F28" s="150" t="s">
+      <c r="F28" s="135" t="s">
         <v>254</v>
       </c>
       <c r="G28" s="103">
@@ -10023,7 +10023,7 @@
       <c r="E29" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G29" s="97">
@@ -10061,7 +10061,7 @@
       <c r="E30" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F30" s="151" t="s">
+      <c r="F30" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G30" s="97">
@@ -10099,7 +10099,7 @@
       <c r="E31" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G31" s="97">
@@ -10169,7 +10169,7 @@
       <c r="E33" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G33" s="97">
@@ -10207,7 +10207,7 @@
       <c r="E34" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F34" s="151" t="s">
+      <c r="F34" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G34" s="97">
@@ -10245,7 +10245,7 @@
       <c r="E35" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="136" t="s">
         <v>254</v>
       </c>
       <c r="G35" s="97">
@@ -10376,28 +10376,28 @@
       <c r="A39" s="115">
         <v>3</v>
       </c>
-      <c r="B39" s="152" t="s">
+      <c r="B39" s="137" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="152" t="s">
+      <c r="C39" s="137" t="s">
         <v>209</v>
       </c>
-      <c r="D39" s="152" t="s">
+      <c r="D39" s="137" t="s">
         <v>153</v>
       </c>
-      <c r="E39" s="152" t="s">
+      <c r="E39" s="137" t="s">
         <v>220</v>
       </c>
-      <c r="F39" s="152" t="s">
+      <c r="F39" s="137" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="152">
+      <c r="G39" s="137">
         <v>1.8</v>
       </c>
-      <c r="H39" s="153" t="s">
+      <c r="H39" s="138" t="s">
         <v>211</v>
       </c>
-      <c r="I39" s="153" t="s">
+      <c r="I39" s="138" t="s">
         <v>212</v>
       </c>
       <c r="J39" s="115" t="s">

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="899" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B160EFCB-19D6-5C4E-82A9-9568FFC12958}"/>
+  <xr:revisionPtr revIDLastSave="904" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1420C5-299A-964B-B6E9-93BCFD5C64F3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1280" yWindow="-19540" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="255">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -2421,28 +2421,21 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2452,11 +2445,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="140"/>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="145" t="s">
+      <c r="G4" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="139" t="s">
+      <c r="B15" s="141" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="140"/>
@@ -3055,24 +3055,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="141">
+      <c r="H16" s="151">
         <v>45359</v>
       </c>
-      <c r="I16" s="142"/>
-      <c r="J16" s="143">
+      <c r="I16" s="150"/>
+      <c r="J16" s="152">
         <v>47204</v>
       </c>
-      <c r="K16" s="142"/>
-      <c r="L16" s="144" t="s">
+      <c r="K16" s="150"/>
+      <c r="L16" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="142"/>
-      <c r="N16" s="141">
+      <c r="M16" s="150"/>
+      <c r="N16" s="151">
         <v>45429</v>
       </c>
-      <c r="O16" s="142"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="142"/>
+      <c r="O16" s="150"/>
+      <c r="P16" s="151"/>
+      <c r="Q16" s="150"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="145" t="s">
+      <c r="G18" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="139" t="s">
+      <c r="B32" s="141" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="140"/>
@@ -3630,12 +3630,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="146" t="s">
+      <c r="H33" s="149" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="142"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="142"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="150"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3660,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="145" t="s">
+      <c r="G34" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3922,10 +3922,10 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="147" t="s">
+      <c r="C44" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="147" t="s">
+      <c r="D44" s="143" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
@@ -4184,10 +4184,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="152">
+      <c r="B54" s="139">
         <v>16</v>
       </c>
-      <c r="C54" s="153" t="s">
+      <c r="C54" s="144" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4228,10 +4228,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="148">
+      <c r="B56" s="145">
         <v>17</v>
       </c>
-      <c r="C56" s="150" t="s">
+      <c r="C56" s="147" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4253,8 +4253,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="149"/>
-      <c r="C57" s="151"/>
+      <c r="B57" s="146"/>
+      <c r="C57" s="148"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4274,10 +4274,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="152">
+      <c r="B58" s="139">
         <v>18</v>
       </c>
-      <c r="C58" s="153" t="s">
+      <c r="C58" s="144" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4318,10 +4318,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="148">
+      <c r="B60" s="145">
         <v>19</v>
       </c>
-      <c r="C60" s="150" t="s">
+      <c r="C60" s="147" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4343,8 +4343,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="149"/>
-      <c r="C61" s="151"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="148"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4364,7 +4364,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="152">
+      <c r="B62" s="139">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4564,7 +4564,7 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="139" t="s">
+      <c r="B74" s="141" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="140"/>
@@ -4649,7 +4649,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="145" t="s">
+      <c r="G76" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -8709,6 +8709,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8719,22 +8735,6 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9031,7 +9031,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -9087,7 +9087,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="97">
         <v>0</v>
       </c>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="L2" s="81"/>
     </row>
-    <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="97">
         <v>0</v>
       </c>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="L3" s="81"/>
     </row>
-    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="97">
         <v>0</v>
       </c>
@@ -9193,7 +9193,7 @@
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
     </row>
-    <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="97">
         <v>0</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="97">
         <v>0</v>
       </c>
@@ -9269,280 +9269,274 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="97">
+    <row r="7" spans="1:12" s="104" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="103">
+        <v>1</v>
+      </c>
+      <c r="B7" s="121" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="108" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="78">
         <v>0</v>
       </c>
-      <c r="B7" s="120" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="96" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" s="78" t="s">
+      <c r="H7" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="105" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="103" t="s">
+        <v>124</v>
+      </c>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+    </row>
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="97">
+        <v>1</v>
+      </c>
+      <c r="B8" s="120" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="109" t="s">
+      <c r="E8" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F7" s="110" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="84">
-        <v>0.9</v>
-      </c>
-      <c r="H7" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7" s="97" t="s">
+      <c r="F8" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="78">
+        <v>125</v>
+      </c>
+      <c r="H8" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="K7" s="81">
-        <v>2</v>
-      </c>
-      <c r="L7" s="94" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="104" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="103">
-        <v>1</v>
-      </c>
-      <c r="B8" s="121" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="104" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="108" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="F8" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="78">
-        <v>0</v>
-      </c>
-      <c r="H8" s="127" t="s">
-        <v>180</v>
-      </c>
-      <c r="I8" s="105" t="s">
-        <v>150</v>
-      </c>
-      <c r="J8" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="K8" s="103"/>
-      <c r="L8" s="103"/>
-    </row>
-    <row r="9" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="97">
         <v>1</v>
       </c>
       <c r="B9" s="120" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C9" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" s="109" t="s">
-        <v>220</v>
-      </c>
-      <c r="F9" s="78" t="s">
-        <v>151</v>
+        <v>185</v>
+      </c>
+      <c r="D9" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="78">
+        <v>1</v>
       </c>
       <c r="G9" s="78">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="H9" s="126" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I9" s="81" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J9" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="97">
         <v>1</v>
       </c>
-      <c r="B10" s="120" t="s">
-        <v>176</v>
+      <c r="B10" s="122" t="s">
+        <v>188</v>
       </c>
       <c r="C10" s="96" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="F10" s="78">
-        <v>1</v>
-      </c>
-      <c r="G10" s="78">
-        <v>1</v>
+        <v>189</v>
+      </c>
+      <c r="D10" s="115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="115" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="115">
+        <v>5</v>
+      </c>
+      <c r="G10" s="115">
+        <v>5</v>
       </c>
       <c r="H10" s="126" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="I10" s="81" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="J10" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="97">
-        <v>1</v>
-      </c>
-      <c r="B11" s="122" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="96" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="115" t="s">
-        <v>224</v>
-      </c>
-      <c r="E11" s="115" t="s">
-        <v>224</v>
-      </c>
-      <c r="F11" s="115">
-        <v>5</v>
-      </c>
-      <c r="G11" s="115">
-        <v>5</v>
-      </c>
-      <c r="H11" s="126" t="s">
-        <v>192</v>
-      </c>
-      <c r="I11" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="J11" s="97" t="s">
+    <row r="11" spans="1:12" s="104" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="103">
+        <v>2</v>
+      </c>
+      <c r="B11" s="121" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="108" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="78">
+        <v>0</v>
+      </c>
+      <c r="H11" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="105" t="s">
+        <v>150</v>
+      </c>
+      <c r="J11" s="103" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" s="104" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="103">
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="97">
         <v>2</v>
       </c>
-      <c r="B12" s="121" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="104" t="s">
+      <c r="B12" s="120" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="96" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="108" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="108" t="s">
-        <v>221</v>
+      <c r="D12" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="109" t="s">
+        <v>220</v>
       </c>
       <c r="F12" s="78" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="G12" s="78">
-        <v>0</v>
-      </c>
-      <c r="H12" s="127" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="126" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="105" t="s">
+      <c r="I12" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="J12" s="103" t="s">
+      <c r="J12" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-    </row>
-    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="97">
         <v>2</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C13" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="109" t="s">
-        <v>220</v>
-      </c>
-      <c r="F13" s="78" t="s">
-        <v>151</v>
+        <v>185</v>
+      </c>
+      <c r="D13" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" s="78">
+        <v>0</v>
       </c>
       <c r="G13" s="78">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H13" s="126" t="s">
-        <v>180</v>
-      </c>
-      <c r="I13" s="81" t="s">
-        <v>150</v>
+        <v>177</v>
+      </c>
+      <c r="I13" s="91" t="s">
+        <v>154</v>
       </c>
       <c r="J13" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="96" t="s">
-        <v>185</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="78">
-        <v>0</v>
-      </c>
-      <c r="G14" s="78">
-        <v>0</v>
-      </c>
-      <c r="H14" s="126" t="s">
-        <v>177</v>
-      </c>
-      <c r="I14" s="91" t="s">
-        <v>154</v>
+      <c r="B14" s="123" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F14" s="114" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="114">
+        <v>20</v>
+      </c>
+      <c r="H14" s="100" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="100" t="s">
+        <v>197</v>
       </c>
       <c r="J14" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="97">
         <v>2</v>
       </c>
-      <c r="B15" s="123" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="100" t="s">
+      <c r="B15" s="124" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="101" t="s">
         <v>190</v>
       </c>
       <c r="D15" s="78" t="s">
@@ -9551,14 +9545,14 @@
       <c r="E15" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="114" t="s">
-        <v>226</v>
+      <c r="F15" s="114">
+        <v>20</v>
       </c>
       <c r="G15" s="114">
         <v>20</v>
       </c>
-      <c r="H15" s="100" t="s">
-        <v>196</v>
+      <c r="H15" s="101" t="s">
+        <v>200</v>
       </c>
       <c r="I15" s="100" t="s">
         <v>197</v>
@@ -9567,15 +9561,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="124" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="101" t="s">
-        <v>190</v>
+      <c r="B16" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="100" t="s">
+        <v>204</v>
       </c>
       <c r="D16" s="78" t="s">
         <v>153</v>
@@ -9583,31 +9577,31 @@
       <c r="E16" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F16" s="114">
-        <v>20</v>
+      <c r="F16" s="114" t="s">
+        <v>225</v>
       </c>
       <c r="G16" s="114">
-        <v>20</v>
-      </c>
-      <c r="H16" s="101" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="H16" s="100" t="s">
+        <v>201</v>
       </c>
       <c r="I16" s="100" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J16" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="123" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="100" t="s">
-        <v>204</v>
+      <c r="B17" s="125" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="102" t="s">
+        <v>190</v>
       </c>
       <c r="D17" s="78" t="s">
         <v>153</v>
@@ -9615,60 +9609,60 @@
       <c r="E17" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="114" t="s">
-        <v>225</v>
+      <c r="F17" s="114">
+        <v>10</v>
       </c>
       <c r="G17" s="114">
-        <v>30</v>
-      </c>
-      <c r="H17" s="100" t="s">
-        <v>201</v>
+        <v>10</v>
+      </c>
+      <c r="H17" s="102" t="s">
+        <v>203</v>
       </c>
       <c r="I17" s="100" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J17" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="125" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="102" t="s">
-        <v>190</v>
+      <c r="B18" s="123" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="100" t="s">
+        <v>204</v>
       </c>
       <c r="D18" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="109" t="s">
+      <c r="E18" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="114">
-        <v>10</v>
+      <c r="F18" s="114" t="s">
+        <v>227</v>
       </c>
       <c r="G18" s="114">
-        <v>10</v>
-      </c>
-      <c r="H18" s="102" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="100" t="s">
-        <v>199</v>
+        <v>45</v>
+      </c>
+      <c r="H18" s="100" t="s">
+        <v>205</v>
+      </c>
+      <c r="I18" s="106" t="s">
+        <v>207</v>
       </c>
       <c r="J18" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A19" s="97">
         <v>2</v>
       </c>
       <c r="B19" s="123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C19" s="100" t="s">
         <v>204</v>
@@ -9679,92 +9673,92 @@
       <c r="E19" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="114" t="s">
-        <v>227</v>
+      <c r="F19" s="114">
+        <v>9</v>
       </c>
       <c r="G19" s="114">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H19" s="100" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I19" s="106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J19" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="97">
         <v>2</v>
       </c>
       <c r="B20" s="123" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="78" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" s="114" t="s">
         <v>153</v>
       </c>
       <c r="E20" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F20" s="114">
-        <v>9</v>
+      <c r="F20" s="114" t="s">
+        <v>96</v>
       </c>
       <c r="G20" s="114">
-        <v>9</v>
-      </c>
-      <c r="H20" s="100" t="s">
-        <v>206</v>
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="106" t="s">
+        <v>211</v>
       </c>
       <c r="I20" s="106" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="J20" s="97" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="123" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="100" t="s">
-        <v>209</v>
-      </c>
-      <c r="D21" s="114" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="114" t="s">
-        <v>220</v>
-      </c>
-      <c r="F21" s="114" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="114">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="106" t="s">
-        <v>211</v>
-      </c>
-      <c r="I21" s="106" t="s">
-        <v>212</v>
+      <c r="B21" s="120" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="109" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="117" t="s">
+        <v>230</v>
+      </c>
+      <c r="G21" s="78">
+        <v>75</v>
+      </c>
+      <c r="H21" s="126" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="107" t="s">
+        <v>215</v>
       </c>
       <c r="J21" s="97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="97">
         <v>2</v>
       </c>
       <c r="B22" s="120" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="116" t="s">
         <v>186</v>
@@ -9791,76 +9785,82 @@
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="97">
         <v>2</v>
       </c>
-      <c r="B23" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="116" t="s">
-        <v>186</v>
+      <c r="B23" s="124" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="100" t="s">
+        <v>187</v>
       </c>
       <c r="D23" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E23" s="109" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>230</v>
-      </c>
-      <c r="G23" s="78">
-        <v>75</v>
+        <v>220</v>
+      </c>
+      <c r="F23" s="114" t="s">
+        <v>228</v>
+      </c>
+      <c r="G23" s="114">
+        <v>10</v>
       </c>
       <c r="H23" s="126" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="I23" s="107" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J23" s="97" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="97">
         <v>2</v>
       </c>
-      <c r="B24" s="124" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="100" t="s">
+      <c r="B24" s="123" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="96" t="s">
         <v>187</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E24" s="109" t="s">
-        <v>220</v>
-      </c>
-      <c r="F24" s="114" t="s">
-        <v>228</v>
-      </c>
-      <c r="G24" s="114">
-        <v>10</v>
-      </c>
-      <c r="H24" s="126" t="s">
-        <v>216</v>
-      </c>
-      <c r="I24" s="107" t="s">
-        <v>217</v>
+        <v>159</v>
+      </c>
+      <c r="F24" s="117" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" s="78">
+        <v>75</v>
+      </c>
+      <c r="H24" s="96" t="s">
+        <v>231</v>
+      </c>
+      <c r="I24" s="118" t="s">
+        <v>229</v>
       </c>
       <c r="J24" s="97" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K24" s="97">
+        <v>3</v>
+      </c>
+      <c r="L24" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="97">
         <v>2</v>
       </c>
       <c r="B25" s="123" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C25" s="96" t="s">
         <v>187</v>
@@ -9878,7 +9878,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I25" s="118" t="s">
         <v>229</v>
@@ -9893,12 +9893,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="97">
         <v>2</v>
       </c>
       <c r="B26" s="123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C26" s="96" t="s">
         <v>187</v>
@@ -9916,7 +9916,7 @@
         <v>75</v>
       </c>
       <c r="H26" s="96" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I26" s="118" t="s">
         <v>229</v>
@@ -9931,88 +9931,88 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="97">
+    <row r="27" spans="1:12" s="104" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="103">
+        <v>3</v>
+      </c>
+      <c r="B27" s="130" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="128" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="129" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="135" t="s">
+        <v>254</v>
+      </c>
+      <c r="G27" s="103">
+        <v>95</v>
+      </c>
+      <c r="H27" s="131" t="s">
+        <v>237</v>
+      </c>
+      <c r="I27" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" s="103" t="s">
+        <v>124</v>
+      </c>
+      <c r="K27" s="103">
         <v>2</v>
       </c>
-      <c r="B27" s="123" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="96" t="s">
+      <c r="L27" s="103" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A28" s="97">
+        <v>3</v>
+      </c>
+      <c r="B28" s="132" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" s="109" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="117" t="s">
-        <v>230</v>
-      </c>
-      <c r="G27" s="78">
-        <v>75</v>
-      </c>
-      <c r="H27" s="96" t="s">
-        <v>233</v>
-      </c>
-      <c r="I27" s="118" t="s">
-        <v>229</v>
-      </c>
-      <c r="J27" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K27" s="97">
-        <v>3</v>
-      </c>
-      <c r="L27" s="97" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="104" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A28" s="103">
-        <v>3</v>
-      </c>
-      <c r="B28" s="130" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="103" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" s="128" t="s">
+      <c r="D28" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="129" t="s">
+      <c r="E28" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F28" s="135" t="s">
+      <c r="F28" s="136" t="s">
         <v>254</v>
       </c>
-      <c r="G28" s="103">
+      <c r="G28" s="97">
         <v>95</v>
       </c>
-      <c r="H28" s="131" t="s">
-        <v>237</v>
-      </c>
-      <c r="I28" s="131" t="s">
-        <v>238</v>
-      </c>
-      <c r="J28" s="103" t="s">
+      <c r="H28" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="I28" s="134" t="s">
+        <v>241</v>
+      </c>
+      <c r="J28" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="K28" s="103">
+      <c r="K28" s="97">
         <v>2</v>
       </c>
-      <c r="L28" s="103" t="s">
+      <c r="L28" s="97" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="97">
         <v>3</v>
       </c>
       <c r="B29" s="132" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="97" t="s">
         <v>187</v>
@@ -10030,10 +10030,10 @@
         <v>95</v>
       </c>
       <c r="H29" s="133" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I29" s="134" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J29" s="97" t="s">
         <v>124</v>
@@ -10045,15 +10045,15 @@
         <v>236</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="97">
         <v>3</v>
       </c>
       <c r="B30" s="132" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C30" s="97" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D30" s="78" t="s">
         <v>153</v>
@@ -10068,27 +10068,24 @@
         <v>95</v>
       </c>
       <c r="H30" s="133" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I30" s="134" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J30" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K30" s="97">
-        <v>2</v>
-      </c>
-      <c r="L30" s="97" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="97">
         <v>3</v>
       </c>
       <c r="B31" s="132" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C31" s="97" t="s">
         <v>190</v>
@@ -10099,17 +10096,17 @@
       <c r="E31" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="136" t="s">
-        <v>254</v>
+      <c r="F31" s="97">
+        <v>22</v>
       </c>
       <c r="G31" s="97">
-        <v>95</v>
-      </c>
-      <c r="H31" s="133" t="s">
-        <v>244</v>
+        <v>22</v>
+      </c>
+      <c r="H31" s="134" t="s">
+        <v>246</v>
       </c>
       <c r="I31" s="134" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J31" s="97" t="s">
         <v>124</v>
@@ -10118,15 +10115,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A32" s="97">
         <v>3</v>
       </c>
       <c r="B32" s="132" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="C32" s="97" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D32" s="78" t="s">
         <v>153</v>
@@ -10134,23 +10131,26 @@
       <c r="E32" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F32" s="97">
-        <v>22</v>
+      <c r="F32" s="136" t="s">
+        <v>254</v>
       </c>
       <c r="G32" s="97">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H32" s="134" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="I32" s="134" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="J32" s="97" t="s">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="K32" s="97">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L32" s="97" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
@@ -10158,7 +10158,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="132" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="97" t="s">
         <v>187</v>
@@ -10176,7 +10176,7 @@
         <v>95</v>
       </c>
       <c r="H33" s="134" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I33" s="134" t="s">
         <v>229</v>
@@ -10196,7 +10196,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="132" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C34" s="97" t="s">
         <v>187</v>
@@ -10214,7 +10214,7 @@
         <v>95</v>
       </c>
       <c r="H34" s="134" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I34" s="134" t="s">
         <v>229</v>
@@ -10229,50 +10229,47 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A35" s="97">
         <v>3</v>
       </c>
       <c r="B35" s="132" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="C35" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D35" s="78" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" s="114" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="109" t="s">
+      <c r="E35" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F35" s="136" t="s">
-        <v>254</v>
+      <c r="F35" s="97" t="s">
+        <v>239</v>
       </c>
       <c r="G35" s="97">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="H35" s="134" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="I35" s="134" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="J35" s="97" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="K35" s="97">
-        <v>3</v>
-      </c>
-      <c r="L35" s="97" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="97">
         <v>3</v>
       </c>
       <c r="B36" s="132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C36" s="97" t="s">
         <v>204</v>
@@ -10290,7 +10287,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="134" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I36" s="134" t="s">
         <v>252</v>
@@ -10302,15 +10299,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="97">
         <v>3</v>
       </c>
       <c r="B37" s="132" t="s">
-        <v>250</v>
-      </c>
-      <c r="C37" s="97" t="s">
-        <v>204</v>
+        <v>139</v>
+      </c>
+      <c r="C37" s="114" t="s">
+        <v>209</v>
       </c>
       <c r="D37" s="114" t="s">
         <v>153</v>
@@ -10318,111 +10315,76 @@
       <c r="E37" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="F37" s="97" t="s">
-        <v>239</v>
-      </c>
-      <c r="G37" s="97">
-        <v>15</v>
-      </c>
-      <c r="H37" s="134" t="s">
-        <v>251</v>
+      <c r="F37" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" s="114">
+        <v>1.8</v>
+      </c>
+      <c r="H37" s="97" t="s">
+        <v>248</v>
       </c>
       <c r="I37" s="134" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J37" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="K37" s="97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="97">
+      <c r="L37" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="115" customFormat="1" ht="68" x14ac:dyDescent="0.15">
+      <c r="A38" s="115">
         <v>3</v>
       </c>
-      <c r="B38" s="132" t="s">
-        <v>139</v>
-      </c>
-      <c r="C38" s="114" t="s">
+      <c r="B38" s="137" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="137" t="s">
         <v>209</v>
       </c>
-      <c r="D38" s="114" t="s">
+      <c r="D38" s="137" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="114" t="s">
+      <c r="E38" s="137" t="s">
         <v>220</v>
       </c>
-      <c r="F38" s="114" t="s">
+      <c r="F38" s="137" t="s">
         <v>140</v>
       </c>
-      <c r="G38" s="114">
+      <c r="G38" s="137">
         <v>1.8</v>
       </c>
-      <c r="H38" s="97" t="s">
-        <v>248</v>
-      </c>
-      <c r="I38" s="134" t="s">
-        <v>248</v>
-      </c>
-      <c r="J38" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="L38" s="97" t="s">
+      <c r="H38" s="138" t="s">
+        <v>211</v>
+      </c>
+      <c r="I38" s="138" t="s">
+        <v>212</v>
+      </c>
+      <c r="J38" s="115" t="s">
+        <v>214</v>
+      </c>
+      <c r="L38" s="115" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="115" customFormat="1" ht="68" x14ac:dyDescent="0.15">
-      <c r="A39" s="115">
-        <v>3</v>
-      </c>
-      <c r="B39" s="137" t="s">
-        <v>210</v>
-      </c>
-      <c r="C39" s="137" t="s">
-        <v>209</v>
-      </c>
-      <c r="D39" s="137" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" s="137" t="s">
-        <v>220</v>
-      </c>
-      <c r="F39" s="137" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="137">
-        <v>1.8</v>
-      </c>
-      <c r="H39" s="138" t="s">
-        <v>211</v>
-      </c>
-      <c r="I39" s="138" t="s">
-        <v>212</v>
-      </c>
-      <c r="J39" s="115" t="s">
-        <v>214</v>
-      </c>
-      <c r="L39" s="115" t="s">
-        <v>170</v>
-      </c>
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="132"/>
+      <c r="C39" s="97"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="134"/>
     </row>
     <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="132"/>
-      <c r="C40" s="97"/>
-      <c r="H40" s="97"/>
+      <c r="B40" s="123"/>
       <c r="I40" s="134"/>
     </row>
     <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="B41" s="123"/>
-      <c r="I41" s="134"/>
+      <c r="I41" s="97"/>
     </row>
     <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B42" s="123"/>
       <c r="I42" s="97"/>
-    </row>
-    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="I43" s="97"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="904" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1420C5-299A-964B-B6E9-93BCFD5C64F3}"/>
+  <xr:revisionPtr revIDLastSave="910" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29B6ED75-FC04-AF42-B471-37DB77E0B786}"/>
   <bookViews>
     <workbookView xWindow="-1280" yWindow="-19540" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="259">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1588,6 +1588,18 @@
   </si>
   <si>
     <t>95%</t>
+  </si>
+  <si>
+    <t>Single Leg Hop</t>
+  </si>
+  <si>
+    <t>Triple Hop</t>
+  </si>
+  <si>
+    <t>Triple Cross Over Hop</t>
+  </si>
+  <si>
+    <t>Side Hop</t>
   </si>
 </sst>
 </file>
@@ -9936,7 +9948,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="130" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="C27" s="103" t="s">
         <v>187</v>
@@ -9974,7 +9986,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="132" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="C28" s="97" t="s">
         <v>187</v>
@@ -10012,7 +10024,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="132" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="C29" s="97" t="s">
         <v>187</v>
@@ -10050,7 +10062,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="132" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="C30" s="97" t="s">
         <v>190</v>
@@ -10085,7 +10097,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="132" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="C31" s="97" t="s">
         <v>190</v>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="910" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29B6ED75-FC04-AF42-B471-37DB77E0B786}"/>
+  <xr:revisionPtr revIDLastSave="1118" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1404772C-210A-D843-A6D9-8467CCCD6661}"/>
   <bookViews>
-    <workbookView xWindow="-1280" yWindow="-19540" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="295">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1600,6 +1600,118 @@
   </si>
   <si>
     <t>Side Hop</t>
+  </si>
+  <si>
+    <t>Composite Score</t>
+  </si>
+  <si>
+    <t>A+PL+PM/3*100</t>
+  </si>
+  <si>
+    <t>3 Each</t>
+  </si>
+  <si>
+    <t>Pistol Squat</t>
+  </si>
+  <si>
+    <t>The composite score combines Anterior, Postero-Medial and Postero-Lateral.  Our current calculation places equal weight on each score.  The displayed score represents the average score on the injured limb as a percentage of the average score on the non-injured limb. placing equal weight on each score.  Currently we are not multiplying by limb length so this is not necessarily comparable between athletes.  Composite score will be used for Phase Criteria, while individual Y-Balance scores can be found in the more detialed Phase Progress reports.</t>
+  </si>
+  <si>
+    <t>Full range of motion single leg squats while standing on a box.</t>
+  </si>
+  <si>
+    <t>The athlete stands on a box that is high enough to let their opposite leg hang to the side and not touch the ground in the bottom of the squat.  For a repetition to be succesful, the angle of the knee joint must exceed 90 degrees.  Practitioner discretion is crucial to determine proper technique.  If there is excessive frontal plan motion (i.e. knee valgus) or excessive hip lift (off-loading the quads), consider carefully whether reps should be counted towards succesful achievment of this criteria.</t>
+  </si>
+  <si>
+    <t>CMJ Height</t>
+  </si>
+  <si>
+    <t>CMJ RSImod</t>
+  </si>
+  <si>
+    <t>CMJ Lengthening Asymmetry</t>
+  </si>
+  <si>
+    <t>CMJ Shortening Asymmetry</t>
+  </si>
+  <si>
+    <t>CMJ Lengthening Impulse</t>
+  </si>
+  <si>
+    <t>CMJ Shortening Impulse</t>
+  </si>
+  <si>
+    <t>Drop and Stick - Landing Force</t>
+  </si>
+  <si>
+    <t>Drop and Stick - Time to Stabilization</t>
+  </si>
+  <si>
+    <t>Drop and Stick - Landing Asymmetry</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>N*s</t>
+  </si>
+  <si>
+    <t>N*s (%)</t>
+  </si>
+  <si>
+    <t>N/kg</t>
+  </si>
+  <si>
+    <t>Scores are relative to baseline data</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>3.5x BM</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>Mean ± CI</t>
+  </si>
+  <si>
+    <t>Confidence interval around the mean of 5 jumps must be entirely within ± 10%</t>
+  </si>
+  <si>
+    <t>Participant steps forward off 50cm box with their preferred leg and lands on the force plates in a squat with thighs parallel to the floor and arms held out ion front of them.  
+Cue: "Land softly and stabilize as quickly as possible"
+TTS target scores are based off old research for now.</t>
+  </si>
+  <si>
+    <t>Participant steps forward off 50cm box with their preferred leg and lands on the force plates in a squat with thighs parallel to the floor and arms held out ion front of them.  
+Cue: "Land softly and stabilize as quickly as possible"
+rPLF target scores are based off old research for now.</t>
+  </si>
+  <si>
+    <t>The amount of force required to bring the body to a stable state following a 50cm drop landing.</t>
+  </si>
+  <si>
+    <t>Time taken to return the body to a stable state following a 50cm drop landing.</t>
+  </si>
+  <si>
+    <t>Height in cm</t>
+  </si>
+  <si>
+    <t>Height of jump divided by total contraction time</t>
+  </si>
+  <si>
+    <t>Ratio of force produced by each limb in the lengthening (lowering) phase of the jump</t>
+  </si>
+  <si>
+    <t>Ratio of force produced by each limb in the shortening (propulsive) phase of the jump</t>
+  </si>
+  <si>
+    <t>Phase impulse is tracked independently to ensure that ratio data does not represent a drop in force production of the non-injured limb.</t>
+  </si>
+  <si>
+    <t>0.75s'</t>
   </si>
 </sst>
 </file>
@@ -1610,11 +1722,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2093,381 +2212,372 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="21" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2723,13 +2833,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2787,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="142" t="s">
+      <c r="G4" s="130" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2820,7 +2930,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="140"/>
+      <c r="G5" s="125"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2848,7 +2958,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="140"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2872,7 +2982,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="140"/>
+      <c r="G7" s="125"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -2895,7 +3005,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="140"/>
+      <c r="G8" s="125"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -2923,7 +3033,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="140"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3006,13 +3116,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3067,24 +3177,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="151">
+      <c r="H16" s="126">
         <v>45359</v>
       </c>
-      <c r="I16" s="150"/>
-      <c r="J16" s="152">
+      <c r="I16" s="127"/>
+      <c r="J16" s="128">
         <v>47204</v>
       </c>
-      <c r="K16" s="150"/>
-      <c r="L16" s="153" t="s">
+      <c r="K16" s="127"/>
+      <c r="L16" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="150"/>
-      <c r="N16" s="151">
+      <c r="M16" s="127"/>
+      <c r="N16" s="126">
         <v>45429</v>
       </c>
-      <c r="O16" s="150"/>
-      <c r="P16" s="151"/>
-      <c r="Q16" s="150"/>
+      <c r="O16" s="127"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="127"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3158,7 +3268,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="142" t="s">
+      <c r="G18" s="130" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3202,7 +3312,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="140"/>
+      <c r="G19" s="125"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3240,7 +3350,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="140"/>
+      <c r="G20" s="125"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3286,7 +3396,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="140"/>
+      <c r="G21" s="125"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3322,7 +3432,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="140"/>
+      <c r="G22" s="125"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3360,7 +3470,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="140"/>
+      <c r="G23" s="125"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3400,7 +3510,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="140"/>
+      <c r="G24" s="125"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3591,13 +3701,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="141" t="s">
+      <c r="B32" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="125"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3642,12 +3752,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="149" t="s">
+      <c r="H33" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="150"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="150"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="126"/>
+      <c r="K33" s="127"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3672,7 +3782,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="142" t="s">
+      <c r="G34" s="130" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3703,7 +3813,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="140"/>
+      <c r="G35" s="125"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3732,7 +3842,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="140"/>
+      <c r="G36" s="125"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3761,7 +3871,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="140"/>
+      <c r="G37" s="125"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3790,7 +3900,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="140"/>
+      <c r="G38" s="125"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3811,7 +3921,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="140"/>
+      <c r="G39" s="125"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3840,7 +3950,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="140"/>
+      <c r="G40" s="125"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3861,7 +3971,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="140"/>
+      <c r="G41" s="125"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -3890,7 +4000,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="140"/>
+      <c r="G42" s="125"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -3911,7 +4021,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="140"/>
+      <c r="G43" s="125"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -3934,17 +4044,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="143" t="s">
+      <c r="C44" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="D44" s="132" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="140"/>
+      <c r="G44" s="125"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -3959,13 +4069,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="140"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="140"/>
+      <c r="G45" s="125"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -3994,7 +4104,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="140"/>
+      <c r="G46" s="125"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4015,7 +4125,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="140"/>
+      <c r="G47" s="125"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4044,7 +4154,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="140"/>
+      <c r="G48" s="125"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4073,7 +4183,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="140"/>
+      <c r="G49" s="125"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4100,7 +4210,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="140"/>
+      <c r="G50" s="125"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4196,10 +4306,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="139">
+      <c r="B54" s="137">
         <v>16</v>
       </c>
-      <c r="C54" s="144" t="s">
+      <c r="C54" s="138" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4220,8 +4330,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="140"/>
-      <c r="C55" s="140"/>
+      <c r="B55" s="125"/>
+      <c r="C55" s="125"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4240,10 +4350,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="145">
+      <c r="B56" s="133">
         <v>17</v>
       </c>
-      <c r="C56" s="147" t="s">
+      <c r="C56" s="135" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4265,8 +4375,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="146"/>
-      <c r="C57" s="148"/>
+      <c r="B57" s="134"/>
+      <c r="C57" s="136"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4286,10 +4396,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="139">
+      <c r="B58" s="137">
         <v>18</v>
       </c>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="138" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4310,8 +4420,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="140"/>
+      <c r="B59" s="125"/>
+      <c r="C59" s="125"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4330,10 +4440,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="145">
+      <c r="B60" s="133">
         <v>19</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="135" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4355,8 +4465,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="146"/>
-      <c r="C61" s="148"/>
+      <c r="B61" s="134"/>
+      <c r="C61" s="136"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4376,7 +4486,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="139">
+      <c r="B62" s="137">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4400,7 +4510,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="140"/>
+      <c r="B63" s="125"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4576,13 +4686,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="141" t="s">
+      <c r="B74" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="140"/>
-      <c r="D74" s="140"/>
-      <c r="E74" s="140"/>
-      <c r="F74" s="140"/>
+      <c r="C74" s="125"/>
+      <c r="D74" s="125"/>
+      <c r="E74" s="125"/>
+      <c r="F74" s="125"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4661,7 +4771,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="142" t="s">
+      <c r="G76" s="130" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4688,7 +4798,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="140"/>
+      <c r="G77" s="125"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4713,7 +4823,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="140"/>
+      <c r="G78" s="125"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4740,7 +4850,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="140"/>
+      <c r="G79" s="125"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4772,7 +4882,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="140"/>
+      <c r="G80" s="125"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4801,7 +4911,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="140"/>
+      <c r="G81" s="125"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4830,7 +4940,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="140"/>
+      <c r="G82" s="125"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4859,7 +4969,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="140"/>
+      <c r="G83" s="125"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -4888,7 +4998,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="140"/>
+      <c r="G84" s="125"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -4917,7 +5027,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="140"/>
+      <c r="G85" s="125"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -4946,7 +5056,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="140"/>
+      <c r="G86" s="125"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -4975,7 +5085,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="140"/>
+      <c r="G87" s="125"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8721,22 +8831,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8747,6 +8841,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9043,44 +9153,44 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
-    <col min="2" max="2" width="47" style="122" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="96"/>
+    <col min="2" max="2" width="47" style="97" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="97"/>
     <col min="4" max="4" width="16.5" style="97" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.1640625" style="97" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" style="97" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="97"/>
-    <col min="8" max="8" width="73.1640625" style="96" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="116" style="96" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="73.1640625" style="120" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="116" style="120" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.33203125" style="97" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="97" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.6640625" style="97" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="79" t="s">
         <v>143</v>
       </c>
       <c r="C1" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="98" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="98" t="s">
         <v>218</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="F1" s="98" t="s">
         <v>222</v>
       </c>
-      <c r="G1" s="99" t="s">
+      <c r="G1" s="98" t="s">
         <v>145</v>
       </c>
       <c r="H1" s="82" t="s">
@@ -9089,7 +9199,7 @@
       <c r="I1" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="99" t="s">
+      <c r="J1" s="98" t="s">
         <v>144</v>
       </c>
       <c r="K1" s="82" t="s">
@@ -9099,20 +9209,20 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97">
         <v>0</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="140" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="97" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="103" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F2" s="78" t="s">
@@ -9121,7 +9231,7 @@
       <c r="G2" s="78">
         <v>0</v>
       </c>
-      <c r="H2" s="126" t="s">
+      <c r="H2" s="112" t="s">
         <v>180</v>
       </c>
       <c r="I2" s="81" t="s">
@@ -9135,20 +9245,20 @@
       </c>
       <c r="L2" s="81"/>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="97">
         <v>0</v>
       </c>
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="97" t="s">
         <v>184</v>
       </c>
       <c r="D3" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="109" t="s">
+      <c r="E3" s="104" t="s">
         <v>220</v>
       </c>
       <c r="F3" s="78" t="s">
@@ -9157,7 +9267,7 @@
       <c r="G3" s="78">
         <v>125</v>
       </c>
-      <c r="H3" s="126" t="s">
+      <c r="H3" s="112" t="s">
         <v>180</v>
       </c>
       <c r="I3" s="81" t="s">
@@ -9171,20 +9281,20 @@
       </c>
       <c r="L3" s="81"/>
     </row>
-    <row r="4" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="97">
         <v>0</v>
       </c>
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="97" t="s">
         <v>185</v>
       </c>
       <c r="D4" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F4" s="78">
@@ -9193,7 +9303,7 @@
       <c r="G4" s="78">
         <v>1</v>
       </c>
-      <c r="H4" s="126" t="s">
+      <c r="H4" s="112" t="s">
         <v>177</v>
       </c>
       <c r="I4" s="91" t="s">
@@ -9205,29 +9315,29 @@
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
     </row>
-    <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="97">
         <v>0</v>
       </c>
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="97" t="s">
         <v>186</v>
       </c>
       <c r="D5" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="109" t="s">
+      <c r="E5" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F5" s="105" t="s">
         <v>223</v>
       </c>
       <c r="G5" s="78">
         <v>90</v>
       </c>
-      <c r="H5" s="126" t="s">
+      <c r="H5" s="112" t="s">
         <v>157</v>
       </c>
       <c r="I5" s="92" t="s">
@@ -9243,29 +9353,29 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="97">
         <v>0</v>
       </c>
-      <c r="B6" s="120" t="s">
+      <c r="B6" s="140" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="97" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="111" t="s">
+      <c r="D6" s="106" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="112" t="s">
+      <c r="E6" s="107" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="113" t="s">
+      <c r="F6" s="108" t="s">
         <v>223</v>
       </c>
-      <c r="G6" s="111">
+      <c r="G6" s="106">
         <v>90</v>
       </c>
-      <c r="H6" s="126" t="s">
+      <c r="H6" s="112" t="s">
         <v>157</v>
       </c>
       <c r="I6" s="92" t="s">
@@ -9281,20 +9391,20 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="104" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="103">
+    <row r="7" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="99">
         <v>1</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="104" t="s">
+      <c r="C7" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="108" t="s">
+      <c r="D7" s="103" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="108" t="s">
+      <c r="E7" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F7" s="78" t="s">
@@ -9303,32 +9413,32 @@
       <c r="G7" s="78">
         <v>0</v>
       </c>
-      <c r="H7" s="127" t="s">
+      <c r="H7" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="I7" s="105" t="s">
+      <c r="I7" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="103" t="s">
+      <c r="J7" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-    </row>
-    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+    </row>
+    <row r="8" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="97">
         <v>1</v>
       </c>
-      <c r="B8" s="120" t="s">
+      <c r="B8" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="96" t="s">
+      <c r="C8" s="97" t="s">
         <v>184</v>
       </c>
       <c r="D8" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="104" t="s">
         <v>220</v>
       </c>
       <c r="F8" s="78" t="s">
@@ -9337,7 +9447,7 @@
       <c r="G8" s="78">
         <v>125</v>
       </c>
-      <c r="H8" s="126" t="s">
+      <c r="H8" s="112" t="s">
         <v>180</v>
       </c>
       <c r="I8" s="81" t="s">
@@ -9347,20 +9457,20 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="97">
         <v>1</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="97" t="s">
         <v>185</v>
       </c>
       <c r="D9" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E9" s="108" t="s">
+      <c r="E9" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F9" s="78">
@@ -9369,7 +9479,7 @@
       <c r="G9" s="78">
         <v>1</v>
       </c>
-      <c r="H9" s="126" t="s">
+      <c r="H9" s="112" t="s">
         <v>177</v>
       </c>
       <c r="I9" s="81" t="s">
@@ -9379,29 +9489,29 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="97">
         <v>1</v>
       </c>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="97" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="97" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="115" t="s">
+      <c r="D10" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="F10" s="115">
+      <c r="F10" s="110">
         <v>5</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="110">
         <v>5</v>
       </c>
-      <c r="H10" s="126" t="s">
+      <c r="H10" s="112" t="s">
         <v>192</v>
       </c>
       <c r="I10" s="81" t="s">
@@ -9411,20 +9521,20 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="104" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="103">
+    <row r="11" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="99">
         <v>2</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="108" t="s">
+      <c r="D11" s="103" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F11" s="78" t="s">
@@ -9433,32 +9543,32 @@
       <c r="G11" s="78">
         <v>0</v>
       </c>
-      <c r="H11" s="127" t="s">
+      <c r="H11" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="I11" s="105" t="s">
+      <c r="I11" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="J11" s="103" t="s">
+      <c r="J11" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="K11" s="103"/>
-      <c r="L11" s="103"/>
-    </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+    </row>
+    <row r="12" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="97">
         <v>2</v>
       </c>
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="97" t="s">
         <v>184</v>
       </c>
       <c r="D12" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E12" s="109" t="s">
+      <c r="E12" s="104" t="s">
         <v>220</v>
       </c>
       <c r="F12" s="78" t="s">
@@ -9467,7 +9577,7 @@
       <c r="G12" s="78">
         <v>125</v>
       </c>
-      <c r="H12" s="126" t="s">
+      <c r="H12" s="112" t="s">
         <v>180</v>
       </c>
       <c r="I12" s="81" t="s">
@@ -9477,20 +9587,20 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="97">
         <v>2</v>
       </c>
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="97" t="s">
         <v>185</v>
       </c>
       <c r="D13" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="108" t="s">
+      <c r="E13" s="103" t="s">
         <v>221</v>
       </c>
       <c r="F13" s="78">
@@ -9499,7 +9609,7 @@
       <c r="G13" s="78">
         <v>0</v>
       </c>
-      <c r="H13" s="126" t="s">
+      <c r="H13" s="112" t="s">
         <v>177</v>
       </c>
       <c r="I13" s="91" t="s">
@@ -9509,303 +9619,303 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="123" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="100" t="s">
-        <v>190</v>
+      <c r="B14" s="142" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="109" t="s">
+        <v>187</v>
       </c>
       <c r="D14" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="109" t="s">
+      <c r="E14" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F14" s="114" t="s">
-        <v>226</v>
-      </c>
-      <c r="G14" s="114">
-        <v>20</v>
-      </c>
-      <c r="H14" s="100" t="s">
-        <v>196</v>
-      </c>
-      <c r="I14" s="100" t="s">
-        <v>197</v>
+      <c r="F14" s="109" t="s">
+        <v>228</v>
+      </c>
+      <c r="G14" s="109">
+        <v>10</v>
+      </c>
+      <c r="H14" s="112" t="s">
+        <v>216</v>
+      </c>
+      <c r="I14" s="102" t="s">
+        <v>217</v>
       </c>
       <c r="J14" s="97" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="97">
         <v>2</v>
       </c>
-      <c r="B15" s="124" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="101" t="s">
+      <c r="B15" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="109" t="s">
         <v>190</v>
       </c>
       <c r="D15" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="109" t="s">
+      <c r="E15" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="114">
+      <c r="F15" s="109" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" s="109">
         <v>20</v>
       </c>
-      <c r="G15" s="114">
-        <v>20</v>
-      </c>
-      <c r="H15" s="101" t="s">
-        <v>200</v>
-      </c>
-      <c r="I15" s="100" t="s">
+      <c r="H15" s="144" t="s">
+        <v>196</v>
+      </c>
+      <c r="I15" s="144" t="s">
         <v>197</v>
       </c>
       <c r="J15" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="123" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="100" t="s">
-        <v>204</v>
+      <c r="B16" s="142" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="142" t="s">
+        <v>190</v>
       </c>
       <c r="D16" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="109" t="s">
+      <c r="E16" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F16" s="114" t="s">
-        <v>225</v>
-      </c>
-      <c r="G16" s="114">
-        <v>30</v>
-      </c>
-      <c r="H16" s="100" t="s">
-        <v>201</v>
-      </c>
-      <c r="I16" s="100" t="s">
-        <v>198</v>
+      <c r="F16" s="109">
+        <v>20</v>
+      </c>
+      <c r="G16" s="109">
+        <v>20</v>
+      </c>
+      <c r="H16" s="143" t="s">
+        <v>200</v>
+      </c>
+      <c r="I16" s="144" t="s">
+        <v>197</v>
       </c>
       <c r="J16" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="125" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="102" t="s">
-        <v>190</v>
+      <c r="B17" s="118" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="109" t="s">
+        <v>204</v>
       </c>
       <c r="D17" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E17" s="109" t="s">
+      <c r="E17" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="114">
-        <v>10</v>
-      </c>
-      <c r="G17" s="114">
-        <v>10</v>
-      </c>
-      <c r="H17" s="102" t="s">
-        <v>203</v>
-      </c>
-      <c r="I17" s="100" t="s">
-        <v>199</v>
+      <c r="F17" s="109" t="s">
+        <v>225</v>
+      </c>
+      <c r="G17" s="109">
+        <v>30</v>
+      </c>
+      <c r="H17" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="I17" s="144" t="s">
+        <v>198</v>
       </c>
       <c r="J17" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="123" t="s">
-        <v>234</v>
-      </c>
-      <c r="C18" s="100" t="s">
-        <v>204</v>
+      <c r="B18" s="143" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="143" t="s">
+        <v>190</v>
       </c>
       <c r="D18" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="114" t="s">
+      <c r="E18" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="114" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="114">
-        <v>45</v>
-      </c>
-      <c r="H18" s="100" t="s">
-        <v>205</v>
-      </c>
-      <c r="I18" s="106" t="s">
-        <v>207</v>
+      <c r="F18" s="109">
+        <v>10</v>
+      </c>
+      <c r="G18" s="109">
+        <v>10</v>
+      </c>
+      <c r="H18" s="143" t="s">
+        <v>203</v>
+      </c>
+      <c r="I18" s="144" t="s">
+        <v>199</v>
       </c>
       <c r="J18" s="97" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="97">
         <v>2</v>
       </c>
-      <c r="B19" s="123" t="s">
-        <v>235</v>
-      </c>
-      <c r="C19" s="100" t="s">
-        <v>204</v>
-      </c>
-      <c r="D19" s="78" t="s">
+      <c r="B19" s="118" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="114" t="s">
+      <c r="E19" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="114">
-        <v>9</v>
-      </c>
-      <c r="G19" s="114">
-        <v>9</v>
-      </c>
-      <c r="H19" s="100" t="s">
-        <v>206</v>
-      </c>
-      <c r="I19" s="106" t="s">
-        <v>208</v>
+      <c r="F19" s="109" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="109">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="I19" s="144" t="s">
+        <v>212</v>
       </c>
       <c r="J19" s="97" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="97">
         <v>2</v>
       </c>
-      <c r="B20" s="123" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="100" t="s">
-        <v>209</v>
-      </c>
-      <c r="D20" s="114" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="114" t="s">
-        <v>220</v>
-      </c>
-      <c r="F20" s="114" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="114">
-        <v>1.5</v>
-      </c>
-      <c r="H20" s="106" t="s">
-        <v>211</v>
-      </c>
-      <c r="I20" s="106" t="s">
-        <v>212</v>
+      <c r="B20" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="111" t="s">
+        <v>230</v>
+      </c>
+      <c r="G20" s="78">
+        <v>75</v>
+      </c>
+      <c r="H20" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="102" t="s">
+        <v>215</v>
       </c>
       <c r="J20" s="97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="120" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="116" t="s">
+      <c r="B21" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="80" t="s">
         <v>186</v>
       </c>
       <c r="D21" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="109" t="s">
+      <c r="E21" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F21" s="117" t="s">
+      <c r="F21" s="111" t="s">
         <v>230</v>
       </c>
       <c r="G21" s="78">
         <v>75</v>
       </c>
-      <c r="H21" s="126" t="s">
+      <c r="H21" s="112" t="s">
         <v>157</v>
       </c>
-      <c r="I21" s="107" t="s">
+      <c r="I21" s="102" t="s">
         <v>215</v>
       </c>
       <c r="J21" s="97" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="97">
         <v>2</v>
       </c>
-      <c r="B22" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="116" t="s">
-        <v>186</v>
+      <c r="B22" s="118" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="109" t="s">
+        <v>204</v>
       </c>
       <c r="D22" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E22" s="109" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="117" t="s">
-        <v>230</v>
-      </c>
-      <c r="G22" s="78">
-        <v>75</v>
-      </c>
-      <c r="H22" s="126" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" s="107" t="s">
-        <v>215</v>
+        <v>220</v>
+      </c>
+      <c r="F22" s="109" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="109">
+        <v>45</v>
+      </c>
+      <c r="H22" s="144" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="144" t="s">
+        <v>207</v>
       </c>
       <c r="J22" s="97" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="97">
         <v>2</v>
       </c>
-      <c r="B23" s="124" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="100" t="s">
-        <v>187</v>
+      <c r="B23" s="118" t="s">
+        <v>235</v>
+      </c>
+      <c r="C23" s="109" t="s">
+        <v>204</v>
       </c>
       <c r="D23" s="78" t="s">
         <v>153</v>
@@ -9813,48 +9923,48 @@
       <c r="E23" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F23" s="114" t="s">
-        <v>228</v>
-      </c>
-      <c r="G23" s="114">
-        <v>10</v>
-      </c>
-      <c r="H23" s="126" t="s">
-        <v>216</v>
-      </c>
-      <c r="I23" s="107" t="s">
-        <v>217</v>
+      <c r="F23" s="109">
+        <v>9</v>
+      </c>
+      <c r="G23" s="109">
+        <v>9</v>
+      </c>
+      <c r="H23" s="144" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" s="144" t="s">
+        <v>208</v>
       </c>
       <c r="J23" s="97" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="97">
         <v>2</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="118" t="s">
         <v>193</v>
       </c>
-      <c r="C24" s="96" t="s">
+      <c r="C24" s="97" t="s">
         <v>187</v>
       </c>
       <c r="D24" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E24" s="109" t="s">
+      <c r="E24" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F24" s="111" t="s">
         <v>230</v>
       </c>
       <c r="G24" s="78">
         <v>75</v>
       </c>
-      <c r="H24" s="96" t="s">
+      <c r="H24" s="120" t="s">
         <v>231</v>
       </c>
-      <c r="I24" s="118" t="s">
+      <c r="I24" s="120" t="s">
         <v>229</v>
       </c>
       <c r="J24" s="97" t="s">
@@ -9867,32 +9977,32 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="97">
         <v>2</v>
       </c>
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="96" t="s">
+      <c r="C25" s="97" t="s">
         <v>187</v>
       </c>
       <c r="D25" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="109" t="s">
+      <c r="E25" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F25" s="117" t="s">
+      <c r="F25" s="111" t="s">
         <v>230</v>
       </c>
       <c r="G25" s="78">
         <v>75</v>
       </c>
-      <c r="H25" s="96" t="s">
+      <c r="H25" s="120" t="s">
         <v>232</v>
       </c>
-      <c r="I25" s="118" t="s">
+      <c r="I25" s="120" t="s">
         <v>229</v>
       </c>
       <c r="J25" s="97" t="s">
@@ -9905,32 +10015,32 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="97">
         <v>2</v>
       </c>
-      <c r="B26" s="123" t="s">
+      <c r="B26" s="118" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="96" t="s">
+      <c r="C26" s="97" t="s">
         <v>187</v>
       </c>
       <c r="D26" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="E26" s="109" t="s">
+      <c r="E26" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="117" t="s">
+      <c r="F26" s="111" t="s">
         <v>230</v>
       </c>
       <c r="G26" s="78">
         <v>75</v>
       </c>
-      <c r="H26" s="96" t="s">
+      <c r="H26" s="120" t="s">
         <v>233</v>
       </c>
-      <c r="I26" s="118" t="s">
+      <c r="I26" s="120" t="s">
         <v>229</v>
       </c>
       <c r="J26" s="97" t="s">
@@ -9943,88 +10053,88 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="104" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A27" s="103">
+    <row r="27" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="97">
+        <v>2</v>
+      </c>
+      <c r="B27" s="109" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="122" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="97">
+        <v>75</v>
+      </c>
+      <c r="H27" s="120" t="s">
+        <v>259</v>
+      </c>
+      <c r="I27" s="120" t="s">
+        <v>263</v>
+      </c>
+      <c r="J27" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27" s="97" t="s">
+        <v>261</v>
+      </c>
+      <c r="L27" s="139" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="99">
         <v>3</v>
       </c>
-      <c r="B27" s="130" t="s">
+      <c r="B28" s="116" t="s">
         <v>255</v>
       </c>
-      <c r="C27" s="103" t="s">
+      <c r="C28" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="128" t="s">
+      <c r="D28" s="114" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="129" t="s">
+      <c r="E28" s="115" t="s">
         <v>220</v>
       </c>
-      <c r="F27" s="135" t="s">
+      <c r="F28" s="121" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="103">
+      <c r="G28" s="99">
         <v>95</v>
       </c>
-      <c r="H27" s="131" t="s">
+      <c r="H28" s="117" t="s">
         <v>237</v>
       </c>
-      <c r="I27" s="131" t="s">
+      <c r="I28" s="117" t="s">
         <v>238</v>
       </c>
-      <c r="J27" s="103" t="s">
+      <c r="J28" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="K27" s="103">
+      <c r="K28" s="99">
         <v>2</v>
       </c>
-      <c r="L27" s="103" t="s">
+      <c r="L28" s="99" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="85" x14ac:dyDescent="0.2">
-      <c r="A28" s="97">
-        <v>3</v>
-      </c>
-      <c r="B28" s="132" t="s">
-        <v>256</v>
-      </c>
-      <c r="C28" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" s="109" t="s">
-        <v>220</v>
-      </c>
-      <c r="F28" s="136" t="s">
-        <v>254</v>
-      </c>
-      <c r="G28" s="97">
-        <v>95</v>
-      </c>
-      <c r="H28" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="I28" s="134" t="s">
-        <v>241</v>
-      </c>
-      <c r="J28" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="97">
-        <v>2</v>
-      </c>
-      <c r="L28" s="97" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="97">
         <v>3</v>
       </c>
-      <c r="B29" s="132" t="s">
-        <v>257</v>
+      <c r="B29" s="118" t="s">
+        <v>256</v>
       </c>
       <c r="C29" s="97" t="s">
         <v>187</v>
@@ -10032,20 +10142,20 @@
       <c r="D29" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="109" t="s">
+      <c r="E29" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F29" s="136" t="s">
+      <c r="F29" s="122" t="s">
         <v>254</v>
       </c>
       <c r="G29" s="97">
         <v>95</v>
       </c>
-      <c r="H29" s="133" t="s">
-        <v>242</v>
-      </c>
-      <c r="I29" s="134" t="s">
-        <v>243</v>
+      <c r="H29" s="119" t="s">
+        <v>240</v>
+      </c>
+      <c r="I29" s="120" t="s">
+        <v>241</v>
       </c>
       <c r="J29" s="97" t="s">
         <v>124</v>
@@ -10057,47 +10167,50 @@
         <v>236</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="97">
         <v>3</v>
       </c>
-      <c r="B30" s="132" t="s">
-        <v>258</v>
+      <c r="B30" s="118" t="s">
+        <v>257</v>
       </c>
       <c r="C30" s="97" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D30" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="109" t="s">
+      <c r="E30" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F30" s="136" t="s">
+      <c r="F30" s="122" t="s">
         <v>254</v>
       </c>
       <c r="G30" s="97">
         <v>95</v>
       </c>
-      <c r="H30" s="133" t="s">
-        <v>244</v>
-      </c>
-      <c r="I30" s="134" t="s">
-        <v>245</v>
+      <c r="H30" s="119" t="s">
+        <v>242</v>
+      </c>
+      <c r="I30" s="120" t="s">
+        <v>243</v>
       </c>
       <c r="J30" s="97" t="s">
         <v>124</v>
       </c>
       <c r="K30" s="97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="L30" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="97">
         <v>3</v>
       </c>
-      <c r="B31" s="132" t="s">
-        <v>202</v>
+      <c r="B31" s="118" t="s">
+        <v>258</v>
       </c>
       <c r="C31" s="97" t="s">
         <v>190</v>
@@ -10105,20 +10218,20 @@
       <c r="D31" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="109" t="s">
+      <c r="E31" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="97">
-        <v>22</v>
+      <c r="F31" s="122" t="s">
+        <v>254</v>
       </c>
       <c r="G31" s="97">
-        <v>22</v>
-      </c>
-      <c r="H31" s="134" t="s">
-        <v>246</v>
-      </c>
-      <c r="I31" s="134" t="s">
-        <v>247</v>
+        <v>95</v>
+      </c>
+      <c r="H31" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="I31" s="120" t="s">
+        <v>245</v>
       </c>
       <c r="J31" s="97" t="s">
         <v>124</v>
@@ -10127,276 +10240,823 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="97">
         <v>3</v>
       </c>
-      <c r="B32" s="132" t="s">
-        <v>193</v>
+      <c r="B32" s="118" t="s">
+        <v>202</v>
       </c>
       <c r="C32" s="97" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D32" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="109" t="s">
+      <c r="E32" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F32" s="136" t="s">
-        <v>254</v>
+      <c r="F32" s="97">
+        <v>22</v>
       </c>
       <c r="G32" s="97">
-        <v>95</v>
-      </c>
-      <c r="H32" s="134" t="s">
-        <v>231</v>
-      </c>
-      <c r="I32" s="134" t="s">
-        <v>229</v>
+        <v>22</v>
+      </c>
+      <c r="H32" s="120" t="s">
+        <v>246</v>
+      </c>
+      <c r="I32" s="120" t="s">
+        <v>247</v>
       </c>
       <c r="J32" s="97" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="K32" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="80">
         <v>3</v>
       </c>
-      <c r="L32" s="97" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
-      <c r="A33" s="97">
-        <v>3</v>
-      </c>
-      <c r="B33" s="132" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="78" t="s">
+      <c r="B33" s="109" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E33" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F33" s="136" t="s">
-        <v>254</v>
-      </c>
-      <c r="G33" s="97">
-        <v>95</v>
-      </c>
-      <c r="H33" s="134" t="s">
-        <v>232</v>
-      </c>
-      <c r="I33" s="134" t="s">
-        <v>229</v>
-      </c>
-      <c r="J33" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="97">
-        <v>3</v>
-      </c>
-      <c r="L33" s="97" t="s">
+      <c r="F33" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="109">
+        <v>1.8</v>
+      </c>
+      <c r="H33" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="I33" s="144" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="80" t="s">
+        <v>214</v>
+      </c>
+      <c r="L33" s="80" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="97" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="97">
         <v>3</v>
       </c>
-      <c r="B34" s="132" t="s">
-        <v>195</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D34" s="78" t="s">
+      <c r="B34" s="118" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F34" s="136" t="s">
-        <v>254</v>
-      </c>
-      <c r="G34" s="97">
-        <v>95</v>
-      </c>
-      <c r="H34" s="134" t="s">
-        <v>233</v>
-      </c>
-      <c r="I34" s="134" t="s">
-        <v>229</v>
+      <c r="F34" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="109">
+        <v>1.8</v>
+      </c>
+      <c r="H34" s="120" t="s">
+        <v>248</v>
+      </c>
+      <c r="I34" s="120" t="s">
+        <v>248</v>
       </c>
       <c r="J34" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K34" s="97">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="L34" s="97" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="97">
         <v>3</v>
       </c>
-      <c r="B35" s="132" t="s">
-        <v>249</v>
-      </c>
-      <c r="C35" s="97" t="s">
-        <v>204</v>
-      </c>
-      <c r="D35" s="114" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="114" t="s">
-        <v>220</v>
-      </c>
-      <c r="F35" s="97" t="s">
-        <v>239</v>
-      </c>
-      <c r="G35" s="97">
-        <v>15</v>
-      </c>
-      <c r="H35" s="134" t="s">
-        <v>253</v>
-      </c>
-      <c r="I35" s="134" t="s">
-        <v>252</v>
-      </c>
-      <c r="J35" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="K35" s="97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="B35" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="148" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="78">
+        <v>90</v>
+      </c>
+      <c r="H35" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" s="102" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="97">
         <v>3</v>
       </c>
-      <c r="B36" s="132" t="s">
+      <c r="B36" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="148" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="78">
+        <v>90</v>
+      </c>
+      <c r="H36" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="102" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="80">
+        <v>3</v>
+      </c>
+      <c r="B37" s="109" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="145" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="80">
+        <v>95</v>
+      </c>
+      <c r="H37" s="83" t="s">
+        <v>231</v>
+      </c>
+      <c r="I37" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="J37" s="80" t="s">
+        <v>213</v>
+      </c>
+      <c r="K37" s="80">
+        <v>3</v>
+      </c>
+      <c r="L37" s="80" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="97">
+        <v>3</v>
+      </c>
+      <c r="B38" s="118" t="s">
+        <v>194</v>
+      </c>
+      <c r="C38" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="122" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="97">
+        <v>95</v>
+      </c>
+      <c r="H38" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>229</v>
+      </c>
+      <c r="J38" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K38" s="97">
+        <v>3</v>
+      </c>
+      <c r="L38" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="97">
+        <v>3</v>
+      </c>
+      <c r="B39" s="118" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="122" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="97">
+        <v>95</v>
+      </c>
+      <c r="H39" s="120" t="s">
+        <v>233</v>
+      </c>
+      <c r="I39" s="120" t="s">
+        <v>229</v>
+      </c>
+      <c r="J39" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" s="97">
+        <v>3</v>
+      </c>
+      <c r="L39" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="97">
+        <v>3</v>
+      </c>
+      <c r="B40" s="109" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="F40" s="122" t="s">
+        <v>254</v>
+      </c>
+      <c r="G40" s="97">
+        <v>95</v>
+      </c>
+      <c r="H40" s="120" t="s">
+        <v>259</v>
+      </c>
+      <c r="I40" s="120" t="s">
+        <v>263</v>
+      </c>
+      <c r="J40" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K40" s="97" t="s">
+        <v>261</v>
+      </c>
+      <c r="L40" s="139" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="97">
+        <v>3</v>
+      </c>
+      <c r="B41" s="118" t="s">
+        <v>249</v>
+      </c>
+      <c r="C41" s="97" t="s">
+        <v>204</v>
+      </c>
+      <c r="D41" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F41" s="97" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="97">
+        <v>15</v>
+      </c>
+      <c r="H41" s="120" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="120" t="s">
+        <v>252</v>
+      </c>
+      <c r="J41" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K41" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="147" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="110">
+        <v>3</v>
+      </c>
+      <c r="B42" s="123" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="97" t="s">
+      <c r="C42" s="110" t="s">
         <v>204</v>
       </c>
-      <c r="D36" s="114" t="s">
+      <c r="D42" s="123" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="114" t="s">
+      <c r="E42" s="123" t="s">
         <v>220</v>
       </c>
-      <c r="F36" s="97" t="s">
+      <c r="F42" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="G36" s="97">
+      <c r="G42" s="110">
         <v>15</v>
       </c>
-      <c r="H36" s="134" t="s">
+      <c r="H42" s="146" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="134" t="s">
+      <c r="I42" s="146" t="s">
         <v>252</v>
       </c>
-      <c r="J36" s="97" t="s">
+      <c r="J42" s="110" t="s">
         <v>124</v>
       </c>
-      <c r="K36" s="97">
+      <c r="K42" s="110">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="97">
+      <c r="L42" s="110"/>
+    </row>
+    <row r="43" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="97">
+        <v>4</v>
+      </c>
+      <c r="B43" s="118" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" s="97">
+        <v>5</v>
+      </c>
+      <c r="G43" s="97">
+        <v>5</v>
+      </c>
+      <c r="H43" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="I43" s="120" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" s="97" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="97">
+        <v>4</v>
+      </c>
+      <c r="B44" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F44" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G44" s="78">
+        <v>95</v>
+      </c>
+      <c r="H44" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I44" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="K44" s="97">
         <v>3</v>
       </c>
-      <c r="B37" s="132" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="114" t="s">
-        <v>209</v>
-      </c>
-      <c r="D37" s="114" t="s">
+      <c r="L44" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="97">
+        <v>4</v>
+      </c>
+      <c r="B45" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" s="78">
+        <v>95</v>
+      </c>
+      <c r="H45" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I45" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="K45" s="97">
+        <v>3</v>
+      </c>
+      <c r="L45" s="97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="97">
+        <v>4</v>
+      </c>
+      <c r="B46" s="97" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D46" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="114" t="s">
+      <c r="E46" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F37" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" s="114">
-        <v>1.8</v>
-      </c>
-      <c r="H37" s="97" t="s">
-        <v>248</v>
-      </c>
-      <c r="I37" s="134" t="s">
-        <v>248</v>
-      </c>
-      <c r="J37" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="L37" s="97" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="115" customFormat="1" ht="68" x14ac:dyDescent="0.15">
-      <c r="A38" s="115">
-        <v>3</v>
-      </c>
-      <c r="B38" s="137" t="s">
-        <v>210</v>
-      </c>
-      <c r="C38" s="137" t="s">
-        <v>209</v>
-      </c>
-      <c r="D38" s="137" t="s">
+      <c r="F46" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G46" s="97">
+        <v>95</v>
+      </c>
+      <c r="H46" s="120" t="s">
+        <v>279</v>
+      </c>
+      <c r="I46" s="120" t="s">
+        <v>289</v>
+      </c>
+      <c r="K46" s="97">
+        <v>5</v>
+      </c>
+      <c r="L46" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="97">
+        <v>4</v>
+      </c>
+      <c r="B47" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="C47" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="137" t="s">
+      <c r="E47" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F38" s="137" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" s="137">
-        <v>1.8</v>
-      </c>
-      <c r="H38" s="138" t="s">
-        <v>211</v>
-      </c>
-      <c r="I38" s="138" t="s">
-        <v>212</v>
-      </c>
-      <c r="J38" s="115" t="s">
+      <c r="F47" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G47" s="97">
+        <v>95</v>
+      </c>
+      <c r="H47" s="120" t="s">
+        <v>279</v>
+      </c>
+      <c r="I47" s="120" t="s">
+        <v>290</v>
+      </c>
+      <c r="K47" s="97">
+        <v>5</v>
+      </c>
+      <c r="L47" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="97">
+        <v>4</v>
+      </c>
+      <c r="B48" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C48" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D48" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48" s="139" t="s">
+        <v>280</v>
+      </c>
+      <c r="G48" s="97">
+        <v>10</v>
+      </c>
+      <c r="H48" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="I48" s="120" t="s">
+        <v>291</v>
+      </c>
+      <c r="K48" s="97">
+        <v>5</v>
+      </c>
+      <c r="L48" s="97" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="97">
+        <v>4</v>
+      </c>
+      <c r="B49" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D49" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="97">
+        <v>95</v>
+      </c>
+      <c r="H49" s="120" t="s">
+        <v>279</v>
+      </c>
+      <c r="I49" s="120" t="s">
+        <v>293</v>
+      </c>
+      <c r="J49" s="97" t="s">
         <v>214</v>
       </c>
-      <c r="L38" s="115" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B39" s="132"/>
-      <c r="C39" s="97"/>
-      <c r="H39" s="97"/>
-      <c r="I39" s="134"/>
-    </row>
-    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="123"/>
-      <c r="I40" s="134"/>
-    </row>
-    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="123"/>
-      <c r="I41" s="97"/>
-    </row>
-    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="I42" s="97"/>
+      <c r="K49" s="97">
+        <v>5</v>
+      </c>
+      <c r="L49" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="97">
+        <v>4</v>
+      </c>
+      <c r="B50" s="97" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D50" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E50" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F50" s="139" t="s">
+        <v>280</v>
+      </c>
+      <c r="G50" s="97">
+        <v>10</v>
+      </c>
+      <c r="H50" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="I50" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="K50" s="97">
+        <v>5</v>
+      </c>
+      <c r="L50" s="97" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="97">
+        <v>4</v>
+      </c>
+      <c r="B51" s="97" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="148" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="97">
+        <v>95</v>
+      </c>
+      <c r="H51" s="120" t="s">
+        <v>279</v>
+      </c>
+      <c r="I51" s="120" t="s">
+        <v>293</v>
+      </c>
+      <c r="J51" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="K51" s="97">
+        <v>5</v>
+      </c>
+      <c r="L51" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="97">
+        <v>4</v>
+      </c>
+      <c r="B52" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="C52" s="97" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F52" s="97" t="s">
+        <v>294</v>
+      </c>
+      <c r="G52" s="97">
+        <v>0.75</v>
+      </c>
+      <c r="H52" s="120" t="s">
+        <v>288</v>
+      </c>
+      <c r="I52" s="120" t="s">
+        <v>285</v>
+      </c>
+      <c r="J52" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="K52" s="97">
+        <v>5</v>
+      </c>
+      <c r="L52" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="97">
+        <v>4</v>
+      </c>
+      <c r="B53" s="97" t="s">
+        <v>272</v>
+      </c>
+      <c r="C53" s="97" t="s">
+        <v>278</v>
+      </c>
+      <c r="D53" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E53" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53" s="109" t="s">
+        <v>281</v>
+      </c>
+      <c r="G53" s="109">
+        <v>3.5</v>
+      </c>
+      <c r="H53" s="120" t="s">
+        <v>287</v>
+      </c>
+      <c r="I53" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="J53" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="K53" s="97">
+        <v>5</v>
+      </c>
+      <c r="L53" s="97" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="97">
+        <v>4</v>
+      </c>
+      <c r="B54" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="F54" s="139" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" s="97">
+        <v>15</v>
+      </c>
+      <c r="H54" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="I54" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="J54" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="K54" s="97">
+        <v>5</v>
+      </c>
+      <c r="L54" s="97" t="s">
+        <v>283</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1118" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1404772C-210A-D843-A6D9-8467CCCD6661}"/>
+  <xr:revisionPtr revIDLastSave="1119" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369AF6C9-A3DA-ED40-9C05-478744B6F10A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1711,7 +1711,7 @@
     <t>Phase impulse is tracked independently to ensure that ratio data does not represent a drop in force production of the non-injured limb.</t>
   </si>
   <si>
-    <t>0.75s'</t>
+    <t>0.75s</t>
   </si>
 </sst>
 </file>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1119" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369AF6C9-A3DA-ED40-9C05-478744B6F10A}"/>
+  <xr:revisionPtr revIDLastSave="1134" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{948C3A0F-17FB-B443-A068-98C30D05C86D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="297">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1712,6 +1712,12 @@
   </si>
   <si>
     <t>0.75s</t>
+  </si>
+  <si>
+    <t>images/placeholder.jpg</t>
+  </si>
+  <si>
+    <t>image path</t>
   </si>
 </sst>
 </file>
@@ -9153,7 +9159,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -9168,10 +9174,11 @@
     <col min="10" max="10" width="22.33203125" style="97" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="97" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.6640625" style="97" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="96"/>
+    <col min="13" max="13" width="80.83203125" style="97" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="98" t="s">
         <v>182</v>
       </c>
@@ -9208,8 +9215,11 @@
       <c r="L1" s="82" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M1" s="82" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97">
         <v>0</v>
       </c>
@@ -9244,8 +9254,11 @@
         <v>1</v>
       </c>
       <c r="L2" s="81"/>
-    </row>
-    <row r="3" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M2" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="97">
         <v>0</v>
       </c>
@@ -9280,8 +9293,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="81"/>
-    </row>
-    <row r="4" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M3" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="97">
         <v>0</v>
       </c>
@@ -9314,8 +9330,11 @@
       </c>
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
-    </row>
-    <row r="5" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="97">
         <v>0</v>
       </c>
@@ -9352,8 +9371,11 @@
       <c r="L5" s="81" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="97">
         <v>0</v>
       </c>
@@ -9390,8 +9412,11 @@
       <c r="L6" s="81" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="99">
         <v>1</v>
       </c>
@@ -9424,8 +9449,11 @@
       </c>
       <c r="K7" s="99"/>
       <c r="L7" s="99"/>
-    </row>
-    <row r="8" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="97">
         <v>1</v>
       </c>
@@ -9456,8 +9484,11 @@
       <c r="J8" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="97">
         <v>1</v>
       </c>
@@ -9488,8 +9519,11 @@
       <c r="J9" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="97">
         <v>1</v>
       </c>
@@ -9520,8 +9554,11 @@
       <c r="J10" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M10" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -9554,8 +9591,11 @@
       </c>
       <c r="K11" s="99"/>
       <c r="L11" s="99"/>
-    </row>
-    <row r="12" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="97">
         <v>2</v>
       </c>
@@ -9586,8 +9626,11 @@
       <c r="J12" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M12" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="97">
         <v>2</v>
       </c>
@@ -9618,8 +9661,11 @@
       <c r="J13" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="97">
         <v>2</v>
       </c>
@@ -9650,8 +9696,11 @@
       <c r="J14" s="97" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M14" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="97">
         <v>2</v>
       </c>
@@ -9682,8 +9731,11 @@
       <c r="J15" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M15" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="97">
         <v>2</v>
       </c>
@@ -9714,8 +9766,11 @@
       <c r="J16" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="97">
         <v>2</v>
       </c>
@@ -9746,8 +9801,11 @@
       <c r="J17" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="97">
         <v>2</v>
       </c>
@@ -9778,8 +9836,11 @@
       <c r="J18" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="97">
         <v>2</v>
       </c>
@@ -9810,8 +9871,11 @@
       <c r="J19" s="97" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="97">
         <v>2</v>
       </c>
@@ -9842,8 +9906,11 @@
       <c r="J20" s="97" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="97">
         <v>2</v>
       </c>
@@ -9874,8 +9941,11 @@
       <c r="J21" s="97" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="97">
         <v>2</v>
       </c>
@@ -9906,8 +9976,11 @@
       <c r="J22" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="97">
         <v>2</v>
       </c>
@@ -9938,8 +10011,11 @@
       <c r="J23" s="97" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M23" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="97">
         <v>2</v>
       </c>
@@ -9976,8 +10052,11 @@
       <c r="L24" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="97">
         <v>2</v>
       </c>
@@ -10014,8 +10093,11 @@
       <c r="L25" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M25" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="97">
         <v>2</v>
       </c>
@@ -10052,8 +10134,11 @@
       <c r="L26" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M26" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="97">
         <v>2</v>
       </c>
@@ -10090,8 +10175,11 @@
       <c r="L27" s="139" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M27" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="99">
         <v>3</v>
       </c>
@@ -10128,8 +10216,11 @@
       <c r="L28" s="99" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M28" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="97">
         <v>3</v>
       </c>
@@ -10166,8 +10257,11 @@
       <c r="L29" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M29" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="97">
         <v>3</v>
       </c>
@@ -10204,8 +10298,11 @@
       <c r="L30" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M30" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="97">
         <v>3</v>
       </c>
@@ -10239,8 +10336,11 @@
       <c r="K31" s="97">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M31" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="97">
         <v>3</v>
       </c>
@@ -10274,8 +10374,11 @@
       <c r="K32" s="97">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M32" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="80">
         <v>3</v>
       </c>
@@ -10309,8 +10412,11 @@
       <c r="L33" s="80" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M33" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="97">
         <v>3</v>
       </c>
@@ -10344,8 +10450,11 @@
       <c r="L34" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M34" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="97">
         <v>3</v>
       </c>
@@ -10373,8 +10482,11 @@
       <c r="I35" s="102" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M35" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="97">
         <v>3</v>
       </c>
@@ -10402,8 +10514,11 @@
       <c r="I36" s="102" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M36" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="80">
         <v>3</v>
       </c>
@@ -10440,8 +10555,11 @@
       <c r="L37" s="80" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M37" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="97">
         <v>3</v>
       </c>
@@ -10478,8 +10596,11 @@
       <c r="L38" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M38" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="97">
         <v>3</v>
       </c>
@@ -10516,8 +10637,11 @@
       <c r="L39" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M39" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="97">
         <v>3</v>
       </c>
@@ -10554,8 +10678,11 @@
       <c r="L40" s="139" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M40" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="97">
         <v>3</v>
       </c>
@@ -10589,8 +10716,11 @@
       <c r="K41" s="97">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" s="147" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M41" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="147" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="110">
         <v>3</v>
       </c>
@@ -10625,8 +10755,11 @@
         <v>1</v>
       </c>
       <c r="L42" s="110"/>
-    </row>
-    <row r="43" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M42" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="97">
         <v>4</v>
       </c>
@@ -10657,8 +10790,11 @@
       <c r="J43" s="97" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M43" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="97">
         <v>4</v>
       </c>
@@ -10692,8 +10828,11 @@
       <c r="L44" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M44" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="97">
         <v>4</v>
       </c>
@@ -10727,8 +10866,11 @@
       <c r="L45" s="97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M45" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="97">
         <v>4</v>
       </c>
@@ -10762,8 +10904,11 @@
       <c r="L46" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M46" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="97">
         <v>4</v>
       </c>
@@ -10797,8 +10942,11 @@
       <c r="L47" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M47" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="97">
         <v>4</v>
       </c>
@@ -10832,8 +10980,11 @@
       <c r="L48" s="97" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M48" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="97">
         <v>4</v>
       </c>
@@ -10870,8 +11021,11 @@
       <c r="L49" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M49" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="97">
         <v>4</v>
       </c>
@@ -10905,8 +11059,11 @@
       <c r="L50" s="97" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M50" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="97">
         <v>4</v>
       </c>
@@ -10943,8 +11100,11 @@
       <c r="L51" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M51" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="97">
         <v>4</v>
       </c>
@@ -10981,8 +11141,11 @@
       <c r="L52" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M52" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="97">
         <v>4</v>
       </c>
@@ -11019,8 +11182,11 @@
       <c r="L53" s="97" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M53" s="97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="97">
         <v>4</v>
       </c>
@@ -11056,6 +11222,9 @@
       </c>
       <c r="L54" s="97" t="s">
         <v>283</v>
+      </c>
+      <c r="M54" s="97" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1134" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{948C3A0F-17FB-B443-A068-98C30D05C86D}"/>
+  <xr:revisionPtr revIDLastSave="1142" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9114B7D6-E39F-F54B-8B51-8E972EB806F6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="299">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1718,6 +1718,12 @@
   </si>
   <si>
     <t>image path</t>
+  </si>
+  <si>
+    <t>images/testing/slhop.png</t>
+  </si>
+  <si>
+    <t>images/testing/m90hop.png</t>
   </si>
 </sst>
 </file>
@@ -2521,6 +2527,34 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2557,34 +2591,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2839,13 +2845,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2903,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="130" t="s">
+      <c r="G4" s="140" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2936,7 +2942,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="125"/>
+      <c r="G5" s="135"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2964,7 +2970,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="125"/>
+      <c r="G6" s="135"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -2988,7 +2994,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="125"/>
+      <c r="G7" s="135"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3011,7 +3017,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="125"/>
+      <c r="G8" s="135"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3039,7 +3045,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="125"/>
+      <c r="G9" s="135"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3122,13 +3128,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3183,24 +3189,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="126">
+      <c r="H16" s="136">
         <v>45359</v>
       </c>
-      <c r="I16" s="127"/>
-      <c r="J16" s="128">
+      <c r="I16" s="137"/>
+      <c r="J16" s="138">
         <v>47204</v>
       </c>
-      <c r="K16" s="127"/>
-      <c r="L16" s="129" t="s">
+      <c r="K16" s="137"/>
+      <c r="L16" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="127"/>
-      <c r="N16" s="126">
+      <c r="M16" s="137"/>
+      <c r="N16" s="136">
         <v>45429</v>
       </c>
-      <c r="O16" s="127"/>
-      <c r="P16" s="126"/>
-      <c r="Q16" s="127"/>
+      <c r="O16" s="137"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="137"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3274,7 +3280,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="130" t="s">
+      <c r="G18" s="140" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3318,7 +3324,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="125"/>
+      <c r="G19" s="135"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3356,7 +3362,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="125"/>
+      <c r="G20" s="135"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="125"/>
+      <c r="G21" s="135"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3438,7 +3444,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="125"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3476,7 +3482,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="125"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3516,7 +3522,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="125"/>
+      <c r="G24" s="135"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3707,13 +3713,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="124" t="s">
+      <c r="B32" s="134" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="125"/>
+      <c r="C32" s="135"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="135"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3758,12 +3764,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="131" t="s">
+      <c r="H33" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="127"/>
-      <c r="J33" s="126"/>
-      <c r="K33" s="127"/>
+      <c r="I33" s="137"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3788,7 +3794,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="130" t="s">
+      <c r="G34" s="140" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3819,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="125"/>
+      <c r="G35" s="135"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3848,7 +3854,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="125"/>
+      <c r="G36" s="135"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3877,7 +3883,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="125"/>
+      <c r="G37" s="135"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3906,7 +3912,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="125"/>
+      <c r="G38" s="135"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3927,7 +3933,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="125"/>
+      <c r="G39" s="135"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3956,7 +3962,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="125"/>
+      <c r="G40" s="135"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3977,7 +3983,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="125"/>
+      <c r="G41" s="135"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4006,7 +4012,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="125"/>
+      <c r="G42" s="135"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4027,7 +4033,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="125"/>
+      <c r="G43" s="135"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4050,17 +4056,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="132" t="s">
+      <c r="C44" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="132" t="s">
+      <c r="D44" s="142" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="125"/>
+      <c r="G44" s="135"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4075,13 +4081,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
+      <c r="C45" s="135"/>
+      <c r="D45" s="135"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="125"/>
+      <c r="G45" s="135"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4110,7 +4116,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="125"/>
+      <c r="G46" s="135"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4131,7 +4137,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="125"/>
+      <c r="G47" s="135"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4160,7 +4166,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="125"/>
+      <c r="G48" s="135"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4189,7 +4195,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="125"/>
+      <c r="G49" s="135"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4216,7 +4222,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="125"/>
+      <c r="G50" s="135"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4312,10 +4318,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="137">
+      <c r="B54" s="147">
         <v>16</v>
       </c>
-      <c r="C54" s="138" t="s">
+      <c r="C54" s="148" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4336,8 +4342,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="125"/>
-      <c r="C55" s="125"/>
+      <c r="B55" s="135"/>
+      <c r="C55" s="135"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4356,10 +4362,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="133">
+      <c r="B56" s="143">
         <v>17</v>
       </c>
-      <c r="C56" s="135" t="s">
+      <c r="C56" s="145" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4381,8 +4387,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="134"/>
-      <c r="C57" s="136"/>
+      <c r="B57" s="144"/>
+      <c r="C57" s="146"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4402,10 +4408,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="137">
+      <c r="B58" s="147">
         <v>18</v>
       </c>
-      <c r="C58" s="138" t="s">
+      <c r="C58" s="148" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4426,8 +4432,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="125"/>
-      <c r="C59" s="125"/>
+      <c r="B59" s="135"/>
+      <c r="C59" s="135"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4446,10 +4452,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="133">
+      <c r="B60" s="143">
         <v>19</v>
       </c>
-      <c r="C60" s="135" t="s">
+      <c r="C60" s="145" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4471,8 +4477,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="136"/>
+      <c r="B61" s="144"/>
+      <c r="C61" s="146"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4492,7 +4498,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="137">
+      <c r="B62" s="147">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4516,7 +4522,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="125"/>
+      <c r="B63" s="135"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4692,13 +4698,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="124" t="s">
+      <c r="B74" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="125"/>
-      <c r="D74" s="125"/>
-      <c r="E74" s="125"/>
-      <c r="F74" s="125"/>
+      <c r="C74" s="135"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4777,7 +4783,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="130" t="s">
+      <c r="G76" s="140" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4804,7 +4810,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="125"/>
+      <c r="G77" s="135"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4829,7 +4835,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="125"/>
+      <c r="G78" s="135"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4856,7 +4862,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="125"/>
+      <c r="G79" s="135"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4888,7 +4894,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="125"/>
+      <c r="G80" s="135"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4917,7 +4923,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="125"/>
+      <c r="G81" s="135"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4946,7 +4952,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="125"/>
+      <c r="G82" s="135"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4975,7 +4981,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="125"/>
+      <c r="G83" s="135"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5004,7 +5010,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="125"/>
+      <c r="G84" s="135"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5033,7 +5039,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="125"/>
+      <c r="G85" s="135"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5062,7 +5068,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="125"/>
+      <c r="G86" s="135"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5091,7 +5097,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="125"/>
+      <c r="G87" s="135"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -9223,7 +9229,7 @@
       <c r="A2" s="97">
         <v>0</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="125" t="s">
         <v>146</v>
       </c>
       <c r="C2" s="97" t="s">
@@ -9262,7 +9268,7 @@
       <c r="A3" s="97">
         <v>0</v>
       </c>
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="125" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="97" t="s">
@@ -9301,7 +9307,7 @@
       <c r="A4" s="97">
         <v>0</v>
       </c>
-      <c r="B4" s="140" t="s">
+      <c r="B4" s="125" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="97" t="s">
@@ -9338,7 +9344,7 @@
       <c r="A5" s="97">
         <v>0</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="125" t="s">
         <v>155</v>
       </c>
       <c r="C5" s="97" t="s">
@@ -9379,7 +9385,7 @@
       <c r="A6" s="97">
         <v>0</v>
       </c>
-      <c r="B6" s="140" t="s">
+      <c r="B6" s="125" t="s">
         <v>156</v>
       </c>
       <c r="C6" s="97" t="s">
@@ -9420,7 +9426,7 @@
       <c r="A7" s="99">
         <v>1</v>
       </c>
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="126" t="s">
         <v>146</v>
       </c>
       <c r="C7" s="99" t="s">
@@ -9457,7 +9463,7 @@
       <c r="A8" s="97">
         <v>1</v>
       </c>
-      <c r="B8" s="140" t="s">
+      <c r="B8" s="125" t="s">
         <v>147</v>
       </c>
       <c r="C8" s="97" t="s">
@@ -9492,7 +9498,7 @@
       <c r="A9" s="97">
         <v>1</v>
       </c>
-      <c r="B9" s="140" t="s">
+      <c r="B9" s="125" t="s">
         <v>176</v>
       </c>
       <c r="C9" s="97" t="s">
@@ -9562,7 +9568,7 @@
       <c r="A11" s="99">
         <v>2</v>
       </c>
-      <c r="B11" s="141" t="s">
+      <c r="B11" s="126" t="s">
         <v>146</v>
       </c>
       <c r="C11" s="99" t="s">
@@ -9599,7 +9605,7 @@
       <c r="A12" s="97">
         <v>2</v>
       </c>
-      <c r="B12" s="140" t="s">
+      <c r="B12" s="125" t="s">
         <v>147</v>
       </c>
       <c r="C12" s="97" t="s">
@@ -9634,7 +9640,7 @@
       <c r="A13" s="97">
         <v>2</v>
       </c>
-      <c r="B13" s="140" t="s">
+      <c r="B13" s="125" t="s">
         <v>176</v>
       </c>
       <c r="C13" s="97" t="s">
@@ -9669,7 +9675,7 @@
       <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="127" t="s">
         <v>115</v>
       </c>
       <c r="C14" s="109" t="s">
@@ -9722,10 +9728,10 @@
       <c r="G15" s="109">
         <v>20</v>
       </c>
-      <c r="H15" s="144" t="s">
+      <c r="H15" s="129" t="s">
         <v>196</v>
       </c>
-      <c r="I15" s="144" t="s">
+      <c r="I15" s="129" t="s">
         <v>197</v>
       </c>
       <c r="J15" s="97" t="s">
@@ -9739,10 +9745,10 @@
       <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="127" t="s">
         <v>190</v>
       </c>
       <c r="D16" s="78" t="s">
@@ -9757,10 +9763,10 @@
       <c r="G16" s="109">
         <v>20</v>
       </c>
-      <c r="H16" s="143" t="s">
+      <c r="H16" s="128" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="144" t="s">
+      <c r="I16" s="129" t="s">
         <v>197</v>
       </c>
       <c r="J16" s="97" t="s">
@@ -9792,10 +9798,10 @@
       <c r="G17" s="109">
         <v>30</v>
       </c>
-      <c r="H17" s="144" t="s">
+      <c r="H17" s="129" t="s">
         <v>201</v>
       </c>
-      <c r="I17" s="144" t="s">
+      <c r="I17" s="129" t="s">
         <v>198</v>
       </c>
       <c r="J17" s="97" t="s">
@@ -9809,10 +9815,10 @@
       <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="143" t="s">
+      <c r="B18" s="128" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="128" t="s">
         <v>190</v>
       </c>
       <c r="D18" s="78" t="s">
@@ -9827,10 +9833,10 @@
       <c r="G18" s="109">
         <v>10</v>
       </c>
-      <c r="H18" s="143" t="s">
+      <c r="H18" s="128" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="144" t="s">
+      <c r="I18" s="129" t="s">
         <v>199</v>
       </c>
       <c r="J18" s="97" t="s">
@@ -9862,10 +9868,10 @@
       <c r="G19" s="109">
         <v>1.5</v>
       </c>
-      <c r="H19" s="144" t="s">
+      <c r="H19" s="129" t="s">
         <v>211</v>
       </c>
-      <c r="I19" s="144" t="s">
+      <c r="I19" s="129" t="s">
         <v>212</v>
       </c>
       <c r="J19" s="97" t="s">
@@ -9879,7 +9885,7 @@
       <c r="A20" s="97">
         <v>2</v>
       </c>
-      <c r="B20" s="140" t="s">
+      <c r="B20" s="125" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="80" t="s">
@@ -9914,7 +9920,7 @@
       <c r="A21" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="140" t="s">
+      <c r="B21" s="125" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="80" t="s">
@@ -9967,10 +9973,10 @@
       <c r="G22" s="109">
         <v>45</v>
       </c>
-      <c r="H22" s="144" t="s">
+      <c r="H22" s="129" t="s">
         <v>205</v>
       </c>
-      <c r="I22" s="144" t="s">
+      <c r="I22" s="129" t="s">
         <v>207</v>
       </c>
       <c r="J22" s="97" t="s">
@@ -10002,10 +10008,10 @@
       <c r="G23" s="109">
         <v>9</v>
       </c>
-      <c r="H23" s="144" t="s">
+      <c r="H23" s="129" t="s">
         <v>206</v>
       </c>
-      <c r="I23" s="144" t="s">
+      <c r="I23" s="129" t="s">
         <v>208</v>
       </c>
       <c r="J23" s="97" t="s">
@@ -10172,7 +10178,7 @@
       <c r="K27" s="97" t="s">
         <v>261</v>
       </c>
-      <c r="L27" s="139" t="s">
+      <c r="L27" s="124" t="s">
         <v>260</v>
       </c>
       <c r="M27" s="97" t="s">
@@ -10217,7 +10223,7 @@
         <v>236</v>
       </c>
       <c r="M28" s="97" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10258,7 +10264,7 @@
         <v>236</v>
       </c>
       <c r="M29" s="97" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10400,10 +10406,10 @@
       <c r="G33" s="109">
         <v>1.8</v>
       </c>
-      <c r="H33" s="144" t="s">
+      <c r="H33" s="129" t="s">
         <v>211</v>
       </c>
-      <c r="I33" s="144" t="s">
+      <c r="I33" s="129" t="s">
         <v>212</v>
       </c>
       <c r="J33" s="80" t="s">
@@ -10458,7 +10464,7 @@
       <c r="A35" s="97">
         <v>3</v>
       </c>
-      <c r="B35" s="140" t="s">
+      <c r="B35" s="125" t="s">
         <v>155</v>
       </c>
       <c r="C35" s="80" t="s">
@@ -10470,7 +10476,7 @@
       <c r="E35" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F35" s="148" t="s">
+      <c r="F35" s="133" t="s">
         <v>223</v>
       </c>
       <c r="G35" s="78">
@@ -10490,7 +10496,7 @@
       <c r="A36" s="97">
         <v>3</v>
       </c>
-      <c r="B36" s="140" t="s">
+      <c r="B36" s="125" t="s">
         <v>156</v>
       </c>
       <c r="C36" s="80" t="s">
@@ -10502,7 +10508,7 @@
       <c r="E36" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F36" s="148" t="s">
+      <c r="F36" s="133" t="s">
         <v>223</v>
       </c>
       <c r="G36" s="78">
@@ -10534,7 +10540,7 @@
       <c r="E37" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="F37" s="145" t="s">
+      <c r="F37" s="130" t="s">
         <v>254</v>
       </c>
       <c r="G37" s="80">
@@ -10675,7 +10681,7 @@
       <c r="K40" s="97" t="s">
         <v>261</v>
       </c>
-      <c r="L40" s="139" t="s">
+      <c r="L40" s="124" t="s">
         <v>260</v>
       </c>
       <c r="M40" s="97" t="s">
@@ -10720,7 +10726,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="147" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="110">
         <v>3</v>
       </c>
@@ -10742,10 +10748,10 @@
       <c r="G42" s="110">
         <v>15</v>
       </c>
-      <c r="H42" s="146" t="s">
+      <c r="H42" s="131" t="s">
         <v>251</v>
       </c>
-      <c r="I42" s="146" t="s">
+      <c r="I42" s="131" t="s">
         <v>252</v>
       </c>
       <c r="J42" s="110" t="s">
@@ -10798,7 +10804,7 @@
       <c r="A44" s="97">
         <v>4</v>
       </c>
-      <c r="B44" s="140" t="s">
+      <c r="B44" s="125" t="s">
         <v>155</v>
       </c>
       <c r="C44" s="80" t="s">
@@ -10810,7 +10816,7 @@
       <c r="E44" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F44" s="148" t="s">
+      <c r="F44" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G44" s="78">
@@ -10836,7 +10842,7 @@
       <c r="A45" s="97">
         <v>4</v>
       </c>
-      <c r="B45" s="140" t="s">
+      <c r="B45" s="125" t="s">
         <v>156</v>
       </c>
       <c r="C45" s="80" t="s">
@@ -10848,7 +10854,7 @@
       <c r="E45" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F45" s="148" t="s">
+      <c r="F45" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G45" s="78">
@@ -10886,7 +10892,7 @@
       <c r="E46" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F46" s="148" t="s">
+      <c r="F46" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G46" s="97">
@@ -10924,7 +10930,7 @@
       <c r="E47" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F47" s="148" t="s">
+      <c r="F47" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G47" s="97">
@@ -10962,7 +10968,7 @@
       <c r="E48" s="97" t="s">
         <v>224</v>
       </c>
-      <c r="F48" s="139" t="s">
+      <c r="F48" s="124" t="s">
         <v>280</v>
       </c>
       <c r="G48" s="97">
@@ -11000,7 +11006,7 @@
       <c r="E49" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F49" s="148" t="s">
+      <c r="F49" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G49" s="97">
@@ -11041,7 +11047,7 @@
       <c r="E50" s="97" t="s">
         <v>224</v>
       </c>
-      <c r="F50" s="139" t="s">
+      <c r="F50" s="124" t="s">
         <v>280</v>
       </c>
       <c r="G50" s="97">
@@ -11079,7 +11085,7 @@
       <c r="E51" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="F51" s="148" t="s">
+      <c r="F51" s="133" t="s">
         <v>254</v>
       </c>
       <c r="G51" s="97">
@@ -11202,7 +11208,7 @@
       <c r="E54" s="97" t="s">
         <v>224</v>
       </c>
-      <c r="F54" s="139" t="s">
+      <c r="F54" s="124" t="s">
         <v>282</v>
       </c>
       <c r="G54" s="97">

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1142" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9114B7D6-E39F-F54B-8B51-8E972EB806F6}"/>
+  <xr:revisionPtr revIDLastSave="1146" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98DA8CD-4126-3C4B-8FC3-FED6A8E41E51}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="300">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1385,9 +1385,6 @@
   </si>
   <si>
     <t>Y-Balance (Postero-Lateral)</t>
-  </si>
-  <si>
-    <t>﻿Subjects lie supine on the floor with one heel on a 60cm (~24") high box. The knee of the test leg is slightly bent at 20° and opposite leg is bent to 90° hip and knee flexion with their arms crossed over chest. Subjects elevate the hips as high as possible and the assessor places a target at this height. Repeat this action as many times as possible touching the target each time. The test concludes when the subject is unable to bridge to the target ﻿(Freckleton et al, 2013).</t>
   </si>
   <si>
     <t>Input the number of reps completed.  The goal is &gt;20 reps and injured leg reps &gt;85% of un-injured leg.</t>
@@ -1723,7 +1720,13 @@
     <t>images/testing/slhop.png</t>
   </si>
   <si>
-    <t>images/testing/m90hop.png</t>
+    <t>images/testing/triplehop.png</t>
+  </si>
+  <si>
+    <t>images/testing/sidehop.png</t>
+  </si>
+  <si>
+    <t>﻿Subjects lie supine on the floor with one heel on a 60cm (~24") high box. The knee of the test leg is slightly bent at 20° and opposite leg is bent to 90° hip and knee flexion with their arms crossed over chest. Subjects elevate the hips as high as possible and the assessor places a target at this height. Repeat this action as many times as possible touching the target each time. The test concludes when the subject is unable to bridge to the target [@freckleton2013].</t>
   </si>
 </sst>
 </file>
@@ -2555,28 +2558,21 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2586,11 +2582,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2845,7 +2848,7 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="136" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="135"/>
@@ -2909,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="140" t="s">
+      <c r="G4" s="137" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3128,7 +3131,7 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="134" t="s">
+      <c r="B15" s="136" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="135"/>
@@ -3189,24 +3192,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="136">
+      <c r="H16" s="146">
         <v>45359</v>
       </c>
-      <c r="I16" s="137"/>
-      <c r="J16" s="138">
+      <c r="I16" s="145"/>
+      <c r="J16" s="147">
         <v>47204</v>
       </c>
-      <c r="K16" s="137"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="145"/>
+      <c r="L16" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="137"/>
-      <c r="N16" s="136">
+      <c r="M16" s="145"/>
+      <c r="N16" s="146">
         <v>45429</v>
       </c>
-      <c r="O16" s="137"/>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="137"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="145"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3280,7 +3283,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="140" t="s">
+      <c r="G18" s="137" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3713,7 +3716,7 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="134" t="s">
+      <c r="B32" s="136" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="135"/>
@@ -3764,12 +3767,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="141" t="s">
+      <c r="H33" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="137"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="137"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="145"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3794,7 +3797,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="140" t="s">
+      <c r="G34" s="137" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -4056,10 +4059,10 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="138" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="142" t="s">
+      <c r="D44" s="138" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
@@ -4318,10 +4321,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="147">
+      <c r="B54" s="134">
         <v>16</v>
       </c>
-      <c r="C54" s="148" t="s">
+      <c r="C54" s="139" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4362,10 +4365,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="143">
+      <c r="B56" s="140">
         <v>17</v>
       </c>
-      <c r="C56" s="145" t="s">
+      <c r="C56" s="142" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4387,8 +4390,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="144"/>
-      <c r="C57" s="146"/>
+      <c r="B57" s="141"/>
+      <c r="C57" s="143"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4408,10 +4411,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="147">
+      <c r="B58" s="134">
         <v>18</v>
       </c>
-      <c r="C58" s="148" t="s">
+      <c r="C58" s="139" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4452,10 +4455,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="143">
+      <c r="B60" s="140">
         <v>19</v>
       </c>
-      <c r="C60" s="145" t="s">
+      <c r="C60" s="142" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4477,8 +4480,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="144"/>
-      <c r="C61" s="146"/>
+      <c r="B61" s="141"/>
+      <c r="C61" s="143"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4498,7 +4501,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="147">
+      <c r="B62" s="134">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4698,7 +4701,7 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="134" t="s">
+      <c r="B74" s="136" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="135"/>
@@ -4783,7 +4786,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="140" t="s">
+      <c r="G76" s="137" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -8843,6 +8846,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8853,22 +8872,6 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9195,13 +9198,13 @@
         <v>183</v>
       </c>
       <c r="D1" s="98" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E1" s="98" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F1" s="98" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G1" s="98" t="s">
         <v>145</v>
@@ -9222,7 +9225,7 @@
         <v>166</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9239,7 +9242,7 @@
         <v>172</v>
       </c>
       <c r="E2" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F2" s="78" t="s">
         <v>8</v>
@@ -9261,7 +9264,7 @@
       </c>
       <c r="L2" s="81"/>
       <c r="M2" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9278,7 +9281,7 @@
         <v>153</v>
       </c>
       <c r="E3" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F3" s="78" t="s">
         <v>151</v>
@@ -9300,7 +9303,7 @@
       </c>
       <c r="L3" s="81"/>
       <c r="M3" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9317,7 +9320,7 @@
         <v>172</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F4" s="78">
         <v>1</v>
@@ -9337,7 +9340,7 @@
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
       <c r="M4" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9357,7 +9360,7 @@
         <v>159</v>
       </c>
       <c r="F5" s="105" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G5" s="78">
         <v>90</v>
@@ -9378,7 +9381,7 @@
         <v>170</v>
       </c>
       <c r="M5" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9398,7 +9401,7 @@
         <v>159</v>
       </c>
       <c r="F6" s="108" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G6" s="106">
         <v>90</v>
@@ -9419,7 +9422,7 @@
         <v>170</v>
       </c>
       <c r="M6" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9436,7 +9439,7 @@
         <v>172</v>
       </c>
       <c r="E7" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F7" s="78" t="s">
         <v>8</v>
@@ -9456,7 +9459,7 @@
       <c r="K7" s="99"/>
       <c r="L7" s="99"/>
       <c r="M7" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9473,7 +9476,7 @@
         <v>153</v>
       </c>
       <c r="E8" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F8" s="78" t="s">
         <v>151</v>
@@ -9491,7 +9494,7 @@
         <v>124</v>
       </c>
       <c r="M8" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9508,7 +9511,7 @@
         <v>172</v>
       </c>
       <c r="E9" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F9" s="78">
         <v>1</v>
@@ -9526,7 +9529,7 @@
         <v>124</v>
       </c>
       <c r="M9" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9540,10 +9543,10 @@
         <v>189</v>
       </c>
       <c r="D10" s="110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E10" s="110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F10" s="110">
         <v>5</v>
@@ -9561,7 +9564,7 @@
         <v>124</v>
       </c>
       <c r="M10" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9578,7 +9581,7 @@
         <v>172</v>
       </c>
       <c r="E11" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F11" s="78" t="s">
         <v>8</v>
@@ -9598,7 +9601,7 @@
       <c r="K11" s="99"/>
       <c r="L11" s="99"/>
       <c r="M11" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9615,7 +9618,7 @@
         <v>153</v>
       </c>
       <c r="E12" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F12" s="78" t="s">
         <v>151</v>
@@ -9633,7 +9636,7 @@
         <v>124</v>
       </c>
       <c r="M12" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9650,7 +9653,7 @@
         <v>172</v>
       </c>
       <c r="E13" s="103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F13" s="78">
         <v>0</v>
@@ -9668,7 +9671,7 @@
         <v>124</v>
       </c>
       <c r="M13" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9685,25 +9688,25 @@
         <v>153</v>
       </c>
       <c r="E14" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F14" s="109" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G14" s="109">
         <v>10</v>
       </c>
       <c r="H14" s="112" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="102" t="s">
         <v>216</v>
       </c>
-      <c r="I14" s="102" t="s">
-        <v>217</v>
-      </c>
       <c r="J14" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M14" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9720,25 +9723,25 @@
         <v>153</v>
       </c>
       <c r="E15" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F15" s="109" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G15" s="109">
         <v>20</v>
       </c>
       <c r="H15" s="129" t="s">
+        <v>299</v>
+      </c>
+      <c r="I15" s="129" t="s">
         <v>196</v>
-      </c>
-      <c r="I15" s="129" t="s">
-        <v>197</v>
       </c>
       <c r="J15" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M15" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9755,7 +9758,7 @@
         <v>153</v>
       </c>
       <c r="E16" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F16" s="109">
         <v>20</v>
@@ -9764,16 +9767,16 @@
         <v>20</v>
       </c>
       <c r="H16" s="128" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I16" s="129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J16" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M16" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9784,31 +9787,31 @@
         <v>84</v>
       </c>
       <c r="C17" s="109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D17" s="78" t="s">
         <v>153</v>
       </c>
       <c r="E17" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F17" s="109" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G17" s="109">
         <v>30</v>
       </c>
       <c r="H17" s="129" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I17" s="129" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J17" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M17" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9816,7 +9819,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="128" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C18" s="128" t="s">
         <v>190</v>
@@ -9825,7 +9828,7 @@
         <v>153</v>
       </c>
       <c r="E18" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F18" s="109">
         <v>10</v>
@@ -9834,16 +9837,16 @@
         <v>10</v>
       </c>
       <c r="H18" s="128" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I18" s="129" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J18" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M18" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9851,16 +9854,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="118" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D19" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E19" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F19" s="109" t="s">
         <v>96</v>
@@ -9869,16 +9872,16 @@
         <v>1.5</v>
       </c>
       <c r="H19" s="129" t="s">
+        <v>210</v>
+      </c>
+      <c r="I19" s="129" t="s">
         <v>211</v>
       </c>
-      <c r="I19" s="129" t="s">
-        <v>212</v>
-      </c>
       <c r="J19" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M19" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9898,7 +9901,7 @@
         <v>159</v>
       </c>
       <c r="F20" s="111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G20" s="78">
         <v>75</v>
@@ -9907,13 +9910,13 @@
         <v>157</v>
       </c>
       <c r="I20" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J20" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M20" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9933,7 +9936,7 @@
         <v>159</v>
       </c>
       <c r="F21" s="111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G21" s="78">
         <v>75</v>
@@ -9942,13 +9945,13 @@
         <v>157</v>
       </c>
       <c r="I21" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J21" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M21" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9956,34 +9959,34 @@
         <v>2</v>
       </c>
       <c r="B22" s="118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" s="109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D22" s="78" t="s">
         <v>153</v>
       </c>
       <c r="E22" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F22" s="109" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G22" s="109">
         <v>45</v>
       </c>
       <c r="H22" s="129" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I22" s="129" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J22" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M22" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9991,16 +9994,16 @@
         <v>2</v>
       </c>
       <c r="B23" s="118" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D23" s="78" t="s">
         <v>153</v>
       </c>
       <c r="E23" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F23" s="109">
         <v>9</v>
@@ -10009,16 +10012,16 @@
         <v>9</v>
       </c>
       <c r="H23" s="129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I23" s="129" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J23" s="97" t="s">
         <v>124</v>
       </c>
       <c r="M23" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10038,19 +10041,19 @@
         <v>159</v>
       </c>
       <c r="F24" s="111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G24" s="78">
         <v>75</v>
       </c>
       <c r="H24" s="120" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I24" s="120" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J24" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K24" s="97">
         <v>3</v>
@@ -10059,7 +10062,7 @@
         <v>170</v>
       </c>
       <c r="M24" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10079,19 +10082,19 @@
         <v>159</v>
       </c>
       <c r="F25" s="111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G25" s="78">
         <v>75</v>
       </c>
       <c r="H25" s="120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I25" s="120" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J25" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K25" s="97">
         <v>3</v>
@@ -10100,7 +10103,7 @@
         <v>170</v>
       </c>
       <c r="M25" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10120,19 +10123,19 @@
         <v>159</v>
       </c>
       <c r="F26" s="111" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G26" s="78">
         <v>75</v>
       </c>
       <c r="H26" s="120" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I26" s="120" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J26" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K26" s="97">
         <v>3</v>
@@ -10141,7 +10144,7 @@
         <v>170</v>
       </c>
       <c r="M26" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10158,31 +10161,31 @@
         <v>153</v>
       </c>
       <c r="E27" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F27" s="122" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G27" s="97">
         <v>75</v>
       </c>
       <c r="H27" s="120" t="s">
+        <v>258</v>
+      </c>
+      <c r="I27" s="120" t="s">
+        <v>262</v>
+      </c>
+      <c r="J27" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="L27" s="124" t="s">
         <v>259</v>
       </c>
-      <c r="I27" s="120" t="s">
-        <v>263</v>
-      </c>
-      <c r="J27" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K27" s="97" t="s">
-        <v>261</v>
-      </c>
-      <c r="L27" s="124" t="s">
-        <v>260</v>
-      </c>
       <c r="M27" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10190,7 +10193,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="116" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" s="99" t="s">
         <v>187</v>
@@ -10199,19 +10202,19 @@
         <v>153</v>
       </c>
       <c r="E28" s="115" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F28" s="121" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G28" s="99">
         <v>95</v>
       </c>
       <c r="H28" s="117" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="117" t="s">
         <v>237</v>
-      </c>
-      <c r="I28" s="117" t="s">
-        <v>238</v>
       </c>
       <c r="J28" s="99" t="s">
         <v>124</v>
@@ -10220,10 +10223,10 @@
         <v>2</v>
       </c>
       <c r="L28" s="99" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M28" s="97" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10231,7 +10234,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="118" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="97" t="s">
         <v>187</v>
@@ -10240,19 +10243,19 @@
         <v>153</v>
       </c>
       <c r="E29" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F29" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G29" s="97">
         <v>95</v>
       </c>
       <c r="H29" s="119" t="s">
+        <v>239</v>
+      </c>
+      <c r="I29" s="120" t="s">
         <v>240</v>
-      </c>
-      <c r="I29" s="120" t="s">
-        <v>241</v>
       </c>
       <c r="J29" s="97" t="s">
         <v>124</v>
@@ -10261,10 +10264,10 @@
         <v>2</v>
       </c>
       <c r="L29" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M29" s="97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10272,7 +10275,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="97" t="s">
         <v>187</v>
@@ -10281,19 +10284,19 @@
         <v>153</v>
       </c>
       <c r="E30" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F30" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G30" s="97">
         <v>95</v>
       </c>
       <c r="H30" s="119" t="s">
+        <v>241</v>
+      </c>
+      <c r="I30" s="120" t="s">
         <v>242</v>
-      </c>
-      <c r="I30" s="120" t="s">
-        <v>243</v>
       </c>
       <c r="J30" s="97" t="s">
         <v>124</v>
@@ -10302,10 +10305,10 @@
         <v>2</v>
       </c>
       <c r="L30" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M30" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10313,7 +10316,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="118" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="97" t="s">
         <v>190</v>
@@ -10322,19 +10325,19 @@
         <v>153</v>
       </c>
       <c r="E31" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F31" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G31" s="97">
         <v>95</v>
       </c>
       <c r="H31" s="119" t="s">
+        <v>243</v>
+      </c>
+      <c r="I31" s="120" t="s">
         <v>244</v>
-      </c>
-      <c r="I31" s="120" t="s">
-        <v>245</v>
       </c>
       <c r="J31" s="97" t="s">
         <v>124</v>
@@ -10343,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="97" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10351,7 +10354,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="118" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C32" s="97" t="s">
         <v>190</v>
@@ -10360,7 +10363,7 @@
         <v>153</v>
       </c>
       <c r="E32" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F32" s="97">
         <v>22</v>
@@ -10369,10 +10372,10 @@
         <v>22</v>
       </c>
       <c r="H32" s="120" t="s">
+        <v>245</v>
+      </c>
+      <c r="I32" s="120" t="s">
         <v>246</v>
-      </c>
-      <c r="I32" s="120" t="s">
-        <v>247</v>
       </c>
       <c r="J32" s="97" t="s">
         <v>124</v>
@@ -10381,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10389,16 +10392,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="109" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C33" s="109" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D33" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E33" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F33" s="109" t="s">
         <v>140</v>
@@ -10407,19 +10410,19 @@
         <v>1.8</v>
       </c>
       <c r="H33" s="129" t="s">
+        <v>210</v>
+      </c>
+      <c r="I33" s="129" t="s">
         <v>211</v>
       </c>
-      <c r="I33" s="129" t="s">
-        <v>212</v>
-      </c>
       <c r="J33" s="80" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L33" s="80" t="s">
         <v>170</v>
       </c>
       <c r="M33" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10430,13 +10433,13 @@
         <v>139</v>
       </c>
       <c r="C34" s="109" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D34" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F34" s="109" t="s">
         <v>140</v>
@@ -10445,10 +10448,10 @@
         <v>1.8</v>
       </c>
       <c r="H34" s="120" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I34" s="120" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J34" s="97" t="s">
         <v>124</v>
@@ -10457,7 +10460,7 @@
         <v>170</v>
       </c>
       <c r="M34" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10477,7 +10480,7 @@
         <v>159</v>
       </c>
       <c r="F35" s="133" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G35" s="78">
         <v>90</v>
@@ -10486,10 +10489,10 @@
         <v>157</v>
       </c>
       <c r="I35" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M35" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10509,7 +10512,7 @@
         <v>159</v>
       </c>
       <c r="F36" s="133" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G36" s="78">
         <v>90</v>
@@ -10518,10 +10521,10 @@
         <v>157</v>
       </c>
       <c r="I36" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M36" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10538,22 +10541,22 @@
         <v>153</v>
       </c>
       <c r="E37" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F37" s="130" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G37" s="80">
         <v>95</v>
       </c>
       <c r="H37" s="83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I37" s="83" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J37" s="80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K37" s="80">
         <v>3</v>
@@ -10562,7 +10565,7 @@
         <v>170</v>
       </c>
       <c r="M37" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10579,22 +10582,22 @@
         <v>153</v>
       </c>
       <c r="E38" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F38" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G38" s="97">
         <v>95</v>
       </c>
       <c r="H38" s="120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I38" s="120" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J38" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K38" s="97">
         <v>3</v>
@@ -10603,7 +10606,7 @@
         <v>170</v>
       </c>
       <c r="M38" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10620,22 +10623,22 @@
         <v>153</v>
       </c>
       <c r="E39" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F39" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G39" s="97">
         <v>95</v>
       </c>
       <c r="H39" s="120" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I39" s="120" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J39" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K39" s="97">
         <v>3</v>
@@ -10644,7 +10647,7 @@
         <v>170</v>
       </c>
       <c r="M39" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10661,31 +10664,31 @@
         <v>153</v>
       </c>
       <c r="E40" s="104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F40" s="122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G40" s="97">
         <v>95</v>
       </c>
       <c r="H40" s="120" t="s">
+        <v>258</v>
+      </c>
+      <c r="I40" s="120" t="s">
+        <v>262</v>
+      </c>
+      <c r="J40" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="K40" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="L40" s="124" t="s">
         <v>259</v>
       </c>
-      <c r="I40" s="120" t="s">
-        <v>263</v>
-      </c>
-      <c r="J40" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K40" s="97" t="s">
-        <v>261</v>
-      </c>
-      <c r="L40" s="124" t="s">
-        <v>260</v>
-      </c>
       <c r="M40" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10693,28 +10696,28 @@
         <v>3</v>
       </c>
       <c r="B41" s="118" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C41" s="97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D41" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E41" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F41" s="97" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G41" s="97">
         <v>15</v>
       </c>
       <c r="H41" s="120" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I41" s="120" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J41" s="97" t="s">
         <v>124</v>
@@ -10723,7 +10726,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10731,28 +10734,28 @@
         <v>3</v>
       </c>
       <c r="B42" s="123" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C42" s="110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D42" s="123" t="s">
         <v>153</v>
       </c>
       <c r="E42" s="123" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F42" s="110" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G42" s="110">
         <v>15</v>
       </c>
       <c r="H42" s="131" t="s">
+        <v>250</v>
+      </c>
+      <c r="I42" s="131" t="s">
         <v>251</v>
-      </c>
-      <c r="I42" s="131" t="s">
-        <v>252</v>
       </c>
       <c r="J42" s="110" t="s">
         <v>124</v>
@@ -10762,7 +10765,7 @@
       </c>
       <c r="L42" s="110"/>
       <c r="M42" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10770,7 +10773,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="118" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C43" s="97" t="s">
         <v>190</v>
@@ -10779,7 +10782,7 @@
         <v>153</v>
       </c>
       <c r="E43" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F43" s="97">
         <v>5</v>
@@ -10788,16 +10791,16 @@
         <v>5</v>
       </c>
       <c r="H43" s="120" t="s">
+        <v>263</v>
+      </c>
+      <c r="I43" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="I43" s="120" t="s">
-        <v>265</v>
-      </c>
       <c r="J43" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M43" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10817,7 +10820,7 @@
         <v>159</v>
       </c>
       <c r="F44" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G44" s="78">
         <v>95</v>
@@ -10826,7 +10829,7 @@
         <v>157</v>
       </c>
       <c r="I44" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K44" s="97">
         <v>3</v>
@@ -10835,7 +10838,7 @@
         <v>170</v>
       </c>
       <c r="M44" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10855,7 +10858,7 @@
         <v>159</v>
       </c>
       <c r="F45" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G45" s="78">
         <v>95</v>
@@ -10864,7 +10867,7 @@
         <v>157</v>
       </c>
       <c r="I45" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K45" s="97">
         <v>3</v>
@@ -10873,7 +10876,7 @@
         <v>170</v>
       </c>
       <c r="M45" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10881,7 +10884,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="97" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C46" s="97" t="s">
         <v>187</v>
@@ -10890,28 +10893,28 @@
         <v>153</v>
       </c>
       <c r="E46" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F46" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G46" s="97">
         <v>95</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K46" s="97">
         <v>5</v>
       </c>
       <c r="L46" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M46" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10919,37 +10922,37 @@
         <v>4</v>
       </c>
       <c r="B47" s="97" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C47" s="97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D47" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F47" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G47" s="97">
         <v>95</v>
       </c>
       <c r="H47" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I47" s="120" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K47" s="97">
         <v>5</v>
       </c>
       <c r="L47" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M47" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10957,37 +10960,37 @@
         <v>4</v>
       </c>
       <c r="B48" s="97" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C48" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D48" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E48" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F48" s="124" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G48" s="97">
         <v>10</v>
       </c>
       <c r="H48" s="120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I48" s="120" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K48" s="97">
         <v>5</v>
       </c>
       <c r="L48" s="97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M48" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10995,40 +10998,40 @@
         <v>4</v>
       </c>
       <c r="B49" s="97" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C49" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D49" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E49" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F49" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G49" s="97">
         <v>95</v>
       </c>
       <c r="H49" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I49" s="120" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J49" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K49" s="97">
         <v>5</v>
       </c>
       <c r="L49" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M49" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11036,37 +11039,37 @@
         <v>4</v>
       </c>
       <c r="B50" s="97" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C50" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D50" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F50" s="124" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G50" s="97">
         <v>10</v>
       </c>
       <c r="H50" s="120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I50" s="120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K50" s="97">
         <v>5</v>
       </c>
       <c r="L50" s="97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M50" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11074,40 +11077,40 @@
         <v>4</v>
       </c>
       <c r="B51" s="97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C51" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D51" s="109" t="s">
         <v>153</v>
       </c>
       <c r="E51" s="109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F51" s="133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G51" s="97">
         <v>95</v>
       </c>
       <c r="H51" s="120" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I51" s="120" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J51" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K51" s="97">
         <v>5</v>
       </c>
       <c r="L51" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M51" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11115,40 +11118,40 @@
         <v>4</v>
       </c>
       <c r="B52" s="97" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C52" s="97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D52" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E52" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F52" s="97" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G52" s="97">
         <v>0.75</v>
       </c>
       <c r="H52" s="120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I52" s="120" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J52" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K52" s="97">
         <v>5</v>
       </c>
       <c r="L52" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M52" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11156,40 +11159,40 @@
         <v>4</v>
       </c>
       <c r="B53" s="97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C53" s="97" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D53" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E53" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F53" s="109" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G53" s="109">
         <v>3.5</v>
       </c>
       <c r="H53" s="120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I53" s="120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J53" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K53" s="97">
         <v>5</v>
       </c>
       <c r="L53" s="97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M53" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11197,40 +11200,40 @@
         <v>4</v>
       </c>
       <c r="B54" s="97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C54" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D54" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E54" s="97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F54" s="124" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G54" s="97">
         <v>15</v>
       </c>
       <c r="H54" s="120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I54" s="120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J54" s="97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K54" s="97">
         <v>5</v>
       </c>
       <c r="L54" s="97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M54" s="97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1146" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98DA8CD-4126-3C4B-8FC3-FED6A8E41E51}"/>
+  <xr:revisionPtr revIDLastSave="1164" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E491F0-D920-C240-B03C-DFC70C301F05}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="301">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1727,6 +1727,9 @@
   </si>
   <si>
     <t>﻿Subjects lie supine on the floor with one heel on a 60cm (~24") high box. The knee of the test leg is slightly bent at 20° and opposite leg is bent to 90° hip and knee flexion with their arms crossed over chest. Subjects elevate the hips as high as possible and the assessor places a target at this height. Repeat this action as many times as possible touching the target each time. The test concludes when the subject is unable to bridge to the target [@freckleton2013].</t>
+  </si>
+  <si>
+    <t>9s</t>
   </si>
 </sst>
 </file>
@@ -2229,7 +2232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2595,6 +2598,9 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9705,6 +9711,12 @@
       <c r="J14" s="97" t="s">
         <v>212</v>
       </c>
+      <c r="K14" s="97">
+        <v>2</v>
+      </c>
+      <c r="L14" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M14" s="97" t="s">
         <v>294</v>
       </c>
@@ -9880,6 +9892,12 @@
       <c r="J19" s="97" t="s">
         <v>213</v>
       </c>
+      <c r="K19" s="97">
+        <v>1</v>
+      </c>
+      <c r="L19" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M19" s="97" t="s">
         <v>294</v>
       </c>
@@ -9915,6 +9933,12 @@
       <c r="J20" s="97" t="s">
         <v>212</v>
       </c>
+      <c r="K20" s="97">
+        <v>2</v>
+      </c>
+      <c r="L20" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M20" s="97" t="s">
         <v>294</v>
       </c>
@@ -9950,6 +9974,12 @@
       <c r="J21" s="97" t="s">
         <v>212</v>
       </c>
+      <c r="K21" s="97">
+        <v>2</v>
+      </c>
+      <c r="L21" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M21" s="97" t="s">
         <v>294</v>
       </c>
@@ -9985,6 +10015,12 @@
       <c r="J22" s="97" t="s">
         <v>124</v>
       </c>
+      <c r="K22" s="97">
+        <v>2</v>
+      </c>
+      <c r="L22" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M22" s="97" t="s">
         <v>294</v>
       </c>
@@ -10005,8 +10041,8 @@
       <c r="E23" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="109">
-        <v>9</v>
+      <c r="F23" s="109" t="s">
+        <v>300</v>
       </c>
       <c r="G23" s="109">
         <v>9</v>
@@ -10019,6 +10055,12 @@
       </c>
       <c r="J23" s="97" t="s">
         <v>124</v>
+      </c>
+      <c r="K23" s="97">
+        <v>2</v>
+      </c>
+      <c r="L23" s="97" t="s">
+        <v>170</v>
       </c>
       <c r="M23" s="97" t="s">
         <v>294</v>
@@ -10491,6 +10533,12 @@
       <c r="I35" s="102" t="s">
         <v>214</v>
       </c>
+      <c r="K35" s="97">
+        <v>2</v>
+      </c>
+      <c r="L35" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M35" s="97" t="s">
         <v>294</v>
       </c>
@@ -10523,6 +10571,12 @@
       <c r="I36" s="102" t="s">
         <v>214</v>
       </c>
+      <c r="K36" s="97">
+        <v>2</v>
+      </c>
+      <c r="L36" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M36" s="97" t="s">
         <v>294</v>
       </c>
@@ -11195,44 +11249,44 @@
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="97">
+    <row r="54" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="110">
         <v>4</v>
       </c>
-      <c r="B54" s="97" t="s">
+      <c r="B54" s="110" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="97" t="s">
+      <c r="C54" s="110" t="s">
         <v>276</v>
       </c>
-      <c r="D54" s="97" t="s">
+      <c r="D54" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="97" t="s">
+      <c r="E54" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="F54" s="124" t="s">
+      <c r="F54" s="149" t="s">
         <v>281</v>
       </c>
-      <c r="G54" s="97">
+      <c r="G54" s="110">
         <v>15</v>
       </c>
-      <c r="H54" s="120" t="s">
+      <c r="H54" s="131" t="s">
         <v>283</v>
       </c>
-      <c r="I54" s="120" t="s">
+      <c r="I54" s="131" t="s">
         <v>285</v>
       </c>
-      <c r="J54" s="97" t="s">
+      <c r="J54" s="110" t="s">
         <v>213</v>
       </c>
-      <c r="K54" s="97">
+      <c r="K54" s="110">
         <v>5</v>
       </c>
-      <c r="L54" s="97" t="s">
+      <c r="L54" s="110" t="s">
         <v>282</v>
       </c>
-      <c r="M54" s="97" t="s">
+      <c r="M54" s="110" t="s">
         <v>294</v>
       </c>
     </row>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1164" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E491F0-D920-C240-B03C-DFC70C301F05}"/>
+  <xr:revisionPtr revIDLastSave="1334" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAC1390-D49C-2F49-BFD2-0306A61E6A17}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Phase0" sheetId="2" r:id="rId2"/>
     <sheet name="criteria_full" sheetId="5" r:id="rId3"/>
-    <sheet name="calcs" sheetId="3" r:id="rId4"/>
+    <sheet name="criteria_overview" sheetId="6" r:id="rId4"/>
+    <sheet name="calcs" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -793,7 +794,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="316">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1730,6 +1731,51 @@
   </si>
   <si>
     <t>9s</t>
+  </si>
+  <si>
+    <t>Phase 0</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Phase 4</t>
+  </si>
+  <si>
+    <t>Phase 5</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Jumps</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Pre- Operation</t>
+  </si>
+  <si>
+    <t>Confidence interval around the mean of 5 jumps must be entirely within ± 15%</t>
+  </si>
+  <si>
+    <t>Confidence interval around the mean of 5 jumps must be entirely within ± 20%</t>
   </si>
 </sst>
 </file>
@@ -1740,11 +1786,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1974,8 +2027,22 @@
       <sz val="12"/>
       <name val="Arial (Body)"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2016,6 +2083,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
         <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2230,375 +2303,429 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="22" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2854,13 +2981,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2918,7 +3045,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="137" t="s">
+      <c r="G4" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -2951,7 +3078,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="135"/>
+      <c r="G5" s="136"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -2979,7 +3106,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="135"/>
+      <c r="G6" s="136"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3003,7 +3130,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="135"/>
+      <c r="G7" s="136"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3026,7 +3153,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="135"/>
+      <c r="G8" s="136"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3054,7 +3181,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="135"/>
+      <c r="G9" s="136"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3137,13 +3264,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3198,24 +3325,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="146">
+      <c r="H16" s="137">
         <v>45359</v>
       </c>
-      <c r="I16" s="145"/>
-      <c r="J16" s="147">
+      <c r="I16" s="138"/>
+      <c r="J16" s="139">
         <v>47204</v>
       </c>
-      <c r="K16" s="145"/>
-      <c r="L16" s="148" t="s">
+      <c r="K16" s="138"/>
+      <c r="L16" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="145"/>
-      <c r="N16" s="146">
+      <c r="M16" s="138"/>
+      <c r="N16" s="137">
         <v>45429</v>
       </c>
-      <c r="O16" s="145"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="145"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="138"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3289,7 +3416,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="137" t="s">
+      <c r="G18" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3333,7 +3460,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="135"/>
+      <c r="G19" s="136"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3371,7 +3498,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3417,7 +3544,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="135"/>
+      <c r="G21" s="136"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3453,7 +3580,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="135"/>
+      <c r="G22" s="136"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3491,7 +3618,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="135"/>
+      <c r="G23" s="136"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3531,7 +3658,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="135"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3722,13 +3849,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="136" t="s">
+      <c r="B32" s="135" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="135"/>
-      <c r="D32" s="135"/>
-      <c r="E32" s="135"/>
-      <c r="F32" s="135"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="136"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3773,12 +3900,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="144" t="s">
+      <c r="H33" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="145"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="145"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="137"/>
+      <c r="K33" s="138"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3803,7 +3930,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="137" t="s">
+      <c r="G34" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3834,7 +3961,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="135"/>
+      <c r="G35" s="136"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3863,7 +3990,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="135"/>
+      <c r="G36" s="136"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -3892,7 +4019,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="135"/>
+      <c r="G37" s="136"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -3921,7 +4048,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="135"/>
+      <c r="G38" s="136"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -3942,7 +4069,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="135"/>
+      <c r="G39" s="136"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -3971,7 +4098,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="135"/>
+      <c r="G40" s="136"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -3992,7 +4119,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="135"/>
+      <c r="G41" s="136"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4021,7 +4148,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="135"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4042,7 +4169,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="135"/>
+      <c r="G43" s="136"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4065,17 +4192,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="138" t="s">
+      <c r="C44" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="138" t="s">
+      <c r="D44" s="143" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="135"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4090,13 +4217,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="135"/>
-      <c r="D45" s="135"/>
+      <c r="C45" s="136"/>
+      <c r="D45" s="136"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="135"/>
+      <c r="G45" s="136"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4125,7 +4252,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="135"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4146,7 +4273,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="135"/>
+      <c r="G47" s="136"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4175,7 +4302,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="135"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4204,7 +4331,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="135"/>
+      <c r="G49" s="136"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4231,7 +4358,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="135"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4327,10 +4454,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="134">
+      <c r="B54" s="148">
         <v>16</v>
       </c>
-      <c r="C54" s="139" t="s">
+      <c r="C54" s="149" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4351,8 +4478,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="135"/>
-      <c r="C55" s="135"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4371,10 +4498,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="140">
+      <c r="B56" s="144">
         <v>17</v>
       </c>
-      <c r="C56" s="142" t="s">
+      <c r="C56" s="146" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4396,8 +4523,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="141"/>
-      <c r="C57" s="143"/>
+      <c r="B57" s="145"/>
+      <c r="C57" s="147"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4417,10 +4544,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="134">
+      <c r="B58" s="148">
         <v>18</v>
       </c>
-      <c r="C58" s="139" t="s">
+      <c r="C58" s="149" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4441,8 +4568,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="135"/>
-      <c r="C59" s="135"/>
+      <c r="B59" s="136"/>
+      <c r="C59" s="136"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4461,10 +4588,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="140">
+      <c r="B60" s="144">
         <v>19</v>
       </c>
-      <c r="C60" s="142" t="s">
+      <c r="C60" s="146" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4486,8 +4613,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="141"/>
-      <c r="C61" s="143"/>
+      <c r="B61" s="145"/>
+      <c r="C61" s="147"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4507,7 +4634,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="134">
+      <c r="B62" s="148">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4531,7 +4658,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="135"/>
+      <c r="B63" s="136"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4707,13 +4834,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="136" t="s">
+      <c r="B74" s="135" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="135"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
+      <c r="C74" s="136"/>
+      <c r="D74" s="136"/>
+      <c r="E74" s="136"/>
+      <c r="F74" s="136"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4792,7 +4919,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="137" t="s">
+      <c r="G76" s="141" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4819,7 +4946,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="135"/>
+      <c r="G77" s="136"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4844,7 +4971,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="135"/>
+      <c r="G78" s="136"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4871,7 +4998,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="135"/>
+      <c r="G79" s="136"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -4903,7 +5030,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="135"/>
+      <c r="G80" s="136"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -4932,7 +5059,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="135"/>
+      <c r="G81" s="136"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -4961,7 +5088,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="135"/>
+      <c r="G82" s="136"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -4990,7 +5117,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="135"/>
+      <c r="G83" s="136"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5019,7 +5146,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="135"/>
+      <c r="G84" s="136"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5048,7 +5175,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="135"/>
+      <c r="G85" s="136"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5077,7 +5204,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="135"/>
+      <c r="G86" s="136"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5106,7 +5233,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="135"/>
+      <c r="G87" s="136"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8852,22 +8979,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8878,6 +8989,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9174,7 +9301,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -10395,73 +10522,73 @@
       <c r="A32" s="97">
         <v>3</v>
       </c>
-      <c r="B32" s="118" t="s">
-        <v>201</v>
+      <c r="B32" s="97" t="s">
+        <v>265</v>
       </c>
       <c r="C32" s="97" t="s">
-        <v>190</v>
-      </c>
-      <c r="D32" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="104" t="s">
+      <c r="E32" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F32" s="97">
-        <v>22</v>
+      <c r="F32" s="169" t="s">
+        <v>311</v>
       </c>
       <c r="G32" s="97">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="H32" s="120" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="I32" s="120" t="s">
-        <v>246</v>
-      </c>
-      <c r="J32" s="97" t="s">
-        <v>124</v>
+        <v>288</v>
       </c>
       <c r="K32" s="97">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="L32" s="97" t="s">
+        <v>235</v>
       </c>
       <c r="M32" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="80">
+    <row r="33" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="97">
         <v>3</v>
       </c>
-      <c r="B33" s="109" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="109" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F33" s="109" t="s">
-        <v>140</v>
-      </c>
-      <c r="G33" s="109">
-        <v>1.8</v>
-      </c>
-      <c r="H33" s="129" t="s">
-        <v>210</v>
-      </c>
-      <c r="I33" s="129" t="s">
-        <v>211</v>
-      </c>
-      <c r="J33" s="80" t="s">
-        <v>213</v>
-      </c>
-      <c r="L33" s="80" t="s">
-        <v>170</v>
+      <c r="B33" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D33" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E33" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F33" s="124" t="s">
+        <v>281</v>
+      </c>
+      <c r="G33" s="97">
+        <v>15</v>
+      </c>
+      <c r="H33" s="120" t="s">
+        <v>314</v>
+      </c>
+      <c r="I33" s="120" t="s">
+        <v>290</v>
+      </c>
+      <c r="K33" s="97">
+        <v>5</v>
+      </c>
+      <c r="L33" s="97" t="s">
+        <v>282</v>
       </c>
       <c r="M33" s="97" t="s">
         <v>294</v>
@@ -10471,35 +10598,35 @@
       <c r="A34" s="97">
         <v>3</v>
       </c>
-      <c r="B34" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="C34" s="109" t="s">
-        <v>208</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F34" s="109" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" s="109">
-        <v>1.8</v>
+      <c r="B34" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F34" s="124" t="s">
+        <v>312</v>
+      </c>
+      <c r="G34" s="97">
+        <v>20</v>
       </c>
       <c r="H34" s="120" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="I34" s="120" t="s">
-        <v>247</v>
-      </c>
-      <c r="J34" s="97" t="s">
-        <v>124</v>
+        <v>291</v>
+      </c>
+      <c r="K34" s="97">
+        <v>5</v>
       </c>
       <c r="L34" s="97" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="M34" s="97" t="s">
         <v>294</v>
@@ -10509,152 +10636,146 @@
       <c r="A35" s="97">
         <v>3</v>
       </c>
-      <c r="B35" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="80" t="s">
-        <v>186</v>
+      <c r="B35" s="118" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="97" t="s">
+        <v>190</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E35" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="G35" s="78">
-        <v>90</v>
-      </c>
-      <c r="H35" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I35" s="102" t="s">
-        <v>214</v>
+        <v>219</v>
+      </c>
+      <c r="F35" s="97">
+        <v>22</v>
+      </c>
+      <c r="G35" s="97">
+        <v>22</v>
+      </c>
+      <c r="H35" s="120" t="s">
+        <v>245</v>
+      </c>
+      <c r="I35" s="120" t="s">
+        <v>246</v>
+      </c>
+      <c r="J35" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K35" s="97">
-        <v>2</v>
-      </c>
-      <c r="L35" s="97" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="M35" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="97">
+    <row r="36" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="80">
         <v>3</v>
       </c>
-      <c r="B36" s="125" t="s">
-        <v>156</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="G36" s="78">
-        <v>90</v>
-      </c>
-      <c r="H36" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I36" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="K36" s="97">
-        <v>2</v>
-      </c>
-      <c r="L36" s="97" t="s">
+      <c r="B36" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="109" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F36" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="109">
+        <v>1.8</v>
+      </c>
+      <c r="H36" s="129" t="s">
+        <v>210</v>
+      </c>
+      <c r="I36" s="129" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" s="80" t="s">
+        <v>213</v>
+      </c>
+      <c r="L36" s="80" t="s">
         <v>170</v>
       </c>
       <c r="M36" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="80">
+    <row r="37" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="97">
         <v>3</v>
       </c>
-      <c r="B37" s="109" t="s">
-        <v>193</v>
-      </c>
-      <c r="C37" s="80" t="s">
-        <v>187</v>
-      </c>
-      <c r="D37" s="78" t="s">
+      <c r="B37" s="118" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="109" t="s">
+        <v>208</v>
+      </c>
+      <c r="D37" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="104" t="s">
+      <c r="E37" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F37" s="130" t="s">
-        <v>253</v>
-      </c>
-      <c r="G37" s="80">
-        <v>95</v>
-      </c>
-      <c r="H37" s="83" t="s">
-        <v>230</v>
-      </c>
-      <c r="I37" s="83" t="s">
-        <v>228</v>
-      </c>
-      <c r="J37" s="80" t="s">
-        <v>212</v>
-      </c>
-      <c r="K37" s="80">
-        <v>3</v>
-      </c>
-      <c r="L37" s="80" t="s">
+      <c r="F37" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" s="109">
+        <v>1.8</v>
+      </c>
+      <c r="H37" s="120" t="s">
+        <v>247</v>
+      </c>
+      <c r="I37" s="120" t="s">
+        <v>247</v>
+      </c>
+      <c r="J37" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="L37" s="97" t="s">
         <v>170</v>
       </c>
       <c r="M37" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="97">
         <v>3</v>
       </c>
-      <c r="B38" s="118" t="s">
-        <v>194</v>
-      </c>
-      <c r="C38" s="97" t="s">
-        <v>187</v>
+      <c r="B38" s="125" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="80" t="s">
+        <v>186</v>
       </c>
       <c r="D38" s="78" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E38" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F38" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="G38" s="97">
-        <v>95</v>
-      </c>
-      <c r="H38" s="120" t="s">
-        <v>231</v>
-      </c>
-      <c r="I38" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="J38" s="97" t="s">
-        <v>212</v>
+        <v>159</v>
+      </c>
+      <c r="F38" s="133" t="s">
+        <v>222</v>
+      </c>
+      <c r="G38" s="78">
+        <v>90</v>
+      </c>
+      <c r="H38" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K38" s="97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="97" t="s">
         <v>170</v>
@@ -10663,39 +10784,36 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="97">
         <v>3</v>
       </c>
-      <c r="B39" s="118" t="s">
-        <v>195</v>
-      </c>
-      <c r="C39" s="97" t="s">
-        <v>187</v>
+      <c r="B39" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="80" t="s">
+        <v>186</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E39" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F39" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="G39" s="97">
-        <v>95</v>
-      </c>
-      <c r="H39" s="120" t="s">
-        <v>232</v>
-      </c>
-      <c r="I39" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="J39" s="97" t="s">
-        <v>212</v>
+        <v>159</v>
+      </c>
+      <c r="F39" s="133" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="78">
+        <v>90</v>
+      </c>
+      <c r="H39" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K39" s="97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" s="97" t="s">
         <v>170</v>
@@ -10704,14 +10822,14 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="97">
+    <row r="40" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="80">
         <v>3</v>
       </c>
       <c r="B40" s="109" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="97" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="80" t="s">
         <v>187</v>
       </c>
       <c r="D40" s="78" t="s">
@@ -10720,138 +10838,149 @@
       <c r="E40" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="122" t="s">
+      <c r="F40" s="130" t="s">
         <v>253</v>
       </c>
-      <c r="G40" s="97">
+      <c r="G40" s="80">
         <v>95</v>
       </c>
-      <c r="H40" s="120" t="s">
-        <v>258</v>
-      </c>
-      <c r="I40" s="120" t="s">
-        <v>262</v>
-      </c>
-      <c r="J40" s="97" t="s">
+      <c r="H40" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="J40" s="80" t="s">
         <v>212</v>
       </c>
-      <c r="K40" s="97" t="s">
-        <v>260</v>
-      </c>
-      <c r="L40" s="124" t="s">
-        <v>259</v>
+      <c r="K40" s="80">
+        <v>3</v>
+      </c>
+      <c r="L40" s="80" t="s">
+        <v>170</v>
       </c>
       <c r="M40" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="97">
         <v>3</v>
       </c>
       <c r="B41" s="118" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="C41" s="97" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E41" s="109" t="s">
+      <c r="E41" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F41" s="97" t="s">
-        <v>238</v>
+      <c r="F41" s="122" t="s">
+        <v>253</v>
       </c>
       <c r="G41" s="97">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="H41" s="120" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="I41" s="120" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J41" s="97" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="K41" s="97">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L41" s="97" t="s">
+        <v>170</v>
       </c>
       <c r="M41" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="110">
+    <row r="42" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="97">
         <v>3</v>
       </c>
-      <c r="B42" s="123" t="s">
-        <v>249</v>
-      </c>
-      <c r="C42" s="110" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" s="123" t="s">
+      <c r="B42" s="118" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="123" t="s">
+      <c r="E42" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F42" s="110" t="s">
-        <v>238</v>
-      </c>
-      <c r="G42" s="110">
-        <v>15</v>
-      </c>
-      <c r="H42" s="131" t="s">
-        <v>250</v>
-      </c>
-      <c r="I42" s="131" t="s">
-        <v>251</v>
-      </c>
-      <c r="J42" s="110" t="s">
-        <v>124</v>
-      </c>
-      <c r="K42" s="110">
-        <v>1</v>
-      </c>
-      <c r="L42" s="110"/>
+      <c r="F42" s="122" t="s">
+        <v>253</v>
+      </c>
+      <c r="G42" s="97">
+        <v>95</v>
+      </c>
+      <c r="H42" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="I42" s="120" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="K42" s="97">
+        <v>3</v>
+      </c>
+      <c r="L42" s="97" t="s">
+        <v>170</v>
+      </c>
       <c r="M42" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="97">
-        <v>4</v>
-      </c>
-      <c r="B43" s="118" t="s">
-        <v>261</v>
+        <v>3</v>
+      </c>
+      <c r="B43" s="109" t="s">
+        <v>117</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>190</v>
-      </c>
-      <c r="D43" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="109" t="s">
+      <c r="E43" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F43" s="97">
-        <v>5</v>
+      <c r="F43" s="122" t="s">
+        <v>253</v>
       </c>
       <c r="G43" s="97">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="H43" s="120" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I43" s="120" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J43" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
+      </c>
+      <c r="K43" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="L43" s="124" t="s">
+        <v>259</v>
       </c>
       <c r="M43" s="97" t="s">
         <v>294</v>
@@ -10859,76 +10988,77 @@
     </row>
     <row r="44" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="97">
-        <v>4</v>
-      </c>
-      <c r="B44" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="80" t="s">
-        <v>186</v>
-      </c>
-      <c r="D44" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E44" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F44" s="133" t="s">
-        <v>253</v>
-      </c>
-      <c r="G44" s="78">
-        <v>95</v>
-      </c>
-      <c r="H44" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I44" s="102" t="s">
-        <v>214</v>
+        <v>3</v>
+      </c>
+      <c r="B44" s="118" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="97" t="s">
+        <v>203</v>
+      </c>
+      <c r="D44" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44" s="97" t="s">
+        <v>238</v>
+      </c>
+      <c r="G44" s="97">
+        <v>15</v>
+      </c>
+      <c r="H44" s="120" t="s">
+        <v>252</v>
+      </c>
+      <c r="I44" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="J44" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K44" s="97">
-        <v>3</v>
-      </c>
-      <c r="L44" s="97" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="M44" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="97">
-        <v>4</v>
-      </c>
-      <c r="B45" s="125" t="s">
-        <v>156</v>
-      </c>
-      <c r="C45" s="80" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F45" s="133" t="s">
-        <v>253</v>
-      </c>
-      <c r="G45" s="78">
-        <v>95</v>
-      </c>
-      <c r="H45" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I45" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="K45" s="97">
+    <row r="45" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="110">
         <v>3</v>
       </c>
-      <c r="L45" s="97" t="s">
-        <v>170</v>
-      </c>
+      <c r="B45" s="123" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="110" t="s">
+        <v>203</v>
+      </c>
+      <c r="D45" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="123" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45" s="110" t="s">
+        <v>238</v>
+      </c>
+      <c r="G45" s="110">
+        <v>15</v>
+      </c>
+      <c r="H45" s="131" t="s">
+        <v>250</v>
+      </c>
+      <c r="I45" s="131" t="s">
+        <v>251</v>
+      </c>
+      <c r="J45" s="110" t="s">
+        <v>124</v>
+      </c>
+      <c r="K45" s="110">
+        <v>1</v>
+      </c>
+      <c r="L45" s="110"/>
       <c r="M45" s="97" t="s">
         <v>294</v>
       </c>
@@ -10937,11 +11067,11 @@
       <c r="A46" s="97">
         <v>4</v>
       </c>
-      <c r="B46" s="97" t="s">
-        <v>265</v>
+      <c r="B46" s="118" t="s">
+        <v>261</v>
       </c>
       <c r="C46" s="97" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D46" s="109" t="s">
         <v>153</v>
@@ -10949,23 +11079,20 @@
       <c r="E46" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F46" s="133" t="s">
-        <v>253</v>
+      <c r="F46" s="97">
+        <v>5</v>
       </c>
       <c r="G46" s="97">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="K46" s="97">
-        <v>5</v>
-      </c>
-      <c r="L46" s="97" t="s">
-        <v>235</v>
+        <v>264</v>
+      </c>
+      <c r="J46" s="97" t="s">
+        <v>213</v>
       </c>
       <c r="M46" s="97" t="s">
         <v>294</v>
@@ -10975,35 +11102,35 @@
       <c r="A47" s="97">
         <v>4</v>
       </c>
-      <c r="B47" s="97" t="s">
-        <v>266</v>
-      </c>
-      <c r="C47" s="97" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" s="109" t="s">
-        <v>219</v>
+      <c r="B47" s="125" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D47" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" s="104" t="s">
+        <v>159</v>
       </c>
       <c r="F47" s="133" t="s">
         <v>253</v>
       </c>
-      <c r="G47" s="97">
+      <c r="G47" s="78">
         <v>95</v>
       </c>
-      <c r="H47" s="120" t="s">
-        <v>278</v>
-      </c>
-      <c r="I47" s="120" t="s">
-        <v>289</v>
+      <c r="H47" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I47" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K47" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="97" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="M47" s="97" t="s">
         <v>294</v>
@@ -11013,35 +11140,35 @@
       <c r="A48" s="97">
         <v>4</v>
       </c>
-      <c r="B48" s="97" t="s">
-        <v>267</v>
-      </c>
-      <c r="C48" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D48" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E48" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F48" s="124" t="s">
-        <v>279</v>
-      </c>
-      <c r="G48" s="97">
-        <v>10</v>
-      </c>
-      <c r="H48" s="120" t="s">
-        <v>283</v>
-      </c>
-      <c r="I48" s="120" t="s">
-        <v>290</v>
+      <c r="B48" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" s="78">
+        <v>95</v>
+      </c>
+      <c r="H48" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I48" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K48" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L48" s="97" t="s">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="M48" s="97" t="s">
         <v>294</v>
@@ -11052,10 +11179,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="97" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C49" s="97" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="D49" s="109" t="s">
         <v>153</v>
@@ -11073,10 +11200,7 @@
         <v>278</v>
       </c>
       <c r="I49" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="J49" s="97" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="K49" s="97">
         <v>5</v>
@@ -11093,34 +11217,34 @@
         <v>4</v>
       </c>
       <c r="B50" s="97" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C50" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D50" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F50" s="124" t="s">
-        <v>279</v>
+        <v>274</v>
+      </c>
+      <c r="D50" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E50" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50" s="133" t="s">
+        <v>253</v>
       </c>
       <c r="G50" s="97">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="H50" s="120" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I50" s="120" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K50" s="97">
         <v>5</v>
       </c>
       <c r="L50" s="97" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="M50" s="97" t="s">
         <v>294</v>
@@ -11131,37 +11255,34 @@
         <v>4</v>
       </c>
       <c r="B51" s="97" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C51" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="D51" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E51" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F51" s="133" t="s">
-        <v>253</v>
+        <v>276</v>
+      </c>
+      <c r="D51" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F51" s="124" t="s">
+        <v>279</v>
       </c>
       <c r="G51" s="97">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H51" s="120" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="I51" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="J51" s="97" t="s">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="K51" s="97">
         <v>5</v>
       </c>
       <c r="L51" s="97" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="M51" s="97" t="s">
         <v>294</v>
@@ -11172,28 +11293,28 @@
         <v>4</v>
       </c>
       <c r="B52" s="97" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C52" s="97" t="s">
-        <v>203</v>
-      </c>
-      <c r="D52" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E52" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F52" s="97" t="s">
-        <v>293</v>
+        <v>275</v>
+      </c>
+      <c r="D52" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="133" t="s">
+        <v>253</v>
       </c>
       <c r="G52" s="97">
-        <v>0.75</v>
+        <v>95</v>
       </c>
       <c r="H52" s="120" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I52" s="120" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="J52" s="97" t="s">
         <v>213</v>
@@ -11213,10 +11334,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="97" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C53" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D53" s="97" t="s">
         <v>223</v>
@@ -11224,69 +11345,189 @@
       <c r="E53" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="F53" s="109" t="s">
-        <v>280</v>
-      </c>
-      <c r="G53" s="109">
-        <v>3.5</v>
+      <c r="F53" s="124" t="s">
+        <v>279</v>
+      </c>
+      <c r="G53" s="97">
+        <v>10</v>
       </c>
       <c r="H53" s="120" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I53" s="120" t="s">
-        <v>285</v>
-      </c>
-      <c r="J53" s="97" t="s">
-        <v>213</v>
+        <v>291</v>
       </c>
       <c r="K53" s="97">
         <v>5</v>
       </c>
       <c r="L53" s="97" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="M53" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="110">
+    <row r="54" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="97">
         <v>4</v>
       </c>
-      <c r="B54" s="110" t="s">
+      <c r="B54" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E54" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F54" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="G54" s="97">
+        <v>95</v>
+      </c>
+      <c r="H54" s="120" t="s">
+        <v>278</v>
+      </c>
+      <c r="I54" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="J54" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K54" s="97">
+        <v>5</v>
+      </c>
+      <c r="L54" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M54" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="97">
+        <v>4</v>
+      </c>
+      <c r="B55" s="97" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" s="97" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="97" t="s">
+        <v>293</v>
+      </c>
+      <c r="G55" s="97">
+        <v>0.75</v>
+      </c>
+      <c r="H55" s="120" t="s">
+        <v>287</v>
+      </c>
+      <c r="I55" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="J55" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55" s="97">
+        <v>5</v>
+      </c>
+      <c r="L55" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M55" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="97">
+        <v>4</v>
+      </c>
+      <c r="B56" s="97" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D56" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E56" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F56" s="109" t="s">
+        <v>280</v>
+      </c>
+      <c r="G56" s="109">
+        <v>3.5</v>
+      </c>
+      <c r="H56" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="I56" s="120" t="s">
+        <v>285</v>
+      </c>
+      <c r="J56" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K56" s="97">
+        <v>5</v>
+      </c>
+      <c r="L56" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M56" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="110">
+        <v>4</v>
+      </c>
+      <c r="B57" s="110" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="110" t="s">
+      <c r="C57" s="110" t="s">
         <v>276</v>
       </c>
-      <c r="D54" s="110" t="s">
+      <c r="D57" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="110" t="s">
+      <c r="E57" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="F54" s="149" t="s">
+      <c r="F57" s="134" t="s">
         <v>281</v>
       </c>
-      <c r="G54" s="110">
+      <c r="G57" s="110">
         <v>15</v>
       </c>
-      <c r="H54" s="131" t="s">
+      <c r="H57" s="131" t="s">
         <v>283</v>
       </c>
-      <c r="I54" s="131" t="s">
+      <c r="I57" s="131" t="s">
         <v>285</v>
       </c>
-      <c r="J54" s="110" t="s">
+      <c r="J57" s="110" t="s">
         <v>213</v>
       </c>
-      <c r="K54" s="110">
+      <c r="K57" s="110">
         <v>5</v>
       </c>
-      <c r="L54" s="110" t="s">
+      <c r="L57" s="110" t="s">
         <v>282</v>
       </c>
-      <c r="M54" s="110" t="s">
+      <c r="M57" s="110" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11299,6 +11540,1045 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A797E27-8800-F04C-B6DD-3411CE39E1CB}">
+  <dimension ref="A1:M92"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="151"/>
+    <col min="2" max="2" width="23.5" style="151" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="151" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="151" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" style="151" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="151" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="151" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="151"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="162" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="163" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" s="163"/>
+    </row>
+    <row r="2" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="164" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
+    </row>
+    <row r="3" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="152" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="167" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="167" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="167" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="167" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="152" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="167" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="167" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="167" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="167" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="167" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="152" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="167">
+        <v>1</v>
+      </c>
+      <c r="D5" s="167" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="167">
+        <v>1</v>
+      </c>
+      <c r="F5" s="167" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="155" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="164" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="L9" s="165"/>
+      <c r="M9" s="165"/>
+    </row>
+    <row r="10" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F11" s="155" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="H11" s="155" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F12" s="155" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="155" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F13" s="155" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="H13" s="155" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F14" s="155" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="156" t="s">
+        <v>229</v>
+      </c>
+      <c r="H14" s="155" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F15" s="155" t="s">
+        <v>233</v>
+      </c>
+      <c r="G15" s="155" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F16" s="155" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="155" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="155" t="s">
+        <v>248</v>
+      </c>
+      <c r="I17" s="152" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H18" s="155" t="s">
+        <v>249</v>
+      </c>
+      <c r="I18" s="152" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="164" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
+      <c r="L20" s="165"/>
+      <c r="M20" s="165"/>
+    </row>
+    <row r="21" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="152" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="F21" s="167" t="s">
+        <v>155</v>
+      </c>
+      <c r="G21" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="H21" s="167" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="J21" s="167" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="168" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="152" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="F22" s="167" t="s">
+        <v>156</v>
+      </c>
+      <c r="G22" s="168" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" s="167" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="J22" s="167" t="s">
+        <v>156</v>
+      </c>
+      <c r="K22" s="168" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F23" s="155" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="155" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F24" s="155" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F25" s="155" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="155" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F26" s="160" t="s">
+        <v>201</v>
+      </c>
+      <c r="G26" s="155">
+        <v>10</v>
+      </c>
+      <c r="H26" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="I26" s="152">
+        <v>22</v>
+      </c>
+      <c r="J26" s="155" t="s">
+        <v>261</v>
+      </c>
+      <c r="K26" s="152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F27" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="G27" s="155" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="I27" s="155" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F28" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="155" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="I28" s="155" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="164" t="s">
+        <v>309</v>
+      </c>
+      <c r="B30" s="165"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="165"/>
+      <c r="E30" s="165"/>
+      <c r="F30" s="165"/>
+      <c r="G30" s="165"/>
+      <c r="H30" s="165"/>
+      <c r="I30" s="165"/>
+      <c r="J30" s="165"/>
+      <c r="K30" s="165"/>
+      <c r="L30" s="165"/>
+      <c r="M30" s="165"/>
+    </row>
+    <row r="31" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H31" s="155" t="s">
+        <v>254</v>
+      </c>
+      <c r="I31" s="156" t="s">
+        <v>310</v>
+      </c>
+      <c r="J31" s="155" t="s">
+        <v>254</v>
+      </c>
+      <c r="K31" s="156" t="s">
+        <v>222</v>
+      </c>
+      <c r="L31" s="155" t="s">
+        <v>254</v>
+      </c>
+      <c r="M31" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H32" s="155" t="s">
+        <v>255</v>
+      </c>
+      <c r="I32" s="156" t="s">
+        <v>310</v>
+      </c>
+      <c r="J32" s="155" t="s">
+        <v>255</v>
+      </c>
+      <c r="K32" s="156" t="s">
+        <v>222</v>
+      </c>
+      <c r="L32" s="155" t="s">
+        <v>255</v>
+      </c>
+      <c r="M32" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" s="155" t="s">
+        <v>256</v>
+      </c>
+      <c r="I33" s="156" t="s">
+        <v>310</v>
+      </c>
+      <c r="J33" s="155" t="s">
+        <v>256</v>
+      </c>
+      <c r="K33" s="156" t="s">
+        <v>222</v>
+      </c>
+      <c r="L33" s="155" t="s">
+        <v>256</v>
+      </c>
+      <c r="M33" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H34" s="155" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="156" t="s">
+        <v>310</v>
+      </c>
+      <c r="J34" s="155" t="s">
+        <v>257</v>
+      </c>
+      <c r="K34" s="156" t="s">
+        <v>222</v>
+      </c>
+      <c r="L34" s="155" t="s">
+        <v>257</v>
+      </c>
+      <c r="M34" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="35" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H36" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="I36" s="168" t="s">
+        <v>311</v>
+      </c>
+      <c r="J36" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="K36" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="L36" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="M36" s="168" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H37" s="152" t="s">
+        <v>267</v>
+      </c>
+      <c r="I37" s="159" t="s">
+        <v>281</v>
+      </c>
+      <c r="J37" s="152" t="s">
+        <v>267</v>
+      </c>
+      <c r="K37" s="159" t="s">
+        <v>279</v>
+      </c>
+      <c r="L37" s="152" t="s">
+        <v>267</v>
+      </c>
+      <c r="M37" s="159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H38" s="152" t="s">
+        <v>269</v>
+      </c>
+      <c r="I38" s="168" t="s">
+        <v>311</v>
+      </c>
+      <c r="J38" s="152" t="s">
+        <v>269</v>
+      </c>
+      <c r="K38" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="L38" s="152" t="s">
+        <v>269</v>
+      </c>
+      <c r="M38" s="168" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H39" s="152" t="s">
+        <v>268</v>
+      </c>
+      <c r="I39" s="159" t="s">
+        <v>312</v>
+      </c>
+      <c r="J39" s="152" t="s">
+        <v>268</v>
+      </c>
+      <c r="K39" s="159" t="s">
+        <v>281</v>
+      </c>
+      <c r="L39" s="152" t="s">
+        <v>268</v>
+      </c>
+      <c r="M39" s="159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H40" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="I40" s="168" t="s">
+        <v>311</v>
+      </c>
+      <c r="J40" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="K40" s="168" t="s">
+        <v>222</v>
+      </c>
+      <c r="L40" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="M40" s="168" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H42" s="152" t="s">
+        <v>272</v>
+      </c>
+      <c r="I42" s="152" t="s">
+        <v>293</v>
+      </c>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="152"/>
+    </row>
+    <row r="43" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" s="152" t="s">
+        <v>271</v>
+      </c>
+      <c r="I43" s="155" t="s">
+        <v>280</v>
+      </c>
+      <c r="J43" s="152"/>
+      <c r="K43" s="155"/>
+      <c r="L43" s="152"/>
+      <c r="M43" s="155"/>
+    </row>
+    <row r="44" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H44" s="152" t="s">
+        <v>273</v>
+      </c>
+      <c r="I44" s="159" t="s">
+        <v>281</v>
+      </c>
+      <c r="J44" s="152"/>
+      <c r="K44" s="159"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="159"/>
+    </row>
+    <row r="45" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" s="151"/>
+      <c r="I52" s="151"/>
+      <c r="J52" s="151"/>
+      <c r="K52" s="151"/>
+      <c r="L52" s="151"/>
+      <c r="M52" s="151"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="H74" s="150" t="s">
+        <v>304</v>
+      </c>
+      <c r="I74" s="150"/>
+      <c r="J74" s="150" t="s">
+        <v>305</v>
+      </c>
+      <c r="K74" s="150"/>
+      <c r="L74" s="150" t="s">
+        <v>306</v>
+      </c>
+      <c r="M74" s="150"/>
+    </row>
+    <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B75" s="150" t="s">
+        <v>301</v>
+      </c>
+      <c r="C75" s="150"/>
+      <c r="D75" s="150" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" s="150"/>
+      <c r="F75" s="150" t="s">
+        <v>303</v>
+      </c>
+      <c r="G75" s="150"/>
+      <c r="H75" s="155" t="s">
+        <v>254</v>
+      </c>
+      <c r="I75" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J75" s="155" t="s">
+        <v>261</v>
+      </c>
+      <c r="K75" s="152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B76" s="152" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="153" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="154" t="s">
+        <v>146</v>
+      </c>
+      <c r="E76" s="153" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="154" t="s">
+        <v>146</v>
+      </c>
+      <c r="G76" s="153" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="155" t="s">
+        <v>255</v>
+      </c>
+      <c r="I76" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J76" s="154" t="s">
+        <v>155</v>
+      </c>
+      <c r="K76" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B77" s="152" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" s="153" t="s">
+        <v>151</v>
+      </c>
+      <c r="D77" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="153" t="s">
+        <v>151</v>
+      </c>
+      <c r="F77" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="G77" s="153" t="s">
+        <v>151</v>
+      </c>
+      <c r="H77" s="155" t="s">
+        <v>256</v>
+      </c>
+      <c r="I77" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J77" s="154" t="s">
+        <v>156</v>
+      </c>
+      <c r="K77" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B78" s="152" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="153">
+        <v>1</v>
+      </c>
+      <c r="D78" s="154" t="s">
+        <v>176</v>
+      </c>
+      <c r="E78" s="153">
+        <v>1</v>
+      </c>
+      <c r="F78" s="154" t="s">
+        <v>176</v>
+      </c>
+      <c r="G78" s="153">
+        <v>0</v>
+      </c>
+      <c r="H78" s="155" t="s">
+        <v>257</v>
+      </c>
+      <c r="I78" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J78" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="K78" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B79" s="152" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="158" t="s">
+        <v>222</v>
+      </c>
+      <c r="D79" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="E79" s="152">
+        <v>5</v>
+      </c>
+      <c r="F79" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="G79" s="155" t="s">
+        <v>227</v>
+      </c>
+      <c r="H79" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="I79" s="152">
+        <v>22</v>
+      </c>
+      <c r="J79" s="152" t="s">
+        <v>266</v>
+      </c>
+      <c r="K79" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" ht="16" x14ac:dyDescent="0.15">
+      <c r="B80" s="152" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="158" t="s">
+        <v>222</v>
+      </c>
+      <c r="F80" s="155" t="s">
+        <v>78</v>
+      </c>
+      <c r="G80" s="155" t="s">
+        <v>225</v>
+      </c>
+      <c r="H80" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="I80" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="J80" s="152" t="s">
+        <v>267</v>
+      </c>
+      <c r="K80" s="159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F81" s="155" t="s">
+        <v>82</v>
+      </c>
+      <c r="G81" s="155">
+        <v>20</v>
+      </c>
+      <c r="H81" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="I81" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="J81" s="152" t="s">
+        <v>269</v>
+      </c>
+      <c r="K81" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="82" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F82" s="155" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82" s="155" t="s">
+        <v>224</v>
+      </c>
+      <c r="H82" s="154" t="s">
+        <v>155</v>
+      </c>
+      <c r="I82" s="157" t="s">
+        <v>222</v>
+      </c>
+      <c r="J82" s="152" t="s">
+        <v>268</v>
+      </c>
+      <c r="K82" s="159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" spans="6:11" ht="17" x14ac:dyDescent="0.15">
+      <c r="F83" s="160" t="s">
+        <v>201</v>
+      </c>
+      <c r="G83" s="155">
+        <v>10</v>
+      </c>
+      <c r="H83" s="154" t="s">
+        <v>156</v>
+      </c>
+      <c r="I83" s="157" t="s">
+        <v>222</v>
+      </c>
+      <c r="J83" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="K83" s="157" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="84" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F84" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="G84" s="155" t="s">
+        <v>96</v>
+      </c>
+      <c r="H84" s="155" t="s">
+        <v>193</v>
+      </c>
+      <c r="I84" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J84" s="152" t="s">
+        <v>272</v>
+      </c>
+      <c r="K84" s="152" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="85" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F85" s="154" t="s">
+        <v>155</v>
+      </c>
+      <c r="G85" s="161" t="s">
+        <v>229</v>
+      </c>
+      <c r="H85" s="155" t="s">
+        <v>194</v>
+      </c>
+      <c r="I85" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J85" s="152" t="s">
+        <v>271</v>
+      </c>
+      <c r="K85" s="155" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="86" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F86" s="154" t="s">
+        <v>156</v>
+      </c>
+      <c r="G86" s="161" t="s">
+        <v>229</v>
+      </c>
+      <c r="H86" s="155" t="s">
+        <v>195</v>
+      </c>
+      <c r="I86" s="156" t="s">
+        <v>253</v>
+      </c>
+      <c r="J86" s="152" t="s">
+        <v>273</v>
+      </c>
+      <c r="K86" s="159" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="87" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F87" s="155" t="s">
+        <v>233</v>
+      </c>
+      <c r="G87" s="155" t="s">
+        <v>226</v>
+      </c>
+      <c r="H87" s="155" t="s">
+        <v>117</v>
+      </c>
+      <c r="I87" s="156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="88" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F88" s="155" t="s">
+        <v>234</v>
+      </c>
+      <c r="G88" s="155" t="s">
+        <v>300</v>
+      </c>
+      <c r="H88" s="155" t="s">
+        <v>248</v>
+      </c>
+      <c r="I88" s="152" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="89" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F89" s="155" t="s">
+        <v>193</v>
+      </c>
+      <c r="G89" s="161" t="s">
+        <v>229</v>
+      </c>
+      <c r="H89" s="155" t="s">
+        <v>249</v>
+      </c>
+      <c r="I89" s="152" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F90" s="155" t="s">
+        <v>194</v>
+      </c>
+      <c r="G90" s="161" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="91" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F91" s="155" t="s">
+        <v>195</v>
+      </c>
+      <c r="G91" s="161" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="92" spans="6:11" ht="16" x14ac:dyDescent="0.15">
+      <c r="F92" s="155" t="s">
+        <v>117</v>
+      </c>
+      <c r="G92" s="156" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+  </mergeCells>
+  <phoneticPr fontId="34" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01440D2E-D5CB-624F-A307-D0DE876488BF}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1334" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAC1390-D49C-2F49-BFD2-0306A61E6A17}"/>
+  <xr:revisionPtr revIDLastSave="1423" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FAB954-2471-6D43-B7D1-4E2C3EF09753}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3880" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -794,7 +794,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="330">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1776,6 +1776,48 @@
   </si>
   <si>
     <t>Confidence interval around the mean of 5 jumps must be entirely within ± 20%</t>
+  </si>
+  <si>
+    <t>Countermovement Jump</t>
+  </si>
+  <si>
+    <t>Standing still on the force plates with hands on hips.  Jump as high as you can.</t>
+  </si>
+  <si>
+    <t>Metrics of interest at this stage include jump height, lengthening (eccentric) bilateral asymmetry, shortening (concentric) asymmetry.  Other metrics may be examined by the practitioner to allow deeper understanding of the jump, and inform exercise programming.</t>
+  </si>
+  <si>
+    <t>Drop and Stick</t>
+  </si>
+  <si>
+    <t>Ensure that the athlete steps straight forward and does not lower themselves from the box.</t>
+  </si>
+  <si>
+    <t>Step forward off a 50cm box placed 15cm behind the force plates.  Land on both legs in a squat with thighs parallel to the floor.  Land soft and freeze like a statue. Hold the position for five seconds.</t>
+  </si>
+  <si>
+    <t>How quickly the athlete can return GRFs to a stable state.</t>
+  </si>
+  <si>
+    <t>Currently using RAW method.</t>
+  </si>
+  <si>
+    <t>Ratio of force produced by each limb during the landing.</t>
+  </si>
+  <si>
+    <t>How effectively can the athlete disippate the force produced by the ground.</t>
+  </si>
+  <si>
+    <t>The highest force recorded, relative to body mass.</t>
+  </si>
+  <si>
+    <t>Drop and Stick - TTS</t>
+  </si>
+  <si>
+    <t>3.5*BM</t>
+  </si>
+  <si>
+    <t>Drop and Stick Asymmetry</t>
   </si>
 </sst>
 </file>
@@ -2305,7 +2347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2603,9 +2645,6 @@
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2637,28 +2676,39 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2668,64 +2718,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2981,13 +2993,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3045,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="141" t="s">
+      <c r="G4" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3078,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="136"/>
+      <c r="G5" s="143"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3106,7 +3118,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="136"/>
+      <c r="G6" s="143"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3130,7 +3142,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="136"/>
+      <c r="G7" s="143"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3153,7 +3165,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="136"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3181,7 +3193,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="136"/>
+      <c r="G9" s="143"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3264,13 +3276,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="135" t="s">
+      <c r="B15" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3325,24 +3337,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="137">
+      <c r="H16" s="154">
         <v>45359</v>
       </c>
-      <c r="I16" s="138"/>
-      <c r="J16" s="139">
+      <c r="I16" s="153"/>
+      <c r="J16" s="155">
         <v>47204</v>
       </c>
-      <c r="K16" s="138"/>
-      <c r="L16" s="140" t="s">
+      <c r="K16" s="153"/>
+      <c r="L16" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="138"/>
-      <c r="N16" s="137">
+      <c r="M16" s="153"/>
+      <c r="N16" s="154">
         <v>45429</v>
       </c>
-      <c r="O16" s="138"/>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="138"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="154"/>
+      <c r="Q16" s="153"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3416,7 +3428,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="141" t="s">
+      <c r="G18" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3460,7 +3472,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="136"/>
+      <c r="G19" s="143"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3498,7 +3510,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="136"/>
+      <c r="G20" s="143"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3544,7 +3556,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="136"/>
+      <c r="G21" s="143"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3580,7 +3592,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="136"/>
+      <c r="G22" s="143"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3618,7 +3630,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="136"/>
+      <c r="G23" s="143"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3658,7 +3670,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="136"/>
+      <c r="G24" s="143"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3849,13 +3861,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="135" t="s">
+      <c r="B32" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3900,12 +3912,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="142" t="s">
+      <c r="H33" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="138"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="138"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="153"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3930,7 +3942,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="141" t="s">
+      <c r="G34" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3961,7 +3973,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="136"/>
+      <c r="G35" s="143"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3990,7 +4002,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="136"/>
+      <c r="G36" s="143"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4019,7 +4031,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="136"/>
+      <c r="G37" s="143"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4048,7 +4060,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="136"/>
+      <c r="G38" s="143"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4069,7 +4081,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="136"/>
+      <c r="G39" s="143"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4098,7 +4110,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="136"/>
+      <c r="G40" s="143"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4119,7 +4131,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="136"/>
+      <c r="G41" s="143"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4148,7 +4160,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="136"/>
+      <c r="G42" s="143"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4169,7 +4181,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="136"/>
+      <c r="G43" s="143"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4192,17 +4204,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="143" t="s">
+      <c r="C44" s="146" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="D44" s="146" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="136"/>
+      <c r="G44" s="143"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4217,13 +4229,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="136"/>
+      <c r="G45" s="143"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4252,7 +4264,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="136"/>
+      <c r="G46" s="143"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4273,7 +4285,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="136"/>
+      <c r="G47" s="143"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4302,7 +4314,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="136"/>
+      <c r="G48" s="143"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4331,7 +4343,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="136"/>
+      <c r="G49" s="143"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4358,7 +4370,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="136"/>
+      <c r="G50" s="143"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4454,10 +4466,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="148">
+      <c r="B54" s="142">
         <v>16</v>
       </c>
-      <c r="C54" s="149" t="s">
+      <c r="C54" s="147" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4478,8 +4490,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="136"/>
-      <c r="C55" s="136"/>
+      <c r="B55" s="143"/>
+      <c r="C55" s="143"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4498,10 +4510,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="144">
+      <c r="B56" s="148">
         <v>17</v>
       </c>
-      <c r="C56" s="146" t="s">
+      <c r="C56" s="150" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4523,8 +4535,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="145"/>
-      <c r="C57" s="147"/>
+      <c r="B57" s="149"/>
+      <c r="C57" s="151"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4544,10 +4556,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="148">
+      <c r="B58" s="142">
         <v>18</v>
       </c>
-      <c r="C58" s="149" t="s">
+      <c r="C58" s="147" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4568,8 +4580,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="136"/>
-      <c r="C59" s="136"/>
+      <c r="B59" s="143"/>
+      <c r="C59" s="143"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4588,10 +4600,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="144">
+      <c r="B60" s="148">
         <v>19</v>
       </c>
-      <c r="C60" s="146" t="s">
+      <c r="C60" s="150" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4613,8 +4625,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="145"/>
-      <c r="C61" s="147"/>
+      <c r="B61" s="149"/>
+      <c r="C61" s="151"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4634,7 +4646,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="148">
+      <c r="B62" s="142">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4658,7 +4670,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="136"/>
+      <c r="B63" s="143"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4834,13 +4846,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="135" t="s">
+      <c r="B74" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="136"/>
-      <c r="D74" s="136"/>
-      <c r="E74" s="136"/>
-      <c r="F74" s="136"/>
+      <c r="C74" s="143"/>
+      <c r="D74" s="143"/>
+      <c r="E74" s="143"/>
+      <c r="F74" s="143"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4919,7 +4931,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="141" t="s">
+      <c r="G76" s="145" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4946,7 +4958,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="136"/>
+      <c r="G77" s="143"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4971,7 +4983,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="136"/>
+      <c r="G78" s="143"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4998,7 +5010,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="136"/>
+      <c r="G79" s="143"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5030,7 +5042,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="136"/>
+      <c r="G80" s="143"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5059,7 +5071,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="136"/>
+      <c r="G81" s="143"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5088,7 +5100,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="136"/>
+      <c r="G82" s="143"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5117,7 +5129,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="136"/>
+      <c r="G83" s="143"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5146,7 +5158,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="136"/>
+      <c r="G84" s="143"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5175,7 +5187,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="136"/>
+      <c r="G85" s="143"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5204,7 +5216,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="136"/>
+      <c r="G86" s="143"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5233,7 +5245,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="136"/>
+      <c r="G87" s="143"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8979,6 +8991,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8989,22 +9017,6 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9301,7 +9313,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -9365,7 +9377,7 @@
       <c r="A2" s="97">
         <v>0</v>
       </c>
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="124" t="s">
         <v>146</v>
       </c>
       <c r="C2" s="97" t="s">
@@ -9404,7 +9416,7 @@
       <c r="A3" s="97">
         <v>0</v>
       </c>
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="124" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="97" t="s">
@@ -9443,7 +9455,7 @@
       <c r="A4" s="97">
         <v>0</v>
       </c>
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="124" t="s">
         <v>176</v>
       </c>
       <c r="C4" s="97" t="s">
@@ -9480,7 +9492,7 @@
       <c r="A5" s="97">
         <v>0</v>
       </c>
-      <c r="B5" s="125" t="s">
+      <c r="B5" s="124" t="s">
         <v>155</v>
       </c>
       <c r="C5" s="97" t="s">
@@ -9521,7 +9533,7 @@
       <c r="A6" s="97">
         <v>0</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="124" t="s">
         <v>156</v>
       </c>
       <c r="C6" s="97" t="s">
@@ -9562,7 +9574,7 @@
       <c r="A7" s="99">
         <v>1</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="125" t="s">
         <v>146</v>
       </c>
       <c r="C7" s="99" t="s">
@@ -9599,7 +9611,7 @@
       <c r="A8" s="97">
         <v>1</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="124" t="s">
         <v>147</v>
       </c>
       <c r="C8" s="97" t="s">
@@ -9634,7 +9646,7 @@
       <c r="A9" s="97">
         <v>1</v>
       </c>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="124" t="s">
         <v>176</v>
       </c>
       <c r="C9" s="97" t="s">
@@ -9704,7 +9716,7 @@
       <c r="A11" s="99">
         <v>2</v>
       </c>
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="125" t="s">
         <v>146</v>
       </c>
       <c r="C11" s="99" t="s">
@@ -9741,7 +9753,7 @@
       <c r="A12" s="97">
         <v>2</v>
       </c>
-      <c r="B12" s="125" t="s">
+      <c r="B12" s="124" t="s">
         <v>147</v>
       </c>
       <c r="C12" s="97" t="s">
@@ -9776,7 +9788,7 @@
       <c r="A13" s="97">
         <v>2</v>
       </c>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="124" t="s">
         <v>176</v>
       </c>
       <c r="C13" s="97" t="s">
@@ -9811,7 +9823,7 @@
       <c r="A14" s="97">
         <v>2</v>
       </c>
-      <c r="B14" s="127" t="s">
+      <c r="B14" s="126" t="s">
         <v>115</v>
       </c>
       <c r="C14" s="109" t="s">
@@ -9870,10 +9882,10 @@
       <c r="G15" s="109">
         <v>20</v>
       </c>
-      <c r="H15" s="129" t="s">
+      <c r="H15" s="128" t="s">
         <v>299</v>
       </c>
-      <c r="I15" s="129" t="s">
+      <c r="I15" s="128" t="s">
         <v>196</v>
       </c>
       <c r="J15" s="97" t="s">
@@ -9887,10 +9899,10 @@
       <c r="A16" s="97">
         <v>2</v>
       </c>
-      <c r="B16" s="127" t="s">
+      <c r="B16" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="127" t="s">
+      <c r="C16" s="126" t="s">
         <v>190</v>
       </c>
       <c r="D16" s="78" t="s">
@@ -9905,10 +9917,10 @@
       <c r="G16" s="109">
         <v>20</v>
       </c>
-      <c r="H16" s="128" t="s">
+      <c r="H16" s="127" t="s">
         <v>199</v>
       </c>
-      <c r="I16" s="129" t="s">
+      <c r="I16" s="128" t="s">
         <v>196</v>
       </c>
       <c r="J16" s="97" t="s">
@@ -9940,10 +9952,10 @@
       <c r="G17" s="109">
         <v>30</v>
       </c>
-      <c r="H17" s="129" t="s">
+      <c r="H17" s="128" t="s">
         <v>200</v>
       </c>
-      <c r="I17" s="129" t="s">
+      <c r="I17" s="128" t="s">
         <v>197</v>
       </c>
       <c r="J17" s="97" t="s">
@@ -9957,10 +9969,10 @@
       <c r="A18" s="97">
         <v>2</v>
       </c>
-      <c r="B18" s="128" t="s">
+      <c r="B18" s="127" t="s">
         <v>201</v>
       </c>
-      <c r="C18" s="128" t="s">
+      <c r="C18" s="127" t="s">
         <v>190</v>
       </c>
       <c r="D18" s="78" t="s">
@@ -9975,10 +9987,10 @@
       <c r="G18" s="109">
         <v>10</v>
       </c>
-      <c r="H18" s="128" t="s">
+      <c r="H18" s="127" t="s">
         <v>202</v>
       </c>
-      <c r="I18" s="129" t="s">
+      <c r="I18" s="128" t="s">
         <v>198</v>
       </c>
       <c r="J18" s="97" t="s">
@@ -10010,10 +10022,10 @@
       <c r="G19" s="109">
         <v>1.5</v>
       </c>
-      <c r="H19" s="129" t="s">
+      <c r="H19" s="128" t="s">
         <v>210</v>
       </c>
-      <c r="I19" s="129" t="s">
+      <c r="I19" s="128" t="s">
         <v>211</v>
       </c>
       <c r="J19" s="97" t="s">
@@ -10033,7 +10045,7 @@
       <c r="A20" s="97">
         <v>2</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="124" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="80" t="s">
@@ -10074,7 +10086,7 @@
       <c r="A21" s="97">
         <v>2</v>
       </c>
-      <c r="B21" s="125" t="s">
+      <c r="B21" s="124" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="80" t="s">
@@ -10133,10 +10145,10 @@
       <c r="G22" s="109">
         <v>45</v>
       </c>
-      <c r="H22" s="129" t="s">
+      <c r="H22" s="128" t="s">
         <v>204</v>
       </c>
-      <c r="I22" s="129" t="s">
+      <c r="I22" s="128" t="s">
         <v>206</v>
       </c>
       <c r="J22" s="97" t="s">
@@ -10174,10 +10186,10 @@
       <c r="G23" s="109">
         <v>9</v>
       </c>
-      <c r="H23" s="129" t="s">
+      <c r="H23" s="128" t="s">
         <v>205</v>
       </c>
-      <c r="I23" s="129" t="s">
+      <c r="I23" s="128" t="s">
         <v>207</v>
       </c>
       <c r="J23" s="97" t="s">
@@ -10350,19 +10362,19 @@
       <c r="K27" s="97" t="s">
         <v>260</v>
       </c>
-      <c r="L27" s="124" t="s">
+      <c r="L27" s="123" t="s">
         <v>259</v>
       </c>
       <c r="M27" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" s="99" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="99">
         <v>3</v>
       </c>
       <c r="B28" s="116" t="s">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="C28" s="99" t="s">
         <v>187</v>
@@ -10380,103 +10392,99 @@
         <v>95</v>
       </c>
       <c r="H28" s="117" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="I28" s="117" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="J28" s="99" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="99" t="s">
+        <v>260</v>
+      </c>
+      <c r="L28" s="159" t="s">
+        <v>259</v>
+      </c>
+      <c r="M28" s="99" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="80">
+        <v>3</v>
+      </c>
+      <c r="B29" s="109" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="G29" s="80">
+        <v>15</v>
+      </c>
+      <c r="H29" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" s="83" t="s">
+        <v>251</v>
+      </c>
+      <c r="J29" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="K28" s="99">
-        <v>2</v>
-      </c>
-      <c r="L28" s="99" t="s">
-        <v>235</v>
-      </c>
-      <c r="M28" s="97" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="97">
+      <c r="K29" s="80">
+        <v>1</v>
+      </c>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="80">
         <v>3</v>
       </c>
-      <c r="B29" s="118" t="s">
-        <v>255</v>
-      </c>
-      <c r="C29" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="78" t="s">
+      <c r="B30" s="109" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="104" t="s">
+      <c r="E30" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F29" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="G29" s="97">
-        <v>95</v>
-      </c>
-      <c r="H29" s="119" t="s">
-        <v>239</v>
-      </c>
-      <c r="I29" s="120" t="s">
-        <v>240</v>
-      </c>
-      <c r="J29" s="97" t="s">
+      <c r="F30" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="G30" s="80">
+        <v>15</v>
+      </c>
+      <c r="H30" s="83" t="s">
+        <v>250</v>
+      </c>
+      <c r="I30" s="83" t="s">
+        <v>251</v>
+      </c>
+      <c r="J30" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="K29" s="97">
-        <v>2</v>
-      </c>
-      <c r="L29" s="97" t="s">
-        <v>235</v>
-      </c>
-      <c r="M29" s="97" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="97">
-        <v>3</v>
-      </c>
-      <c r="B30" s="118" t="s">
-        <v>256</v>
-      </c>
-      <c r="C30" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F30" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="G30" s="97">
-        <v>95</v>
-      </c>
-      <c r="H30" s="119" t="s">
-        <v>241</v>
-      </c>
-      <c r="I30" s="120" t="s">
-        <v>242</v>
-      </c>
-      <c r="J30" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="K30" s="97">
-        <v>2</v>
-      </c>
-      <c r="L30" s="97" t="s">
-        <v>235</v>
-      </c>
-      <c r="M30" s="97" t="s">
+      <c r="K30" s="80">
+        <v>1</v>
+      </c>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10485,7 +10493,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="118" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="C31" s="97" t="s">
         <v>190</v>
@@ -10496,17 +10504,17 @@
       <c r="E31" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F31" s="122" t="s">
-        <v>253</v>
+      <c r="F31" s="97">
+        <v>22</v>
       </c>
       <c r="G31" s="97">
-        <v>95</v>
-      </c>
-      <c r="H31" s="119" t="s">
-        <v>243</v>
+        <v>22</v>
+      </c>
+      <c r="H31" s="120" t="s">
+        <v>245</v>
       </c>
       <c r="I31" s="120" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J31" s="97" t="s">
         <v>124</v>
@@ -10515,18 +10523,18 @@
         <v>1</v>
       </c>
       <c r="M31" s="97" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="97">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="80">
         <v>3</v>
       </c>
-      <c r="B32" s="97" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" s="97" t="s">
-        <v>187</v>
+      <c r="B32" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="109" t="s">
+        <v>208</v>
       </c>
       <c r="D32" s="109" t="s">
         <v>153</v>
@@ -10534,23 +10542,23 @@
       <c r="E32" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F32" s="169" t="s">
-        <v>311</v>
-      </c>
-      <c r="G32" s="97">
-        <v>80</v>
-      </c>
-      <c r="H32" s="120" t="s">
-        <v>278</v>
-      </c>
-      <c r="I32" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="K32" s="97">
-        <v>5</v>
-      </c>
-      <c r="L32" s="97" t="s">
-        <v>235</v>
+      <c r="F32" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="109">
+        <v>1.8</v>
+      </c>
+      <c r="H32" s="128" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="128" t="s">
+        <v>211</v>
+      </c>
+      <c r="J32" s="80" t="s">
+        <v>213</v>
+      </c>
+      <c r="L32" s="80" t="s">
+        <v>170</v>
       </c>
       <c r="M32" s="97" t="s">
         <v>294</v>
@@ -10560,35 +10568,35 @@
       <c r="A33" s="97">
         <v>3</v>
       </c>
-      <c r="B33" s="97" t="s">
-        <v>267</v>
-      </c>
-      <c r="C33" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D33" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E33" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F33" s="124" t="s">
-        <v>281</v>
-      </c>
-      <c r="G33" s="97">
-        <v>15</v>
+      <c r="B33" s="118" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="109" t="s">
+        <v>208</v>
+      </c>
+      <c r="D33" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F33" s="109" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="109">
+        <v>1.8</v>
       </c>
       <c r="H33" s="120" t="s">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="I33" s="120" t="s">
-        <v>290</v>
-      </c>
-      <c r="K33" s="97">
-        <v>5</v>
+        <v>247</v>
+      </c>
+      <c r="J33" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="L33" s="97" t="s">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="M33" s="97" t="s">
         <v>294</v>
@@ -10598,35 +10606,35 @@
       <c r="A34" s="97">
         <v>3</v>
       </c>
-      <c r="B34" s="97" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D34" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E34" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F34" s="124" t="s">
-        <v>312</v>
-      </c>
-      <c r="G34" s="97">
-        <v>20</v>
-      </c>
-      <c r="H34" s="120" t="s">
-        <v>315</v>
-      </c>
-      <c r="I34" s="120" t="s">
-        <v>291</v>
+      <c r="B34" s="124" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" s="132" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="78">
+        <v>90</v>
+      </c>
+      <c r="H34" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I34" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K34" s="97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L34" s="97" t="s">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="M34" s="97" t="s">
         <v>294</v>
@@ -10636,76 +10644,79 @@
       <c r="A35" s="97">
         <v>3</v>
       </c>
-      <c r="B35" s="118" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="97" t="s">
-        <v>190</v>
+      <c r="B35" s="124" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>186</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E35" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F35" s="97">
-        <v>22</v>
-      </c>
-      <c r="G35" s="97">
-        <v>22</v>
-      </c>
-      <c r="H35" s="120" t="s">
-        <v>245</v>
-      </c>
-      <c r="I35" s="120" t="s">
-        <v>246</v>
-      </c>
-      <c r="J35" s="97" t="s">
-        <v>124</v>
+        <v>159</v>
+      </c>
+      <c r="F35" s="132" t="s">
+        <v>222</v>
+      </c>
+      <c r="G35" s="78">
+        <v>90</v>
+      </c>
+      <c r="H35" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K35" s="97">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L35" s="97" t="s">
+        <v>170</v>
       </c>
       <c r="M35" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="80">
         <v>3</v>
       </c>
       <c r="B36" s="109" t="s">
-        <v>209</v>
-      </c>
-      <c r="C36" s="109" t="s">
-        <v>208</v>
-      </c>
-      <c r="D36" s="109" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="109" t="s">
+      <c r="E36" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F36" s="109" t="s">
-        <v>140</v>
-      </c>
-      <c r="G36" s="109">
-        <v>1.8</v>
-      </c>
-      <c r="H36" s="129" t="s">
-        <v>210</v>
-      </c>
-      <c r="I36" s="129" t="s">
-        <v>211</v>
+      <c r="F36" s="129" t="s">
+        <v>310</v>
+      </c>
+      <c r="G36" s="80">
+        <v>85</v>
+      </c>
+      <c r="H36" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="I36" s="83" t="s">
+        <v>237</v>
       </c>
       <c r="J36" s="80" t="s">
-        <v>213</v>
+        <v>124</v>
+      </c>
+      <c r="K36" s="80">
+        <v>2</v>
       </c>
       <c r="L36" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="M36" s="97" t="s">
-        <v>294</v>
+        <v>235</v>
+      </c>
+      <c r="M36" s="80" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10713,72 +10724,78 @@
         <v>3</v>
       </c>
       <c r="B37" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="109" t="s">
-        <v>208</v>
-      </c>
-      <c r="D37" s="109" t="s">
+        <v>255</v>
+      </c>
+      <c r="C37" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="109" t="s">
+      <c r="E37" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F37" s="109" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" s="109">
-        <v>1.8</v>
-      </c>
-      <c r="H37" s="120" t="s">
-        <v>247</v>
+      <c r="F37" s="129" t="s">
+        <v>310</v>
+      </c>
+      <c r="G37" s="97">
+        <v>85</v>
+      </c>
+      <c r="H37" s="119" t="s">
+        <v>239</v>
       </c>
       <c r="I37" s="120" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="J37" s="97" t="s">
         <v>124</v>
       </c>
+      <c r="K37" s="97">
+        <v>2</v>
+      </c>
       <c r="L37" s="97" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="M37" s="97" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="97">
         <v>3</v>
       </c>
-      <c r="B38" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="80" t="s">
-        <v>186</v>
+      <c r="B38" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="C38" s="97" t="s">
+        <v>187</v>
       </c>
       <c r="D38" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E38" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="G38" s="78">
-        <v>90</v>
-      </c>
-      <c r="H38" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I38" s="102" t="s">
-        <v>214</v>
+        <v>219</v>
+      </c>
+      <c r="F38" s="129" t="s">
+        <v>310</v>
+      </c>
+      <c r="G38" s="97">
+        <v>85</v>
+      </c>
+      <c r="H38" s="119" t="s">
+        <v>241</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>242</v>
+      </c>
+      <c r="J38" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K38" s="97">
         <v>2</v>
       </c>
       <c r="L38" s="97" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="M38" s="97" t="s">
         <v>294</v>
@@ -10788,199 +10805,199 @@
       <c r="A39" s="97">
         <v>3</v>
       </c>
-      <c r="B39" s="125" t="s">
-        <v>156</v>
-      </c>
-      <c r="C39" s="80" t="s">
-        <v>186</v>
+      <c r="B39" s="118" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="97" t="s">
+        <v>190</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E39" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F39" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="G39" s="78">
-        <v>90</v>
-      </c>
-      <c r="H39" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I39" s="102" t="s">
-        <v>214</v>
+        <v>219</v>
+      </c>
+      <c r="F39" s="129" t="s">
+        <v>310</v>
+      </c>
+      <c r="G39" s="97">
+        <v>85</v>
+      </c>
+      <c r="H39" s="119" t="s">
+        <v>243</v>
+      </c>
+      <c r="I39" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="J39" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K39" s="97">
-        <v>2</v>
-      </c>
-      <c r="L39" s="97" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="M39" s="97" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="80">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="97">
         <v>3</v>
       </c>
       <c r="B40" s="109" t="s">
-        <v>193</v>
-      </c>
-      <c r="C40" s="80" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="D40" s="78" t="s">
+      <c r="D40" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="104" t="s">
+      <c r="E40" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="130" t="s">
-        <v>253</v>
-      </c>
-      <c r="G40" s="80">
-        <v>95</v>
-      </c>
-      <c r="H40" s="83" t="s">
-        <v>230</v>
-      </c>
-      <c r="I40" s="83" t="s">
-        <v>228</v>
-      </c>
-      <c r="J40" s="80" t="s">
-        <v>212</v>
-      </c>
-      <c r="K40" s="80">
-        <v>3</v>
-      </c>
-      <c r="L40" s="80" t="s">
-        <v>170</v>
+      <c r="F40" s="141" t="s">
+        <v>311</v>
+      </c>
+      <c r="G40" s="97">
+        <v>80</v>
+      </c>
+      <c r="H40" s="119" t="s">
+        <v>317</v>
+      </c>
+      <c r="I40" s="120" t="s">
+        <v>318</v>
+      </c>
+      <c r="J40" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K40" s="97">
+        <v>5</v>
+      </c>
+      <c r="L40" s="97" t="s">
+        <v>235</v>
       </c>
       <c r="M40" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="97">
         <v>3</v>
       </c>
-      <c r="B41" s="118" t="s">
-        <v>194</v>
+      <c r="B41" s="97" t="s">
+        <v>265</v>
       </c>
       <c r="C41" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="78" t="s">
+      <c r="D41" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="E41" s="104" t="s">
+      <c r="E41" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F41" s="122" t="s">
-        <v>253</v>
+      <c r="F41" s="141" t="s">
+        <v>311</v>
       </c>
       <c r="G41" s="97">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H41" s="120" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="I41" s="120" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="J41" s="97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K41" s="97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L41" s="97" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="M41" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="97">
         <v>3</v>
       </c>
-      <c r="B42" s="118" t="s">
-        <v>195</v>
+      <c r="B42" s="97" t="s">
+        <v>267</v>
       </c>
       <c r="C42" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D42" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F42" s="122" t="s">
-        <v>253</v>
+        <v>276</v>
+      </c>
+      <c r="D42" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" s="123" t="s">
+        <v>281</v>
       </c>
       <c r="G42" s="97">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="H42" s="120" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="I42" s="120" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="J42" s="97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K42" s="97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42" s="97" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="M42" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="97">
         <v>3</v>
       </c>
-      <c r="B43" s="109" t="s">
-        <v>117</v>
+      <c r="B43" s="97" t="s">
+        <v>268</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="F43" s="122" t="s">
-        <v>253</v>
+        <v>276</v>
+      </c>
+      <c r="D43" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E43" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" s="123" t="s">
+        <v>312</v>
       </c>
       <c r="G43" s="97">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="H43" s="120" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="I43" s="120" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="J43" s="97" t="s">
-        <v>212</v>
-      </c>
-      <c r="K43" s="97" t="s">
-        <v>260</v>
-      </c>
-      <c r="L43" s="124" t="s">
-        <v>259</v>
+        <v>213</v>
+      </c>
+      <c r="K43" s="97">
+        <v>5</v>
+      </c>
+      <c r="L43" s="97" t="s">
+        <v>282</v>
       </c>
       <c r="M43" s="97" t="s">
         <v>294</v>
@@ -10990,301 +11007,323 @@
       <c r="A44" s="97">
         <v>3</v>
       </c>
-      <c r="B44" s="118" t="s">
-        <v>248</v>
+      <c r="B44" s="97" t="s">
+        <v>319</v>
       </c>
       <c r="C44" s="97" t="s">
         <v>203</v>
       </c>
-      <c r="D44" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F44" s="97" t="s">
-        <v>238</v>
+      <c r="D44" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F44" s="123" t="s">
+        <v>293</v>
       </c>
       <c r="G44" s="97">
-        <v>15</v>
+        <v>0.75</v>
       </c>
       <c r="H44" s="120" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="I44" s="120" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="J44" s="97" t="s">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="K44" s="97">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="L44" s="97" t="s">
+        <v>235</v>
       </c>
       <c r="M44" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="110">
+    <row r="45" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="97">
         <v>3</v>
       </c>
-      <c r="B45" s="123" t="s">
-        <v>249</v>
-      </c>
-      <c r="C45" s="110" t="s">
+      <c r="B45" s="97" t="s">
+        <v>327</v>
+      </c>
+      <c r="C45" s="97" t="s">
         <v>203</v>
       </c>
-      <c r="D45" s="123" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" s="123" t="s">
-        <v>219</v>
-      </c>
-      <c r="F45" s="110" t="s">
-        <v>238</v>
-      </c>
-      <c r="G45" s="110">
-        <v>15</v>
-      </c>
-      <c r="H45" s="131" t="s">
-        <v>250</v>
-      </c>
-      <c r="I45" s="131" t="s">
-        <v>251</v>
-      </c>
-      <c r="J45" s="110" t="s">
-        <v>124</v>
-      </c>
-      <c r="K45" s="110">
-        <v>1</v>
-      </c>
-      <c r="L45" s="110"/>
+      <c r="D45" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E45" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="123" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="97">
+        <v>0.75</v>
+      </c>
+      <c r="H45" s="120" t="s">
+        <v>322</v>
+      </c>
+      <c r="I45" s="120" t="s">
+        <v>323</v>
+      </c>
+      <c r="J45" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K45" s="97">
+        <v>5</v>
+      </c>
+      <c r="L45" s="97" t="s">
+        <v>235</v>
+      </c>
       <c r="M45" s="97" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="97">
-        <v>4</v>
-      </c>
-      <c r="B46" s="118" t="s">
-        <v>261</v>
+        <v>3</v>
+      </c>
+      <c r="B46" s="97" t="s">
+        <v>271</v>
       </c>
       <c r="C46" s="97" t="s">
-        <v>190</v>
-      </c>
-      <c r="D46" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F46" s="97">
-        <v>5</v>
+        <v>277</v>
+      </c>
+      <c r="D46" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E46" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46" s="123" t="s">
+        <v>328</v>
       </c>
       <c r="G46" s="97">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="J46" s="97" t="s">
         <v>213</v>
       </c>
+      <c r="K46" s="97">
+        <v>5</v>
+      </c>
+      <c r="L46" s="97" t="s">
+        <v>235</v>
+      </c>
       <c r="M46" s="97" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="97">
-        <v>4</v>
-      </c>
-      <c r="B47" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="C47" s="80" t="s">
-        <v>186</v>
-      </c>
-      <c r="D47" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F47" s="133" t="s">
-        <v>253</v>
-      </c>
-      <c r="G47" s="78">
-        <v>95</v>
-      </c>
-      <c r="H47" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I47" s="102" t="s">
-        <v>214</v>
+        <v>3</v>
+      </c>
+      <c r="B47" s="97" t="s">
+        <v>329</v>
+      </c>
+      <c r="C47" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D47" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F47" s="123" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47" s="97">
+        <v>15</v>
+      </c>
+      <c r="H47" s="120" t="s">
+        <v>314</v>
+      </c>
+      <c r="I47" s="120" t="s">
+        <v>324</v>
+      </c>
+      <c r="J47" s="97" t="s">
+        <v>213</v>
       </c>
       <c r="K47" s="97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47" s="97" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="M47" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="97">
-        <v>4</v>
-      </c>
-      <c r="B48" s="125" t="s">
-        <v>156</v>
+    <row r="48" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="80">
+        <v>3</v>
+      </c>
+      <c r="B48" s="109" t="s">
+        <v>193</v>
       </c>
       <c r="C48" s="80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D48" s="78" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E48" s="104" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" s="133" t="s">
+        <v>219</v>
+      </c>
+      <c r="F48" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="G48" s="78">
+      <c r="G48" s="80">
         <v>95</v>
       </c>
-      <c r="H48" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="I48" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="K48" s="97">
+      <c r="H48" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="J48" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="K48" s="80">
         <v>3</v>
       </c>
-      <c r="L48" s="97" t="s">
+      <c r="L48" s="80" t="s">
         <v>170</v>
       </c>
       <c r="M48" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="97">
-        <v>4</v>
-      </c>
-      <c r="B49" s="97" t="s">
-        <v>265</v>
+        <v>3</v>
+      </c>
+      <c r="B49" s="118" t="s">
+        <v>194</v>
       </c>
       <c r="C49" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="109" t="s">
+      <c r="D49" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E49" s="109" t="s">
+      <c r="E49" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F49" s="133" t="s">
+      <c r="F49" s="122" t="s">
         <v>253</v>
       </c>
       <c r="G49" s="97">
         <v>95</v>
       </c>
       <c r="H49" s="120" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="I49" s="120" t="s">
-        <v>288</v>
+        <v>228</v>
+      </c>
+      <c r="J49" s="97" t="s">
+        <v>212</v>
       </c>
       <c r="K49" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L49" s="97" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="M49" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="97">
-        <v>4</v>
-      </c>
-      <c r="B50" s="97" t="s">
-        <v>266</v>
+        <v>3</v>
+      </c>
+      <c r="B50" s="118" t="s">
+        <v>195</v>
       </c>
       <c r="C50" s="97" t="s">
-        <v>274</v>
-      </c>
-      <c r="D50" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E50" s="109" t="s">
+      <c r="E50" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F50" s="133" t="s">
+      <c r="F50" s="122" t="s">
         <v>253</v>
       </c>
       <c r="G50" s="97">
         <v>95</v>
       </c>
       <c r="H50" s="120" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="I50" s="120" t="s">
-        <v>289</v>
+        <v>228</v>
+      </c>
+      <c r="J50" s="97" t="s">
+        <v>212</v>
       </c>
       <c r="K50" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L50" s="97" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="M50" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="97">
+    <row r="51" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="99">
         <v>4</v>
       </c>
-      <c r="B51" s="97" t="s">
-        <v>267</v>
-      </c>
-      <c r="C51" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D51" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E51" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F51" s="124" t="s">
-        <v>279</v>
-      </c>
-      <c r="G51" s="97">
-        <v>10</v>
-      </c>
-      <c r="H51" s="120" t="s">
-        <v>283</v>
-      </c>
-      <c r="I51" s="120" t="s">
-        <v>290</v>
-      </c>
-      <c r="K51" s="97">
+      <c r="B51" s="116" t="s">
+        <v>261</v>
+      </c>
+      <c r="C51" s="99" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" s="116" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="F51" s="99">
         <v>5</v>
       </c>
-      <c r="L51" s="97" t="s">
-        <v>282</v>
-      </c>
-      <c r="M51" s="97" t="s">
+      <c r="G51" s="99">
+        <v>5</v>
+      </c>
+      <c r="H51" s="117" t="s">
+        <v>263</v>
+      </c>
+      <c r="I51" s="117" t="s">
+        <v>264</v>
+      </c>
+      <c r="J51" s="99" t="s">
+        <v>213</v>
+      </c>
+      <c r="K51" s="99"/>
+      <c r="L51" s="99"/>
+      <c r="M51" s="99" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11292,38 +11331,35 @@
       <c r="A52" s="97">
         <v>4</v>
       </c>
-      <c r="B52" s="97" t="s">
-        <v>269</v>
-      </c>
-      <c r="C52" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="D52" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="F52" s="133" t="s">
+      <c r="B52" s="124" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D52" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" s="132" t="s">
         <v>253</v>
       </c>
-      <c r="G52" s="97">
+      <c r="G52" s="78">
         <v>95</v>
       </c>
-      <c r="H52" s="120" t="s">
-        <v>278</v>
-      </c>
-      <c r="I52" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="J52" s="97" t="s">
-        <v>213</v>
+      <c r="H52" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I52" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K52" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L52" s="97" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="M52" s="97" t="s">
         <v>294</v>
@@ -11333,35 +11369,35 @@
       <c r="A53" s="97">
         <v>4</v>
       </c>
-      <c r="B53" s="97" t="s">
-        <v>268</v>
-      </c>
-      <c r="C53" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D53" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E53" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F53" s="124" t="s">
-        <v>279</v>
-      </c>
-      <c r="G53" s="97">
-        <v>10</v>
-      </c>
-      <c r="H53" s="120" t="s">
-        <v>283</v>
-      </c>
-      <c r="I53" s="120" t="s">
-        <v>291</v>
+      <c r="B53" s="124" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D53" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="132" t="s">
+        <v>253</v>
+      </c>
+      <c r="G53" s="78">
+        <v>95</v>
+      </c>
+      <c r="H53" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I53" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="K53" s="97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L53" s="97" t="s">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="M53" s="97" t="s">
         <v>294</v>
@@ -11372,10 +11408,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="97" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C54" s="97" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="D54" s="109" t="s">
         <v>153</v>
@@ -11383,7 +11419,7 @@
       <c r="E54" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F54" s="133" t="s">
+      <c r="F54" s="132" t="s">
         <v>253</v>
       </c>
       <c r="G54" s="97">
@@ -11393,10 +11429,7 @@
         <v>278</v>
       </c>
       <c r="I54" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="J54" s="97" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="K54" s="97">
         <v>5</v>
@@ -11413,31 +11446,28 @@
         <v>4</v>
       </c>
       <c r="B55" s="97" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C55" s="97" t="s">
-        <v>203</v>
-      </c>
-      <c r="D55" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E55" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F55" s="97" t="s">
-        <v>293</v>
+        <v>274</v>
+      </c>
+      <c r="D55" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F55" s="132" t="s">
+        <v>253</v>
       </c>
       <c r="G55" s="97">
-        <v>0.75</v>
+        <v>95</v>
       </c>
       <c r="H55" s="120" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I55" s="120" t="s">
-        <v>284</v>
-      </c>
-      <c r="J55" s="97" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="K55" s="97">
         <v>5</v>
@@ -11454,10 +11484,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="97" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C56" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D56" s="97" t="s">
         <v>223</v>
@@ -11465,69 +11495,268 @@
       <c r="E56" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="F56" s="109" t="s">
-        <v>280</v>
-      </c>
-      <c r="G56" s="109">
-        <v>3.5</v>
+      <c r="F56" s="123" t="s">
+        <v>279</v>
+      </c>
+      <c r="G56" s="97">
+        <v>10</v>
       </c>
       <c r="H56" s="120" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I56" s="120" t="s">
-        <v>285</v>
-      </c>
-      <c r="J56" s="97" t="s">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="K56" s="97">
         <v>5</v>
       </c>
       <c r="L56" s="97" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="M56" s="97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="132" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="110">
+    <row r="57" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="97">
         <v>4</v>
       </c>
-      <c r="B57" s="110" t="s">
+      <c r="B57" s="97" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D57" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F57" s="132" t="s">
+        <v>253</v>
+      </c>
+      <c r="G57" s="97">
+        <v>95</v>
+      </c>
+      <c r="H57" s="120" t="s">
+        <v>278</v>
+      </c>
+      <c r="I57" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="J57" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K57" s="97">
+        <v>5</v>
+      </c>
+      <c r="L57" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M57" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="97">
+        <v>4</v>
+      </c>
+      <c r="B58" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C58" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" s="123" t="s">
+        <v>279</v>
+      </c>
+      <c r="G58" s="97">
+        <v>10</v>
+      </c>
+      <c r="H58" s="120" t="s">
+        <v>283</v>
+      </c>
+      <c r="I58" s="120" t="s">
+        <v>291</v>
+      </c>
+      <c r="K58" s="97">
+        <v>5</v>
+      </c>
+      <c r="L58" s="97" t="s">
+        <v>282</v>
+      </c>
+      <c r="M58" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="97">
+        <v>4</v>
+      </c>
+      <c r="B59" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C59" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D59" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E59" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F59" s="132" t="s">
+        <v>253</v>
+      </c>
+      <c r="G59" s="97">
+        <v>95</v>
+      </c>
+      <c r="H59" s="120" t="s">
+        <v>278</v>
+      </c>
+      <c r="I59" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="J59" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K59" s="97">
+        <v>5</v>
+      </c>
+      <c r="L59" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M59" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="97">
+        <v>4</v>
+      </c>
+      <c r="B60" s="97" t="s">
+        <v>272</v>
+      </c>
+      <c r="C60" s="97" t="s">
+        <v>203</v>
+      </c>
+      <c r="D60" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F60" s="97" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" s="97">
+        <v>0.75</v>
+      </c>
+      <c r="H60" s="120" t="s">
+        <v>287</v>
+      </c>
+      <c r="I60" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="J60" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K60" s="97">
+        <v>5</v>
+      </c>
+      <c r="L60" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M60" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="97">
+        <v>4</v>
+      </c>
+      <c r="B61" s="97" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D61" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F61" s="109" t="s">
+        <v>280</v>
+      </c>
+      <c r="G61" s="109">
+        <v>3.5</v>
+      </c>
+      <c r="H61" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="I61" s="120" t="s">
+        <v>285</v>
+      </c>
+      <c r="J61" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K61" s="97">
+        <v>5</v>
+      </c>
+      <c r="L61" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M61" s="97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="131" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="110">
+        <v>4</v>
+      </c>
+      <c r="B62" s="110" t="s">
         <v>273</v>
       </c>
-      <c r="C57" s="110" t="s">
+      <c r="C62" s="110" t="s">
         <v>276</v>
       </c>
-      <c r="D57" s="110" t="s">
+      <c r="D62" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="E57" s="110" t="s">
+      <c r="E62" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="F57" s="134" t="s">
+      <c r="F62" s="133" t="s">
         <v>281</v>
       </c>
-      <c r="G57" s="110">
+      <c r="G62" s="110">
         <v>15</v>
       </c>
-      <c r="H57" s="131" t="s">
+      <c r="H62" s="130" t="s">
         <v>283</v>
       </c>
-      <c r="I57" s="131" t="s">
+      <c r="I62" s="130" t="s">
         <v>285</v>
       </c>
-      <c r="J57" s="110" t="s">
+      <c r="J62" s="110" t="s">
         <v>213</v>
       </c>
-      <c r="K57" s="110">
+      <c r="K62" s="110">
         <v>5</v>
       </c>
-      <c r="L57" s="110" t="s">
+      <c r="L62" s="110" t="s">
         <v>282</v>
       </c>
-      <c r="M57" s="110" t="s">
+      <c r="M62" s="110" t="s">
         <v>294</v>
       </c>
     </row>
@@ -11544,1027 +11773,1022 @@
   <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="151"/>
-    <col min="2" max="2" width="23.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="151" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33" style="151" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.1640625" style="151" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="151"/>
+    <col min="1" max="1" width="10.83203125" style="134"/>
+    <col min="2" max="2" width="23.5" style="134" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="134" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="134" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="134" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" style="134" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="134" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="134" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="134" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="134"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="162" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="163" t="s">
+    <row r="1" spans="1:13" s="136" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="157" t="s">
         <v>313</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163" t="s">
+      <c r="C1" s="157"/>
+      <c r="D1" s="157" t="s">
         <v>302</v>
       </c>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163" t="s">
+      <c r="E1" s="157"/>
+      <c r="F1" s="157" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163" t="s">
+      <c r="G1" s="157"/>
+      <c r="H1" s="157" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="163"/>
-      <c r="J1" s="163" t="s">
+      <c r="I1" s="157"/>
+      <c r="J1" s="157" t="s">
         <v>305</v>
       </c>
-      <c r="K1" s="163"/>
-      <c r="L1" s="163" t="s">
+      <c r="K1" s="157"/>
+      <c r="L1" s="157" t="s">
         <v>306</v>
       </c>
-      <c r="M1" s="163"/>
-    </row>
-    <row r="2" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="M1" s="157"/>
+    </row>
+    <row r="2" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="137" t="s">
         <v>307</v>
       </c>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
-      <c r="L2" s="165"/>
-      <c r="M2" s="165"/>
-    </row>
-    <row r="3" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="152" t="s">
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+    </row>
+    <row r="3" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="167" t="s">
+      <c r="D3" s="140" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="167" t="s">
+      <c r="E3" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="167" t="s">
+      <c r="F3" s="140" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="167" t="s">
+      <c r="G3" s="140" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="152" t="s">
+    <row r="4" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="C4" s="140" t="s">
         <v>151</v>
       </c>
-      <c r="D4" s="167" t="s">
+      <c r="D4" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="167" t="s">
+      <c r="E4" s="140" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="167" t="s">
+      <c r="F4" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="167" t="s">
+      <c r="G4" s="140" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="152" t="s">
+    <row r="5" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="80" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="167">
+      <c r="C5" s="140">
         <v>1</v>
       </c>
-      <c r="D5" s="167" t="s">
+      <c r="D5" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="167">
+      <c r="E5" s="140">
         <v>1</v>
       </c>
-      <c r="F5" s="167" t="s">
+      <c r="F5" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="167">
+      <c r="G5" s="140">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F6" s="155" t="s">
+    <row r="6" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="155" t="s">
+      <c r="G6" s="109" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="164" t="s">
+    <row r="7" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="137" t="s">
         <v>308</v>
       </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
-      <c r="L9" s="165"/>
-      <c r="M9" s="165"/>
-    </row>
-    <row r="10" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="152" t="s">
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138"/>
+      <c r="K9" s="138"/>
+      <c r="L9" s="138"/>
+      <c r="M9" s="138"/>
+    </row>
+    <row r="10" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="152">
+      <c r="E10" s="80">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F11" s="155" t="s">
+    <row r="11" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F11" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="168" t="s">
+      <c r="G11" s="141" t="s">
         <v>229</v>
       </c>
-      <c r="H11" s="155" t="s">
+      <c r="H11" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="156" t="s">
+      <c r="I11" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F12" s="155" t="s">
+    <row r="12" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F12" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="G12" s="168" t="s">
+      <c r="G12" s="141" t="s">
         <v>229</v>
       </c>
-      <c r="H12" s="155" t="s">
+      <c r="H12" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="156" t="s">
+      <c r="I12" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F13" s="155" t="s">
+    <row r="13" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F13" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="168" t="s">
+      <c r="G13" s="141" t="s">
         <v>229</v>
       </c>
-      <c r="H13" s="155" t="s">
+      <c r="H13" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="I13" s="156" t="s">
+      <c r="I13" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F14" s="155" t="s">
+    <row r="14" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F14" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="156" t="s">
+      <c r="G14" s="129" t="s">
         <v>229</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="156" t="s">
+      <c r="I14" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F15" s="155" t="s">
+    <row r="15" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F15" s="109" t="s">
         <v>233</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="109" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F16" s="155" t="s">
+    <row r="16" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F16" s="109" t="s">
         <v>234</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="109" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H17" s="155" t="s">
+    <row r="17" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="109" t="s">
         <v>248</v>
       </c>
-      <c r="I17" s="152" t="s">
+      <c r="I17" s="80" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H18" s="155" t="s">
+    <row r="18" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H18" s="109" t="s">
         <v>249</v>
       </c>
-      <c r="I18" s="152" t="s">
+      <c r="I18" s="80" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="164" t="s">
+    <row r="19" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="165"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
-      <c r="H20" s="165"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="165"/>
-      <c r="K20" s="165"/>
-      <c r="L20" s="165"/>
-      <c r="M20" s="165"/>
-    </row>
-    <row r="21" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="152" t="s">
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="138"/>
+    </row>
+    <row r="21" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="C21" s="168" t="s">
+      <c r="C21" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="F21" s="167" t="s">
+      <c r="F21" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="G21" s="168" t="s">
+      <c r="G21" s="141" t="s">
         <v>229</v>
       </c>
-      <c r="H21" s="167" t="s">
+      <c r="H21" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="I21" s="168" t="s">
+      <c r="I21" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="J21" s="167" t="s">
+      <c r="J21" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="K21" s="168" t="s">
+      <c r="K21" s="141" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="152" t="s">
+    <row r="22" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="168" t="s">
+      <c r="C22" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="F22" s="167" t="s">
+      <c r="F22" s="140" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="168" t="s">
+      <c r="G22" s="141" t="s">
         <v>229</v>
       </c>
-      <c r="H22" s="167" t="s">
+      <c r="H22" s="140" t="s">
         <v>156</v>
       </c>
-      <c r="I22" s="168" t="s">
+      <c r="I22" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="J22" s="167" t="s">
+      <c r="J22" s="140" t="s">
         <v>156</v>
       </c>
-      <c r="K22" s="168" t="s">
+      <c r="K22" s="141" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F23" s="155" t="s">
+    <row r="23" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F23" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="155" t="s">
+      <c r="G23" s="109" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F24" s="155" t="s">
+    <row r="24" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F24" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="155">
+      <c r="G24" s="109">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F25" s="155" t="s">
+    <row r="25" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F25" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="G25" s="155" t="s">
+      <c r="G25" s="109" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F26" s="160" t="s">
+    <row r="26" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F26" s="128" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="155">
+      <c r="G26" s="109">
         <v>10</v>
       </c>
-      <c r="H26" s="155" t="s">
+      <c r="H26" s="109" t="s">
         <v>201</v>
       </c>
-      <c r="I26" s="152">
+      <c r="I26" s="80">
         <v>22</v>
       </c>
-      <c r="J26" s="155" t="s">
+      <c r="J26" s="109" t="s">
         <v>261</v>
       </c>
-      <c r="K26" s="152">
+      <c r="K26" s="80">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F27" s="155" t="s">
+    <row r="27" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F27" s="109" t="s">
         <v>209</v>
       </c>
-      <c r="G27" s="155" t="s">
+      <c r="G27" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="H27" s="155" t="s">
+      <c r="H27" s="109" t="s">
         <v>209</v>
       </c>
-      <c r="I27" s="155" t="s">
+      <c r="I27" s="109" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F28" s="155" t="s">
+    <row r="28" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F28" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="155" t="s">
+      <c r="G28" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="H28" s="155" t="s">
+      <c r="H28" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="155" t="s">
+      <c r="I28" s="109" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="164" t="s">
+    <row r="29" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="137" t="s">
         <v>309</v>
       </c>
-      <c r="B30" s="165"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="165"/>
-      <c r="F30" s="165"/>
-      <c r="G30" s="165"/>
-      <c r="H30" s="165"/>
-      <c r="I30" s="165"/>
-      <c r="J30" s="165"/>
-      <c r="K30" s="165"/>
-      <c r="L30" s="165"/>
-      <c r="M30" s="165"/>
-    </row>
-    <row r="31" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H31" s="155" t="s">
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="138"/>
+    </row>
+    <row r="31" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H31" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="I31" s="156" t="s">
+      <c r="I31" s="129" t="s">
         <v>310</v>
       </c>
-      <c r="J31" s="155" t="s">
+      <c r="J31" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="K31" s="156" t="s">
+      <c r="K31" s="129" t="s">
         <v>222</v>
       </c>
-      <c r="L31" s="155" t="s">
+      <c r="L31" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="M31" s="156" t="s">
+      <c r="M31" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H32" s="155" t="s">
+    <row r="32" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H32" s="109" t="s">
         <v>255</v>
       </c>
-      <c r="I32" s="156" t="s">
+      <c r="I32" s="129" t="s">
         <v>310</v>
       </c>
-      <c r="J32" s="155" t="s">
+      <c r="J32" s="109" t="s">
         <v>255</v>
       </c>
-      <c r="K32" s="156" t="s">
+      <c r="K32" s="129" t="s">
         <v>222</v>
       </c>
-      <c r="L32" s="155" t="s">
+      <c r="L32" s="109" t="s">
         <v>255</v>
       </c>
-      <c r="M32" s="156" t="s">
+      <c r="M32" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="33" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H33" s="155" t="s">
+    <row r="33" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" s="109" t="s">
         <v>256</v>
       </c>
-      <c r="I33" s="156" t="s">
+      <c r="I33" s="129" t="s">
         <v>310</v>
       </c>
-      <c r="J33" s="155" t="s">
+      <c r="J33" s="109" t="s">
         <v>256</v>
       </c>
-      <c r="K33" s="156" t="s">
+      <c r="K33" s="129" t="s">
         <v>222</v>
       </c>
-      <c r="L33" s="155" t="s">
+      <c r="L33" s="109" t="s">
         <v>256</v>
       </c>
-      <c r="M33" s="156" t="s">
+      <c r="M33" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="34" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H34" s="155" t="s">
+    <row r="34" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H34" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="I34" s="156" t="s">
+      <c r="I34" s="129" t="s">
         <v>310</v>
       </c>
-      <c r="J34" s="155" t="s">
+      <c r="J34" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="K34" s="156" t="s">
+      <c r="K34" s="129" t="s">
         <v>222</v>
       </c>
-      <c r="L34" s="155" t="s">
+      <c r="L34" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="M34" s="156" t="s">
+      <c r="M34" s="129" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="35" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H36" s="152" t="s">
+    <row r="35" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="I36" s="168" t="s">
+      <c r="I36" s="141" t="s">
         <v>311</v>
       </c>
-      <c r="J36" s="152" t="s">
+      <c r="J36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="K36" s="168" t="s">
+      <c r="K36" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="L36" s="152" t="s">
+      <c r="L36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="M36" s="168" t="s">
+      <c r="M36" s="141" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="37" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H37" s="152" t="s">
+    <row r="37" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="I37" s="159" t="s">
+      <c r="I37" s="135" t="s">
         <v>281</v>
       </c>
-      <c r="J37" s="152" t="s">
+      <c r="J37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="K37" s="159" t="s">
+      <c r="K37" s="135" t="s">
         <v>279</v>
       </c>
-      <c r="L37" s="152" t="s">
+      <c r="L37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="M37" s="159" t="s">
+      <c r="M37" s="135" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H38" s="152" t="s">
+    <row r="38" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="I38" s="168" t="s">
+      <c r="I38" s="141" t="s">
         <v>311</v>
       </c>
-      <c r="J38" s="152" t="s">
+      <c r="J38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="K38" s="168" t="s">
+      <c r="K38" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="L38" s="152" t="s">
+      <c r="L38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="M38" s="168" t="s">
+      <c r="M38" s="141" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="39" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H39" s="152" t="s">
+    <row r="39" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="159" t="s">
+      <c r="I39" s="135" t="s">
         <v>312</v>
       </c>
-      <c r="J39" s="152" t="s">
+      <c r="J39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="K39" s="159" t="s">
+      <c r="K39" s="135" t="s">
         <v>281</v>
       </c>
-      <c r="L39" s="152" t="s">
+      <c r="L39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="M39" s="159" t="s">
+      <c r="M39" s="135" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="40" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H40" s="152" t="s">
+    <row r="40" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="I40" s="168" t="s">
+      <c r="I40" s="141" t="s">
         <v>311</v>
       </c>
-      <c r="J40" s="152" t="s">
+      <c r="J40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="K40" s="168" t="s">
+      <c r="K40" s="141" t="s">
         <v>222</v>
       </c>
-      <c r="L40" s="152" t="s">
+      <c r="L40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="M40" s="168" t="s">
+      <c r="M40" s="141" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H42" s="152" t="s">
+    <row r="41" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H42" s="80" t="s">
         <v>272</v>
       </c>
-      <c r="I42" s="152" t="s">
+      <c r="I42" s="80" t="s">
         <v>293</v>
       </c>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="152"/>
-    </row>
-    <row r="43" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H43" s="152" t="s">
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="80"/>
+      <c r="M42" s="80"/>
+    </row>
+    <row r="43" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="I43" s="155" t="s">
+      <c r="I43" s="109" t="s">
         <v>280</v>
       </c>
-      <c r="J43" s="152"/>
-      <c r="K43" s="155"/>
-      <c r="L43" s="152"/>
-      <c r="M43" s="155"/>
-    </row>
-    <row r="44" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H44" s="152" t="s">
+      <c r="J43" s="80"/>
+      <c r="K43" s="109"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="109"/>
+    </row>
+    <row r="44" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H44" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="I44" s="159" t="s">
+      <c r="I44" s="135" t="s">
         <v>281</v>
       </c>
-      <c r="J44" s="152"/>
-      <c r="K44" s="159"/>
-      <c r="L44" s="152"/>
-      <c r="M44" s="159"/>
-    </row>
-    <row r="45" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="8:13" s="166" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H52" s="151"/>
-      <c r="I52" s="151"/>
-      <c r="J52" s="151"/>
-      <c r="K52" s="151"/>
-      <c r="L52" s="151"/>
-      <c r="M52" s="151"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="135"/>
+      <c r="L44" s="80"/>
+      <c r="M44" s="135"/>
+    </row>
+    <row r="45" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" s="134"/>
+      <c r="I52" s="134"/>
+      <c r="J52" s="134"/>
+      <c r="K52" s="134"/>
+      <c r="L52" s="134"/>
+      <c r="M52" s="134"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="150" t="s">
+      <c r="H74" s="158" t="s">
         <v>304</v>
       </c>
-      <c r="I74" s="150"/>
-      <c r="J74" s="150" t="s">
+      <c r="I74" s="158"/>
+      <c r="J74" s="158" t="s">
         <v>305</v>
       </c>
-      <c r="K74" s="150"/>
-      <c r="L74" s="150" t="s">
+      <c r="K74" s="158"/>
+      <c r="L74" s="158" t="s">
         <v>306</v>
       </c>
-      <c r="M74" s="150"/>
+      <c r="M74" s="158"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="150" t="s">
+      <c r="B75" s="158" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="150"/>
-      <c r="D75" s="150" t="s">
+      <c r="C75" s="158"/>
+      <c r="D75" s="158" t="s">
         <v>302</v>
       </c>
-      <c r="E75" s="150"/>
-      <c r="F75" s="150" t="s">
+      <c r="E75" s="158"/>
+      <c r="F75" s="158" t="s">
         <v>303</v>
       </c>
-      <c r="G75" s="150"/>
-      <c r="H75" s="155" t="s">
+      <c r="G75" s="158"/>
+      <c r="H75" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="I75" s="156" t="s">
+      <c r="I75" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J75" s="155" t="s">
+      <c r="J75" s="109" t="s">
         <v>261</v>
       </c>
-      <c r="K75" s="152">
+      <c r="K75" s="80">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B76" s="152" t="s">
+      <c r="B76" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="153" t="s">
+      <c r="C76" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="154" t="s">
+      <c r="D76" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="E76" s="153" t="s">
+      <c r="E76" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="154" t="s">
+      <c r="F76" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="G76" s="153" t="s">
+      <c r="G76" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="H76" s="155" t="s">
+      <c r="H76" s="109" t="s">
         <v>255</v>
       </c>
-      <c r="I76" s="156" t="s">
+      <c r="I76" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J76" s="154" t="s">
+      <c r="J76" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="K76" s="157" t="s">
+      <c r="K76" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="77" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B77" s="152" t="s">
+      <c r="B77" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C77" s="153" t="s">
+      <c r="C77" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="D77" s="154" t="s">
+      <c r="D77" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="E77" s="153" t="s">
+      <c r="E77" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="F77" s="154" t="s">
+      <c r="F77" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="G77" s="153" t="s">
+      <c r="G77" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="H77" s="155" t="s">
+      <c r="H77" s="109" t="s">
         <v>256</v>
       </c>
-      <c r="I77" s="156" t="s">
+      <c r="I77" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J77" s="154" t="s">
+      <c r="J77" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="K77" s="157" t="s">
+      <c r="K77" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="78" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B78" s="152" t="s">
+      <c r="B78" s="80" t="s">
         <v>176</v>
       </c>
-      <c r="C78" s="153">
+      <c r="C78" s="78">
         <v>1</v>
       </c>
-      <c r="D78" s="154" t="s">
+      <c r="D78" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="E78" s="153">
+      <c r="E78" s="78">
         <v>1</v>
       </c>
-      <c r="F78" s="154" t="s">
+      <c r="F78" s="124" t="s">
         <v>176</v>
       </c>
-      <c r="G78" s="153">
+      <c r="G78" s="78">
         <v>0</v>
       </c>
-      <c r="H78" s="155" t="s">
+      <c r="H78" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="I78" s="156" t="s">
+      <c r="I78" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J78" s="152" t="s">
+      <c r="J78" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="K78" s="157" t="s">
+      <c r="K78" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="79" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B79" s="152" t="s">
+      <c r="B79" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="C79" s="158" t="s">
+      <c r="C79" s="105" t="s">
         <v>222</v>
       </c>
-      <c r="D79" s="152" t="s">
+      <c r="D79" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="E79" s="152">
+      <c r="E79" s="80">
         <v>5</v>
       </c>
-      <c r="F79" s="155" t="s">
+      <c r="F79" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="G79" s="155" t="s">
+      <c r="G79" s="109" t="s">
         <v>227</v>
       </c>
-      <c r="H79" s="155" t="s">
+      <c r="H79" s="109" t="s">
         <v>201</v>
       </c>
-      <c r="I79" s="152">
+      <c r="I79" s="80">
         <v>22</v>
       </c>
-      <c r="J79" s="152" t="s">
+      <c r="J79" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="K79" s="157" t="s">
+      <c r="K79" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="80" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B80" s="152" t="s">
+      <c r="B80" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="C80" s="158" t="s">
+      <c r="C80" s="105" t="s">
         <v>222</v>
       </c>
-      <c r="F80" s="155" t="s">
+      <c r="F80" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="G80" s="155" t="s">
+      <c r="G80" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="H80" s="155" t="s">
+      <c r="H80" s="109" t="s">
         <v>209</v>
       </c>
-      <c r="I80" s="155" t="s">
+      <c r="I80" s="109" t="s">
         <v>140</v>
       </c>
-      <c r="J80" s="152" t="s">
+      <c r="J80" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="K80" s="159" t="s">
+      <c r="K80" s="135" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="81" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F81" s="155" t="s">
+      <c r="F81" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="G81" s="155">
+      <c r="G81" s="109">
         <v>20</v>
       </c>
-      <c r="H81" s="155" t="s">
+      <c r="H81" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="I81" s="155" t="s">
+      <c r="I81" s="109" t="s">
         <v>140</v>
       </c>
-      <c r="J81" s="152" t="s">
+      <c r="J81" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="K81" s="157" t="s">
+      <c r="K81" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="82" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F82" s="155" t="s">
+      <c r="F82" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="G82" s="155" t="s">
+      <c r="G82" s="109" t="s">
         <v>224</v>
       </c>
-      <c r="H82" s="154" t="s">
+      <c r="H82" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="I82" s="157" t="s">
+      <c r="I82" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="J82" s="152" t="s">
+      <c r="J82" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="K82" s="159" t="s">
+      <c r="K82" s="135" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="83" spans="6:11" ht="17" x14ac:dyDescent="0.15">
-      <c r="F83" s="160" t="s">
+      <c r="F83" s="128" t="s">
         <v>201</v>
       </c>
-      <c r="G83" s="155">
+      <c r="G83" s="109">
         <v>10</v>
       </c>
-      <c r="H83" s="154" t="s">
+      <c r="H83" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="I83" s="157" t="s">
+      <c r="I83" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="J83" s="152" t="s">
+      <c r="J83" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="K83" s="157" t="s">
+      <c r="K83" s="132" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="84" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F84" s="155" t="s">
+      <c r="F84" s="109" t="s">
         <v>209</v>
       </c>
-      <c r="G84" s="155" t="s">
+      <c r="G84" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="H84" s="155" t="s">
+      <c r="H84" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="I84" s="156" t="s">
+      <c r="I84" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J84" s="152" t="s">
+      <c r="J84" s="80" t="s">
         <v>272</v>
       </c>
-      <c r="K84" s="152" t="s">
+      <c r="K84" s="80" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="85" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F85" s="154" t="s">
+      <c r="F85" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="G85" s="161" t="s">
+      <c r="G85" s="111" t="s">
         <v>229</v>
       </c>
-      <c r="H85" s="155" t="s">
+      <c r="H85" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="I85" s="156" t="s">
+      <c r="I85" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J85" s="152" t="s">
+      <c r="J85" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="K85" s="155" t="s">
+      <c r="K85" s="109" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="86" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F86" s="154" t="s">
+      <c r="F86" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="G86" s="161" t="s">
+      <c r="G86" s="111" t="s">
         <v>229</v>
       </c>
-      <c r="H86" s="155" t="s">
+      <c r="H86" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="I86" s="156" t="s">
+      <c r="I86" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="J86" s="152" t="s">
+      <c r="J86" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="K86" s="159" t="s">
+      <c r="K86" s="135" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="87" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F87" s="155" t="s">
+      <c r="F87" s="109" t="s">
         <v>233</v>
       </c>
-      <c r="G87" s="155" t="s">
+      <c r="G87" s="109" t="s">
         <v>226</v>
       </c>
-      <c r="H87" s="155" t="s">
+      <c r="H87" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="I87" s="156" t="s">
+      <c r="I87" s="129" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="88" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F88" s="155" t="s">
+      <c r="F88" s="109" t="s">
         <v>234</v>
       </c>
-      <c r="G88" s="155" t="s">
+      <c r="G88" s="109" t="s">
         <v>300</v>
       </c>
-      <c r="H88" s="155" t="s">
+      <c r="H88" s="109" t="s">
         <v>248</v>
       </c>
-      <c r="I88" s="152" t="s">
+      <c r="I88" s="80" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="89" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F89" s="155" t="s">
+      <c r="F89" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="G89" s="161" t="s">
+      <c r="G89" s="111" t="s">
         <v>229</v>
       </c>
-      <c r="H89" s="155" t="s">
+      <c r="H89" s="109" t="s">
         <v>249</v>
       </c>
-      <c r="I89" s="152" t="s">
+      <c r="I89" s="80" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="90" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F90" s="155" t="s">
+      <c r="F90" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="G90" s="161" t="s">
+      <c r="G90" s="111" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="91" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F91" s="155" t="s">
+      <c r="F91" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="G91" s="161" t="s">
+      <c r="G91" s="111" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="92" spans="6:11" ht="16" x14ac:dyDescent="0.15">
-      <c r="F92" s="155" t="s">
+      <c r="F92" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="G92" s="156" t="s">
+      <c r="G92" s="129" t="s">
         <v>229</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="D75:E75"/>
@@ -12572,6 +12796,11 @@
     <mergeCell ref="H74:I74"/>
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1423" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FAB954-2471-6D43-B7D1-4E2C3EF09753}"/>
+  <xr:revisionPtr revIDLastSave="1483" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB57DC61-75B1-E849-83C0-1BB1F441833B}"/>
   <bookViews>
-    <workbookView xWindow="-3880" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -794,7 +794,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="324">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1648,9 +1648,6 @@
     <t>Drop and Stick - Landing Asymmetry</t>
   </si>
   <si>
-    <t>m/s</t>
-  </si>
-  <si>
     <t>N*s</t>
   </si>
   <si>
@@ -1678,28 +1675,9 @@
     <t>Confidence interval around the mean of 5 jumps must be entirely within ± 10%</t>
   </si>
   <si>
-    <t>Participant steps forward off 50cm box with their preferred leg and lands on the force plates in a squat with thighs parallel to the floor and arms held out ion front of them.  
-Cue: "Land softly and stabilize as quickly as possible"
-TTS target scores are based off old research for now.</t>
-  </si>
-  <si>
-    <t>Participant steps forward off 50cm box with their preferred leg and lands on the force plates in a squat with thighs parallel to the floor and arms held out ion front of them.  
-Cue: "Land softly and stabilize as quickly as possible"
-rPLF target scores are based off old research for now.</t>
-  </si>
-  <si>
-    <t>The amount of force required to bring the body to a stable state following a 50cm drop landing.</t>
-  </si>
-  <si>
-    <t>Time taken to return the body to a stable state following a 50cm drop landing.</t>
-  </si>
-  <si>
     <t>Height in cm</t>
   </si>
   <si>
-    <t>Height of jump divided by total contraction time</t>
-  </si>
-  <si>
     <t>Ratio of force produced by each limb in the lengthening (lowering) phase of the jump</t>
   </si>
   <si>
@@ -1817,7 +1795,7 @@
     <t>3.5*BM</t>
   </si>
   <si>
-    <t>Drop and Stick Asymmetry</t>
+    <t>Drop and Stick - Asymmetry</t>
   </si>
 </sst>
 </file>
@@ -2347,7 +2325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2666,14 +2644,7 @@
     <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
@@ -2993,13 +2964,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3057,7 +3028,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="145" t="s">
+      <c r="G4" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3090,7 +3061,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="143"/>
+      <c r="G5" s="140"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3118,7 +3089,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="143"/>
+      <c r="G6" s="140"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3142,7 +3113,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="143"/>
+      <c r="G7" s="140"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3165,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="143"/>
+      <c r="G8" s="140"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3193,7 +3164,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="143"/>
+      <c r="G9" s="140"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3276,13 +3247,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="144" t="s">
+      <c r="B15" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3337,24 +3308,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="154">
+      <c r="H16" s="151">
         <v>45359</v>
       </c>
-      <c r="I16" s="153"/>
-      <c r="J16" s="155">
+      <c r="I16" s="150"/>
+      <c r="J16" s="152">
         <v>47204</v>
       </c>
-      <c r="K16" s="153"/>
-      <c r="L16" s="156" t="s">
+      <c r="K16" s="150"/>
+      <c r="L16" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="153"/>
-      <c r="N16" s="154">
+      <c r="M16" s="150"/>
+      <c r="N16" s="151">
         <v>45429</v>
       </c>
-      <c r="O16" s="153"/>
-      <c r="P16" s="154"/>
-      <c r="Q16" s="153"/>
+      <c r="O16" s="150"/>
+      <c r="P16" s="151"/>
+      <c r="Q16" s="150"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3428,7 +3399,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="145" t="s">
+      <c r="G18" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3472,7 +3443,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="143"/>
+      <c r="G19" s="140"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3510,7 +3481,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="143"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3556,7 +3527,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="143"/>
+      <c r="G21" s="140"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3592,7 +3563,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="143"/>
+      <c r="G22" s="140"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3630,7 +3601,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="143"/>
+      <c r="G23" s="140"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3670,7 +3641,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="143"/>
+      <c r="G24" s="140"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3861,13 +3832,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="144" t="s">
+      <c r="B32" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="143"/>
-      <c r="D32" s="143"/>
-      <c r="E32" s="143"/>
-      <c r="F32" s="143"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3912,12 +3883,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="152" t="s">
+      <c r="H33" s="149" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="153"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="153"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="150"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3942,7 +3913,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="145" t="s">
+      <c r="G34" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3973,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="143"/>
+      <c r="G35" s="140"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -4002,7 +3973,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="143"/>
+      <c r="G36" s="140"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4031,7 +4002,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="143"/>
+      <c r="G37" s="140"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4060,7 +4031,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="143"/>
+      <c r="G38" s="140"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4081,7 +4052,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="143"/>
+      <c r="G39" s="140"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4110,7 +4081,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="143"/>
+      <c r="G40" s="140"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4131,7 +4102,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="143"/>
+      <c r="G41" s="140"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4160,7 +4131,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="143"/>
+      <c r="G42" s="140"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4181,7 +4152,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="143"/>
+      <c r="G43" s="140"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4204,17 +4175,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="146" t="s">
+      <c r="C44" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="146" t="s">
+      <c r="D44" s="143" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="143"/>
+      <c r="G44" s="140"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4229,13 +4200,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="143"/>
+      <c r="G45" s="140"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4264,7 +4235,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="143"/>
+      <c r="G46" s="140"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4285,7 +4256,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="143"/>
+      <c r="G47" s="140"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4314,7 +4285,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="140"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4343,7 +4314,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="143"/>
+      <c r="G49" s="140"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4370,7 +4341,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="143"/>
+      <c r="G50" s="140"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4466,10 +4437,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="142">
+      <c r="B54" s="139">
         <v>16</v>
       </c>
-      <c r="C54" s="147" t="s">
+      <c r="C54" s="144" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4490,8 +4461,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="143"/>
-      <c r="C55" s="143"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="140"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4510,10 +4481,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="148">
+      <c r="B56" s="145">
         <v>17</v>
       </c>
-      <c r="C56" s="150" t="s">
+      <c r="C56" s="147" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4535,8 +4506,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="149"/>
-      <c r="C57" s="151"/>
+      <c r="B57" s="146"/>
+      <c r="C57" s="148"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4556,10 +4527,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="142">
+      <c r="B58" s="139">
         <v>18</v>
       </c>
-      <c r="C58" s="147" t="s">
+      <c r="C58" s="144" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4580,8 +4551,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="143"/>
-      <c r="C59" s="143"/>
+      <c r="B59" s="140"/>
+      <c r="C59" s="140"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4600,10 +4571,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="148">
+      <c r="B60" s="145">
         <v>19</v>
       </c>
-      <c r="C60" s="150" t="s">
+      <c r="C60" s="147" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4625,8 +4596,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="149"/>
-      <c r="C61" s="151"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="148"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4646,7 +4617,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="142">
+      <c r="B62" s="139">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4670,7 +4641,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="143"/>
+      <c r="B63" s="140"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4846,13 +4817,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="144" t="s">
+      <c r="B74" s="141" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="143"/>
-      <c r="D74" s="143"/>
-      <c r="E74" s="143"/>
-      <c r="F74" s="143"/>
+      <c r="C74" s="140"/>
+      <c r="D74" s="140"/>
+      <c r="E74" s="140"/>
+      <c r="F74" s="140"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4931,7 +4902,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="145" t="s">
+      <c r="G76" s="142" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4958,7 +4929,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="143"/>
+      <c r="G77" s="140"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4983,7 +4954,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="143"/>
+      <c r="G78" s="140"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -5010,7 +4981,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="143"/>
+      <c r="G79" s="140"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5042,7 +5013,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="143"/>
+      <c r="G80" s="140"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5071,7 +5042,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="143"/>
+      <c r="G81" s="140"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5100,7 +5071,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="143"/>
+      <c r="G82" s="140"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5129,7 +5100,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="143"/>
+      <c r="G83" s="140"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5158,7 +5129,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="143"/>
+      <c r="G84" s="140"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5187,7 +5158,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="143"/>
+      <c r="G85" s="140"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5216,7 +5187,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="143"/>
+      <c r="G86" s="140"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5245,7 +5216,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="143"/>
+      <c r="G87" s="140"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -9313,7 +9284,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -9370,7 +9341,7 @@
         <v>166</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9409,7 +9380,7 @@
       </c>
       <c r="L2" s="81"/>
       <c r="M2" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9448,7 +9419,7 @@
       </c>
       <c r="L3" s="81"/>
       <c r="M3" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9485,7 +9456,7 @@
       <c r="K4" s="81"/>
       <c r="L4" s="81"/>
       <c r="M4" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9526,7 +9497,7 @@
         <v>170</v>
       </c>
       <c r="M5" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9567,7 +9538,7 @@
         <v>170</v>
       </c>
       <c r="M6" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9604,7 +9575,7 @@
       <c r="K7" s="99"/>
       <c r="L7" s="99"/>
       <c r="M7" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9639,7 +9610,7 @@
         <v>124</v>
       </c>
       <c r="M8" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9674,7 +9645,7 @@
         <v>124</v>
       </c>
       <c r="M9" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9709,7 +9680,7 @@
         <v>124</v>
       </c>
       <c r="M10" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9746,7 +9717,7 @@
       <c r="K11" s="99"/>
       <c r="L11" s="99"/>
       <c r="M11" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9781,7 +9752,7 @@
         <v>124</v>
       </c>
       <c r="M12" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9816,7 +9787,7 @@
         <v>124</v>
       </c>
       <c r="M13" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9857,7 +9828,7 @@
         <v>170</v>
       </c>
       <c r="M14" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9883,7 +9854,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="128" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="I15" s="128" t="s">
         <v>196</v>
@@ -9892,7 +9863,7 @@
         <v>124</v>
       </c>
       <c r="M15" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9927,7 +9898,7 @@
         <v>124</v>
       </c>
       <c r="M16" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9962,7 +9933,7 @@
         <v>124</v>
       </c>
       <c r="M17" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9997,7 +9968,7 @@
         <v>124</v>
       </c>
       <c r="M18" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10038,7 +10009,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10079,7 +10050,7 @@
         <v>170</v>
       </c>
       <c r="M20" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10120,7 +10091,7 @@
         <v>170</v>
       </c>
       <c r="M21" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10161,7 +10132,7 @@
         <v>170</v>
       </c>
       <c r="M22" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10181,7 +10152,7 @@
         <v>219</v>
       </c>
       <c r="F23" s="109" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G23" s="109">
         <v>9</v>
@@ -10202,7 +10173,7 @@
         <v>170</v>
       </c>
       <c r="M23" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10243,7 +10214,7 @@
         <v>170</v>
       </c>
       <c r="M24" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10284,7 +10255,7 @@
         <v>170</v>
       </c>
       <c r="M25" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10325,7 +10296,7 @@
         <v>170</v>
       </c>
       <c r="M26" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10366,7 +10337,7 @@
         <v>259</v>
       </c>
       <c r="M27" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="99" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10403,14 +10374,14 @@
       <c r="K28" s="99" t="s">
         <v>260</v>
       </c>
-      <c r="L28" s="159" t="s">
+      <c r="L28" s="156" t="s">
         <v>259</v>
       </c>
       <c r="M28" s="99" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="136" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="80">
         <v>3</v>
       </c>
@@ -10446,10 +10417,10 @@
       </c>
       <c r="L29" s="80"/>
       <c r="M29" s="80" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="136" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="80">
         <v>3</v>
       </c>
@@ -10485,7 +10456,7 @@
       </c>
       <c r="L30" s="80"/>
       <c r="M30" s="80" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10523,7 +10494,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -10561,7 +10532,7 @@
         <v>170</v>
       </c>
       <c r="M32" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10599,7 +10570,7 @@
         <v>170</v>
       </c>
       <c r="M33" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10618,7 +10589,7 @@
       <c r="E34" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F34" s="132" t="s">
+      <c r="F34" s="130" t="s">
         <v>222</v>
       </c>
       <c r="G34" s="78">
@@ -10637,7 +10608,7 @@
         <v>170</v>
       </c>
       <c r="M34" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10656,7 +10627,7 @@
       <c r="E35" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F35" s="132" t="s">
+      <c r="F35" s="130" t="s">
         <v>222</v>
       </c>
       <c r="G35" s="78">
@@ -10675,10 +10646,10 @@
         <v>170</v>
       </c>
       <c r="M35" s="97" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="139" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="136" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="80">
         <v>3</v>
       </c>
@@ -10695,7 +10666,7 @@
         <v>219</v>
       </c>
       <c r="F36" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G36" s="80">
         <v>85</v>
@@ -10716,7 +10687,7 @@
         <v>235</v>
       </c>
       <c r="M36" s="80" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10736,7 +10707,7 @@
         <v>219</v>
       </c>
       <c r="F37" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G37" s="97">
         <v>85</v>
@@ -10757,7 +10728,7 @@
         <v>235</v>
       </c>
       <c r="M37" s="97" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10777,7 +10748,7 @@
         <v>219</v>
       </c>
       <c r="F38" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G38" s="97">
         <v>85</v>
@@ -10798,7 +10769,7 @@
         <v>235</v>
       </c>
       <c r="M38" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10818,7 +10789,7 @@
         <v>219</v>
       </c>
       <c r="F39" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G39" s="97">
         <v>85</v>
@@ -10836,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="97" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10844,7 +10815,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="109" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C40" s="97" t="s">
         <v>187</v>
@@ -10855,17 +10826,17 @@
       <c r="E40" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="141" t="s">
-        <v>311</v>
+      <c r="F40" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="G40" s="97">
         <v>80</v>
       </c>
       <c r="H40" s="119" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I40" s="120" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="J40" s="97" t="s">
         <v>213</v>
@@ -10877,7 +10848,7 @@
         <v>235</v>
       </c>
       <c r="M40" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10896,17 +10867,17 @@
       <c r="E41" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F41" s="141" t="s">
-        <v>311</v>
+      <c r="F41" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="G41" s="97">
         <v>80</v>
       </c>
       <c r="H41" s="120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I41" s="120" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="J41" s="97" t="s">
         <v>213</v>
@@ -10918,7 +10889,7 @@
         <v>235</v>
       </c>
       <c r="M41" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10929,7 +10900,7 @@
         <v>267</v>
       </c>
       <c r="C42" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D42" s="97" t="s">
         <v>223</v>
@@ -10938,16 +10909,16 @@
         <v>223</v>
       </c>
       <c r="F42" s="123" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G42" s="97">
         <v>15</v>
       </c>
       <c r="H42" s="120" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I42" s="120" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="J42" s="97" t="s">
         <v>213</v>
@@ -10956,10 +10927,10 @@
         <v>5</v>
       </c>
       <c r="L42" s="97" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M42" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -10970,7 +10941,7 @@
         <v>268</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D43" s="97" t="s">
         <v>223</v>
@@ -10979,16 +10950,16 @@
         <v>223</v>
       </c>
       <c r="F43" s="123" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="G43" s="97">
         <v>20</v>
       </c>
       <c r="H43" s="120" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I43" s="120" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J43" s="97" t="s">
         <v>213</v>
@@ -10997,10 +10968,10 @@
         <v>5</v>
       </c>
       <c r="L43" s="97" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M43" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11008,7 +10979,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="97" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C44" s="97" t="s">
         <v>203</v>
@@ -11020,16 +10991,16 @@
         <v>223</v>
       </c>
       <c r="F44" s="123" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G44" s="97">
         <v>0.75</v>
       </c>
       <c r="H44" s="120" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I44" s="120" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J44" s="97" t="s">
         <v>213</v>
@@ -11041,7 +11012,7 @@
         <v>235</v>
       </c>
       <c r="M44" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11049,7 +11020,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="97" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C45" s="97" t="s">
         <v>203</v>
@@ -11061,16 +11032,16 @@
         <v>223</v>
       </c>
       <c r="F45" s="123" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G45" s="97">
         <v>0.75</v>
       </c>
       <c r="H45" s="120" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I45" s="120" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="J45" s="97" t="s">
         <v>213</v>
@@ -11082,7 +11053,7 @@
         <v>235</v>
       </c>
       <c r="M45" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11093,7 +11064,7 @@
         <v>271</v>
       </c>
       <c r="C46" s="97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D46" s="97" t="s">
         <v>223</v>
@@ -11102,16 +11073,16 @@
         <v>223</v>
       </c>
       <c r="F46" s="123" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G46" s="97">
         <v>3.5</v>
       </c>
       <c r="H46" s="120" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I46" s="120" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="J46" s="97" t="s">
         <v>213</v>
@@ -11123,7 +11094,7 @@
         <v>235</v>
       </c>
       <c r="M46" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11131,10 +11102,10 @@
         <v>3</v>
       </c>
       <c r="B47" s="97" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C47" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D47" s="97" t="s">
         <v>223</v>
@@ -11143,16 +11114,16 @@
         <v>223</v>
       </c>
       <c r="F47" s="123" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G47" s="97">
         <v>15</v>
       </c>
       <c r="H47" s="120" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I47" s="120" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J47" s="97" t="s">
         <v>213</v>
@@ -11164,7 +11135,7 @@
         <v>235</v>
       </c>
       <c r="M47" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="80" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -11205,7 +11176,7 @@
         <v>170</v>
       </c>
       <c r="M48" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -11246,7 +11217,7 @@
         <v>170</v>
       </c>
       <c r="M49" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="97" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
@@ -11287,7 +11258,7 @@
         <v>170</v>
       </c>
       <c r="M50" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11321,10 +11292,14 @@
       <c r="J51" s="99" t="s">
         <v>213</v>
       </c>
-      <c r="K51" s="99"/>
-      <c r="L51" s="99"/>
+      <c r="K51" s="99">
+        <v>1</v>
+      </c>
+      <c r="L51" s="99" t="s">
+        <v>170</v>
+      </c>
       <c r="M51" s="99" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11343,7 +11318,7 @@
       <c r="E52" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F52" s="132" t="s">
+      <c r="F52" s="130" t="s">
         <v>253</v>
       </c>
       <c r="G52" s="78">
@@ -11362,7 +11337,7 @@
         <v>170</v>
       </c>
       <c r="M52" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11381,7 +11356,7 @@
       <c r="E53" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F53" s="132" t="s">
+      <c r="F53" s="130" t="s">
         <v>253</v>
       </c>
       <c r="G53" s="78">
@@ -11400,200 +11375,212 @@
         <v>170</v>
       </c>
       <c r="M53" s="97" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="97">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="136" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="80">
         <v>4</v>
       </c>
-      <c r="B54" s="97" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="97" t="s">
+      <c r="B54" s="109" t="s">
+        <v>254</v>
+      </c>
+      <c r="C54" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D54" s="109" t="s">
+      <c r="D54" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E54" s="109" t="s">
+      <c r="E54" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F54" s="132" t="s">
-        <v>253</v>
-      </c>
-      <c r="G54" s="97">
-        <v>95</v>
-      </c>
-      <c r="H54" s="120" t="s">
-        <v>278</v>
-      </c>
-      <c r="I54" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="K54" s="97">
-        <v>5</v>
-      </c>
-      <c r="L54" s="97" t="s">
+      <c r="F54" s="129" t="s">
+        <v>222</v>
+      </c>
+      <c r="G54" s="80">
+        <v>90</v>
+      </c>
+      <c r="H54" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="I54" s="83" t="s">
+        <v>237</v>
+      </c>
+      <c r="J54" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="K54" s="80">
+        <v>2</v>
+      </c>
+      <c r="L54" s="80" t="s">
         <v>235</v>
       </c>
-      <c r="M54" s="97" t="s">
-        <v>294</v>
+      <c r="M54" s="80" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="97">
         <v>4</v>
       </c>
-      <c r="B55" s="97" t="s">
-        <v>266</v>
+      <c r="B55" s="118" t="s">
+        <v>255</v>
       </c>
       <c r="C55" s="97" t="s">
-        <v>274</v>
-      </c>
-      <c r="D55" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="D55" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E55" s="109" t="s">
+      <c r="E55" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F55" s="132" t="s">
-        <v>253</v>
+      <c r="F55" s="129" t="s">
+        <v>222</v>
       </c>
       <c r="G55" s="97">
-        <v>95</v>
-      </c>
-      <c r="H55" s="120" t="s">
-        <v>278</v>
+        <v>90</v>
+      </c>
+      <c r="H55" s="119" t="s">
+        <v>239</v>
       </c>
       <c r="I55" s="120" t="s">
-        <v>289</v>
+        <v>240</v>
+      </c>
+      <c r="J55" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K55" s="97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L55" s="97" t="s">
         <v>235</v>
       </c>
       <c r="M55" s="97" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="97">
         <v>4</v>
       </c>
-      <c r="B56" s="97" t="s">
-        <v>267</v>
+      <c r="B56" s="118" t="s">
+        <v>256</v>
       </c>
       <c r="C56" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D56" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E56" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F56" s="123" t="s">
-        <v>279</v>
+        <v>187</v>
+      </c>
+      <c r="D56" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F56" s="129" t="s">
+        <v>222</v>
       </c>
       <c r="G56" s="97">
-        <v>10</v>
-      </c>
-      <c r="H56" s="120" t="s">
-        <v>283</v>
+        <v>90</v>
+      </c>
+      <c r="H56" s="119" t="s">
+        <v>241</v>
       </c>
       <c r="I56" s="120" t="s">
-        <v>290</v>
+        <v>242</v>
+      </c>
+      <c r="J56" s="97" t="s">
+        <v>124</v>
       </c>
       <c r="K56" s="97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L56" s="97" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="M56" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="97">
         <v>4</v>
       </c>
-      <c r="B57" s="97" t="s">
-        <v>269</v>
+      <c r="B57" s="118" t="s">
+        <v>257</v>
       </c>
       <c r="C57" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="D57" s="109" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="E57" s="109" t="s">
+      <c r="E57" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="F57" s="132" t="s">
-        <v>253</v>
+      <c r="F57" s="129" t="s">
+        <v>222</v>
       </c>
       <c r="G57" s="97">
-        <v>95</v>
-      </c>
-      <c r="H57" s="120" t="s">
-        <v>278</v>
+        <v>90</v>
+      </c>
+      <c r="H57" s="119" t="s">
+        <v>243</v>
       </c>
       <c r="I57" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="J57" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K57" s="97">
+        <v>1</v>
+      </c>
+      <c r="L57" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="M57" s="97" t="s">
         <v>292</v>
-      </c>
-      <c r="J57" s="97" t="s">
-        <v>213</v>
-      </c>
-      <c r="K57" s="97">
-        <v>5</v>
-      </c>
-      <c r="L57" s="97" t="s">
-        <v>235</v>
-      </c>
-      <c r="M57" s="97" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="97">
         <v>4</v>
       </c>
-      <c r="B58" s="97" t="s">
-        <v>268</v>
+      <c r="B58" s="109" t="s">
+        <v>310</v>
       </c>
       <c r="C58" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="D58" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E58" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F58" s="123" t="s">
-        <v>279</v>
+        <v>187</v>
+      </c>
+      <c r="D58" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F58" s="129" t="s">
+        <v>222</v>
       </c>
       <c r="G58" s="97">
-        <v>10</v>
-      </c>
-      <c r="H58" s="120" t="s">
-        <v>283</v>
+        <v>90</v>
+      </c>
+      <c r="H58" s="119" t="s">
+        <v>311</v>
       </c>
       <c r="I58" s="120" t="s">
-        <v>291</v>
+        <v>312</v>
+      </c>
+      <c r="J58" s="97" t="s">
+        <v>213</v>
       </c>
       <c r="K58" s="97">
         <v>5</v>
       </c>
       <c r="L58" s="97" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="M58" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11601,10 +11588,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="97" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C59" s="97" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="D59" s="109" t="s">
         <v>153</v>
@@ -11612,20 +11599,17 @@
       <c r="E59" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="F59" s="132" t="s">
-        <v>253</v>
+      <c r="F59" s="129" t="s">
+        <v>222</v>
       </c>
       <c r="G59" s="97">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H59" s="120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I59" s="120" t="s">
-        <v>292</v>
-      </c>
-      <c r="J59" s="97" t="s">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="K59" s="97">
         <v>5</v>
@@ -11634,7 +11618,7 @@
         <v>235</v>
       </c>
       <c r="M59" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11642,10 +11626,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="97" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C60" s="97" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="D60" s="97" t="s">
         <v>223</v>
@@ -11653,29 +11637,26 @@
       <c r="E60" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="F60" s="97" t="s">
-        <v>293</v>
+      <c r="F60" s="123" t="s">
+        <v>278</v>
       </c>
       <c r="G60" s="97">
-        <v>0.75</v>
+        <v>10</v>
       </c>
       <c r="H60" s="120" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I60" s="120" t="s">
         <v>284</v>
       </c>
-      <c r="J60" s="97" t="s">
-        <v>213</v>
-      </c>
       <c r="K60" s="97">
         <v>5</v>
       </c>
       <c r="L60" s="97" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="M60" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11683,28 +11664,28 @@
         <v>4</v>
       </c>
       <c r="B61" s="97" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C61" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D61" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E61" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F61" s="129" t="s">
+        <v>222</v>
+      </c>
+      <c r="G61" s="97">
+        <v>90</v>
+      </c>
+      <c r="H61" s="120" t="s">
         <v>277</v>
       </c>
-      <c r="D61" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E61" s="97" t="s">
-        <v>223</v>
-      </c>
-      <c r="F61" s="109" t="s">
-        <v>280</v>
-      </c>
-      <c r="G61" s="109">
-        <v>3.5</v>
-      </c>
-      <c r="H61" s="120" t="s">
+      <c r="I61" s="120" t="s">
         <v>286</v>
-      </c>
-      <c r="I61" s="120" t="s">
-        <v>285</v>
       </c>
       <c r="J61" s="97" t="s">
         <v>213</v>
@@ -11716,48 +11697,487 @@
         <v>235</v>
       </c>
       <c r="M61" s="97" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="131" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="110">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="97">
         <v>4</v>
       </c>
-      <c r="B62" s="110" t="s">
-        <v>273</v>
-      </c>
-      <c r="C62" s="110" t="s">
-        <v>276</v>
-      </c>
-      <c r="D62" s="110" t="s">
+      <c r="B62" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C62" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D62" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="110" t="s">
+      <c r="E62" s="97" t="s">
         <v>223</v>
       </c>
-      <c r="F62" s="133" t="s">
+      <c r="F62" s="123" t="s">
+        <v>280</v>
+      </c>
+      <c r="G62" s="97">
+        <v>15</v>
+      </c>
+      <c r="H62" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="I62" s="120" t="s">
+        <v>285</v>
+      </c>
+      <c r="K62" s="97">
+        <v>5</v>
+      </c>
+      <c r="L62" s="97" t="s">
         <v>281</v>
       </c>
-      <c r="G62" s="110">
-        <v>15</v>
-      </c>
-      <c r="H62" s="130" t="s">
+      <c r="M62" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="97">
+        <v>4</v>
+      </c>
+      <c r="B63" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C63" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E63" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F63" s="129" t="s">
+        <v>222</v>
+      </c>
+      <c r="G63" s="97">
+        <v>90</v>
+      </c>
+      <c r="H63" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I63" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="J63" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K63" s="97">
+        <v>5</v>
+      </c>
+      <c r="L63" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M63" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="136" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="99">
+        <v>5</v>
+      </c>
+      <c r="B64" s="116" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64" s="115" t="s">
+        <v>219</v>
+      </c>
+      <c r="F64" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="G64" s="99">
+        <v>95</v>
+      </c>
+      <c r="H64" s="117" t="s">
+        <v>236</v>
+      </c>
+      <c r="I64" s="117" t="s">
+        <v>237</v>
+      </c>
+      <c r="J64" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="K64" s="99">
+        <v>2</v>
+      </c>
+      <c r="L64" s="99" t="s">
+        <v>235</v>
+      </c>
+      <c r="M64" s="99" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="97">
+        <v>5</v>
+      </c>
+      <c r="B65" s="118" t="s">
+        <v>255</v>
+      </c>
+      <c r="C65" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F65" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G65" s="97">
+        <v>95</v>
+      </c>
+      <c r="H65" s="119" t="s">
+        <v>239</v>
+      </c>
+      <c r="I65" s="120" t="s">
+        <v>240</v>
+      </c>
+      <c r="J65" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K65" s="97">
+        <v>2</v>
+      </c>
+      <c r="L65" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M65" s="97" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="97">
+        <v>5</v>
+      </c>
+      <c r="B66" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="C66" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E66" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F66" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G66" s="97">
+        <v>95</v>
+      </c>
+      <c r="H66" s="119" t="s">
+        <v>241</v>
+      </c>
+      <c r="I66" s="120" t="s">
+        <v>242</v>
+      </c>
+      <c r="J66" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K66" s="97">
+        <v>2</v>
+      </c>
+      <c r="L66" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M66" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="97">
+        <v>5</v>
+      </c>
+      <c r="B67" s="118" t="s">
+        <v>257</v>
+      </c>
+      <c r="C67" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E67" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F67" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G67" s="97">
+        <v>95</v>
+      </c>
+      <c r="H67" s="119" t="s">
+        <v>243</v>
+      </c>
+      <c r="I67" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="J67" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="K67" s="97">
+        <v>1</v>
+      </c>
+      <c r="L67" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="M67" s="97" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="97">
+        <v>5</v>
+      </c>
+      <c r="B68" s="109" t="s">
+        <v>310</v>
+      </c>
+      <c r="C68" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D68" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F68" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G68" s="97">
+        <v>95</v>
+      </c>
+      <c r="H68" s="119" t="s">
+        <v>311</v>
+      </c>
+      <c r="I68" s="120" t="s">
+        <v>312</v>
+      </c>
+      <c r="J68" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K68" s="97">
+        <v>5</v>
+      </c>
+      <c r="L68" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M68" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="97">
+        <v>5</v>
+      </c>
+      <c r="B69" s="97" t="s">
+        <v>265</v>
+      </c>
+      <c r="C69" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D69" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F69" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G69" s="97">
+        <v>95</v>
+      </c>
+      <c r="H69" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I69" s="120" t="s">
         <v>283</v>
       </c>
-      <c r="I62" s="130" t="s">
+      <c r="K69" s="97">
+        <v>5</v>
+      </c>
+      <c r="L69" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M69" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="97">
+        <v>5</v>
+      </c>
+      <c r="B70" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="C70" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D70" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F70" s="123" t="s">
+        <v>278</v>
+      </c>
+      <c r="G70" s="97">
+        <v>10</v>
+      </c>
+      <c r="H70" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="I70" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="K70" s="97">
+        <v>5</v>
+      </c>
+      <c r="L70" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="M70" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="97">
+        <v>5</v>
+      </c>
+      <c r="B71" s="97" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F71" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G71" s="97">
+        <v>95</v>
+      </c>
+      <c r="H71" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I71" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="J71" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K71" s="97">
+        <v>5</v>
+      </c>
+      <c r="L71" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M71" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="97">
+        <v>5</v>
+      </c>
+      <c r="B72" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D72" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F72" s="123" t="s">
+        <v>278</v>
+      </c>
+      <c r="G72" s="97">
+        <v>10</v>
+      </c>
+      <c r="H72" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="I72" s="120" t="s">
         <v>285</v>
       </c>
-      <c r="J62" s="110" t="s">
+      <c r="K72" s="97">
+        <v>5</v>
+      </c>
+      <c r="L72" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="M72" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="97">
+        <v>5</v>
+      </c>
+      <c r="B73" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="C73" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D73" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F73" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G73" s="97">
+        <v>95</v>
+      </c>
+      <c r="H73" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I73" s="120" t="s">
+        <v>286</v>
+      </c>
+      <c r="J73" s="97" t="s">
         <v>213</v>
       </c>
-      <c r="K62" s="110">
+      <c r="K73" s="97">
         <v>5</v>
       </c>
-      <c r="L62" s="110" t="s">
-        <v>282</v>
-      </c>
-      <c r="M62" s="110" t="s">
-        <v>294</v>
+      <c r="L73" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M73" s="97" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -11773,125 +12193,125 @@
   <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="134"/>
-    <col min="2" max="2" width="23.5" style="134" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="134" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="134" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" style="134" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33" style="134" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="134" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="134" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" style="134" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.1640625" style="134" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="134"/>
+    <col min="1" max="1" width="10.83203125" style="131"/>
+    <col min="2" max="2" width="23.5" style="131" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="131" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33" style="131" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="131" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.1640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="131" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="131"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="136" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="157" t="s">
-        <v>313</v>
-      </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157" t="s">
-        <v>302</v>
-      </c>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157" t="s">
-        <v>303</v>
-      </c>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157" t="s">
-        <v>304</v>
-      </c>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157" t="s">
-        <v>306</v>
-      </c>
-      <c r="M1" s="157"/>
-    </row>
-    <row r="2" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="137" t="s">
+    <row r="1" spans="1:13" s="133" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="154" t="s">
         <v>307</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-    </row>
-    <row r="3" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="154"/>
+      <c r="D1" s="154" t="s">
+        <v>296</v>
+      </c>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154" t="s">
+        <v>300</v>
+      </c>
+      <c r="M1" s="154"/>
+    </row>
+    <row r="2" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="134" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+    </row>
+    <row r="3" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="140" t="s">
+      <c r="C3" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="140" t="s">
+      <c r="D3" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="140" t="s">
+      <c r="E3" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="140" t="s">
+      <c r="G3" s="137" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="137" t="s">
         <v>151</v>
       </c>
-      <c r="D4" s="140" t="s">
+      <c r="D4" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="137" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="140" t="s">
+      <c r="F4" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="140" t="s">
+      <c r="G4" s="137" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="80" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="140">
+      <c r="C5" s="137">
         <v>1</v>
       </c>
-      <c r="D5" s="140" t="s">
+      <c r="D5" s="137" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="140">
+      <c r="E5" s="137">
         <v>1</v>
       </c>
-      <c r="F5" s="140" t="s">
+      <c r="F5" s="137" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="140">
+      <c r="G5" s="137">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F6" s="109" t="s">
         <v>115</v>
       </c>
@@ -11899,26 +12319,26 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="137" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
-    </row>
-    <row r="10" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="134" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="135"/>
+    </row>
+    <row r="10" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="80" t="s">
         <v>188</v>
       </c>
@@ -11926,11 +12346,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="141" t="s">
+      <c r="G11" s="138" t="s">
         <v>229</v>
       </c>
       <c r="H11" s="109" t="s">
@@ -11940,11 +12360,11 @@
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F12" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="G12" s="141" t="s">
+      <c r="G12" s="138" t="s">
         <v>229</v>
       </c>
       <c r="H12" s="109" t="s">
@@ -11954,11 +12374,11 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F13" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="141" t="s">
+      <c r="G13" s="138" t="s">
         <v>229</v>
       </c>
       <c r="H13" s="109" t="s">
@@ -11968,7 +12388,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F14" s="109" t="s">
         <v>117</v>
       </c>
@@ -11982,7 +12402,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F15" s="109" t="s">
         <v>233</v>
       </c>
@@ -11990,15 +12410,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F16" s="109" t="s">
         <v>234</v>
       </c>
       <c r="G16" s="109" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H17" s="109" t="s">
         <v>248</v>
       </c>
@@ -12006,7 +12426,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H18" s="109" t="s">
         <v>249</v>
       </c>
@@ -12014,77 +12434,77 @@
         <v>238</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="137" t="s">
+    <row r="19" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138"/>
-      <c r="M20" s="138"/>
-    </row>
-    <row r="21" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+    </row>
+    <row r="21" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="C21" s="141" t="s">
+      <c r="C21" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="F21" s="140" t="s">
+      <c r="F21" s="137" t="s">
         <v>155</v>
       </c>
-      <c r="G21" s="141" t="s">
+      <c r="G21" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="H21" s="140" t="s">
+      <c r="H21" s="137" t="s">
         <v>155</v>
       </c>
-      <c r="I21" s="141" t="s">
+      <c r="I21" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="J21" s="140" t="s">
+      <c r="J21" s="137" t="s">
         <v>155</v>
       </c>
-      <c r="K21" s="141" t="s">
+      <c r="K21" s="138" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="F22" s="140" t="s">
+      <c r="F22" s="137" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="141" t="s">
+      <c r="G22" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="H22" s="140" t="s">
+      <c r="H22" s="137" t="s">
         <v>156</v>
       </c>
-      <c r="I22" s="141" t="s">
+      <c r="I22" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="J22" s="140" t="s">
+      <c r="J22" s="137" t="s">
         <v>156</v>
       </c>
-      <c r="K22" s="141" t="s">
+      <c r="K22" s="138" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F23" s="109" t="s">
         <v>78</v>
       </c>
@@ -12092,7 +12512,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F24" s="109" t="s">
         <v>82</v>
       </c>
@@ -12100,7 +12520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F25" s="109" t="s">
         <v>84</v>
       </c>
@@ -12108,7 +12528,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="128" t="s">
         <v>201</v>
       </c>
@@ -12128,7 +12548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F27" s="109" t="s">
         <v>209</v>
       </c>
@@ -12142,7 +12562,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F28" s="109" t="s">
         <v>139</v>
       </c>
@@ -12156,30 +12576,30 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="137" t="s">
-        <v>309</v>
-      </c>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="138"/>
-    </row>
-    <row r="31" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="134" t="s">
+        <v>303</v>
+      </c>
+      <c r="B30" s="135"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+    </row>
+    <row r="31" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H31" s="109" t="s">
         <v>254</v>
       </c>
       <c r="I31" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J31" s="109" t="s">
         <v>254</v>
@@ -12194,12 +12614,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H32" s="109" t="s">
         <v>255</v>
       </c>
       <c r="I32" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J32" s="109" t="s">
         <v>255</v>
@@ -12214,12 +12634,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="33" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H33" s="109" t="s">
         <v>256</v>
       </c>
       <c r="I33" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J33" s="109" t="s">
         <v>256</v>
@@ -12234,12 +12654,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="34" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H34" s="109" t="s">
         <v>257</v>
       </c>
       <c r="I34" s="129" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J34" s="109" t="s">
         <v>257</v>
@@ -12254,186 +12674,186 @@
         <v>253</v>
       </c>
     </row>
-    <row r="35" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="I36" s="141" t="s">
-        <v>311</v>
+      <c r="I36" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="J36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="K36" s="141" t="s">
+      <c r="K36" s="138" t="s">
         <v>222</v>
       </c>
       <c r="L36" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="M36" s="141" t="s">
+      <c r="M36" s="138" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="37" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="I37" s="135" t="s">
-        <v>281</v>
+      <c r="I37" s="132" t="s">
+        <v>280</v>
       </c>
       <c r="J37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="K37" s="135" t="s">
-        <v>279</v>
+      <c r="K37" s="132" t="s">
+        <v>278</v>
       </c>
       <c r="L37" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="M37" s="135" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="38" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M37" s="132" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="38" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="I38" s="141" t="s">
-        <v>311</v>
+      <c r="I38" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="J38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="K38" s="141" t="s">
+      <c r="K38" s="138" t="s">
         <v>222</v>
       </c>
       <c r="L38" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="M38" s="141" t="s">
+      <c r="M38" s="138" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="39" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="135" t="s">
-        <v>312</v>
+      <c r="I39" s="132" t="s">
+        <v>306</v>
       </c>
       <c r="J39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="K39" s="135" t="s">
-        <v>281</v>
+      <c r="K39" s="132" t="s">
+        <v>280</v>
       </c>
       <c r="L39" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="M39" s="135" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="40" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M39" s="132" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="40" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="I40" s="141" t="s">
-        <v>311</v>
+      <c r="I40" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="J40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="K40" s="141" t="s">
+      <c r="K40" s="138" t="s">
         <v>222</v>
       </c>
       <c r="L40" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="M40" s="141" t="s">
+      <c r="M40" s="138" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H42" s="80" t="s">
         <v>272</v>
       </c>
       <c r="I42" s="80" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J42" s="80"/>
       <c r="K42" s="80"/>
       <c r="L42" s="80"/>
       <c r="M42" s="80"/>
     </row>
-    <row r="43" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H43" s="80" t="s">
         <v>271</v>
       </c>
       <c r="I43" s="109" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J43" s="80"/>
       <c r="K43" s="109"/>
       <c r="L43" s="80"/>
       <c r="M43" s="109"/>
     </row>
-    <row r="44" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H44" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="I44" s="135" t="s">
-        <v>281</v>
+      <c r="I44" s="132" t="s">
+        <v>280</v>
       </c>
       <c r="J44" s="80"/>
-      <c r="K44" s="135"/>
+      <c r="K44" s="132"/>
       <c r="L44" s="80"/>
-      <c r="M44" s="135"/>
-    </row>
-    <row r="45" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="8:13" s="139" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H52" s="134"/>
-      <c r="I52" s="134"/>
-      <c r="J52" s="134"/>
-      <c r="K52" s="134"/>
-      <c r="L52" s="134"/>
-      <c r="M52" s="134"/>
+      <c r="M44" s="132"/>
+    </row>
+    <row r="45" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="8:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" s="131"/>
+      <c r="I52" s="131"/>
+      <c r="J52" s="131"/>
+      <c r="K52" s="131"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="131"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="158" t="s">
-        <v>304</v>
-      </c>
-      <c r="I74" s="158"/>
-      <c r="J74" s="158" t="s">
-        <v>305</v>
-      </c>
-      <c r="K74" s="158"/>
-      <c r="L74" s="158" t="s">
-        <v>306</v>
-      </c>
-      <c r="M74" s="158"/>
+      <c r="H74" s="155" t="s">
+        <v>298</v>
+      </c>
+      <c r="I74" s="155"/>
+      <c r="J74" s="155" t="s">
+        <v>299</v>
+      </c>
+      <c r="K74" s="155"/>
+      <c r="L74" s="155" t="s">
+        <v>300</v>
+      </c>
+      <c r="M74" s="155"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="158" t="s">
-        <v>301</v>
-      </c>
-      <c r="C75" s="158"/>
-      <c r="D75" s="158" t="s">
-        <v>302</v>
-      </c>
-      <c r="E75" s="158"/>
-      <c r="F75" s="158" t="s">
-        <v>303</v>
-      </c>
-      <c r="G75" s="158"/>
+      <c r="B75" s="155" t="s">
+        <v>295</v>
+      </c>
+      <c r="C75" s="155"/>
+      <c r="D75" s="155" t="s">
+        <v>296</v>
+      </c>
+      <c r="E75" s="155"/>
+      <c r="F75" s="155" t="s">
+        <v>297</v>
+      </c>
+      <c r="G75" s="155"/>
       <c r="H75" s="109" t="s">
         <v>254</v>
       </c>
@@ -12475,7 +12895,7 @@
       <c r="J76" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="K76" s="132" t="s">
+      <c r="K76" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12507,7 +12927,7 @@
       <c r="J77" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="K77" s="132" t="s">
+      <c r="K77" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12539,7 +12959,7 @@
       <c r="J78" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="K78" s="132" t="s">
+      <c r="K78" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12571,7 +12991,7 @@
       <c r="J79" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="K79" s="132" t="s">
+      <c r="K79" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12597,8 +13017,8 @@
       <c r="J80" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="K80" s="135" t="s">
-        <v>279</v>
+      <c r="K80" s="132" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="81" spans="6:11" ht="16" x14ac:dyDescent="0.15">
@@ -12617,7 +13037,7 @@
       <c r="J81" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="K81" s="132" t="s">
+      <c r="K81" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12631,14 +13051,14 @@
       <c r="H82" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="I82" s="132" t="s">
+      <c r="I82" s="130" t="s">
         <v>222</v>
       </c>
       <c r="J82" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="K82" s="135" t="s">
-        <v>279</v>
+      <c r="K82" s="132" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="83" spans="6:11" ht="17" x14ac:dyDescent="0.15">
@@ -12651,13 +13071,13 @@
       <c r="H83" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="I83" s="132" t="s">
+      <c r="I83" s="130" t="s">
         <v>222</v>
       </c>
       <c r="J83" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="K83" s="132" t="s">
+      <c r="K83" s="130" t="s">
         <v>253</v>
       </c>
     </row>
@@ -12678,7 +13098,7 @@
         <v>272</v>
       </c>
       <c r="K84" s="80" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="6:11" ht="16" x14ac:dyDescent="0.15">
@@ -12698,7 +13118,7 @@
         <v>271</v>
       </c>
       <c r="K85" s="109" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="86" spans="6:11" ht="16" x14ac:dyDescent="0.15">
@@ -12717,8 +13137,8 @@
       <c r="J86" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="K86" s="135" t="s">
-        <v>281</v>
+      <c r="K86" s="132" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="87" spans="6:11" ht="16" x14ac:dyDescent="0.15">
@@ -12740,7 +13160,7 @@
         <v>234</v>
       </c>
       <c r="G88" s="109" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="H88" s="109" t="s">
         <v>248</v>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1483" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB57DC61-75B1-E849-83C0-1BB1F441833B}"/>
+  <xr:revisionPtr revIDLastSave="1503" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0061C5C-1BCA-684D-92F1-6BD703C3BFBC}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2665,21 +2665,31 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2689,27 +2699,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2964,13 +2964,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3028,7 +3028,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="142" t="s">
+      <c r="G4" s="146" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3061,7 +3061,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="140"/>
+      <c r="G5" s="141"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3089,7 +3089,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="140"/>
+      <c r="G6" s="141"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3113,7 +3113,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="140"/>
+      <c r="G7" s="141"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3136,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="140"/>
+      <c r="G8" s="141"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3164,7 +3164,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="140"/>
+      <c r="G9" s="141"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3247,13 +3247,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3308,24 +3308,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="151">
+      <c r="H16" s="142">
         <v>45359</v>
       </c>
-      <c r="I16" s="150"/>
-      <c r="J16" s="152">
+      <c r="I16" s="143"/>
+      <c r="J16" s="144">
         <v>47204</v>
       </c>
-      <c r="K16" s="150"/>
-      <c r="L16" s="153" t="s">
+      <c r="K16" s="143"/>
+      <c r="L16" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="150"/>
-      <c r="N16" s="151">
+      <c r="M16" s="143"/>
+      <c r="N16" s="142">
         <v>45429</v>
       </c>
-      <c r="O16" s="150"/>
-      <c r="P16" s="151"/>
-      <c r="Q16" s="150"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="142"/>
+      <c r="Q16" s="143"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="142" t="s">
+      <c r="G18" s="146" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3443,7 +3443,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="140"/>
+      <c r="G19" s="141"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3481,7 +3481,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="140"/>
+      <c r="G20" s="141"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="140"/>
+      <c r="G21" s="141"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3563,7 +3563,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="140"/>
+      <c r="G22" s="141"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3601,7 +3601,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="140"/>
+      <c r="G23" s="141"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="140"/>
+      <c r="G24" s="141"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3832,13 +3832,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="141" t="s">
+      <c r="B32" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3883,12 +3883,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="149" t="s">
+      <c r="H33" s="147" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="150"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="150"/>
+      <c r="I33" s="143"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="143"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3913,7 +3913,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="142" t="s">
+      <c r="G34" s="146" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3944,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="140"/>
+      <c r="G35" s="141"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3973,7 +3973,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="140"/>
+      <c r="G36" s="141"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4002,7 +4002,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="140"/>
+      <c r="G37" s="141"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4031,7 +4031,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="140"/>
+      <c r="G38" s="141"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4052,7 +4052,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="140"/>
+      <c r="G39" s="141"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4081,7 +4081,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="140"/>
+      <c r="G40" s="141"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4102,7 +4102,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="140"/>
+      <c r="G41" s="141"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4131,7 +4131,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="140"/>
+      <c r="G42" s="141"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4152,7 +4152,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="140"/>
+      <c r="G43" s="141"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4175,17 +4175,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="143" t="s">
+      <c r="C44" s="148" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="143" t="s">
+      <c r="D44" s="148" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="140"/>
+      <c r="G44" s="141"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4200,13 +4200,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="140"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="141"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="140"/>
+      <c r="G45" s="141"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4235,7 +4235,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="140"/>
+      <c r="G46" s="141"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4256,7 +4256,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="140"/>
+      <c r="G47" s="141"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4285,7 +4285,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="140"/>
+      <c r="G48" s="141"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4314,7 +4314,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="140"/>
+      <c r="G49" s="141"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4341,7 +4341,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="140"/>
+      <c r="G50" s="141"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4437,10 +4437,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="139">
+      <c r="B54" s="153">
         <v>16</v>
       </c>
-      <c r="C54" s="144" t="s">
+      <c r="C54" s="154" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4461,8 +4461,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="140"/>
-      <c r="C55" s="140"/>
+      <c r="B55" s="141"/>
+      <c r="C55" s="141"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4481,10 +4481,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="145">
+      <c r="B56" s="149">
         <v>17</v>
       </c>
-      <c r="C56" s="147" t="s">
+      <c r="C56" s="151" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4506,8 +4506,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="146"/>
-      <c r="C57" s="148"/>
+      <c r="B57" s="150"/>
+      <c r="C57" s="152"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4527,10 +4527,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="139">
+      <c r="B58" s="153">
         <v>18</v>
       </c>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="154" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4551,8 +4551,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="140"/>
+      <c r="B59" s="141"/>
+      <c r="C59" s="141"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4571,10 +4571,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="145">
+      <c r="B60" s="149">
         <v>19</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="151" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4596,8 +4596,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="146"/>
-      <c r="C61" s="148"/>
+      <c r="B61" s="150"/>
+      <c r="C61" s="152"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4617,7 +4617,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="139">
+      <c r="B62" s="153">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4641,7 +4641,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="140"/>
+      <c r="B63" s="141"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4817,13 +4817,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="141" t="s">
+      <c r="B74" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="140"/>
-      <c r="D74" s="140"/>
-      <c r="E74" s="140"/>
-      <c r="F74" s="140"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="141"/>
+      <c r="E74" s="141"/>
+      <c r="F74" s="141"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4902,7 +4902,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="142" t="s">
+      <c r="G76" s="146" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4929,7 +4929,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="140"/>
+      <c r="G77" s="141"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4954,7 +4954,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="140"/>
+      <c r="G78" s="141"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4981,7 +4981,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="140"/>
+      <c r="G79" s="141"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5013,7 +5013,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="140"/>
+      <c r="G80" s="141"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5042,7 +5042,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="140"/>
+      <c r="G81" s="141"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5071,7 +5071,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="140"/>
+      <c r="G82" s="141"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5100,7 +5100,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="140"/>
+      <c r="G83" s="141"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5129,7 +5129,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="140"/>
+      <c r="G84" s="141"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5158,7 +5158,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="140"/>
+      <c r="G85" s="141"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5187,7 +5187,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="140"/>
+      <c r="G86" s="141"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5216,7 +5216,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="140"/>
+      <c r="G87" s="141"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -8962,22 +8962,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -8988,6 +8972,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -10374,7 +10374,7 @@
       <c r="K28" s="99" t="s">
         <v>260</v>
       </c>
-      <c r="L28" s="156" t="s">
+      <c r="L28" s="139" t="s">
         <v>259</v>
       </c>
       <c r="M28" s="99" t="s">
@@ -12209,30 +12209,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="133" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="155" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154" t="s">
+      <c r="C1" s="155"/>
+      <c r="D1" s="155" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154" t="s">
+      <c r="E1" s="155"/>
+      <c r="F1" s="155" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154" t="s">
+      <c r="G1" s="155"/>
+      <c r="H1" s="155" t="s">
         <v>298</v>
       </c>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154" t="s">
+      <c r="I1" s="155"/>
+      <c r="J1" s="155" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154" t="s">
+      <c r="K1" s="155"/>
+      <c r="L1" s="155" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="154"/>
+      <c r="M1" s="155"/>
     </row>
     <row r="2" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="134" t="s">
@@ -12828,32 +12828,32 @@
       <c r="M52" s="131"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="155" t="s">
+      <c r="H74" s="156" t="s">
         <v>298</v>
       </c>
-      <c r="I74" s="155"/>
-      <c r="J74" s="155" t="s">
+      <c r="I74" s="156"/>
+      <c r="J74" s="156" t="s">
         <v>299</v>
       </c>
-      <c r="K74" s="155"/>
-      <c r="L74" s="155" t="s">
+      <c r="K74" s="156"/>
+      <c r="L74" s="156" t="s">
         <v>300</v>
       </c>
-      <c r="M74" s="155"/>
+      <c r="M74" s="156"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="155" t="s">
+      <c r="B75" s="156" t="s">
         <v>295</v>
       </c>
-      <c r="C75" s="155"/>
-      <c r="D75" s="155" t="s">
+      <c r="C75" s="156"/>
+      <c r="D75" s="156" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="155"/>
-      <c r="F75" s="155" t="s">
+      <c r="E75" s="156"/>
+      <c r="F75" s="156" t="s">
         <v>297</v>
       </c>
-      <c r="G75" s="155"/>
+      <c r="G75" s="156"/>
       <c r="H75" s="109" t="s">
         <v>254</v>
       </c>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1503" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0061C5C-1BCA-684D-92F1-6BD703C3BFBC}"/>
+  <xr:revisionPtr revIDLastSave="1579" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58035CDF-F96D-D740-AF90-09BDD740F026}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="-20220" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Phase0" sheetId="2" r:id="rId2"/>
     <sheet name="criteria_full" sheetId="5" r:id="rId3"/>
-    <sheet name="criteria_overview" sheetId="6" r:id="rId4"/>
-    <sheet name="calcs" sheetId="3" r:id="rId5"/>
+    <sheet name="acl_rsi" sheetId="7" r:id="rId4"/>
+    <sheet name="criteria_overview" sheetId="6" r:id="rId5"/>
+    <sheet name="calcs" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -794,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="369">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1796,6 +1797,141 @@
   </si>
   <si>
     <t>Drop and Stick - Asymmetry</t>
+  </si>
+  <si>
+    <t>images/testing/triplecrossoverhop.png</t>
+  </si>
+  <si>
+    <t>1. Are you confident that you can perform at your previous level of sport participation?</t>
+  </si>
+  <si>
+    <t>2. Do you think you are likely to re-injury your knee by participating in your sport?</t>
+  </si>
+  <si>
+    <t>3. Are you nervous about playing your sport?</t>
+  </si>
+  <si>
+    <t>4. Are you confident that your knee will not give way by playing your sport?</t>
+  </si>
+  <si>
+    <t>5. Are you confident that you could play your sport without concern for your knee?</t>
+  </si>
+  <si>
+    <t>6. Do you find it frustrating to have to consider your knee with respect to your sport?</t>
+  </si>
+  <si>
+    <t>7. Are you fearful of re-injuring your knee by playing your sport?</t>
+  </si>
+  <si>
+    <t>8. Are you confident about your knee holding up under pressure?</t>
+  </si>
+  <si>
+    <t>9.Are you afraid of accidentally injuring your knee by playing your sport?</t>
+  </si>
+  <si>
+    <t>10.Do thoughts of having to go through surgery and rehabilitation prevent you from playing your sport?</t>
+  </si>
+  <si>
+    <t>11. Are you confident about your ability to perform well at your sport?</t>
+  </si>
+  <si>
+    <t>12. Do you feel relaxed about playing your sport?</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>Not at all confident</t>
+  </si>
+  <si>
+    <t>Fully confident</t>
+  </si>
+  <si>
+    <t>Extremely likely</t>
+  </si>
+  <si>
+    <t>Extremely nervous</t>
+  </si>
+  <si>
+    <t>Extremely frustrating</t>
+  </si>
+  <si>
+    <t>Not at all frustrating</t>
+  </si>
+  <si>
+    <t>Not at all likely</t>
+  </si>
+  <si>
+    <t>Not at all nervous</t>
+  </si>
+  <si>
+    <t>Extremely fearful</t>
+  </si>
+  <si>
+    <t>No fear at all</t>
+  </si>
+  <si>
+    <t>Extremely afraid</t>
+  </si>
+  <si>
+    <t>Not at all afraid</t>
+  </si>
+  <si>
+    <t>All of the time</t>
+  </si>
+  <si>
+    <t>None of the time</t>
+  </si>
+  <si>
+    <t>Not at all relaxed</t>
+  </si>
+  <si>
+    <t>Fully relaxed</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>aclrsiq1</t>
+  </si>
+  <si>
+    <t>aclrsiq2</t>
+  </si>
+  <si>
+    <t>aclrsiq3</t>
+  </si>
+  <si>
+    <t>aclrsiq4</t>
+  </si>
+  <si>
+    <t>aclrsiq5</t>
+  </si>
+  <si>
+    <t>aclrsiq6</t>
+  </si>
+  <si>
+    <t>aclrsiq7</t>
+  </si>
+  <si>
+    <t>aclrsiq8</t>
+  </si>
+  <si>
+    <t>aclrsiq9</t>
+  </si>
+  <si>
+    <t>aclrsiq10</t>
+  </si>
+  <si>
+    <t>aclrsiq11</t>
+  </si>
+  <si>
+    <t>aclrsiq12</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1942,7 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2060,6 +2196,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2325,7 +2467,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2668,6 +2810,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2964,13 +3107,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3028,7 +3171,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="146" t="s">
+      <c r="G4" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3061,7 +3204,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="141"/>
+      <c r="G5" s="142"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3089,7 +3232,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="141"/>
+      <c r="G6" s="142"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3113,7 +3256,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="141"/>
+      <c r="G7" s="142"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3136,7 +3279,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="141"/>
+      <c r="G8" s="142"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3164,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="141"/>
+      <c r="G9" s="142"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3247,13 +3390,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="140" t="s">
+      <c r="B15" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3308,24 +3451,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="142">
+      <c r="H16" s="143">
         <v>45359</v>
       </c>
-      <c r="I16" s="143"/>
-      <c r="J16" s="144">
+      <c r="I16" s="144"/>
+      <c r="J16" s="145">
         <v>47204</v>
       </c>
-      <c r="K16" s="143"/>
-      <c r="L16" s="145" t="s">
+      <c r="K16" s="144"/>
+      <c r="L16" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="143"/>
-      <c r="N16" s="142">
+      <c r="M16" s="144"/>
+      <c r="N16" s="143">
         <v>45429</v>
       </c>
-      <c r="O16" s="143"/>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="143"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="144"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3399,7 +3542,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="146" t="s">
+      <c r="G18" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3443,7 +3586,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="141"/>
+      <c r="G19" s="142"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3481,7 +3624,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="141"/>
+      <c r="G20" s="142"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3527,7 +3670,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="141"/>
+      <c r="G21" s="142"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3563,7 +3706,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="141"/>
+      <c r="G22" s="142"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3601,7 +3744,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="141"/>
+      <c r="G23" s="142"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3641,7 +3784,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="141"/>
+      <c r="G24" s="142"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -3832,13 +3975,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="140" t="s">
+      <c r="B32" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="141"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="141"/>
+      <c r="C32" s="142"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -3883,12 +4026,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="147" t="s">
+      <c r="H33" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="143"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="143"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3913,7 +4056,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="146" t="s">
+      <c r="G34" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -3944,7 +4087,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="141"/>
+      <c r="G35" s="142"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -3973,7 +4116,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="141"/>
+      <c r="G36" s="142"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4002,7 +4145,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="141"/>
+      <c r="G37" s="142"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4031,7 +4174,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="141"/>
+      <c r="G38" s="142"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4052,7 +4195,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="141"/>
+      <c r="G39" s="142"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4081,7 +4224,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="141"/>
+      <c r="G40" s="142"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4102,7 +4245,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="141"/>
+      <c r="G41" s="142"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4131,7 +4274,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="141"/>
+      <c r="G42" s="142"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4152,7 +4295,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="141"/>
+      <c r="G43" s="142"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4175,17 +4318,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="148" t="s">
+      <c r="C44" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="148" t="s">
+      <c r="D44" s="149" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="141"/>
+      <c r="G44" s="142"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4200,13 +4343,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="141"/>
-      <c r="D45" s="141"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="142"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="141"/>
+      <c r="G45" s="142"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4235,7 +4378,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="141"/>
+      <c r="G46" s="142"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4256,7 +4399,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="141"/>
+      <c r="G47" s="142"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4285,7 +4428,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="141"/>
+      <c r="G48" s="142"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4314,7 +4457,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="141"/>
+      <c r="G49" s="142"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4341,7 +4484,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="141"/>
+      <c r="G50" s="142"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4437,10 +4580,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="153">
+      <c r="B54" s="154">
         <v>16</v>
       </c>
-      <c r="C54" s="154" t="s">
+      <c r="C54" s="155" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4461,8 +4604,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="141"/>
-      <c r="C55" s="141"/>
+      <c r="B55" s="142"/>
+      <c r="C55" s="142"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4481,10 +4624,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="149">
+      <c r="B56" s="150">
         <v>17</v>
       </c>
-      <c r="C56" s="151" t="s">
+      <c r="C56" s="152" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4506,8 +4649,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="150"/>
-      <c r="C57" s="152"/>
+      <c r="B57" s="151"/>
+      <c r="C57" s="153"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4527,10 +4670,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="153">
+      <c r="B58" s="154">
         <v>18</v>
       </c>
-      <c r="C58" s="154" t="s">
+      <c r="C58" s="155" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4551,8 +4694,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="141"/>
-      <c r="C59" s="141"/>
+      <c r="B59" s="142"/>
+      <c r="C59" s="142"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4571,10 +4714,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="149">
+      <c r="B60" s="150">
         <v>19</v>
       </c>
-      <c r="C60" s="151" t="s">
+      <c r="C60" s="152" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4596,8 +4739,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="150"/>
-      <c r="C61" s="152"/>
+      <c r="B61" s="151"/>
+      <c r="C61" s="153"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4617,7 +4760,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="153">
+      <c r="B62" s="154">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4641,7 +4784,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="141"/>
+      <c r="B63" s="142"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4817,13 +4960,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="140" t="s">
+      <c r="B74" s="141" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="141"/>
-      <c r="D74" s="141"/>
-      <c r="E74" s="141"/>
-      <c r="F74" s="141"/>
+      <c r="C74" s="142"/>
+      <c r="D74" s="142"/>
+      <c r="E74" s="142"/>
+      <c r="F74" s="142"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -4902,7 +5045,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="146" t="s">
+      <c r="G76" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -4929,7 +5072,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="141"/>
+      <c r="G77" s="142"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -4954,7 +5097,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="141"/>
+      <c r="G78" s="142"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -4981,7 +5124,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="141"/>
+      <c r="G79" s="142"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5013,7 +5156,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="141"/>
+      <c r="G80" s="142"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5042,7 +5185,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="141"/>
+      <c r="G81" s="142"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5071,7 +5214,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="141"/>
+      <c r="G82" s="142"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5100,7 +5243,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="141"/>
+      <c r="G83" s="142"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5129,7 +5272,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="141"/>
+      <c r="G84" s="142"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5158,7 +5301,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="141"/>
+      <c r="G85" s="142"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5187,7 +5330,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="141"/>
+      <c r="G86" s="142"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5216,7 +5359,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="141"/>
+      <c r="G87" s="142"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -10769,7 +10912,7 @@
         <v>235</v>
       </c>
       <c r="M38" s="97" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11498,7 +11641,7 @@
         <v>235</v>
       </c>
       <c r="M56" s="97" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -11899,7 +12042,7 @@
         <v>235</v>
       </c>
       <c r="M66" s="97" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -12189,6 +12332,204 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1653A7C-21C0-814E-8E44-D921BBCC189F}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="69.6640625" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="86" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1" s="86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="86" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A2" s="86" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="140" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A3" s="86" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="140" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="86" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A4" s="86" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="140" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="86" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A5" s="86" t="s">
+        <v>360</v>
+      </c>
+      <c r="B5" s="140" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A6" s="86" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" s="140" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A7" s="86" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="140" t="s">
+        <v>330</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A8" s="86" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="140" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A9" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="140" t="s">
+        <v>332</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A10" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="140" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A11" s="86" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="140" t="s">
+        <v>334</v>
+      </c>
+      <c r="C11" s="86" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A12" s="86" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="140" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="A13" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="140" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="34" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A797E27-8800-F04C-B6DD-3411CE39E1CB}">
   <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -12209,30 +12550,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="133" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="156" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155" t="s">
+      <c r="C1" s="156"/>
+      <c r="D1" s="156" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155" t="s">
+      <c r="E1" s="156"/>
+      <c r="F1" s="156" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155" t="s">
+      <c r="G1" s="156"/>
+      <c r="H1" s="156" t="s">
         <v>298</v>
       </c>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155" t="s">
+      <c r="I1" s="156"/>
+      <c r="J1" s="156" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155" t="s">
+      <c r="K1" s="156"/>
+      <c r="L1" s="156" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="155"/>
+      <c r="M1" s="156"/>
     </row>
     <row r="2" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="134" t="s">
@@ -12828,32 +13169,32 @@
       <c r="M52" s="131"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="156" t="s">
+      <c r="H74" s="157" t="s">
         <v>298</v>
       </c>
-      <c r="I74" s="156"/>
-      <c r="J74" s="156" t="s">
+      <c r="I74" s="157"/>
+      <c r="J74" s="157" t="s">
         <v>299</v>
       </c>
-      <c r="K74" s="156"/>
-      <c r="L74" s="156" t="s">
+      <c r="K74" s="157"/>
+      <c r="L74" s="157" t="s">
         <v>300</v>
       </c>
-      <c r="M74" s="156"/>
+      <c r="M74" s="157"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="156" t="s">
+      <c r="B75" s="157" t="s">
         <v>295</v>
       </c>
-      <c r="C75" s="156"/>
-      <c r="D75" s="156" t="s">
+      <c r="C75" s="157"/>
+      <c r="D75" s="157" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="156"/>
-      <c r="F75" s="156" t="s">
+      <c r="E75" s="157"/>
+      <c r="F75" s="157" t="s">
         <v>297</v>
       </c>
-      <c r="G75" s="156"/>
+      <c r="G75" s="157"/>
       <c r="H75" s="109" t="s">
         <v>254</v>
       </c>
@@ -13227,7 +13568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01440D2E-D5CB-624F-A307-D0DE876488BF}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1579" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58035CDF-F96D-D740-AF90-09BDD740F026}"/>
+  <xr:revisionPtr revIDLastSave="1623" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FF57B7-4156-2E4A-A9F8-82566B851A95}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="-20220" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="-20220" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="379">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1932,6 +1932,36 @@
   </si>
   <si>
     <t>aclrsiq12</t>
+  </si>
+  <si>
+    <t>20 SJ Mean Power/kg</t>
+  </si>
+  <si>
+    <t>MP/kg</t>
+  </si>
+  <si>
+    <t>Power output unchanged with fatigue</t>
+  </si>
+  <si>
+    <t>CSI-A</t>
+  </si>
+  <si>
+    <t>20 SJ Shortening Asymmetry</t>
+  </si>
+  <si>
+    <t>Ratio of force produced by each limb in the shortening (propulsive) phase of the jump.  Symmetry is unchnaged with fatigue.</t>
+  </si>
+  <si>
+    <t>Drop Jump Height</t>
+  </si>
+  <si>
+    <t>Drop Jump RSI</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>Athlete steps off 30cm box and is cued to jump as high and fast as possible.</t>
   </si>
 </sst>
 </file>
@@ -2811,28 +2841,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2842,11 +2865,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3107,7 +3137,7 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="143" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="142"/>
@@ -3171,7 +3201,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="147" t="s">
+      <c r="G4" s="144" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3390,7 +3420,7 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="143" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="142"/>
@@ -3451,24 +3481,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="143">
+      <c r="H16" s="153">
         <v>45359</v>
       </c>
-      <c r="I16" s="144"/>
-      <c r="J16" s="145">
+      <c r="I16" s="152"/>
+      <c r="J16" s="154">
         <v>47204</v>
       </c>
-      <c r="K16" s="144"/>
-      <c r="L16" s="146" t="s">
+      <c r="K16" s="152"/>
+      <c r="L16" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="144"/>
-      <c r="N16" s="143">
+      <c r="M16" s="152"/>
+      <c r="N16" s="153">
         <v>45429</v>
       </c>
-      <c r="O16" s="144"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="144"/>
+      <c r="O16" s="152"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="152"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3542,7 +3572,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="147" t="s">
+      <c r="G18" s="144" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3975,7 +4005,7 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="141" t="s">
+      <c r="B32" s="143" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="142"/>
@@ -4026,12 +4056,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="148" t="s">
+      <c r="H33" s="151" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="144"/>
-      <c r="J33" s="143"/>
-      <c r="K33" s="144"/>
+      <c r="I33" s="152"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="152"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -4056,7 +4086,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="147" t="s">
+      <c r="G34" s="144" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -4318,10 +4348,10 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="149" t="s">
+      <c r="C44" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="149" t="s">
+      <c r="D44" s="145" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
@@ -4580,10 +4610,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="154">
+      <c r="B54" s="141">
         <v>16</v>
       </c>
-      <c r="C54" s="155" t="s">
+      <c r="C54" s="146" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4624,10 +4654,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="150">
+      <c r="B56" s="147">
         <v>17</v>
       </c>
-      <c r="C56" s="152" t="s">
+      <c r="C56" s="149" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4649,8 +4679,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="151"/>
-      <c r="C57" s="153"/>
+      <c r="B57" s="148"/>
+      <c r="C57" s="150"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4670,10 +4700,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="154">
+      <c r="B58" s="141">
         <v>18</v>
       </c>
-      <c r="C58" s="155" t="s">
+      <c r="C58" s="146" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4714,10 +4744,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="150">
+      <c r="B60" s="147">
         <v>19</v>
       </c>
-      <c r="C60" s="152" t="s">
+      <c r="C60" s="149" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4739,8 +4769,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="151"/>
-      <c r="C61" s="153"/>
+      <c r="B61" s="148"/>
+      <c r="C61" s="150"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4760,7 +4790,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="154">
+      <c r="B62" s="141">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4960,7 +4990,7 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="141" t="s">
+      <c r="B74" s="143" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="142"/>
@@ -5045,7 +5075,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="147" t="s">
+      <c r="G76" s="144" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -9105,6 +9135,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -9115,22 +9161,6 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9427,7 +9457,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -12320,6 +12350,170 @@
         <v>235</v>
       </c>
       <c r="M73" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="97">
+        <v>5</v>
+      </c>
+      <c r="B74" s="97" t="s">
+        <v>369</v>
+      </c>
+      <c r="C74" s="97" t="s">
+        <v>370</v>
+      </c>
+      <c r="D74" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E74" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F74" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G74" s="97">
+        <v>95</v>
+      </c>
+      <c r="H74" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I74" s="120" t="s">
+        <v>371</v>
+      </c>
+      <c r="J74" s="97" t="s">
+        <v>372</v>
+      </c>
+      <c r="K74" s="97">
+        <v>20</v>
+      </c>
+      <c r="L74" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M74" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="97">
+        <v>5</v>
+      </c>
+      <c r="B75" s="97" t="s">
+        <v>373</v>
+      </c>
+      <c r="C75" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D75" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E75" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F75" s="123" t="s">
+        <v>278</v>
+      </c>
+      <c r="G75" s="97">
+        <v>10</v>
+      </c>
+      <c r="H75" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="I75" s="120" t="s">
+        <v>374</v>
+      </c>
+      <c r="J75" s="97" t="s">
+        <v>372</v>
+      </c>
+      <c r="K75" s="97">
+        <v>20</v>
+      </c>
+      <c r="L75" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="M75" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="97">
+        <v>5</v>
+      </c>
+      <c r="B76" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="C76" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D76" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E76" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F76" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G76" s="97">
+        <v>95</v>
+      </c>
+      <c r="H76" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I76" s="120" t="s">
+        <v>378</v>
+      </c>
+      <c r="J76" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K76" s="97">
+        <v>5</v>
+      </c>
+      <c r="L76" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M76" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="97">
+        <v>5</v>
+      </c>
+      <c r="B77" s="97" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="97" t="s">
+        <v>377</v>
+      </c>
+      <c r="D77" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="E77" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="F77" s="129" t="s">
+        <v>253</v>
+      </c>
+      <c r="G77" s="97">
+        <v>95</v>
+      </c>
+      <c r="H77" s="120" t="s">
+        <v>277</v>
+      </c>
+      <c r="I77" s="120" t="s">
+        <v>378</v>
+      </c>
+      <c r="J77" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="K77" s="97">
+        <v>5</v>
+      </c>
+      <c r="L77" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="M77" s="97" t="s">
         <v>288</v>
       </c>
     </row>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1623" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FF57B7-4156-2E4A-A9F8-82566B851A95}"/>
+  <xr:revisionPtr revIDLastSave="1625" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E8E46A3-E610-E844-A418-7145F353C2F5}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="-20220" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="380">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1962,6 +1962,9 @@
   </si>
   <si>
     <t>Athlete steps off 30cm box and is cued to jump as high and fast as possible.</t>
+  </si>
+  <si>
+    <t>images/testing/passive_knee_extension_v4.svg</t>
   </si>
 </sst>
 </file>
@@ -2841,21 +2844,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2865,18 +2875,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3137,7 +3140,7 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="142"/>
@@ -3201,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="144" t="s">
+      <c r="G4" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3420,7 +3423,7 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="143" t="s">
+      <c r="B15" s="141" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="142"/>
@@ -3481,24 +3484,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="153">
+      <c r="H16" s="143">
         <v>45359</v>
       </c>
-      <c r="I16" s="152"/>
-      <c r="J16" s="154">
+      <c r="I16" s="144"/>
+      <c r="J16" s="145">
         <v>47204</v>
       </c>
-      <c r="K16" s="152"/>
-      <c r="L16" s="155" t="s">
+      <c r="K16" s="144"/>
+      <c r="L16" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="152"/>
-      <c r="N16" s="153">
+      <c r="M16" s="144"/>
+      <c r="N16" s="143">
         <v>45429</v>
       </c>
-      <c r="O16" s="152"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="152"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="144"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="144" t="s">
+      <c r="G18" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -4005,7 +4008,7 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="143" t="s">
+      <c r="B32" s="141" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="142"/>
@@ -4056,12 +4059,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="151" t="s">
+      <c r="H33" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="152"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="152"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -4086,7 +4089,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="144" t="s">
+      <c r="G34" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -4348,10 +4351,10 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="145" t="s">
+      <c r="C44" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="145" t="s">
+      <c r="D44" s="149" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
@@ -4610,10 +4613,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="141">
+      <c r="B54" s="154">
         <v>16</v>
       </c>
-      <c r="C54" s="146" t="s">
+      <c r="C54" s="155" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4654,10 +4657,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="147">
+      <c r="B56" s="150">
         <v>17</v>
       </c>
-      <c r="C56" s="149" t="s">
+      <c r="C56" s="152" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4679,8 +4682,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="148"/>
-      <c r="C57" s="150"/>
+      <c r="B57" s="151"/>
+      <c r="C57" s="153"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4700,10 +4703,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="141">
+      <c r="B58" s="154">
         <v>18</v>
       </c>
-      <c r="C58" s="146" t="s">
+      <c r="C58" s="155" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4744,10 +4747,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="147">
+      <c r="B60" s="150">
         <v>19</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="152" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4769,8 +4772,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="148"/>
-      <c r="C61" s="150"/>
+      <c r="B61" s="151"/>
+      <c r="C61" s="153"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4790,7 +4793,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="141">
+      <c r="B62" s="154">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4990,7 +4993,7 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="143" t="s">
+      <c r="B74" s="141" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="142"/>
@@ -5075,7 +5078,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="144" t="s">
+      <c r="G76" s="147" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -9135,22 +9138,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G4:G9"/>
-    <mergeCell ref="G18:G24"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="G34:G50"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="G76:G87"/>
@@ -9161,6 +9148,22 @@
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="G34:G50"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G4:G9"/>
+    <mergeCell ref="G18:G24"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9553,7 +9556,7 @@
       </c>
       <c r="L2" s="81"/>
       <c r="M2" s="97" t="s">
-        <v>288</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1625" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E8E46A3-E610-E844-A418-7145F353C2F5}"/>
+  <xr:revisionPtr revIDLastSave="1648" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9CDE7D-35CC-C443-AF73-80F7AF22C785}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="-20220" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="385">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1965,6 +1965,23 @@
   </si>
   <si>
     <t>images/testing/passive_knee_extension_v4.svg</t>
+  </si>
+  <si>
+    <t>rtr</t>
+  </si>
+  <si>
+    <t>SL Pogos</t>
+  </si>
+  <si>
+    <t>Aspetar</t>
+  </si>
+  <si>
+    <t>Pain free single leg pogo hops</t>
+  </si>
+  <si>
+    <t>The athlete must perform 20 consecutive single leg pogo hops and report no increase in pain during or afterwards.
+There are no height or intensity criteria.
+It is important that the practitioner monitor the quality of repetitions, particulalry the presence of knee valgus.</t>
   </si>
 </sst>
 </file>
@@ -1975,11 +1992,18 @@
     <numFmt numFmtId="164" formatCode="mmm\ d/yy"/>
     <numFmt numFmtId="165" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2498,394 +2522,400 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="19" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="31" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="24" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3140,13 +3170,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3204,7 +3234,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="147" t="s">
+      <c r="G4" s="148" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3237,7 +3267,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="142"/>
+      <c r="G5" s="143"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3265,7 +3295,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="142"/>
+      <c r="G6" s="143"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3289,7 +3319,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="142"/>
+      <c r="G7" s="143"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3312,7 +3342,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="142"/>
+      <c r="G8" s="143"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3340,7 +3370,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="142"/>
+      <c r="G9" s="143"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3423,13 +3453,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3484,24 +3514,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="143">
+      <c r="H16" s="144">
         <v>45359</v>
       </c>
-      <c r="I16" s="144"/>
-      <c r="J16" s="145">
+      <c r="I16" s="145"/>
+      <c r="J16" s="146">
         <v>47204</v>
       </c>
-      <c r="K16" s="144"/>
-      <c r="L16" s="146" t="s">
+      <c r="K16" s="145"/>
+      <c r="L16" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="144"/>
-      <c r="N16" s="143">
+      <c r="M16" s="145"/>
+      <c r="N16" s="144">
         <v>45429</v>
       </c>
-      <c r="O16" s="144"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="144"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="145"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3575,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="147" t="s">
+      <c r="G18" s="148" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3619,7 +3649,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="142"/>
+      <c r="G19" s="143"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3657,7 +3687,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="142"/>
+      <c r="G20" s="143"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3703,7 +3733,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="142"/>
+      <c r="G21" s="143"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3739,7 +3769,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="142"/>
+      <c r="G22" s="143"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3777,7 +3807,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="142"/>
+      <c r="G23" s="143"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3817,7 +3847,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="142"/>
+      <c r="G24" s="143"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -4008,13 +4038,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="141" t="s">
+      <c r="B32" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="142"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -4059,12 +4089,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="148" t="s">
+      <c r="H33" s="149" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="144"/>
-      <c r="J33" s="143"/>
-      <c r="K33" s="144"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="145"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -4089,7 +4119,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="147" t="s">
+      <c r="G34" s="148" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -4120,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="142"/>
+      <c r="G35" s="143"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -4149,7 +4179,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="142"/>
+      <c r="G36" s="143"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4178,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="142"/>
+      <c r="G37" s="143"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4207,7 +4237,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="142"/>
+      <c r="G38" s="143"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4228,7 +4258,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="142"/>
+      <c r="G39" s="143"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4257,7 +4287,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="142"/>
+      <c r="G40" s="143"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4278,7 +4308,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="142"/>
+      <c r="G41" s="143"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4307,7 +4337,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="142"/>
+      <c r="G42" s="143"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4328,7 +4358,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="142"/>
+      <c r="G43" s="143"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4351,17 +4381,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="149" t="s">
+      <c r="C44" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="149" t="s">
+      <c r="D44" s="150" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="142"/>
+      <c r="G44" s="143"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4376,13 +4406,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="142"/>
-      <c r="D45" s="142"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="142"/>
+      <c r="G45" s="143"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4411,7 +4441,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="142"/>
+      <c r="G46" s="143"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4432,7 +4462,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="142"/>
+      <c r="G47" s="143"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4461,7 +4491,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="142"/>
+      <c r="G48" s="143"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4490,7 +4520,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="142"/>
+      <c r="G49" s="143"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4517,7 +4547,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="142"/>
+      <c r="G50" s="143"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4613,10 +4643,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="154">
+      <c r="B54" s="155">
         <v>16</v>
       </c>
-      <c r="C54" s="155" t="s">
+      <c r="C54" s="156" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4637,8 +4667,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="142"/>
-      <c r="C55" s="142"/>
+      <c r="B55" s="143"/>
+      <c r="C55" s="143"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4657,10 +4687,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="150">
+      <c r="B56" s="151">
         <v>17</v>
       </c>
-      <c r="C56" s="152" t="s">
+      <c r="C56" s="153" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4682,8 +4712,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="151"/>
-      <c r="C57" s="153"/>
+      <c r="B57" s="152"/>
+      <c r="C57" s="154"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4703,10 +4733,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="154">
+      <c r="B58" s="155">
         <v>18</v>
       </c>
-      <c r="C58" s="155" t="s">
+      <c r="C58" s="156" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4727,8 +4757,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="142"/>
-      <c r="C59" s="142"/>
+      <c r="B59" s="143"/>
+      <c r="C59" s="143"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4747,10 +4777,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="150">
+      <c r="B60" s="151">
         <v>19</v>
       </c>
-      <c r="C60" s="152" t="s">
+      <c r="C60" s="153" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4772,8 +4802,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="151"/>
-      <c r="C61" s="153"/>
+      <c r="B61" s="152"/>
+      <c r="C61" s="154"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4793,7 +4823,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="154">
+      <c r="B62" s="155">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4817,7 +4847,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="142"/>
+      <c r="B63" s="143"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -4993,13 +5023,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="141" t="s">
+      <c r="B74" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="142"/>
-      <c r="D74" s="142"/>
-      <c r="E74" s="142"/>
-      <c r="F74" s="142"/>
+      <c r="C74" s="143"/>
+      <c r="D74" s="143"/>
+      <c r="E74" s="143"/>
+      <c r="F74" s="143"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -5078,7 +5108,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="147" t="s">
+      <c r="G76" s="148" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -5105,7 +5135,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="142"/>
+      <c r="G77" s="143"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -5130,7 +5160,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="142"/>
+      <c r="G78" s="143"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -5157,7 +5187,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="142"/>
+      <c r="G79" s="143"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5189,7 +5219,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="142"/>
+      <c r="G80" s="143"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5218,7 +5248,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="142"/>
+      <c r="G81" s="143"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5247,7 +5277,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="142"/>
+      <c r="G82" s="143"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5276,7 +5306,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="142"/>
+      <c r="G83" s="143"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5305,7 +5335,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="142"/>
+      <c r="G84" s="143"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5334,7 +5364,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="142"/>
+      <c r="G85" s="143"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5363,7 +5393,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="142"/>
+      <c r="G86" s="143"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5392,7 +5422,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="142"/>
+      <c r="G87" s="143"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -9460,7 +9490,7 @@
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="96" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -12520,6 +12550,224 @@
         <v>288</v>
       </c>
     </row>
+    <row r="78" spans="1:13" s="100" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="99" t="s">
+        <v>380</v>
+      </c>
+      <c r="B78" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="E78" s="141" t="s">
+        <v>220</v>
+      </c>
+      <c r="F78" s="114" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78" s="114">
+        <v>0</v>
+      </c>
+      <c r="H78" s="113" t="s">
+        <v>180</v>
+      </c>
+      <c r="I78" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="J78" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" s="99"/>
+      <c r="L78" s="99"/>
+      <c r="M78" s="99" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B79" s="124" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" s="97" t="s">
+        <v>184</v>
+      </c>
+      <c r="D79" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F79" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G79" s="78">
+        <v>125</v>
+      </c>
+      <c r="H79" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="I79" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="J79" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="M79" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B80" s="124" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E80" s="103" t="s">
+        <v>220</v>
+      </c>
+      <c r="F80" s="78">
+        <v>1</v>
+      </c>
+      <c r="G80" s="78">
+        <v>1</v>
+      </c>
+      <c r="H80" s="112" t="s">
+        <v>177</v>
+      </c>
+      <c r="I80" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="J80" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="M80" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B81" s="124" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D81" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="F81" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="G81" s="78">
+        <v>80</v>
+      </c>
+      <c r="H81" s="112" t="s">
+        <v>157</v>
+      </c>
+      <c r="I81" s="102" t="s">
+        <v>214</v>
+      </c>
+      <c r="K81" s="97">
+        <v>3</v>
+      </c>
+      <c r="L81" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="M81" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="C82" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D82" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E82" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="F82" s="123" t="s">
+        <v>306</v>
+      </c>
+      <c r="G82" s="97">
+        <v>20</v>
+      </c>
+      <c r="H82" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="I82" s="120" t="s">
+        <v>284</v>
+      </c>
+      <c r="K82" s="97">
+        <v>5</v>
+      </c>
+      <c r="L82" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="M82" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B83" s="97" t="s">
+        <v>381</v>
+      </c>
+      <c r="C83" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D83" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="E83" s="104" t="s">
+        <v>219</v>
+      </c>
+      <c r="F83" s="97">
+        <v>20</v>
+      </c>
+      <c r="G83" s="97">
+        <v>20</v>
+      </c>
+      <c r="H83" s="120" t="s">
+        <v>383</v>
+      </c>
+      <c r="I83" s="120" t="s">
+        <v>384</v>
+      </c>
+      <c r="J83" s="97" t="s">
+        <v>382</v>
+      </c>
+      <c r="M83" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -12721,7 +12969,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12747,30 +12995,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="133" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="156" t="s">
+      <c r="B1" s="157" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156" t="s">
+      <c r="C1" s="157"/>
+      <c r="D1" s="157" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156" t="s">
+      <c r="E1" s="157"/>
+      <c r="F1" s="157" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156" t="s">
+      <c r="G1" s="157"/>
+      <c r="H1" s="157" t="s">
         <v>298</v>
       </c>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156" t="s">
+      <c r="I1" s="157"/>
+      <c r="J1" s="157" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156" t="s">
+      <c r="K1" s="157"/>
+      <c r="L1" s="157" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="156"/>
+      <c r="M1" s="157"/>
     </row>
     <row r="2" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="134" t="s">
@@ -13366,32 +13614,32 @@
       <c r="M52" s="131"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="157" t="s">
+      <c r="H74" s="158" t="s">
         <v>298</v>
       </c>
-      <c r="I74" s="157"/>
-      <c r="J74" s="157" t="s">
+      <c r="I74" s="158"/>
+      <c r="J74" s="158" t="s">
         <v>299</v>
       </c>
-      <c r="K74" s="157"/>
-      <c r="L74" s="157" t="s">
+      <c r="K74" s="158"/>
+      <c r="L74" s="158" t="s">
         <v>300</v>
       </c>
-      <c r="M74" s="157"/>
+      <c r="M74" s="158"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="157" t="s">
+      <c r="B75" s="158" t="s">
         <v>295</v>
       </c>
-      <c r="C75" s="157"/>
-      <c r="D75" s="157" t="s">
+      <c r="C75" s="158"/>
+      <c r="D75" s="158" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="157"/>
-      <c r="F75" s="157" t="s">
+      <c r="E75" s="158"/>
+      <c r="F75" s="158" t="s">
         <v>297</v>
       </c>
-      <c r="G75" s="157"/>
+      <c r="G75" s="158"/>
       <c r="H75" s="109" t="s">
         <v>254</v>
       </c>
@@ -13760,7 +14008,7 @@
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/sample_data/acl-protocol-criteria-2025.xlsx
+++ b/sample_data/acl-protocol-criteria-2025.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1648" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9CDE7D-35CC-C443-AF73-80F7AF22C785}"/>
+  <xr:revisionPtr revIDLastSave="1673" documentId="13_ncr:1_{470AE8F2-12FF-4247-93B1-32004E222A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A32C9A1F-AB4B-B840-82CC-666A9EF2628F}"/>
   <bookViews>
-    <workbookView xWindow="-4580" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4580" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criteria" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Phase0" sheetId="2" r:id="rId2"/>
     <sheet name="criteria_full" sheetId="5" r:id="rId3"/>
-    <sheet name="acl_rsi" sheetId="7" r:id="rId4"/>
-    <sheet name="criteria_overview" sheetId="6" r:id="rId5"/>
-    <sheet name="calcs" sheetId="3" r:id="rId6"/>
+    <sheet name="TSK-11" sheetId="8" r:id="rId4"/>
+    <sheet name="acl_rsi" sheetId="7" r:id="rId5"/>
+    <sheet name="criteria_overview" sheetId="6" r:id="rId6"/>
+    <sheet name="calcs" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -795,7 +796,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="407">
   <si>
     <t>Phase 0: Pre Surgery</t>
   </si>
@@ -1982,6 +1983,72 @@
     <t>The athlete must perform 20 consecutive single leg pogo hops and report no increase in pain during or afterwards.
 There are no height or intensity criteria.
 It is important that the practitioner monitor the quality of repetitions, particulalry the presence of knee valgus.</t>
+  </si>
+  <si>
+    <t>tsk1</t>
+  </si>
+  <si>
+    <t>tsk2</t>
+  </si>
+  <si>
+    <t>tsk3</t>
+  </si>
+  <si>
+    <t>tsk4</t>
+  </si>
+  <si>
+    <t>tsk5</t>
+  </si>
+  <si>
+    <t>tsk6</t>
+  </si>
+  <si>
+    <t>tsk7</t>
+  </si>
+  <si>
+    <t>tsk8</t>
+  </si>
+  <si>
+    <t>tsk9</t>
+  </si>
+  <si>
+    <t>tsk10</t>
+  </si>
+  <si>
+    <t>tsk11</t>
+  </si>
+  <si>
+    <t>1. I'm afraid that I might injure myself if I exercise.</t>
+  </si>
+  <si>
+    <t>2. If I were to try to overcome it, my pain would increase.</t>
+  </si>
+  <si>
+    <t>3. My body is telling me I have something dangerously wrong.</t>
+  </si>
+  <si>
+    <t>4. People aren’t taking my medical condition seriously enough.</t>
+  </si>
+  <si>
+    <t>5. My accident has put my body at risk for the rest of my life.</t>
+  </si>
+  <si>
+    <t>6. Pain always means I have injured my body.</t>
+  </si>
+  <si>
+    <t>7. Simply being careful that I do not make any unnecessary movements is the safest thing I can do to prevent my pain from worsening.</t>
+  </si>
+  <si>
+    <t>8. I wouldn’t have this much pain if there weren’t something potentially dangerous going on in my body.</t>
+  </si>
+  <si>
+    <t>9. Pain lets me know when to stop exercising so that I do not injure myself.</t>
+  </si>
+  <si>
+    <t>10. I can’t do all the things normal people do because it’s too easy for me to get injured.</t>
+  </si>
+  <si>
+    <t>11. No one should have to exercise when he/she is in pain.</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2871,6 +2938,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2913,9 +2984,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3170,13 +3238,13 @@
     </row>
     <row r="2" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3234,7 +3302,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12"/>
-      <c r="G4" s="148" t="s">
+      <c r="G4" s="150" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="14"/>
@@ -3267,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="143"/>
+      <c r="G5" s="145"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="R5" s="20">
@@ -3295,7 +3363,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="143"/>
+      <c r="G6" s="145"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="R6" s="20">
@@ -3319,7 +3387,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="143"/>
+      <c r="G7" s="145"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="S7" s="21"/>
@@ -3342,7 +3410,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="143"/>
+      <c r="G8" s="145"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="R8" s="20">
@@ -3370,7 +3438,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="143"/>
+      <c r="G9" s="145"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="R9" s="20">
@@ -3453,13 +3521,13 @@
     </row>
     <row r="15" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="142" t="s">
+      <c r="B15" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
       <c r="G15" s="1"/>
       <c r="H15" s="25" t="s">
         <v>34</v>
@@ -3514,24 +3582,24 @@
       <c r="G16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="144">
+      <c r="H16" s="146">
         <v>45359</v>
       </c>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146">
+      <c r="I16" s="147"/>
+      <c r="J16" s="148">
         <v>47204</v>
       </c>
-      <c r="K16" s="145"/>
-      <c r="L16" s="147" t="s">
+      <c r="K16" s="147"/>
+      <c r="L16" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="145"/>
-      <c r="N16" s="144">
+      <c r="M16" s="147"/>
+      <c r="N16" s="146">
         <v>45429</v>
       </c>
-      <c r="O16" s="145"/>
-      <c r="P16" s="144"/>
-      <c r="Q16" s="145"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="147"/>
       <c r="R16" s="20">
         <v>1</v>
       </c>
@@ -3605,7 +3673,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="12"/>
-      <c r="G18" s="148" t="s">
+      <c r="G18" s="150" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="31"/>
@@ -3649,7 +3717,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="143"/>
+      <c r="G19" s="145"/>
       <c r="H19" s="36"/>
       <c r="I19" s="37">
         <v>45325</v>
@@ -3687,7 +3755,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="12"/>
-      <c r="G20" s="143"/>
+      <c r="G20" s="145"/>
       <c r="H20" s="36">
         <v>39</v>
       </c>
@@ -3733,7 +3801,7 @@
         <v>51</v>
       </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="143"/>
+      <c r="G21" s="145"/>
       <c r="H21" s="31"/>
       <c r="I21" s="34" t="s">
         <v>52</v>
@@ -3769,7 +3837,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="143"/>
+      <c r="G22" s="145"/>
       <c r="H22" s="31"/>
       <c r="I22" s="34" t="s">
         <v>52</v>
@@ -3807,7 +3875,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="143"/>
+      <c r="G23" s="145"/>
       <c r="H23" s="36"/>
       <c r="I23" s="38">
         <v>91</v>
@@ -3847,7 +3915,7 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
-      <c r="G24" s="143"/>
+      <c r="G24" s="145"/>
       <c r="H24" s="31" t="s">
         <v>60</v>
       </c>
@@ -4038,13 +4106,13 @@
     </row>
     <row r="32" spans="1:22" ht="23" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="142" t="s">
+      <c r="B32" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="143"/>
-      <c r="D32" s="143"/>
-      <c r="E32" s="143"/>
-      <c r="F32" s="143"/>
+      <c r="C32" s="145"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="145"/>
       <c r="G32" s="1"/>
       <c r="H32" s="42" t="s">
         <v>34</v>
@@ -4089,12 +4157,12 @@
       <c r="G33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="149" t="s">
+      <c r="H33" s="151" t="s">
         <v>70</v>
       </c>
-      <c r="I33" s="145"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="145"/>
+      <c r="I33" s="147"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="147"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -4119,7 +4187,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="148" t="s">
+      <c r="G34" s="150" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="44"/>
@@ -4150,7 +4218,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="143"/>
+      <c r="G35" s="145"/>
       <c r="H35" s="48"/>
       <c r="I35" s="49"/>
       <c r="J35" s="48"/>
@@ -4179,7 +4247,7 @@
         <v>74</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="143"/>
+      <c r="G36" s="145"/>
       <c r="H36" s="44"/>
       <c r="I36" s="45"/>
       <c r="J36" s="44"/>
@@ -4208,7 +4276,7 @@
         <v>77</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="143"/>
+      <c r="G37" s="145"/>
       <c r="H37" s="48"/>
       <c r="I37" s="49"/>
       <c r="J37" s="48"/>
@@ -4237,7 +4305,7 @@
         <v>80</v>
       </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="143"/>
+      <c r="G38" s="145"/>
       <c r="H38" s="44"/>
       <c r="I38" s="45"/>
       <c r="J38" s="44"/>
@@ -4258,7 +4326,7 @@
         <v>81</v>
       </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="143"/>
+      <c r="G39" s="145"/>
       <c r="H39" s="44"/>
       <c r="I39" s="45"/>
       <c r="J39" s="44"/>
@@ -4287,7 +4355,7 @@
         <v>80</v>
       </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="143"/>
+      <c r="G40" s="145"/>
       <c r="H40" s="48"/>
       <c r="I40" s="49"/>
       <c r="J40" s="48"/>
@@ -4308,7 +4376,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="12"/>
-      <c r="G41" s="143"/>
+      <c r="G41" s="145"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="48"/>
@@ -4337,7 +4405,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="143"/>
+      <c r="G42" s="145"/>
       <c r="H42" s="44"/>
       <c r="I42" s="45"/>
       <c r="J42" s="44"/>
@@ -4358,7 +4426,7 @@
         <v>86</v>
       </c>
       <c r="F43" s="12"/>
-      <c r="G43" s="143"/>
+      <c r="G43" s="145"/>
       <c r="H43" s="55" t="s">
         <v>87</v>
       </c>
@@ -4381,17 +4449,17 @@
       <c r="B44" s="16">
         <v>8</v>
       </c>
-      <c r="C44" s="150" t="s">
+      <c r="C44" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="150" t="s">
+      <c r="D44" s="152" t="s">
         <v>88</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="12"/>
-      <c r="G44" s="143"/>
+      <c r="G44" s="145"/>
       <c r="H44" s="48"/>
       <c r="I44" s="49"/>
       <c r="J44" s="48"/>
@@ -4406,13 +4474,13 @@
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
+      <c r="C45" s="145"/>
+      <c r="D45" s="145"/>
       <c r="E45" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F45" s="12"/>
-      <c r="G45" s="143"/>
+      <c r="G45" s="145"/>
       <c r="H45" s="48"/>
       <c r="I45" s="49"/>
       <c r="J45" s="48"/>
@@ -4441,7 +4509,7 @@
         <v>92</v>
       </c>
       <c r="F46" s="12"/>
-      <c r="G46" s="143"/>
+      <c r="G46" s="145"/>
       <c r="H46" s="44"/>
       <c r="I46" s="45"/>
       <c r="J46" s="44"/>
@@ -4462,7 +4530,7 @@
         <v>93</v>
       </c>
       <c r="F47" s="12"/>
-      <c r="G47" s="143"/>
+      <c r="G47" s="145"/>
       <c r="H47" s="44"/>
       <c r="I47" s="45"/>
       <c r="J47" s="44"/>
@@ -4491,7 +4559,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="12"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="145"/>
       <c r="H48" s="48"/>
       <c r="I48" s="49"/>
       <c r="J48" s="48"/>
@@ -4520,7 +4588,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="12"/>
-      <c r="G49" s="143"/>
+      <c r="G49" s="145"/>
       <c r="H49" s="44"/>
       <c r="I49" s="45"/>
       <c r="J49" s="44"/>
@@ -4547,7 +4615,7 @@
         <v>101</v>
       </c>
       <c r="F50" s="12"/>
-      <c r="G50" s="143"/>
+      <c r="G50" s="145"/>
       <c r="H50" s="48"/>
       <c r="I50" s="49"/>
       <c r="J50" s="48"/>
@@ -4643,10 +4711,10 @@
       <c r="A54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="155">
+      <c r="B54" s="157">
         <v>16</v>
       </c>
-      <c r="C54" s="156" t="s">
+      <c r="C54" s="158" t="s">
         <v>109</v>
       </c>
       <c r="D54" s="17"/>
@@ -4667,8 +4735,8 @@
     </row>
     <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="143"/>
-      <c r="C55" s="143"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="145"/>
       <c r="D55" s="17"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12"/>
@@ -4687,10 +4755,10 @@
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="151">
+      <c r="B56" s="153">
         <v>17</v>
       </c>
-      <c r="C56" s="153" t="s">
+      <c r="C56" s="155" t="s">
         <v>111</v>
       </c>
       <c r="D56" s="57"/>
@@ -4712,8 +4780,8 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="152"/>
-      <c r="C57" s="154"/>
+      <c r="B57" s="154"/>
+      <c r="C57" s="156"/>
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
       <c r="F57" s="12"/>
@@ -4733,10 +4801,10 @@
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="155">
+      <c r="B58" s="157">
         <v>18</v>
       </c>
-      <c r="C58" s="156" t="s">
+      <c r="C58" s="158" t="s">
         <v>112</v>
       </c>
       <c r="D58" s="17"/>
@@ -4757,8 +4825,8 @@
     </row>
     <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
-      <c r="B59" s="143"/>
-      <c r="C59" s="143"/>
+      <c r="B59" s="145"/>
+      <c r="C59" s="145"/>
       <c r="D59" s="17"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12"/>
@@ -4777,10 +4845,10 @@
       <c r="A60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B60" s="151">
+      <c r="B60" s="153">
         <v>19</v>
       </c>
-      <c r="C60" s="153" t="s">
+      <c r="C60" s="155" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="57"/>
@@ -4802,8 +4870,8 @@
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
-      <c r="B61" s="152"/>
-      <c r="C61" s="154"/>
+      <c r="B61" s="154"/>
+      <c r="C61" s="156"/>
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
       <c r="F61" s="12"/>
@@ -4823,7 +4891,7 @@
       <c r="A62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="155">
+      <c r="B62" s="157">
         <v>20</v>
       </c>
       <c r="C62" s="17" t="s">
@@ -4847,7 +4915,7 @@
     </row>
     <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
-      <c r="B63" s="143"/>
+      <c r="B63" s="145"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="18" t="s">
@@ -5023,13 +5091,13 @@
     </row>
     <row r="74" spans="1:17" ht="23" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
-      <c r="B74" s="142" t="s">
+      <c r="B74" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="143"/>
-      <c r="D74" s="143"/>
-      <c r="E74" s="143"/>
-      <c r="F74" s="143"/>
+      <c r="C74" s="145"/>
+      <c r="D74" s="145"/>
+      <c r="E74" s="145"/>
+      <c r="F74" s="145"/>
       <c r="G74" s="1"/>
       <c r="H74" s="42" t="s">
         <v>34</v>
@@ -5108,7 +5176,7 @@
       <c r="F76" s="67">
         <v>1</v>
       </c>
-      <c r="G76" s="148" t="s">
+      <c r="G76" s="150" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="31">
@@ -5135,7 +5203,7 @@
       <c r="F77" s="67">
         <v>2</v>
       </c>
-      <c r="G77" s="143"/>
+      <c r="G77" s="145"/>
       <c r="H77" s="31">
         <v>141</v>
       </c>
@@ -5160,7 +5228,7 @@
       <c r="F78" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="G78" s="143"/>
+      <c r="G78" s="145"/>
       <c r="H78" s="31">
         <f t="shared" ref="H78:I78" si="0">AVERAGE(H76:H77)</f>
         <v>127</v>
@@ -5187,7 +5255,7 @@
       <c r="F79" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="143"/>
+      <c r="G79" s="145"/>
       <c r="H79" s="70">
         <f>I78/H78</f>
         <v>0.59842519685039375</v>
@@ -5219,7 +5287,7 @@
         <v>126</v>
       </c>
       <c r="F80" s="12"/>
-      <c r="G80" s="143"/>
+      <c r="G80" s="145"/>
       <c r="H80" s="36"/>
       <c r="I80" s="38"/>
       <c r="J80" s="74"/>
@@ -5248,7 +5316,7 @@
         <v>126</v>
       </c>
       <c r="F81" s="12"/>
-      <c r="G81" s="143"/>
+      <c r="G81" s="145"/>
       <c r="H81" s="31"/>
       <c r="I81" s="34"/>
       <c r="J81" s="72"/>
@@ -5277,7 +5345,7 @@
         <v>126</v>
       </c>
       <c r="F82" s="12"/>
-      <c r="G82" s="143"/>
+      <c r="G82" s="145"/>
       <c r="H82" s="36"/>
       <c r="I82" s="38"/>
       <c r="J82" s="74"/>
@@ -5306,7 +5374,7 @@
         <v>134</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="143"/>
+      <c r="G83" s="145"/>
       <c r="H83" s="31"/>
       <c r="I83" s="34"/>
       <c r="J83" s="72"/>
@@ -5335,7 +5403,7 @@
         <v>126</v>
       </c>
       <c r="F84" s="12"/>
-      <c r="G84" s="143"/>
+      <c r="G84" s="145"/>
       <c r="H84" s="36"/>
       <c r="I84" s="38"/>
       <c r="J84" s="74"/>
@@ -5364,7 +5432,7 @@
         <v>138</v>
       </c>
       <c r="F85" s="12"/>
-      <c r="G85" s="143"/>
+      <c r="G85" s="145"/>
       <c r="H85" s="31"/>
       <c r="I85" s="34"/>
       <c r="J85" s="72"/>
@@ -5393,7 +5461,7 @@
         <v>140</v>
       </c>
       <c r="F86" s="12"/>
-      <c r="G86" s="143"/>
+      <c r="G86" s="145"/>
       <c r="H86" s="36"/>
       <c r="I86" s="38"/>
       <c r="J86" s="74"/>
@@ -5422,7 +5490,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="12"/>
-      <c r="G87" s="143"/>
+      <c r="G87" s="145"/>
       <c r="H87" s="31"/>
       <c r="I87" s="34"/>
       <c r="J87" s="72"/>
@@ -12673,7 +12741,7 @@
       <c r="E81" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="F81" s="159" t="s">
+      <c r="F81" s="142" t="s">
         <v>305</v>
       </c>
       <c r="G81" s="78">
@@ -12777,6 +12845,123 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142C128A-6A3C-C44D-A6B9-AA743D20FC84}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="86"/>
+    <col min="2" max="2" width="106.33203125" style="86" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="86" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="86"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="143" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="143" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="143" t="s">
+        <v>385</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="143" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="143" t="s">
+        <v>387</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="143" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="86" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="143" t="s">
+        <v>389</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="143" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="143" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="143" t="s">
+        <v>392</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="143" t="s">
+        <v>394</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="143" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" s="86" t="s">
+        <v>406</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1653A7C-21C0-814E-8E44-D921BBCC189F}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -12974,7 +13159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A797E27-8800-F04C-B6DD-3411CE39E1CB}">
   <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -12995,30 +13180,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="133" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="157" t="s">
+      <c r="B1" s="159" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157" t="s">
+      <c r="C1" s="159"/>
+      <c r="D1" s="159" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157" t="s">
+      <c r="E1" s="159"/>
+      <c r="F1" s="159" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157" t="s">
+      <c r="G1" s="159"/>
+      <c r="H1" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157" t="s">
+      <c r="I1" s="159"/>
+      <c r="J1" s="159" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157" t="s">
+      <c r="K1" s="159"/>
+      <c r="L1" s="159" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="157"/>
+      <c r="M1" s="159"/>
     </row>
     <row r="2" spans="1:13" s="136" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="134" t="s">
@@ -13614,32 +13799,32 @@
       <c r="M52" s="131"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="H74" s="158" t="s">
+      <c r="H74" s="160" t="s">
         <v>298</v>
       </c>
-      <c r="I74" s="158"/>
-      <c r="J74" s="158" t="s">
+      <c r="I74" s="160"/>
+      <c r="J74" s="160" t="s">
         <v>299</v>
       </c>
-      <c r="K74" s="158"/>
-      <c r="L74" s="158" t="s">
+      <c r="K74" s="160"/>
+      <c r="L74" s="160" t="s">
         <v>300</v>
       </c>
-      <c r="M74" s="158"/>
+      <c r="M74" s="160"/>
     </row>
     <row r="75" spans="2:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="B75" s="158" t="s">
+      <c r="B75" s="160" t="s">
         <v>295</v>
       </c>
-      <c r="C75" s="158"/>
-      <c r="D75" s="158" t="s">
+      <c r="C75" s="160"/>
+      <c r="D75" s="160" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="158"/>
-      <c r="F75" s="158" t="s">
+      <c r="E75" s="160"/>
+      <c r="F75" s="160" t="s">
         <v>297</v>
       </c>
-      <c r="G75" s="158"/>
+      <c r="G75" s="160"/>
       <c r="H75" s="109" t="s">
         <v>254</v>
       </c>
@@ -14013,7 +14198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01440D2E-D5CB-624F-A307-D0DE876488BF}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
